--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,145 +473,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25800</v>
+        <v>10930</v>
       </c>
       <c r="F2" t="n">
-        <v>2713</v>
+        <v>1833</v>
       </c>
       <c r="G2" t="n">
-        <v>69995400</v>
+        <v>20034690</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206500</v>
+        <v>19850</v>
       </c>
       <c r="F3" t="n">
-        <v>338</v>
+        <v>505</v>
       </c>
       <c r="G3" t="n">
-        <v>69797000</v>
+        <v>10024250</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70100</v>
+        <v>26350</v>
       </c>
       <c r="F4" t="n">
-        <v>998</v>
+        <v>380</v>
       </c>
       <c r="G4" t="n">
-        <v>69959800</v>
+        <v>10013000</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>93300</v>
+        <v>23500</v>
       </c>
       <c r="F5" t="n">
-        <v>214</v>
+        <v>833</v>
       </c>
       <c r="G5" t="n">
-        <v>19966200</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,45 +622,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11300</v>
+        <v>63400</v>
       </c>
       <c r="F6" t="n">
-        <v>4424</v>
+        <v>316</v>
       </c>
       <c r="G6" t="n">
-        <v>49991200</v>
+        <v>20034400</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19740</v>
+        <v>110300</v>
       </c>
       <c r="F7" t="n">
-        <v>2532</v>
+        <v>91</v>
       </c>
       <c r="G7" t="n">
-        <v>49981680</v>
+        <v>10037300</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,12 +672,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,13 +686,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F8" t="n">
-        <v>2385</v>
+        <v>2713</v>
       </c>
       <c r="G8" t="n">
-        <v>59982750</v>
+        <v>69995400</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,12 +704,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,13 +718,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22050</v>
+        <v>206500</v>
       </c>
       <c r="F9" t="n">
-        <v>2267</v>
+        <v>338</v>
       </c>
       <c r="G9" t="n">
-        <v>49987350</v>
+        <v>69797000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,12 +736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,13 +750,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43150</v>
+        <v>70100</v>
       </c>
       <c r="F10" t="n">
-        <v>1390</v>
+        <v>998</v>
       </c>
       <c r="G10" t="n">
-        <v>59978500</v>
+        <v>69959800</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,12 +768,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -780,13 +782,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>310000</v>
+        <v>93300</v>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G11" t="n">
-        <v>69750000</v>
+        <v>19966200</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,12 +800,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -812,13 +814,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6240</v>
+        <v>11300</v>
       </c>
       <c r="F12" t="n">
-        <v>3205</v>
+        <v>4424</v>
       </c>
       <c r="G12" t="n">
-        <v>19999200</v>
+        <v>49991200</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -830,12 +832,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -844,13 +846,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>24000</v>
+        <v>19740</v>
       </c>
       <c r="F13" t="n">
-        <v>833</v>
+        <v>2532</v>
       </c>
       <c r="G13" t="n">
-        <v>19992000</v>
+        <v>49981680</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -862,12 +864,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,13 +878,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>90300</v>
+        <v>25150</v>
       </c>
       <c r="F14" t="n">
-        <v>442</v>
+        <v>2385</v>
       </c>
       <c r="G14" t="n">
-        <v>39912600</v>
+        <v>59982750</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -894,12 +896,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -908,13 +910,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>279500</v>
+        <v>22050</v>
       </c>
       <c r="F15" t="n">
-        <v>357</v>
+        <v>2267</v>
       </c>
       <c r="G15" t="n">
-        <v>99781500</v>
+        <v>49987350</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -926,12 +928,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -940,13 +942,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>366000</v>
+        <v>43150</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>1390</v>
       </c>
       <c r="G16" t="n">
-        <v>19764000</v>
+        <v>59978500</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -958,12 +960,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -972,13 +974,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>91000</v>
+        <v>310000</v>
       </c>
       <c r="F17" t="n">
-        <v>659</v>
+        <v>225</v>
       </c>
       <c r="G17" t="n">
-        <v>59969000</v>
+        <v>69750000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -990,12 +992,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1004,13 +1006,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>120100</v>
+        <v>6240</v>
       </c>
       <c r="F18" t="n">
-        <v>666</v>
+        <v>3205</v>
       </c>
       <c r="G18" t="n">
-        <v>79986600</v>
+        <v>19999200</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1022,12 +1024,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1036,13 +1038,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2405</v>
+        <v>24000</v>
       </c>
       <c r="F19" t="n">
-        <v>415800</v>
+        <v>833</v>
       </c>
       <c r="G19" t="n">
-        <v>999999000</v>
+        <v>19992000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1054,12 +1056,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1068,13 +1070,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69000</v>
+        <v>90300</v>
       </c>
       <c r="F20" t="n">
-        <v>579</v>
+        <v>442</v>
       </c>
       <c r="G20" t="n">
-        <v>39951000</v>
+        <v>39912600</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1086,12 +1088,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1100,13 +1102,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>42300</v>
+        <v>279500</v>
       </c>
       <c r="F21" t="n">
-        <v>709</v>
+        <v>357</v>
       </c>
       <c r="G21" t="n">
-        <v>29990700</v>
+        <v>99781500</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1118,29 +1120,221 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>659</v>
+      </c>
+      <c r="G23" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F24" t="n">
+        <v>666</v>
+      </c>
+      <c r="G24" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F25" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G25" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>579</v>
+      </c>
+      <c r="G26" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F27" t="n">
+        <v>709</v>
+      </c>
+      <c r="G27" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>23350</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F28" t="n">
         <v>856</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G28" t="n">
         <v>19987600</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63400</v>
+        <v>85200</v>
       </c>
       <c r="F6" t="n">
-        <v>316</v>
+        <v>118</v>
       </c>
       <c r="G6" t="n">
-        <v>20034400</v>
+        <v>10053600</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,91 +640,91 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>110300</v>
+        <v>63400</v>
       </c>
       <c r="F7" t="n">
-        <v>91</v>
+        <v>316</v>
       </c>
       <c r="G7" t="n">
-        <v>10037300</v>
+        <v>20034400</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25800</v>
+        <v>110300</v>
       </c>
       <c r="F8" t="n">
-        <v>2713</v>
+        <v>91</v>
       </c>
       <c r="G8" t="n">
-        <v>69995400</v>
+        <v>10037300</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206500</v>
+        <v>66100</v>
       </c>
       <c r="F9" t="n">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="G9" t="n">
-        <v>69797000</v>
+        <v>10047200</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70100</v>
+        <v>25800</v>
       </c>
       <c r="F10" t="n">
-        <v>998</v>
+        <v>2713</v>
       </c>
       <c r="G10" t="n">
-        <v>69959800</v>
+        <v>69995400</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>93300</v>
+        <v>206500</v>
       </c>
       <c r="F11" t="n">
-        <v>214</v>
+        <v>338</v>
       </c>
       <c r="G11" t="n">
-        <v>19966200</v>
+        <v>69797000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11300</v>
+        <v>70100</v>
       </c>
       <c r="F12" t="n">
-        <v>4424</v>
+        <v>998</v>
       </c>
       <c r="G12" t="n">
-        <v>49991200</v>
+        <v>69959800</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>19740</v>
+        <v>93300</v>
       </c>
       <c r="F13" t="n">
-        <v>2532</v>
+        <v>214</v>
       </c>
       <c r="G13" t="n">
-        <v>49981680</v>
+        <v>19966200</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25150</v>
+        <v>11300</v>
       </c>
       <c r="F14" t="n">
-        <v>2385</v>
+        <v>4424</v>
       </c>
       <c r="G14" t="n">
-        <v>59982750</v>
+        <v>49991200</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>22050</v>
+        <v>19740</v>
       </c>
       <c r="F15" t="n">
-        <v>2267</v>
+        <v>2532</v>
       </c>
       <c r="G15" t="n">
-        <v>49987350</v>
+        <v>49981680</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>43150</v>
+        <v>25150</v>
       </c>
       <c r="F16" t="n">
-        <v>1390</v>
+        <v>2385</v>
       </c>
       <c r="G16" t="n">
-        <v>59978500</v>
+        <v>59982750</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>310000</v>
+        <v>22050</v>
       </c>
       <c r="F17" t="n">
-        <v>225</v>
+        <v>2267</v>
       </c>
       <c r="G17" t="n">
-        <v>69750000</v>
+        <v>49987350</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6240</v>
+        <v>43150</v>
       </c>
       <c r="F18" t="n">
-        <v>3205</v>
+        <v>1390</v>
       </c>
       <c r="G18" t="n">
-        <v>19999200</v>
+        <v>59978500</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>24000</v>
+        <v>310000</v>
       </c>
       <c r="F19" t="n">
-        <v>833</v>
+        <v>225</v>
       </c>
       <c r="G19" t="n">
-        <v>19992000</v>
+        <v>69750000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>90300</v>
+        <v>6240</v>
       </c>
       <c r="F20" t="n">
-        <v>442</v>
+        <v>3205</v>
       </c>
       <c r="G20" t="n">
-        <v>39912600</v>
+        <v>19999200</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>279500</v>
+        <v>24000</v>
       </c>
       <c r="F21" t="n">
-        <v>357</v>
+        <v>833</v>
       </c>
       <c r="G21" t="n">
-        <v>99781500</v>
+        <v>19992000</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>366000</v>
+        <v>90300</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>442</v>
       </c>
       <c r="G22" t="n">
-        <v>19764000</v>
+        <v>39912600</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91000</v>
+        <v>279500</v>
       </c>
       <c r="F23" t="n">
-        <v>659</v>
+        <v>357</v>
       </c>
       <c r="G23" t="n">
-        <v>59969000</v>
+        <v>99781500</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>120100</v>
+        <v>366000</v>
       </c>
       <c r="F24" t="n">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="G24" t="n">
-        <v>79986600</v>
+        <v>19764000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2405</v>
+        <v>91000</v>
       </c>
       <c r="F25" t="n">
-        <v>415800</v>
+        <v>659</v>
       </c>
       <c r="G25" t="n">
-        <v>999999000</v>
+        <v>59969000</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>69000</v>
+        <v>120100</v>
       </c>
       <c r="F26" t="n">
-        <v>579</v>
+        <v>666</v>
       </c>
       <c r="G26" t="n">
-        <v>39951000</v>
+        <v>79986600</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>42300</v>
+        <v>2405</v>
       </c>
       <c r="F27" t="n">
-        <v>709</v>
+        <v>415800</v>
       </c>
       <c r="G27" t="n">
-        <v>29990700</v>
+        <v>999999000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1312,29 +1312,93 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>579</v>
+      </c>
+      <c r="G28" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F29" t="n">
+        <v>709</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
         <v>23350</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
         <v>856</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G30" t="n">
         <v>19987600</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,96 +473,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10930</v>
+        <v>83700</v>
       </c>
       <c r="F2" t="n">
-        <v>1833</v>
+        <v>120</v>
       </c>
       <c r="G2" t="n">
-        <v>20034690</v>
+        <v>10044000</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>19850</v>
+        <v>43650</v>
       </c>
       <c r="F3" t="n">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="G3" t="n">
-        <v>10024250</v>
+        <v>20166300</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26350</v>
+        <v>59700</v>
       </c>
       <c r="F4" t="n">
-        <v>380</v>
+        <v>169</v>
       </c>
       <c r="G4" t="n">
-        <v>10013000</v>
+        <v>10089300</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,31 +574,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23500</v>
+        <v>10930</v>
       </c>
       <c r="F5" t="n">
-        <v>833</v>
+        <v>1833</v>
       </c>
       <c r="G5" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20034690</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,27 +606,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>85200</v>
+        <v>19850</v>
       </c>
       <c r="F6" t="n">
-        <v>118</v>
+        <v>505</v>
       </c>
       <c r="G6" t="n">
-        <v>10053600</v>
+        <v>10024250</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,27 +638,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63400</v>
+        <v>26350</v>
       </c>
       <c r="F7" t="n">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="G7" t="n">
-        <v>20034400</v>
+        <v>10013000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -672,29 +670,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>110300</v>
+        <v>23500</v>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>833</v>
       </c>
       <c r="G8" t="n">
-        <v>10037300</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,30 +718,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>66100</v>
+        <v>85200</v>
       </c>
       <c r="F9" t="n">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="G9" t="n">
-        <v>10047200</v>
+        <v>10053600</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,77 +750,77 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25800</v>
+        <v>63400</v>
       </c>
       <c r="F10" t="n">
-        <v>2713</v>
+        <v>316</v>
       </c>
       <c r="G10" t="n">
-        <v>69995400</v>
+        <v>20034400</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206500</v>
+        <v>110300</v>
       </c>
       <c r="F11" t="n">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="G11" t="n">
-        <v>69797000</v>
+        <v>10037300</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70100</v>
+        <v>66100</v>
       </c>
       <c r="F12" t="n">
-        <v>998</v>
+        <v>152</v>
       </c>
       <c r="G12" t="n">
-        <v>69959800</v>
+        <v>10047200</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>93300</v>
+        <v>25800</v>
       </c>
       <c r="F13" t="n">
-        <v>214</v>
+        <v>2713</v>
       </c>
       <c r="G13" t="n">
-        <v>19966200</v>
+        <v>69995400</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11300</v>
+        <v>206500</v>
       </c>
       <c r="F14" t="n">
-        <v>4424</v>
+        <v>338</v>
       </c>
       <c r="G14" t="n">
-        <v>49991200</v>
+        <v>69797000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>19740</v>
+        <v>70100</v>
       </c>
       <c r="F15" t="n">
-        <v>2532</v>
+        <v>998</v>
       </c>
       <c r="G15" t="n">
-        <v>49981680</v>
+        <v>69959800</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25150</v>
+        <v>93300</v>
       </c>
       <c r="F16" t="n">
-        <v>2385</v>
+        <v>214</v>
       </c>
       <c r="G16" t="n">
-        <v>59982750</v>
+        <v>19966200</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>22050</v>
+        <v>11300</v>
       </c>
       <c r="F17" t="n">
-        <v>2267</v>
+        <v>4424</v>
       </c>
       <c r="G17" t="n">
-        <v>49987350</v>
+        <v>49991200</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>43150</v>
+        <v>19740</v>
       </c>
       <c r="F18" t="n">
-        <v>1390</v>
+        <v>2532</v>
       </c>
       <c r="G18" t="n">
-        <v>59978500</v>
+        <v>49981680</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>310000</v>
+        <v>25150</v>
       </c>
       <c r="F19" t="n">
-        <v>225</v>
+        <v>2385</v>
       </c>
       <c r="G19" t="n">
-        <v>69750000</v>
+        <v>59982750</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6240</v>
+        <v>22050</v>
       </c>
       <c r="F20" t="n">
-        <v>3205</v>
+        <v>2267</v>
       </c>
       <c r="G20" t="n">
-        <v>19999200</v>
+        <v>49987350</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>24000</v>
+        <v>43150</v>
       </c>
       <c r="F21" t="n">
-        <v>833</v>
+        <v>1390</v>
       </c>
       <c r="G21" t="n">
-        <v>19992000</v>
+        <v>59978500</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>90300</v>
+        <v>310000</v>
       </c>
       <c r="F22" t="n">
-        <v>442</v>
+        <v>225</v>
       </c>
       <c r="G22" t="n">
-        <v>39912600</v>
+        <v>69750000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F23" t="n">
-        <v>357</v>
+        <v>3205</v>
       </c>
       <c r="G23" t="n">
-        <v>99781500</v>
+        <v>19999200</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>366000</v>
+        <v>24000</v>
       </c>
       <c r="F24" t="n">
-        <v>54</v>
+        <v>833</v>
       </c>
       <c r="G24" t="n">
-        <v>19764000</v>
+        <v>19992000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>91000</v>
+        <v>90300</v>
       </c>
       <c r="F25" t="n">
-        <v>659</v>
+        <v>442</v>
       </c>
       <c r="G25" t="n">
-        <v>59969000</v>
+        <v>39912600</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>120100</v>
+        <v>279500</v>
       </c>
       <c r="F26" t="n">
-        <v>666</v>
+        <v>357</v>
       </c>
       <c r="G26" t="n">
-        <v>79986600</v>
+        <v>99781500</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2405</v>
+        <v>366000</v>
       </c>
       <c r="F27" t="n">
-        <v>415800</v>
+        <v>54</v>
       </c>
       <c r="G27" t="n">
-        <v>999999000</v>
+        <v>19764000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>69000</v>
+        <v>91000</v>
       </c>
       <c r="F28" t="n">
-        <v>579</v>
+        <v>659</v>
       </c>
       <c r="G28" t="n">
-        <v>39951000</v>
+        <v>59969000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>42300</v>
+        <v>120100</v>
       </c>
       <c r="F29" t="n">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="G29" t="n">
-        <v>29990700</v>
+        <v>79986600</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1376,29 +1376,125 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F30" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G30" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>579</v>
+      </c>
+      <c r="G31" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F32" t="n">
+        <v>709</v>
+      </c>
+      <c r="G32" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>23350</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F33" t="n">
         <v>856</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G33" t="n">
         <v>19987600</v>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83700</v>
+        <v>18910</v>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>1068.0212</v>
       </c>
       <c r="G2" t="n">
-        <v>10044000</v>
+        <v>20196280</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,177 +524,179 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>43650</v>
+        <v>32250</v>
       </c>
       <c r="F3" t="n">
-        <v>462</v>
+        <v>626</v>
       </c>
       <c r="G3" t="n">
-        <v>20166300</v>
+        <v>20188500</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>59700</v>
+        <v>82500</v>
       </c>
       <c r="F4" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="G4" t="n">
-        <v>10089300</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10930</v>
+        <v>56800</v>
       </c>
       <c r="F5" t="n">
-        <v>1833</v>
+        <v>258</v>
       </c>
       <c r="G5" t="n">
-        <v>20034690</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19850</v>
+        <v>83700</v>
       </c>
       <c r="F6" t="n">
-        <v>505</v>
+        <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>10024250</v>
+        <v>10044000</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26350</v>
+        <v>43650</v>
       </c>
       <c r="F7" t="n">
-        <v>380</v>
+        <v>462</v>
       </c>
       <c r="G7" t="n">
-        <v>10013000</v>
+        <v>20166300</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>23500</v>
+        <v>59700</v>
       </c>
       <c r="F8" t="n">
-        <v>833</v>
+        <v>169</v>
       </c>
       <c r="G8" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10089300</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -704,27 +706,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>85200</v>
+        <v>10930</v>
       </c>
       <c r="F9" t="n">
-        <v>118</v>
+        <v>1833</v>
       </c>
       <c r="G9" t="n">
-        <v>10053600</v>
+        <v>20034690</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,27 +738,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63400</v>
+        <v>19850</v>
       </c>
       <c r="F10" t="n">
-        <v>316</v>
+        <v>505</v>
       </c>
       <c r="G10" t="n">
-        <v>20034400</v>
+        <v>10024250</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,27 +770,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>110300</v>
+        <v>26350</v>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>380</v>
       </c>
       <c r="G11" t="n">
-        <v>10037300</v>
+        <v>10013000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,76 +802,78 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>66100</v>
+        <v>23500</v>
       </c>
       <c r="F12" t="n">
-        <v>152</v>
+        <v>833</v>
       </c>
       <c r="G12" t="n">
-        <v>10047200</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25800</v>
+        <v>85200</v>
       </c>
       <c r="F13" t="n">
-        <v>2713</v>
+        <v>118</v>
       </c>
       <c r="G13" t="n">
-        <v>69995400</v>
+        <v>10053600</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,77 +882,77 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206500</v>
+        <v>63400</v>
       </c>
       <c r="F14" t="n">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="G14" t="n">
-        <v>69797000</v>
+        <v>20034400</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>70100</v>
+        <v>110300</v>
       </c>
       <c r="F15" t="n">
-        <v>998</v>
+        <v>91</v>
       </c>
       <c r="G15" t="n">
-        <v>69959800</v>
+        <v>10037300</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>93300</v>
+        <v>66100</v>
       </c>
       <c r="F16" t="n">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="G16" t="n">
-        <v>19966200</v>
+        <v>10047200</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,12 +964,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,13 +978,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11300</v>
+        <v>25800</v>
       </c>
       <c r="F17" t="n">
-        <v>4424</v>
+        <v>2713</v>
       </c>
       <c r="G17" t="n">
-        <v>49991200</v>
+        <v>69995400</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,12 +996,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1006,13 +1010,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>19740</v>
+        <v>206500</v>
       </c>
       <c r="F18" t="n">
-        <v>2532</v>
+        <v>338</v>
       </c>
       <c r="G18" t="n">
-        <v>49981680</v>
+        <v>69797000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,12 +1028,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1038,13 +1042,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>25150</v>
+        <v>70100</v>
       </c>
       <c r="F19" t="n">
-        <v>2385</v>
+        <v>998</v>
       </c>
       <c r="G19" t="n">
-        <v>59982750</v>
+        <v>69959800</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1056,12 +1060,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1070,13 +1074,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>22050</v>
+        <v>93300</v>
       </c>
       <c r="F20" t="n">
-        <v>2267</v>
+        <v>214</v>
       </c>
       <c r="G20" t="n">
-        <v>49987350</v>
+        <v>19966200</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1088,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1102,13 +1106,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>43150</v>
+        <v>11300</v>
       </c>
       <c r="F21" t="n">
-        <v>1390</v>
+        <v>4424</v>
       </c>
       <c r="G21" t="n">
-        <v>59978500</v>
+        <v>49991200</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1120,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1134,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>310000</v>
+        <v>19740</v>
       </c>
       <c r="F22" t="n">
-        <v>225</v>
+        <v>2532</v>
       </c>
       <c r="G22" t="n">
-        <v>69750000</v>
+        <v>49981680</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1152,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1166,13 +1170,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6240</v>
+        <v>25150</v>
       </c>
       <c r="F23" t="n">
-        <v>3205</v>
+        <v>2385</v>
       </c>
       <c r="G23" t="n">
-        <v>19999200</v>
+        <v>59982750</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1184,12 +1188,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1198,13 +1202,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>24000</v>
+        <v>22050</v>
       </c>
       <c r="F24" t="n">
-        <v>833</v>
+        <v>2267</v>
       </c>
       <c r="G24" t="n">
-        <v>19992000</v>
+        <v>49987350</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1216,12 +1220,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1230,13 +1234,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>90300</v>
+        <v>43150</v>
       </c>
       <c r="F25" t="n">
-        <v>442</v>
+        <v>1390</v>
       </c>
       <c r="G25" t="n">
-        <v>39912600</v>
+        <v>59978500</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1248,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1262,13 +1266,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>279500</v>
+        <v>310000</v>
       </c>
       <c r="F26" t="n">
-        <v>357</v>
+        <v>225</v>
       </c>
       <c r="G26" t="n">
-        <v>99781500</v>
+        <v>69750000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1280,12 +1284,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1294,13 +1298,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>366000</v>
+        <v>6240</v>
       </c>
       <c r="F27" t="n">
-        <v>54</v>
+        <v>3205</v>
       </c>
       <c r="G27" t="n">
-        <v>19764000</v>
+        <v>19999200</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1312,12 +1316,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1326,13 +1330,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>91000</v>
+        <v>24000</v>
       </c>
       <c r="F28" t="n">
-        <v>659</v>
+        <v>833</v>
       </c>
       <c r="G28" t="n">
-        <v>59969000</v>
+        <v>19992000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1344,12 +1348,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1358,13 +1362,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>120100</v>
+        <v>90300</v>
       </c>
       <c r="F29" t="n">
-        <v>666</v>
+        <v>442</v>
       </c>
       <c r="G29" t="n">
-        <v>79986600</v>
+        <v>39912600</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1376,12 +1380,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1390,13 +1394,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2405</v>
+        <v>279500</v>
       </c>
       <c r="F30" t="n">
-        <v>415800</v>
+        <v>357</v>
       </c>
       <c r="G30" t="n">
-        <v>999999000</v>
+        <v>99781500</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1408,12 +1412,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1422,13 +1426,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>69000</v>
+        <v>366000</v>
       </c>
       <c r="F31" t="n">
-        <v>579</v>
+        <v>54</v>
       </c>
       <c r="G31" t="n">
-        <v>39951000</v>
+        <v>19764000</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1440,12 +1444,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1454,13 +1458,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>42300</v>
+        <v>91000</v>
       </c>
       <c r="F32" t="n">
-        <v>709</v>
+        <v>659</v>
       </c>
       <c r="G32" t="n">
-        <v>29990700</v>
+        <v>59969000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1472,29 +1476,157 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F33" t="n">
+        <v>666</v>
+      </c>
+      <c r="G33" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F34" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G34" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>579</v>
+      </c>
+      <c r="G35" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F36" t="n">
+        <v>709</v>
+      </c>
+      <c r="G36" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>23350</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F37" t="n">
         <v>856</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G37" t="n">
         <v>19987600</v>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,149 +473,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18910</v>
+        <v>27100</v>
       </c>
       <c r="F2" t="n">
-        <v>1068.0212</v>
+        <v>376</v>
       </c>
       <c r="G2" t="n">
-        <v>20196280</v>
+        <v>10189600</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32250</v>
+        <v>67600</v>
       </c>
       <c r="F3" t="n">
-        <v>626</v>
+        <v>998</v>
       </c>
       <c r="G3" t="n">
-        <v>20188500</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>82500</v>
+        <v>11900</v>
       </c>
       <c r="F4" t="n">
-        <v>204</v>
+        <v>856</v>
       </c>
       <c r="G4" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>10186400</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56800</v>
+        <v>29300</v>
       </c>
       <c r="F5" t="n">
-        <v>258</v>
+        <v>2434</v>
       </c>
       <c r="G5" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>71316200</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,271 +622,273 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>83700</v>
+        <v>119300</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="G6" t="n">
-        <v>10044000</v>
+        <v>20400300</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43650</v>
+        <v>2445</v>
       </c>
       <c r="F7" t="n">
-        <v>462</v>
+        <v>82456</v>
       </c>
       <c r="G7" t="n">
-        <v>20166300</v>
+        <v>201604920</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59700</v>
+        <v>18910</v>
       </c>
       <c r="F8" t="n">
-        <v>169</v>
+        <v>1068.0212</v>
       </c>
       <c r="G8" t="n">
-        <v>10089300</v>
+        <v>20196280</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10930</v>
+        <v>32250</v>
       </c>
       <c r="F9" t="n">
-        <v>1833</v>
+        <v>626</v>
       </c>
       <c r="G9" t="n">
-        <v>20034690</v>
+        <v>20188500</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19850</v>
+        <v>82500</v>
       </c>
       <c r="F10" t="n">
-        <v>505</v>
+        <v>204</v>
       </c>
       <c r="G10" t="n">
-        <v>10024250</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26350</v>
+        <v>56800</v>
       </c>
       <c r="F11" t="n">
-        <v>380</v>
+        <v>258</v>
       </c>
       <c r="G11" t="n">
-        <v>10013000</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>23500</v>
+        <v>83700</v>
       </c>
       <c r="F12" t="n">
-        <v>833</v>
+        <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10044000</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>85200</v>
+        <v>43650</v>
       </c>
       <c r="F13" t="n">
-        <v>118</v>
+        <v>462</v>
       </c>
       <c r="G13" t="n">
-        <v>10053600</v>
+        <v>20166300</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>63400</v>
+        <v>59700</v>
       </c>
       <c r="F14" t="n">
-        <v>316</v>
+        <v>169</v>
       </c>
       <c r="G14" t="n">
-        <v>20034400</v>
+        <v>10089300</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -900,27 +900,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>110300</v>
+        <v>10930</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>1833</v>
       </c>
       <c r="G15" t="n">
-        <v>10037300</v>
+        <v>20034690</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -932,140 +932,142 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>66100</v>
+        <v>19850</v>
       </c>
       <c r="F16" t="n">
-        <v>152</v>
+        <v>505</v>
       </c>
       <c r="G16" t="n">
-        <v>10047200</v>
+        <v>10024250</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>25800</v>
+        <v>26350</v>
       </c>
       <c r="F17" t="n">
-        <v>2713</v>
+        <v>380</v>
       </c>
       <c r="G17" t="n">
-        <v>69995400</v>
+        <v>10013000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206500</v>
+        <v>23500</v>
       </c>
       <c r="F18" t="n">
-        <v>338</v>
+        <v>833</v>
       </c>
       <c r="G18" t="n">
-        <v>69797000</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>70100</v>
+        <v>85200</v>
       </c>
       <c r="F19" t="n">
-        <v>998</v>
+        <v>118</v>
       </c>
       <c r="G19" t="n">
-        <v>69959800</v>
+        <v>10053600</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1074,77 +1076,77 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>93300</v>
+        <v>63400</v>
       </c>
       <c r="F20" t="n">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="G20" t="n">
-        <v>19966200</v>
+        <v>20034400</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11300</v>
+        <v>110300</v>
       </c>
       <c r="F21" t="n">
-        <v>4424</v>
+        <v>91</v>
       </c>
       <c r="G21" t="n">
-        <v>49991200</v>
+        <v>10037300</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19740</v>
+        <v>66100</v>
       </c>
       <c r="F22" t="n">
-        <v>2532</v>
+        <v>152</v>
       </c>
       <c r="G22" t="n">
-        <v>49981680</v>
+        <v>10047200</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,12 +1158,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,13 +1172,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F23" t="n">
-        <v>2385</v>
+        <v>2713</v>
       </c>
       <c r="G23" t="n">
-        <v>59982750</v>
+        <v>69995400</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1188,12 +1190,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,13 +1204,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>22050</v>
+        <v>206500</v>
       </c>
       <c r="F24" t="n">
-        <v>2267</v>
+        <v>338</v>
       </c>
       <c r="G24" t="n">
-        <v>49987350</v>
+        <v>69797000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1220,12 +1222,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,13 +1236,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>43150</v>
+        <v>70100</v>
       </c>
       <c r="F25" t="n">
-        <v>1390</v>
+        <v>998</v>
       </c>
       <c r="G25" t="n">
-        <v>59978500</v>
+        <v>69959800</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,12 +1254,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,13 +1268,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>310000</v>
+        <v>93300</v>
       </c>
       <c r="F26" t="n">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G26" t="n">
-        <v>69750000</v>
+        <v>19966200</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,12 +1286,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1298,13 +1300,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6240</v>
+        <v>11300</v>
       </c>
       <c r="F27" t="n">
-        <v>3205</v>
+        <v>4424</v>
       </c>
       <c r="G27" t="n">
-        <v>19999200</v>
+        <v>49991200</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1316,12 +1318,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,13 +1332,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>24000</v>
+        <v>19740</v>
       </c>
       <c r="F28" t="n">
-        <v>833</v>
+        <v>2532</v>
       </c>
       <c r="G28" t="n">
-        <v>19992000</v>
+        <v>49981680</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1348,12 +1350,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,13 +1364,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>90300</v>
+        <v>25150</v>
       </c>
       <c r="F29" t="n">
-        <v>442</v>
+        <v>2385</v>
       </c>
       <c r="G29" t="n">
-        <v>39912600</v>
+        <v>59982750</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,12 +1382,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1394,13 +1396,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>279500</v>
+        <v>22050</v>
       </c>
       <c r="F30" t="n">
-        <v>357</v>
+        <v>2267</v>
       </c>
       <c r="G30" t="n">
-        <v>99781500</v>
+        <v>49987350</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1412,12 +1414,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1426,13 +1428,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>366000</v>
+        <v>43150</v>
       </c>
       <c r="F31" t="n">
-        <v>54</v>
+        <v>1390</v>
       </c>
       <c r="G31" t="n">
-        <v>19764000</v>
+        <v>59978500</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1444,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1458,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>91000</v>
+        <v>310000</v>
       </c>
       <c r="F32" t="n">
-        <v>659</v>
+        <v>225</v>
       </c>
       <c r="G32" t="n">
-        <v>59969000</v>
+        <v>69750000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1476,12 +1478,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1490,13 +1492,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>120100</v>
+        <v>6240</v>
       </c>
       <c r="F33" t="n">
-        <v>666</v>
+        <v>3205</v>
       </c>
       <c r="G33" t="n">
-        <v>79986600</v>
+        <v>19999200</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1508,12 +1510,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1522,13 +1524,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2405</v>
+        <v>24000</v>
       </c>
       <c r="F34" t="n">
-        <v>415800</v>
+        <v>833</v>
       </c>
       <c r="G34" t="n">
-        <v>999999000</v>
+        <v>19992000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1540,12 +1542,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1554,13 +1556,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>69000</v>
+        <v>90300</v>
       </c>
       <c r="F35" t="n">
-        <v>579</v>
+        <v>442</v>
       </c>
       <c r="G35" t="n">
-        <v>39951000</v>
+        <v>39912600</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1572,12 +1574,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1586,13 +1588,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>42300</v>
+        <v>279500</v>
       </c>
       <c r="F36" t="n">
-        <v>709</v>
+        <v>357</v>
       </c>
       <c r="G36" t="n">
-        <v>29990700</v>
+        <v>99781500</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1604,29 +1606,221 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>54</v>
+      </c>
+      <c r="G37" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>659</v>
+      </c>
+      <c r="G38" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F39" t="n">
+        <v>666</v>
+      </c>
+      <c r="G39" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F40" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G40" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F41" t="n">
+        <v>579</v>
+      </c>
+      <c r="G41" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F42" t="n">
+        <v>709</v>
+      </c>
+      <c r="G42" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
         <v>23350</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F43" t="n">
         <v>856</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>19987600</v>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,68 +473,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27100</v>
+        <v>327000</v>
       </c>
       <c r="F2" t="n">
-        <v>376</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>10189600</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67600</v>
+        <v>21750</v>
       </c>
       <c r="F3" t="n">
-        <v>998</v>
+        <v>943.8708</v>
       </c>
       <c r="G3" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>20529189.5</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11900</v>
+        <v>27100</v>
       </c>
       <c r="F4" t="n">
-        <v>856</v>
+        <v>376</v>
       </c>
       <c r="G4" t="n">
-        <v>10186400</v>
+        <v>10189600</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -576,29 +576,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29300</v>
+        <v>67600</v>
       </c>
       <c r="F5" t="n">
-        <v>2434</v>
+        <v>998</v>
       </c>
       <c r="G5" t="n">
-        <v>71316200</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,27 +610,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>119300</v>
+        <v>11900</v>
       </c>
       <c r="F6" t="n">
-        <v>171</v>
+        <v>856</v>
       </c>
       <c r="G6" t="n">
-        <v>20400300</v>
+        <v>10186400</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,91 +642,91 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2445</v>
+        <v>29300</v>
       </c>
       <c r="F7" t="n">
-        <v>82456</v>
+        <v>2434</v>
       </c>
       <c r="G7" t="n">
-        <v>201604920</v>
+        <v>71316200</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18910</v>
+        <v>119300</v>
       </c>
       <c r="F8" t="n">
-        <v>1068.0212</v>
+        <v>171</v>
       </c>
       <c r="G8" t="n">
-        <v>20196280</v>
+        <v>20400300</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32250</v>
+        <v>2445</v>
       </c>
       <c r="F9" t="n">
-        <v>626</v>
+        <v>82456</v>
       </c>
       <c r="G9" t="n">
-        <v>20188500</v>
+        <v>201604920</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,31 +738,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>82500</v>
+        <v>18910</v>
       </c>
       <c r="F10" t="n">
-        <v>204</v>
+        <v>1068.0212</v>
       </c>
       <c r="G10" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>20196280</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,36 +770,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>56800</v>
+        <v>32250</v>
       </c>
       <c r="F11" t="n">
-        <v>258</v>
+        <v>626</v>
       </c>
       <c r="G11" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20188500</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -814,51 +812,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>83700</v>
+        <v>82500</v>
       </c>
       <c r="F12" t="n">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="G12" t="n">
-        <v>10044000</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>43650</v>
+        <v>56800</v>
       </c>
       <c r="F13" t="n">
-        <v>462</v>
+        <v>258</v>
       </c>
       <c r="G13" t="n">
-        <v>20166300</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -868,12 +870,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -882,77 +884,77 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>59700</v>
+        <v>83700</v>
       </c>
       <c r="F14" t="n">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="G14" t="n">
-        <v>10089300</v>
+        <v>10044000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10930</v>
+        <v>43650</v>
       </c>
       <c r="F15" t="n">
-        <v>1833</v>
+        <v>462</v>
       </c>
       <c r="G15" t="n">
-        <v>20034690</v>
+        <v>20166300</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19850</v>
+        <v>59700</v>
       </c>
       <c r="F16" t="n">
-        <v>505</v>
+        <v>169</v>
       </c>
       <c r="G16" t="n">
-        <v>10024250</v>
+        <v>10089300</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -964,12 +966,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -978,13 +980,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>26350</v>
+        <v>10930</v>
       </c>
       <c r="F17" t="n">
-        <v>380</v>
+        <v>1833</v>
       </c>
       <c r="G17" t="n">
-        <v>10013000</v>
+        <v>20034690</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -996,31 +998,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>23500</v>
+        <v>19850</v>
       </c>
       <c r="F18" t="n">
-        <v>833</v>
+        <v>505</v>
       </c>
       <c r="G18" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10024250</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1030,27 +1030,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>85200</v>
+        <v>26350</v>
       </c>
       <c r="F19" t="n">
-        <v>118</v>
+        <v>380</v>
       </c>
       <c r="G19" t="n">
-        <v>10053600</v>
+        <v>10013000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1062,29 +1062,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>63400</v>
+        <v>23500</v>
       </c>
       <c r="F20" t="n">
-        <v>316</v>
+        <v>833</v>
       </c>
       <c r="G20" t="n">
-        <v>20034400</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1094,12 +1096,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1108,13 +1110,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>110300</v>
+        <v>85200</v>
       </c>
       <c r="F21" t="n">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="G21" t="n">
-        <v>10037300</v>
+        <v>10053600</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1126,91 +1128,91 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>66100</v>
+        <v>63400</v>
       </c>
       <c r="F22" t="n">
-        <v>152</v>
+        <v>316</v>
       </c>
       <c r="G22" t="n">
-        <v>10047200</v>
+        <v>20034400</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>25800</v>
+        <v>110300</v>
       </c>
       <c r="F23" t="n">
-        <v>2713</v>
+        <v>91</v>
       </c>
       <c r="G23" t="n">
-        <v>69995400</v>
+        <v>10037300</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206500</v>
+        <v>66100</v>
       </c>
       <c r="F24" t="n">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="G24" t="n">
-        <v>69797000</v>
+        <v>10047200</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1222,12 +1224,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1236,13 +1238,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>70100</v>
+        <v>25800</v>
       </c>
       <c r="F25" t="n">
-        <v>998</v>
+        <v>2713</v>
       </c>
       <c r="G25" t="n">
-        <v>69959800</v>
+        <v>69995400</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1254,12 +1256,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1268,13 +1270,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>93300</v>
+        <v>206500</v>
       </c>
       <c r="F26" t="n">
-        <v>214</v>
+        <v>338</v>
       </c>
       <c r="G26" t="n">
-        <v>19966200</v>
+        <v>69797000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1286,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1300,13 +1302,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>11300</v>
+        <v>70100</v>
       </c>
       <c r="F27" t="n">
-        <v>4424</v>
+        <v>998</v>
       </c>
       <c r="G27" t="n">
-        <v>49991200</v>
+        <v>69959800</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1318,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1332,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>19740</v>
+        <v>93300</v>
       </c>
       <c r="F28" t="n">
-        <v>2532</v>
+        <v>214</v>
       </c>
       <c r="G28" t="n">
-        <v>49981680</v>
+        <v>19966200</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1350,12 +1352,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1364,13 +1366,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25150</v>
+        <v>11300</v>
       </c>
       <c r="F29" t="n">
-        <v>2385</v>
+        <v>4424</v>
       </c>
       <c r="G29" t="n">
-        <v>59982750</v>
+        <v>49991200</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1382,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1396,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>22050</v>
+        <v>19740</v>
       </c>
       <c r="F30" t="n">
-        <v>2267</v>
+        <v>2532</v>
       </c>
       <c r="G30" t="n">
-        <v>49987350</v>
+        <v>49981680</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,12 +1416,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1428,13 +1430,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>43150</v>
+        <v>25150</v>
       </c>
       <c r="F31" t="n">
-        <v>1390</v>
+        <v>2385</v>
       </c>
       <c r="G31" t="n">
-        <v>59978500</v>
+        <v>59982750</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,12 +1448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1462,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>310000</v>
+        <v>22050</v>
       </c>
       <c r="F32" t="n">
-        <v>225</v>
+        <v>2267</v>
       </c>
       <c r="G32" t="n">
-        <v>69750000</v>
+        <v>49987350</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,12 +1480,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1492,13 +1494,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6240</v>
+        <v>43150</v>
       </c>
       <c r="F33" t="n">
-        <v>3205</v>
+        <v>1390</v>
       </c>
       <c r="G33" t="n">
-        <v>19999200</v>
+        <v>59978500</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1510,12 +1512,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1524,13 +1526,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>24000</v>
+        <v>310000</v>
       </c>
       <c r="F34" t="n">
-        <v>833</v>
+        <v>225</v>
       </c>
       <c r="G34" t="n">
-        <v>19992000</v>
+        <v>69750000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1542,12 +1544,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1556,13 +1558,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>90300</v>
+        <v>6240</v>
       </c>
       <c r="F35" t="n">
-        <v>442</v>
+        <v>3205</v>
       </c>
       <c r="G35" t="n">
-        <v>39912600</v>
+        <v>19999200</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1574,12 +1576,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1588,13 +1590,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>279500</v>
+        <v>24000</v>
       </c>
       <c r="F36" t="n">
-        <v>357</v>
+        <v>833</v>
       </c>
       <c r="G36" t="n">
-        <v>99781500</v>
+        <v>19992000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1606,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1620,13 +1622,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>366000</v>
+        <v>90300</v>
       </c>
       <c r="F37" t="n">
-        <v>54</v>
+        <v>442</v>
       </c>
       <c r="G37" t="n">
-        <v>19764000</v>
+        <v>39912600</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1638,12 +1640,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1652,13 +1654,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>91000</v>
+        <v>279500</v>
       </c>
       <c r="F38" t="n">
-        <v>659</v>
+        <v>357</v>
       </c>
       <c r="G38" t="n">
-        <v>59969000</v>
+        <v>99781500</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1670,12 +1672,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1684,13 +1686,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>120100</v>
+        <v>366000</v>
       </c>
       <c r="F39" t="n">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="G39" t="n">
-        <v>79986600</v>
+        <v>19764000</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1702,12 +1704,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,13 +1718,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2405</v>
+        <v>91000</v>
       </c>
       <c r="F40" t="n">
-        <v>415800</v>
+        <v>659</v>
       </c>
       <c r="G40" t="n">
-        <v>999999000</v>
+        <v>59969000</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1734,12 +1736,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1748,13 +1750,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>69000</v>
+        <v>120100</v>
       </c>
       <c r="F41" t="n">
-        <v>579</v>
+        <v>666</v>
       </c>
       <c r="G41" t="n">
-        <v>39951000</v>
+        <v>79986600</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1766,12 +1768,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1780,13 +1782,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>42300</v>
+        <v>2405</v>
       </c>
       <c r="F42" t="n">
-        <v>709</v>
+        <v>415800</v>
       </c>
       <c r="G42" t="n">
-        <v>29990700</v>
+        <v>999999000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1798,29 +1800,93 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>579</v>
+      </c>
+      <c r="G43" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F44" t="n">
+        <v>709</v>
+      </c>
+      <c r="G44" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
         <v>23350</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F45" t="n">
         <v>856</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G45" t="n">
         <v>19987600</v>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -512,12 +512,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21750</v>
+        <v>5130</v>
       </c>
       <c r="F3" t="n">
-        <v>943.8708</v>
+        <v>4001.7913</v>
       </c>
       <c r="G3" t="n">
         <v>20529189.5</v>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,83 +473,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>327000</v>
+        <v>30200</v>
       </c>
       <c r="F2" t="n">
-        <v>54</v>
+        <v>359.55</v>
       </c>
       <c r="G2" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>10858410.6</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5130</v>
+        <v>208500</v>
       </c>
       <c r="F3" t="n">
-        <v>4001.7913</v>
+        <v>338</v>
       </c>
       <c r="G3" t="n">
-        <v>20529189.5</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,128 +558,126 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27100</v>
+        <v>17720</v>
       </c>
       <c r="F4" t="n">
-        <v>376</v>
+        <v>94.9217</v>
       </c>
       <c r="G4" t="n">
-        <v>10189600</v>
+        <v>1682012.5</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67600</v>
+        <v>100500</v>
       </c>
       <c r="F5" t="n">
-        <v>998</v>
+        <v>8.9518</v>
       </c>
       <c r="G5" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>899652.6</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11900</v>
+        <v>11410</v>
       </c>
       <c r="F6" t="n">
-        <v>856</v>
+        <v>6321.2722</v>
       </c>
       <c r="G6" t="n">
-        <v>10186400</v>
+        <v>72125715.8</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29300</v>
+        <v>12880</v>
       </c>
       <c r="F7" t="n">
-        <v>2434</v>
+        <v>713.2027</v>
       </c>
       <c r="G7" t="n">
-        <v>71316200</v>
+        <v>9186050.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,30 +686,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>119300</v>
+        <v>21200</v>
       </c>
       <c r="F8" t="n">
-        <v>171</v>
+        <v>120.8659</v>
       </c>
       <c r="G8" t="n">
-        <v>20400300</v>
+        <v>2562357.9</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -720,52 +718,52 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2445</v>
+        <v>27700</v>
       </c>
       <c r="F9" t="n">
-        <v>82456</v>
+        <v>161.1835</v>
       </c>
       <c r="G9" t="n">
-        <v>201604920</v>
+        <v>4464784.2</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18910</v>
+        <v>21500</v>
       </c>
       <c r="F10" t="n">
-        <v>1068.0212</v>
+        <v>129.2032</v>
       </c>
       <c r="G10" t="n">
-        <v>20196280</v>
+        <v>2777868.4</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -780,166 +778,162 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>32250</v>
+        <v>34100</v>
       </c>
       <c r="F11" t="n">
-        <v>626</v>
+        <v>21.679</v>
       </c>
       <c r="G11" t="n">
-        <v>20188500</v>
+        <v>739252.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>82500</v>
+        <v>40850</v>
       </c>
       <c r="F12" t="n">
-        <v>204</v>
+        <v>123.3915</v>
       </c>
       <c r="G12" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>5040542.1</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>56800</v>
+        <v>308000</v>
       </c>
       <c r="F13" t="n">
-        <v>258</v>
+        <v>9.1744</v>
       </c>
       <c r="G13" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>2825715.8</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>83700</v>
+        <v>6330</v>
       </c>
       <c r="F14" t="n">
-        <v>120</v>
+        <v>50.5051</v>
       </c>
       <c r="G14" t="n">
-        <v>10044000</v>
+        <v>319697.4</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>43650</v>
+        <v>31700</v>
       </c>
       <c r="F15" t="n">
-        <v>462</v>
+        <v>158.7408</v>
       </c>
       <c r="G15" t="n">
-        <v>20166300</v>
+        <v>5032084.2</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -948,30 +942,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>59700</v>
+        <v>68700</v>
       </c>
       <c r="F16" t="n">
-        <v>169</v>
+        <v>16.0386</v>
       </c>
       <c r="G16" t="n">
-        <v>10089300</v>
+        <v>1101852.6</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -980,30 +974,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10930</v>
+        <v>256000</v>
       </c>
       <c r="F17" t="n">
-        <v>1833</v>
+        <v>45.4873</v>
       </c>
       <c r="G17" t="n">
-        <v>20034690</v>
+        <v>11644736.8</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1012,160 +1006,158 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>19850</v>
+        <v>91100</v>
       </c>
       <c r="F18" t="n">
-        <v>505</v>
+        <v>19.6174</v>
       </c>
       <c r="G18" t="n">
-        <v>10024250</v>
+        <v>1787142.1</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>26350</v>
+        <v>130900</v>
       </c>
       <c r="F19" t="n">
-        <v>380</v>
+        <v>89.1437</v>
       </c>
       <c r="G19" t="n">
-        <v>10013000</v>
+        <v>11668905.3</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>23500</v>
+        <v>2400</v>
       </c>
       <c r="F20" t="n">
-        <v>833</v>
+        <v>32820.1843</v>
       </c>
       <c r="G20" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>78768442.40000001</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>85200</v>
+        <v>41150</v>
       </c>
       <c r="F21" t="n">
-        <v>118</v>
+        <v>38.7861</v>
       </c>
       <c r="G21" t="n">
-        <v>10053600</v>
+        <v>1596047.4</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>63400</v>
+        <v>49450</v>
       </c>
       <c r="F22" t="n">
-        <v>316</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>20034400</v>
+        <v>4149029</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,30 +1166,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>110300</v>
+        <v>24750</v>
       </c>
       <c r="F23" t="n">
-        <v>91</v>
+        <v>23.3799</v>
       </c>
       <c r="G23" t="n">
-        <v>10037300</v>
+        <v>578652.6</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,62 +1198,64 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>66100</v>
+        <v>5450</v>
       </c>
       <c r="F24" t="n">
-        <v>152</v>
+        <v>220.6267</v>
       </c>
       <c r="G24" t="n">
-        <v>10047200</v>
+        <v>1202415.4</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>25800</v>
+        <v>327000</v>
       </c>
       <c r="F25" t="n">
-        <v>2713</v>
+        <v>54</v>
       </c>
       <c r="G25" t="n">
-        <v>69995400</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1270,84 +1264,86 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206500</v>
+        <v>5130</v>
       </c>
       <c r="F26" t="n">
-        <v>338</v>
+        <v>4001.7913</v>
       </c>
       <c r="G26" t="n">
-        <v>69797000</v>
+        <v>20529189.5</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>70100</v>
+        <v>27100</v>
       </c>
       <c r="F27" t="n">
-        <v>998</v>
+        <v>376</v>
       </c>
       <c r="G27" t="n">
-        <v>69959800</v>
+        <v>10189600</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>93300</v>
+        <v>67600</v>
       </c>
       <c r="F28" t="n">
-        <v>214</v>
+        <v>998</v>
       </c>
       <c r="G28" t="n">
-        <v>19966200</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1362,34 +1358,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11300</v>
+        <v>11900</v>
       </c>
       <c r="F29" t="n">
-        <v>4424</v>
+        <v>856</v>
       </c>
       <c r="G29" t="n">
-        <v>49991200</v>
+        <v>10186400</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,94 +1394,94 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>19740</v>
+        <v>29300</v>
       </c>
       <c r="F30" t="n">
-        <v>2532</v>
+        <v>2434</v>
       </c>
       <c r="G30" t="n">
-        <v>49981680</v>
+        <v>71316200</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>25150</v>
+        <v>119300</v>
       </c>
       <c r="F31" t="n">
-        <v>2385</v>
+        <v>171</v>
       </c>
       <c r="G31" t="n">
-        <v>59982750</v>
+        <v>20400300</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22050</v>
+        <v>2445</v>
       </c>
       <c r="F32" t="n">
-        <v>2267</v>
+        <v>82456</v>
       </c>
       <c r="G32" t="n">
-        <v>49987350</v>
+        <v>201604920</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1494,30 +1490,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>43150</v>
+        <v>18910</v>
       </c>
       <c r="F33" t="n">
-        <v>1390</v>
+        <v>1068.0212</v>
       </c>
       <c r="G33" t="n">
-        <v>59978500</v>
+        <v>20196280</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1526,84 +1522,88 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>310000</v>
+        <v>32250</v>
       </c>
       <c r="F34" t="n">
-        <v>225</v>
+        <v>626</v>
       </c>
       <c r="G34" t="n">
-        <v>69750000</v>
+        <v>20188500</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6240</v>
+        <v>82500</v>
       </c>
       <c r="F35" t="n">
-        <v>3205</v>
+        <v>204</v>
       </c>
       <c r="G35" t="n">
-        <v>19999200</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>24000</v>
+        <v>56800</v>
       </c>
       <c r="F36" t="n">
-        <v>833</v>
+        <v>258</v>
       </c>
       <c r="G36" t="n">
-        <v>19992000</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1618,34 +1618,34 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>90300</v>
+        <v>83700</v>
       </c>
       <c r="F37" t="n">
-        <v>442</v>
+        <v>120</v>
       </c>
       <c r="G37" t="n">
-        <v>39912600</v>
+        <v>10044000</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,239 +1654,977 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>279500</v>
+        <v>43650</v>
       </c>
       <c r="F38" t="n">
-        <v>357</v>
+        <v>462</v>
       </c>
       <c r="G38" t="n">
-        <v>99781500</v>
+        <v>20166300</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>366000</v>
+        <v>59700</v>
       </c>
       <c r="F39" t="n">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="G39" t="n">
-        <v>19764000</v>
+        <v>10089300</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>91000</v>
+        <v>10930</v>
       </c>
       <c r="F40" t="n">
-        <v>659</v>
+        <v>1833</v>
       </c>
       <c r="G40" t="n">
-        <v>59969000</v>
+        <v>20034690</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>120100</v>
+        <v>19850</v>
       </c>
       <c r="F41" t="n">
-        <v>666</v>
+        <v>505</v>
       </c>
       <c r="G41" t="n">
-        <v>79986600</v>
+        <v>10024250</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2405</v>
+        <v>26350</v>
       </c>
       <c r="F42" t="n">
-        <v>415800</v>
+        <v>380</v>
       </c>
       <c r="G42" t="n">
-        <v>999999000</v>
+        <v>10013000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>69000</v>
+        <v>23500</v>
       </c>
       <c r="F43" t="n">
-        <v>579</v>
+        <v>833</v>
       </c>
       <c r="G43" t="n">
-        <v>39951000</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>42300</v>
+        <v>85200</v>
       </c>
       <c r="F44" t="n">
-        <v>709</v>
+        <v>118</v>
       </c>
       <c r="G44" t="n">
-        <v>29990700</v>
+        <v>10053600</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>인텔리안테크</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>189300</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>63400</v>
+      </c>
+      <c r="F45" t="n">
+        <v>316</v>
+      </c>
+      <c r="G45" t="n">
+        <v>20034400</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>110300</v>
+      </c>
+      <c r="F46" t="n">
+        <v>91</v>
+      </c>
+      <c r="G46" t="n">
+        <v>10037300</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>비중 축소</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>66100</v>
+      </c>
+      <c r="F47" t="n">
+        <v>152</v>
+      </c>
+      <c r="G47" t="n">
+        <v>10047200</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>25800</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2713</v>
+      </c>
+      <c r="G48" t="n">
+        <v>69995400</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>036930</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>206500</v>
+      </c>
+      <c r="F49" t="n">
+        <v>338</v>
+      </c>
+      <c r="G49" t="n">
+        <v>69797000</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>058470</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>70100</v>
+      </c>
+      <c r="F50" t="n">
+        <v>998</v>
+      </c>
+      <c r="G50" t="n">
+        <v>69959800</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>058610</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>93300</v>
+      </c>
+      <c r="F51" t="n">
+        <v>214</v>
+      </c>
+      <c r="G51" t="n">
+        <v>19966200</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>유니테스트</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>086390</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>11300</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4424</v>
+      </c>
+      <c r="G52" t="n">
+        <v>49991200</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>086450</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>19740</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2532</v>
+      </c>
+      <c r="G53" t="n">
+        <v>49981680</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>25150</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2385</v>
+      </c>
+      <c r="G54" t="n">
+        <v>59982750</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>091580</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>22050</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2267</v>
+      </c>
+      <c r="G55" t="n">
+        <v>49987350</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>107640</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>43150</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G56" t="n">
+        <v>59978500</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>108490</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>310000</v>
+      </c>
+      <c r="F57" t="n">
+        <v>225</v>
+      </c>
+      <c r="G57" t="n">
+        <v>69750000</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>티씨머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>125020</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6240</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3205</v>
+      </c>
+      <c r="G58" t="n">
+        <v>19999200</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>138080</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F59" t="n">
+        <v>833</v>
+      </c>
+      <c r="G59" t="n">
+        <v>19992000</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>141080</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>90300</v>
+      </c>
+      <c r="F60" t="n">
+        <v>442</v>
+      </c>
+      <c r="G60" t="n">
+        <v>39912600</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>279500</v>
+      </c>
+      <c r="F61" t="n">
+        <v>357</v>
+      </c>
+      <c r="G61" t="n">
+        <v>99781500</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F62" t="n">
+        <v>54</v>
+      </c>
+      <c r="G62" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F63" t="n">
+        <v>659</v>
+      </c>
+      <c r="G63" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F64" t="n">
+        <v>666</v>
+      </c>
+      <c r="G64" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F65" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G65" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F66" t="n">
+        <v>579</v>
+      </c>
+      <c r="G66" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F67" t="n">
+        <v>709</v>
+      </c>
+      <c r="G67" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
         <v>23350</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F68" t="n">
         <v>856</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G68" t="n">
         <v>19987600</v>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,147 +473,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30200</v>
+        <v>12310</v>
       </c>
       <c r="F2" t="n">
-        <v>359.55</v>
+        <v>2480.1654</v>
       </c>
       <c r="G2" t="n">
-        <v>10858410.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208500</v>
+        <v>40650</v>
       </c>
       <c r="F3" t="n">
-        <v>338</v>
+        <v>751.0661</v>
       </c>
       <c r="G3" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.97</v>
-      </c>
+        <v>30530836.4</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17720</v>
+        <v>283500</v>
       </c>
       <c r="F4" t="n">
-        <v>94.9217</v>
+        <v>71.795</v>
       </c>
       <c r="G4" t="n">
-        <v>1682012.5</v>
+        <v>20353890.9</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100500</v>
+        <v>2390</v>
       </c>
       <c r="F5" t="n">
-        <v>8.9518</v>
+        <v>42581.3618</v>
       </c>
       <c r="G5" t="n">
-        <v>899652.6</v>
+        <v>101769454.6</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,13 +620,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11410</v>
+        <v>20450</v>
       </c>
       <c r="F6" t="n">
-        <v>6321.2722</v>
+        <v>995.3003</v>
       </c>
       <c r="G6" t="n">
-        <v>72125715.8</v>
+        <v>20353890.9</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,12 +638,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,13 +652,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12880</v>
+        <v>30200</v>
       </c>
       <c r="F7" t="n">
-        <v>713.2027</v>
+        <v>359.55</v>
       </c>
       <c r="G7" t="n">
-        <v>9186050.6</v>
+        <v>10858410.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -672,29 +670,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21200</v>
+        <v>208500</v>
       </c>
       <c r="F8" t="n">
-        <v>120.8659</v>
+        <v>338</v>
       </c>
       <c r="G8" t="n">
-        <v>2562357.9</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -704,27 +704,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>27700</v>
+        <v>17720</v>
       </c>
       <c r="F9" t="n">
-        <v>161.1835</v>
+        <v>94.9217</v>
       </c>
       <c r="G9" t="n">
-        <v>4464784.2</v>
+        <v>1682012.5</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,27 +736,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21500</v>
+        <v>100500</v>
       </c>
       <c r="F10" t="n">
-        <v>129.2032</v>
+        <v>8.9518</v>
       </c>
       <c r="G10" t="n">
-        <v>2777868.4</v>
+        <v>899652.6</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,27 +768,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>34100</v>
+        <v>11410</v>
       </c>
       <c r="F11" t="n">
-        <v>21.679</v>
+        <v>6321.2722</v>
       </c>
       <c r="G11" t="n">
-        <v>739252.6</v>
+        <v>72125715.8</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,27 +800,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>40850</v>
+        <v>12880</v>
       </c>
       <c r="F12" t="n">
-        <v>123.3915</v>
+        <v>713.2027</v>
       </c>
       <c r="G12" t="n">
-        <v>5040542.1</v>
+        <v>9186050.6</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,27 +832,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308000</v>
+        <v>21200</v>
       </c>
       <c r="F13" t="n">
-        <v>9.1744</v>
+        <v>120.8659</v>
       </c>
       <c r="G13" t="n">
-        <v>2825715.8</v>
+        <v>2562357.9</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,27 +864,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6330</v>
+        <v>27700</v>
       </c>
       <c r="F14" t="n">
-        <v>50.5051</v>
+        <v>161.1835</v>
       </c>
       <c r="G14" t="n">
-        <v>319697.4</v>
+        <v>4464784.2</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>31700</v>
+        <v>21500</v>
       </c>
       <c r="F15" t="n">
-        <v>158.7408</v>
+        <v>129.2032</v>
       </c>
       <c r="G15" t="n">
-        <v>5032084.2</v>
+        <v>2777868.4</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>68700</v>
+        <v>34100</v>
       </c>
       <c r="F16" t="n">
-        <v>16.0386</v>
+        <v>21.679</v>
       </c>
       <c r="G16" t="n">
-        <v>1101852.6</v>
+        <v>739252.6</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>256000</v>
+        <v>40850</v>
       </c>
       <c r="F17" t="n">
-        <v>45.4873</v>
+        <v>123.3915</v>
       </c>
       <c r="G17" t="n">
-        <v>11644736.8</v>
+        <v>5040542.1</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91100</v>
+        <v>308000</v>
       </c>
       <c r="F18" t="n">
-        <v>19.6174</v>
+        <v>9.1744</v>
       </c>
       <c r="G18" t="n">
-        <v>1787142.1</v>
+        <v>2825715.8</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>130900</v>
+        <v>6330</v>
       </c>
       <c r="F19" t="n">
-        <v>89.1437</v>
+        <v>50.5051</v>
       </c>
       <c r="G19" t="n">
-        <v>11668905.3</v>
+        <v>319697.4</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2400</v>
+        <v>31700</v>
       </c>
       <c r="F20" t="n">
-        <v>32820.1843</v>
+        <v>158.7408</v>
       </c>
       <c r="G20" t="n">
-        <v>78768442.40000001</v>
+        <v>5032084.2</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1088,27 +1088,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>41150</v>
+        <v>68700</v>
       </c>
       <c r="F21" t="n">
-        <v>38.7861</v>
+        <v>16.0386</v>
       </c>
       <c r="G21" t="n">
-        <v>1596047.4</v>
+        <v>1101852.6</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1120,27 +1120,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49450</v>
+        <v>256000</v>
       </c>
       <c r="F22" t="n">
-        <v>83.90349999999999</v>
+        <v>45.4873</v>
       </c>
       <c r="G22" t="n">
-        <v>4149029</v>
+        <v>11644736.8</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1152,27 +1152,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>24750</v>
+        <v>91100</v>
       </c>
       <c r="F23" t="n">
-        <v>23.3799</v>
+        <v>19.6174</v>
       </c>
       <c r="G23" t="n">
-        <v>578652.6</v>
+        <v>1787142.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1198,241 +1198,239 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5450</v>
+        <v>130900</v>
       </c>
       <c r="F24" t="n">
-        <v>220.6267</v>
+        <v>89.1437</v>
       </c>
       <c r="G24" t="n">
-        <v>1202415.4</v>
+        <v>11668905.3</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>327000</v>
+        <v>2400</v>
       </c>
       <c r="F25" t="n">
-        <v>54</v>
+        <v>32820.1843</v>
       </c>
       <c r="G25" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>78768442.40000001</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5130</v>
+        <v>41150</v>
       </c>
       <c r="F26" t="n">
-        <v>4001.7913</v>
+        <v>38.7861</v>
       </c>
       <c r="G26" t="n">
-        <v>20529189.5</v>
+        <v>1596047.4</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>27100</v>
+        <v>49450</v>
       </c>
       <c r="F27" t="n">
-        <v>376</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>10189600</v>
+        <v>4149029</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>67600</v>
+        <v>24750</v>
       </c>
       <c r="F28" t="n">
-        <v>998</v>
+        <v>23.3799</v>
       </c>
       <c r="G28" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>578652.6</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11900</v>
+        <v>5450</v>
       </c>
       <c r="F29" t="n">
-        <v>856</v>
+        <v>220.6267</v>
       </c>
       <c r="G29" t="n">
-        <v>10186400</v>
+        <v>1202415.4</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29300</v>
+        <v>327000</v>
       </c>
       <c r="F30" t="n">
-        <v>2434</v>
+        <v>54</v>
       </c>
       <c r="G30" t="n">
-        <v>71316200</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>119300</v>
+        <v>5130</v>
       </c>
       <c r="F31" t="n">
-        <v>171</v>
+        <v>4001.7913</v>
       </c>
       <c r="G31" t="n">
-        <v>20400300</v>
+        <v>20529189.5</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1444,176 +1442,174 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2445</v>
+        <v>27100</v>
       </c>
       <c r="F32" t="n">
-        <v>82456</v>
+        <v>376</v>
       </c>
       <c r="G32" t="n">
-        <v>201604920</v>
+        <v>10189600</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>18910</v>
+        <v>67600</v>
       </c>
       <c r="F33" t="n">
-        <v>1068.0212</v>
+        <v>998</v>
       </c>
       <c r="G33" t="n">
-        <v>20196280</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>32250</v>
+        <v>11900</v>
       </c>
       <c r="F34" t="n">
-        <v>626</v>
+        <v>856</v>
       </c>
       <c r="G34" t="n">
-        <v>20188500</v>
+        <v>10186400</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>82500</v>
+        <v>29300</v>
       </c>
       <c r="F35" t="n">
-        <v>204</v>
+        <v>2434</v>
       </c>
       <c r="G35" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>71316200</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>56800</v>
+        <v>119300</v>
       </c>
       <c r="F36" t="n">
-        <v>258</v>
+        <v>171</v>
       </c>
       <c r="G36" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20400300</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1622,30 +1618,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>83700</v>
+        <v>2445</v>
       </c>
       <c r="F37" t="n">
-        <v>120</v>
+        <v>82456</v>
       </c>
       <c r="G37" t="n">
-        <v>10044000</v>
+        <v>201604920</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,192 +1650,194 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>43650</v>
+        <v>18910</v>
       </c>
       <c r="F38" t="n">
-        <v>462</v>
+        <v>1068.0212</v>
       </c>
       <c r="G38" t="n">
-        <v>20166300</v>
+        <v>20196280</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>59700</v>
+        <v>32250</v>
       </c>
       <c r="F39" t="n">
-        <v>169</v>
+        <v>626</v>
       </c>
       <c r="G39" t="n">
-        <v>10089300</v>
+        <v>20188500</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10930</v>
+        <v>82500</v>
       </c>
       <c r="F40" t="n">
-        <v>1833</v>
+        <v>204</v>
       </c>
       <c r="G40" t="n">
-        <v>20034690</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>19850</v>
+        <v>56800</v>
       </c>
       <c r="F41" t="n">
-        <v>505</v>
+        <v>258</v>
       </c>
       <c r="G41" t="n">
-        <v>10024250</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>26350</v>
+        <v>83700</v>
       </c>
       <c r="F42" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="G42" t="n">
-        <v>10013000</v>
+        <v>10044000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>23500</v>
+        <v>43650</v>
       </c>
       <c r="F43" t="n">
-        <v>833</v>
+        <v>462</v>
       </c>
       <c r="G43" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20166300</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1848,13 +1846,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>85200</v>
+        <v>59700</v>
       </c>
       <c r="F44" t="n">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="G44" t="n">
-        <v>10053600</v>
+        <v>10089300</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1866,27 +1864,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>63400</v>
+        <v>10930</v>
       </c>
       <c r="F45" t="n">
-        <v>316</v>
+        <v>1833</v>
       </c>
       <c r="G45" t="n">
-        <v>20034400</v>
+        <v>20034690</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1898,27 +1896,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>110300</v>
+        <v>19850</v>
       </c>
       <c r="F46" t="n">
-        <v>91</v>
+        <v>505</v>
       </c>
       <c r="G46" t="n">
-        <v>10037300</v>
+        <v>10024250</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1930,108 +1928,110 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>66100</v>
+        <v>26350</v>
       </c>
       <c r="F47" t="n">
-        <v>152</v>
+        <v>380</v>
       </c>
       <c r="G47" t="n">
-        <v>10047200</v>
+        <v>10013000</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>25800</v>
+        <v>23500</v>
       </c>
       <c r="F48" t="n">
-        <v>2713</v>
+        <v>833</v>
       </c>
       <c r="G48" t="n">
-        <v>69995400</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>206500</v>
+        <v>85200</v>
       </c>
       <c r="F49" t="n">
-        <v>338</v>
+        <v>118</v>
       </c>
       <c r="G49" t="n">
-        <v>69797000</v>
+        <v>10053600</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2040,77 +2040,77 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>70100</v>
+        <v>63400</v>
       </c>
       <c r="F50" t="n">
-        <v>998</v>
+        <v>316</v>
       </c>
       <c r="G50" t="n">
-        <v>69959800</v>
+        <v>20034400</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>93300</v>
+        <v>110300</v>
       </c>
       <c r="F51" t="n">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="G51" t="n">
-        <v>19966200</v>
+        <v>10037300</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>11300</v>
+        <v>66100</v>
       </c>
       <c r="F52" t="n">
-        <v>4424</v>
+        <v>152</v>
       </c>
       <c r="G52" t="n">
-        <v>49991200</v>
+        <v>10047200</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>19740</v>
+        <v>25800</v>
       </c>
       <c r="F53" t="n">
-        <v>2532</v>
+        <v>2713</v>
       </c>
       <c r="G53" t="n">
-        <v>49981680</v>
+        <v>69995400</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>25150</v>
+        <v>206500</v>
       </c>
       <c r="F54" t="n">
-        <v>2385</v>
+        <v>338</v>
       </c>
       <c r="G54" t="n">
-        <v>59982750</v>
+        <v>69797000</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>22050</v>
+        <v>70100</v>
       </c>
       <c r="F55" t="n">
-        <v>2267</v>
+        <v>998</v>
       </c>
       <c r="G55" t="n">
-        <v>49987350</v>
+        <v>69959800</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>43150</v>
+        <v>93300</v>
       </c>
       <c r="F56" t="n">
-        <v>1390</v>
+        <v>214</v>
       </c>
       <c r="G56" t="n">
-        <v>59978500</v>
+        <v>19966200</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2264,13 +2264,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>310000</v>
+        <v>11300</v>
       </c>
       <c r="F57" t="n">
-        <v>225</v>
+        <v>4424</v>
       </c>
       <c r="G57" t="n">
-        <v>69750000</v>
+        <v>49991200</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6240</v>
+        <v>19740</v>
       </c>
       <c r="F58" t="n">
-        <v>3205</v>
+        <v>2532</v>
       </c>
       <c r="G58" t="n">
-        <v>19999200</v>
+        <v>49981680</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2314,12 +2314,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>24000</v>
+        <v>25150</v>
       </c>
       <c r="F59" t="n">
-        <v>833</v>
+        <v>2385</v>
       </c>
       <c r="G59" t="n">
-        <v>19992000</v>
+        <v>59982750</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2360,13 +2360,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>90300</v>
+        <v>22050</v>
       </c>
       <c r="F60" t="n">
-        <v>442</v>
+        <v>2267</v>
       </c>
       <c r="G60" t="n">
-        <v>39912600</v>
+        <v>49987350</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>279500</v>
+        <v>43150</v>
       </c>
       <c r="F61" t="n">
-        <v>357</v>
+        <v>1390</v>
       </c>
       <c r="G61" t="n">
-        <v>99781500</v>
+        <v>59978500</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>366000</v>
+        <v>310000</v>
       </c>
       <c r="F62" t="n">
-        <v>54</v>
+        <v>225</v>
       </c>
       <c r="G62" t="n">
-        <v>19764000</v>
+        <v>69750000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2456,13 +2456,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>91000</v>
+        <v>6240</v>
       </c>
       <c r="F63" t="n">
-        <v>659</v>
+        <v>3205</v>
       </c>
       <c r="G63" t="n">
-        <v>59969000</v>
+        <v>19999200</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>120100</v>
+        <v>24000</v>
       </c>
       <c r="F64" t="n">
-        <v>666</v>
+        <v>833</v>
       </c>
       <c r="G64" t="n">
-        <v>79986600</v>
+        <v>19992000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2520,13 +2520,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2405</v>
+        <v>90300</v>
       </c>
       <c r="F65" t="n">
-        <v>415800</v>
+        <v>442</v>
       </c>
       <c r="G65" t="n">
-        <v>999999000</v>
+        <v>39912600</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>69000</v>
+        <v>279500</v>
       </c>
       <c r="F66" t="n">
-        <v>579</v>
+        <v>357</v>
       </c>
       <c r="G66" t="n">
-        <v>39951000</v>
+        <v>99781500</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>42300</v>
+        <v>366000</v>
       </c>
       <c r="F67" t="n">
-        <v>709</v>
+        <v>54</v>
       </c>
       <c r="G67" t="n">
-        <v>29990700</v>
+        <v>19764000</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2602,29 +2602,189 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F68" t="n">
+        <v>659</v>
+      </c>
+      <c r="G68" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F69" t="n">
+        <v>666</v>
+      </c>
+      <c r="G69" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F70" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G70" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F71" t="n">
+        <v>579</v>
+      </c>
+      <c r="G71" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F72" t="n">
+        <v>709</v>
+      </c>
+      <c r="G72" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
         <v>23350</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F73" t="n">
         <v>856</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G73" t="n">
         <v>19987600</v>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,135 +473,137 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12310</v>
+        <v>58700</v>
       </c>
       <c r="F2" t="n">
-        <v>2480.1654</v>
+        <v>357.1039</v>
       </c>
       <c r="G2" t="n">
-        <v>30530836.4</v>
+        <v>20961998.6</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40650</v>
+        <v>13250</v>
       </c>
       <c r="F3" t="n">
-        <v>751.0661</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>30530836.4</v>
+        <v>10480999.3</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>283500</v>
+        <v>2360</v>
       </c>
       <c r="F4" t="n">
-        <v>71.795</v>
+        <v>66616.5209</v>
       </c>
       <c r="G4" t="n">
-        <v>20353890.9</v>
+        <v>157214989.3</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2390</v>
+        <v>38300</v>
       </c>
       <c r="F5" t="n">
-        <v>42581.3618</v>
+        <v>500.7861</v>
       </c>
       <c r="G5" t="n">
-        <v>101769454.6</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -616,132 +618,132 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20450</v>
+        <v>21150</v>
       </c>
       <c r="F6" t="n">
-        <v>995.3003</v>
+        <v>495.5555</v>
       </c>
       <c r="G6" t="n">
-        <v>20353890.9</v>
+        <v>10480999.3</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30200</v>
+        <v>23650</v>
       </c>
       <c r="F7" t="n">
-        <v>359.55</v>
+        <v>832.6201</v>
       </c>
       <c r="G7" t="n">
-        <v>10858410.6</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208500</v>
+        <v>12310</v>
       </c>
       <c r="F8" t="n">
-        <v>338</v>
+        <v>2480.1654</v>
       </c>
       <c r="G8" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.97</v>
-      </c>
+        <v>30530836.4</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17720</v>
+        <v>40650</v>
       </c>
       <c r="F9" t="n">
-        <v>94.9217</v>
+        <v>751.0661</v>
       </c>
       <c r="G9" t="n">
-        <v>1682012.5</v>
+        <v>30530836.4</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,77 +752,77 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100500</v>
+        <v>283500</v>
       </c>
       <c r="F10" t="n">
-        <v>8.9518</v>
+        <v>71.795</v>
       </c>
       <c r="G10" t="n">
-        <v>899652.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11410</v>
+        <v>2390</v>
       </c>
       <c r="F11" t="n">
-        <v>6321.2722</v>
+        <v>42581.3618</v>
       </c>
       <c r="G11" t="n">
-        <v>72125715.8</v>
+        <v>101769454.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12880</v>
+        <v>20450</v>
       </c>
       <c r="F12" t="n">
-        <v>713.2027</v>
+        <v>995.3003</v>
       </c>
       <c r="G12" t="n">
-        <v>9186050.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +848,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21200</v>
+        <v>30200</v>
       </c>
       <c r="F13" t="n">
-        <v>120.8659</v>
+        <v>359.55</v>
       </c>
       <c r="G13" t="n">
-        <v>2562357.9</v>
+        <v>10858410.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,29 +866,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>27700</v>
+        <v>208500</v>
       </c>
       <c r="F14" t="n">
-        <v>161.1835</v>
+        <v>338</v>
       </c>
       <c r="G14" t="n">
-        <v>4464784.2</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -896,12 +900,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -910,13 +914,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21500</v>
+        <v>17720</v>
       </c>
       <c r="F15" t="n">
-        <v>129.2032</v>
+        <v>94.9217</v>
       </c>
       <c r="G15" t="n">
-        <v>2777868.4</v>
+        <v>1682012.5</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,13 +946,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>34100</v>
+        <v>100500</v>
       </c>
       <c r="F16" t="n">
-        <v>21.679</v>
+        <v>8.9518</v>
       </c>
       <c r="G16" t="n">
-        <v>739252.6</v>
+        <v>899652.6</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,27 +964,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40850</v>
+        <v>11410</v>
       </c>
       <c r="F17" t="n">
-        <v>123.3915</v>
+        <v>6321.2722</v>
       </c>
       <c r="G17" t="n">
-        <v>5040542.1</v>
+        <v>72125715.8</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,27 +996,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308000</v>
+        <v>12880</v>
       </c>
       <c r="F18" t="n">
-        <v>9.1744</v>
+        <v>713.2027</v>
       </c>
       <c r="G18" t="n">
-        <v>2825715.8</v>
+        <v>9186050.6</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,27 +1028,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6330</v>
+        <v>21200</v>
       </c>
       <c r="F19" t="n">
-        <v>50.5051</v>
+        <v>120.8659</v>
       </c>
       <c r="G19" t="n">
-        <v>319697.4</v>
+        <v>2562357.9</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1056,12 +1060,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1070,13 +1074,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31700</v>
+        <v>27700</v>
       </c>
       <c r="F20" t="n">
-        <v>158.7408</v>
+        <v>161.1835</v>
       </c>
       <c r="G20" t="n">
-        <v>5032084.2</v>
+        <v>4464784.2</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1088,27 +1092,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>68700</v>
+        <v>21500</v>
       </c>
       <c r="F21" t="n">
-        <v>16.0386</v>
+        <v>129.2032</v>
       </c>
       <c r="G21" t="n">
-        <v>1101852.6</v>
+        <v>2777868.4</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1120,27 +1124,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>256000</v>
+        <v>34100</v>
       </c>
       <c r="F22" t="n">
-        <v>45.4873</v>
+        <v>21.679</v>
       </c>
       <c r="G22" t="n">
-        <v>11644736.8</v>
+        <v>739252.6</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1152,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1166,13 +1170,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91100</v>
+        <v>40850</v>
       </c>
       <c r="F23" t="n">
-        <v>19.6174</v>
+        <v>123.3915</v>
       </c>
       <c r="G23" t="n">
-        <v>1787142.1</v>
+        <v>5040542.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1184,27 +1188,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>130900</v>
+        <v>308000</v>
       </c>
       <c r="F24" t="n">
-        <v>89.1437</v>
+        <v>9.1744</v>
       </c>
       <c r="G24" t="n">
-        <v>11668905.3</v>
+        <v>2825715.8</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1216,27 +1220,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2400</v>
+        <v>6330</v>
       </c>
       <c r="F25" t="n">
-        <v>32820.1843</v>
+        <v>50.5051</v>
       </c>
       <c r="G25" t="n">
-        <v>78768442.40000001</v>
+        <v>319697.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1248,27 +1252,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>41150</v>
+        <v>31700</v>
       </c>
       <c r="F26" t="n">
-        <v>38.7861</v>
+        <v>158.7408</v>
       </c>
       <c r="G26" t="n">
-        <v>1596047.4</v>
+        <v>5032084.2</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1280,12 +1284,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1294,13 +1298,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49450</v>
+        <v>68700</v>
       </c>
       <c r="F27" t="n">
-        <v>83.90349999999999</v>
+        <v>16.0386</v>
       </c>
       <c r="G27" t="n">
-        <v>4149029</v>
+        <v>1101852.6</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1312,27 +1316,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>24750</v>
+        <v>256000</v>
       </c>
       <c r="F28" t="n">
-        <v>23.3799</v>
+        <v>45.4873</v>
       </c>
       <c r="G28" t="n">
-        <v>578652.6</v>
+        <v>11644736.8</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1344,110 +1348,108 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5450</v>
+        <v>91100</v>
       </c>
       <c r="F29" t="n">
-        <v>220.6267</v>
+        <v>19.6174</v>
       </c>
       <c r="G29" t="n">
-        <v>1202415.4</v>
+        <v>1787142.1</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>327000</v>
+        <v>130900</v>
       </c>
       <c r="F30" t="n">
-        <v>54</v>
+        <v>89.1437</v>
       </c>
       <c r="G30" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>11668905.3</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5130</v>
+        <v>2400</v>
       </c>
       <c r="F31" t="n">
-        <v>4001.7913</v>
+        <v>32820.1843</v>
       </c>
       <c r="G31" t="n">
-        <v>20529189.5</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1456,324 +1458,322 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>27100</v>
+        <v>41150</v>
       </c>
       <c r="F32" t="n">
-        <v>376</v>
+        <v>38.7861</v>
       </c>
       <c r="G32" t="n">
-        <v>10189600</v>
+        <v>1596047.4</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67600</v>
+        <v>49450</v>
       </c>
       <c r="F33" t="n">
-        <v>998</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>4149029</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>11900</v>
+        <v>24750</v>
       </c>
       <c r="F34" t="n">
-        <v>856</v>
+        <v>23.3799</v>
       </c>
       <c r="G34" t="n">
-        <v>10186400</v>
+        <v>578652.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>29300</v>
+        <v>5450</v>
       </c>
       <c r="F35" t="n">
-        <v>2434</v>
+        <v>220.6267</v>
       </c>
       <c r="G35" t="n">
-        <v>71316200</v>
+        <v>1202415.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>119300</v>
+        <v>327000</v>
       </c>
       <c r="F36" t="n">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="G36" t="n">
-        <v>20400300</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2445</v>
+        <v>5130</v>
       </c>
       <c r="F37" t="n">
-        <v>82456</v>
+        <v>4001.7913</v>
       </c>
       <c r="G37" t="n">
-        <v>201604920</v>
+        <v>20529189.5</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>18910</v>
+        <v>27100</v>
       </c>
       <c r="F38" t="n">
-        <v>1068.0212</v>
+        <v>376</v>
       </c>
       <c r="G38" t="n">
-        <v>20196280</v>
+        <v>10189600</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>32250</v>
+        <v>67600</v>
       </c>
       <c r="F39" t="n">
-        <v>626</v>
+        <v>998</v>
       </c>
       <c r="G39" t="n">
-        <v>20188500</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>82500</v>
+        <v>11900</v>
       </c>
       <c r="F40" t="n">
-        <v>204</v>
+        <v>856</v>
       </c>
       <c r="G40" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>10186400</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>56800</v>
+        <v>29300</v>
       </c>
       <c r="F41" t="n">
-        <v>258</v>
+        <v>2434</v>
       </c>
       <c r="G41" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>71316200</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1782,271 +1782,273 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>83700</v>
+        <v>119300</v>
       </c>
       <c r="F42" t="n">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="G42" t="n">
-        <v>10044000</v>
+        <v>20400300</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>43650</v>
+        <v>2445</v>
       </c>
       <c r="F43" t="n">
-        <v>462</v>
+        <v>82456</v>
       </c>
       <c r="G43" t="n">
-        <v>20166300</v>
+        <v>201604920</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>59700</v>
+        <v>18910</v>
       </c>
       <c r="F44" t="n">
-        <v>169</v>
+        <v>1068.0212</v>
       </c>
       <c r="G44" t="n">
-        <v>10089300</v>
+        <v>20196280</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10930</v>
+        <v>32250</v>
       </c>
       <c r="F45" t="n">
-        <v>1833</v>
+        <v>626</v>
       </c>
       <c r="G45" t="n">
-        <v>20034690</v>
+        <v>20188500</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>19850</v>
+        <v>82500</v>
       </c>
       <c r="F46" t="n">
-        <v>505</v>
+        <v>204</v>
       </c>
       <c r="G46" t="n">
-        <v>10024250</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>26350</v>
+        <v>56800</v>
       </c>
       <c r="F47" t="n">
-        <v>380</v>
+        <v>258</v>
       </c>
       <c r="G47" t="n">
-        <v>10013000</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>23500</v>
+        <v>83700</v>
       </c>
       <c r="F48" t="n">
-        <v>833</v>
+        <v>120</v>
       </c>
       <c r="G48" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10044000</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>85200</v>
+        <v>43650</v>
       </c>
       <c r="F49" t="n">
-        <v>118</v>
+        <v>462</v>
       </c>
       <c r="G49" t="n">
-        <v>10053600</v>
+        <v>20166300</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>63400</v>
+        <v>59700</v>
       </c>
       <c r="F50" t="n">
-        <v>316</v>
+        <v>169</v>
       </c>
       <c r="G50" t="n">
-        <v>20034400</v>
+        <v>10089300</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2058,27 +2060,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>110300</v>
+        <v>10930</v>
       </c>
       <c r="F51" t="n">
-        <v>91</v>
+        <v>1833</v>
       </c>
       <c r="G51" t="n">
-        <v>10037300</v>
+        <v>20034690</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2090,140 +2092,142 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>66100</v>
+        <v>19850</v>
       </c>
       <c r="F52" t="n">
-        <v>152</v>
+        <v>505</v>
       </c>
       <c r="G52" t="n">
-        <v>10047200</v>
+        <v>10024250</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>25800</v>
+        <v>26350</v>
       </c>
       <c r="F53" t="n">
-        <v>2713</v>
+        <v>380</v>
       </c>
       <c r="G53" t="n">
-        <v>69995400</v>
+        <v>10013000</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>206500</v>
+        <v>23500</v>
       </c>
       <c r="F54" t="n">
-        <v>338</v>
+        <v>833</v>
       </c>
       <c r="G54" t="n">
-        <v>69797000</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>70100</v>
+        <v>85200</v>
       </c>
       <c r="F55" t="n">
-        <v>998</v>
+        <v>118</v>
       </c>
       <c r="G55" t="n">
-        <v>69959800</v>
+        <v>10053600</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2232,77 +2236,77 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>93300</v>
+        <v>63400</v>
       </c>
       <c r="F56" t="n">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="G56" t="n">
-        <v>19966200</v>
+        <v>20034400</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>11300</v>
+        <v>110300</v>
       </c>
       <c r="F57" t="n">
-        <v>4424</v>
+        <v>91</v>
       </c>
       <c r="G57" t="n">
-        <v>49991200</v>
+        <v>10037300</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>19740</v>
+        <v>66100</v>
       </c>
       <c r="F58" t="n">
-        <v>2532</v>
+        <v>152</v>
       </c>
       <c r="G58" t="n">
-        <v>49981680</v>
+        <v>10047200</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2314,12 +2318,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2328,13 +2332,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F59" t="n">
-        <v>2385</v>
+        <v>2713</v>
       </c>
       <c r="G59" t="n">
-        <v>59982750</v>
+        <v>69995400</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2346,12 +2350,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2360,13 +2364,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>22050</v>
+        <v>206500</v>
       </c>
       <c r="F60" t="n">
-        <v>2267</v>
+        <v>338</v>
       </c>
       <c r="G60" t="n">
-        <v>49987350</v>
+        <v>69797000</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2378,12 +2382,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2392,13 +2396,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>43150</v>
+        <v>70100</v>
       </c>
       <c r="F61" t="n">
-        <v>1390</v>
+        <v>998</v>
       </c>
       <c r="G61" t="n">
-        <v>59978500</v>
+        <v>69959800</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2410,12 +2414,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2424,13 +2428,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>310000</v>
+        <v>93300</v>
       </c>
       <c r="F62" t="n">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G62" t="n">
-        <v>69750000</v>
+        <v>19966200</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2442,12 +2446,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2456,13 +2460,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6240</v>
+        <v>11300</v>
       </c>
       <c r="F63" t="n">
-        <v>3205</v>
+        <v>4424</v>
       </c>
       <c r="G63" t="n">
-        <v>19999200</v>
+        <v>49991200</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2474,12 +2478,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2488,13 +2492,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>24000</v>
+        <v>19740</v>
       </c>
       <c r="F64" t="n">
-        <v>833</v>
+        <v>2532</v>
       </c>
       <c r="G64" t="n">
-        <v>19992000</v>
+        <v>49981680</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2506,12 +2510,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2520,13 +2524,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>90300</v>
+        <v>25150</v>
       </c>
       <c r="F65" t="n">
-        <v>442</v>
+        <v>2385</v>
       </c>
       <c r="G65" t="n">
-        <v>39912600</v>
+        <v>59982750</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2538,12 +2542,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2552,13 +2556,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>279500</v>
+        <v>22050</v>
       </c>
       <c r="F66" t="n">
-        <v>357</v>
+        <v>2267</v>
       </c>
       <c r="G66" t="n">
-        <v>99781500</v>
+        <v>49987350</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2570,12 +2574,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2584,13 +2588,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>366000</v>
+        <v>43150</v>
       </c>
       <c r="F67" t="n">
-        <v>54</v>
+        <v>1390</v>
       </c>
       <c r="G67" t="n">
-        <v>19764000</v>
+        <v>59978500</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2602,12 +2606,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2616,13 +2620,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>91000</v>
+        <v>310000</v>
       </c>
       <c r="F68" t="n">
-        <v>659</v>
+        <v>225</v>
       </c>
       <c r="G68" t="n">
-        <v>59969000</v>
+        <v>69750000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2634,12 +2638,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2648,13 +2652,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>120100</v>
+        <v>6240</v>
       </c>
       <c r="F69" t="n">
-        <v>666</v>
+        <v>3205</v>
       </c>
       <c r="G69" t="n">
-        <v>79986600</v>
+        <v>19999200</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2666,12 +2670,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2680,13 +2684,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2405</v>
+        <v>24000</v>
       </c>
       <c r="F70" t="n">
-        <v>415800</v>
+        <v>833</v>
       </c>
       <c r="G70" t="n">
-        <v>999999000</v>
+        <v>19992000</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2698,12 +2702,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2712,13 +2716,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>69000</v>
+        <v>90300</v>
       </c>
       <c r="F71" t="n">
-        <v>579</v>
+        <v>442</v>
       </c>
       <c r="G71" t="n">
-        <v>39951000</v>
+        <v>39912600</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2730,12 +2734,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2744,13 +2748,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>42300</v>
+        <v>279500</v>
       </c>
       <c r="F72" t="n">
-        <v>709</v>
+        <v>357</v>
       </c>
       <c r="G72" t="n">
-        <v>29990700</v>
+        <v>99781500</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2762,29 +2766,221 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F73" t="n">
+        <v>54</v>
+      </c>
+      <c r="G73" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F74" t="n">
+        <v>659</v>
+      </c>
+      <c r="G74" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F75" t="n">
+        <v>666</v>
+      </c>
+      <c r="G75" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F76" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G76" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F77" t="n">
+        <v>579</v>
+      </c>
+      <c r="G77" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F78" t="n">
+        <v>709</v>
+      </c>
+      <c r="G78" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E79" t="n">
         <v>23350</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F79" t="n">
         <v>856</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G79" t="n">
         <v>19987600</v>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58700</v>
+        <v>6080</v>
       </c>
       <c r="F2" t="n">
-        <v>357.1039</v>
+        <v>3255.5051</v>
       </c>
       <c r="G2" t="n">
-        <v>20961998.6</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,20 +526,20 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>13250</v>
+        <v>95200</v>
       </c>
       <c r="F3" t="n">
-        <v>791.0188000000001</v>
+        <v>221.6088</v>
       </c>
       <c r="G3" t="n">
-        <v>10480999.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,17 +554,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2360</v>
+        <v>2205</v>
       </c>
       <c r="F4" t="n">
-        <v>66616.5209</v>
+        <v>52623.2877</v>
       </c>
       <c r="G4" t="n">
-        <v>157214989.3</v>
+        <v>116034349.3</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,31 +576,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38300</v>
+        <v>58700</v>
       </c>
       <c r="F5" t="n">
-        <v>500.7861</v>
+        <v>357.1039</v>
       </c>
       <c r="G5" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>20961998.6</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21150</v>
+        <v>13250</v>
       </c>
       <c r="F6" t="n">
-        <v>495.5555</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G6" t="n">
         <v>10480999.3</v>
@@ -640,127 +640,129 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>23650</v>
+        <v>2360</v>
       </c>
       <c r="F7" t="n">
-        <v>832.6201</v>
+        <v>66616.5209</v>
       </c>
       <c r="G7" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.28</v>
-      </c>
+        <v>157214989.3</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12310</v>
+        <v>38300</v>
       </c>
       <c r="F8" t="n">
-        <v>2480.1654</v>
+        <v>500.7861</v>
       </c>
       <c r="G8" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>40650</v>
+        <v>21150</v>
       </c>
       <c r="F9" t="n">
-        <v>751.0661</v>
+        <v>495.5555</v>
       </c>
       <c r="G9" t="n">
-        <v>30530836.4</v>
+        <v>10480999.3</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>283500</v>
+        <v>23650</v>
       </c>
       <c r="F10" t="n">
-        <v>71.795</v>
+        <v>832.6201</v>
       </c>
       <c r="G10" t="n">
-        <v>20353890.9</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,12 +772,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,13 +786,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2390</v>
+        <v>12310</v>
       </c>
       <c r="F11" t="n">
-        <v>42581.3618</v>
+        <v>2480.1654</v>
       </c>
       <c r="G11" t="n">
-        <v>101769454.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,44 +804,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20450</v>
+        <v>40650</v>
       </c>
       <c r="F12" t="n">
-        <v>995.3003</v>
+        <v>751.0661</v>
       </c>
       <c r="G12" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,79 +850,77 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30200</v>
+        <v>283500</v>
       </c>
       <c r="F13" t="n">
-        <v>359.55</v>
+        <v>71.795</v>
       </c>
       <c r="G13" t="n">
-        <v>10858410.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208500</v>
+        <v>2390</v>
       </c>
       <c r="F14" t="n">
-        <v>338</v>
+        <v>42581.3618</v>
       </c>
       <c r="G14" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.97</v>
-      </c>
+        <v>101769454.6</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>17720</v>
+        <v>20450</v>
       </c>
       <c r="F15" t="n">
-        <v>94.9217</v>
+        <v>995.3003</v>
       </c>
       <c r="G15" t="n">
-        <v>1682012.5</v>
+        <v>20353890.9</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100500</v>
+        <v>30200</v>
       </c>
       <c r="F16" t="n">
-        <v>8.9518</v>
+        <v>359.55</v>
       </c>
       <c r="G16" t="n">
-        <v>899652.6</v>
+        <v>10858410.6</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -964,29 +964,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11410</v>
+        <v>208500</v>
       </c>
       <c r="F17" t="n">
-        <v>6321.2722</v>
+        <v>338</v>
       </c>
       <c r="G17" t="n">
-        <v>72125715.8</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -996,27 +998,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12880</v>
+        <v>17720</v>
       </c>
       <c r="F18" t="n">
-        <v>713.2027</v>
+        <v>94.9217</v>
       </c>
       <c r="G18" t="n">
-        <v>9186050.6</v>
+        <v>1682012.5</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1028,12 +1030,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1042,13 +1044,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>21200</v>
+        <v>100500</v>
       </c>
       <c r="F19" t="n">
-        <v>120.8659</v>
+        <v>8.9518</v>
       </c>
       <c r="G19" t="n">
-        <v>2562357.9</v>
+        <v>899652.6</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1060,27 +1062,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>27700</v>
+        <v>11410</v>
       </c>
       <c r="F20" t="n">
-        <v>161.1835</v>
+        <v>6321.2722</v>
       </c>
       <c r="G20" t="n">
-        <v>4464784.2</v>
+        <v>72125715.8</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1092,27 +1094,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21500</v>
+        <v>12880</v>
       </c>
       <c r="F21" t="n">
-        <v>129.2032</v>
+        <v>713.2027</v>
       </c>
       <c r="G21" t="n">
-        <v>2777868.4</v>
+        <v>9186050.6</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1124,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,13 +1140,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>34100</v>
+        <v>21200</v>
       </c>
       <c r="F22" t="n">
-        <v>21.679</v>
+        <v>120.8659</v>
       </c>
       <c r="G22" t="n">
-        <v>739252.6</v>
+        <v>2562357.9</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,27 +1158,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>40850</v>
+        <v>27700</v>
       </c>
       <c r="F23" t="n">
-        <v>123.3915</v>
+        <v>161.1835</v>
       </c>
       <c r="G23" t="n">
-        <v>5040542.1</v>
+        <v>4464784.2</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1188,12 +1190,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,13 +1204,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308000</v>
+        <v>21500</v>
       </c>
       <c r="F24" t="n">
-        <v>9.1744</v>
+        <v>129.2032</v>
       </c>
       <c r="G24" t="n">
-        <v>2825715.8</v>
+        <v>2777868.4</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1220,27 +1222,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6330</v>
+        <v>34100</v>
       </c>
       <c r="F25" t="n">
-        <v>50.5051</v>
+        <v>21.679</v>
       </c>
       <c r="G25" t="n">
-        <v>319697.4</v>
+        <v>739252.6</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,27 +1254,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31700</v>
+        <v>40850</v>
       </c>
       <c r="F26" t="n">
-        <v>158.7408</v>
+        <v>123.3915</v>
       </c>
       <c r="G26" t="n">
-        <v>5032084.2</v>
+        <v>5040542.1</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,27 +1286,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>68700</v>
+        <v>308000</v>
       </c>
       <c r="F27" t="n">
-        <v>16.0386</v>
+        <v>9.1744</v>
       </c>
       <c r="G27" t="n">
-        <v>1101852.6</v>
+        <v>2825715.8</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1316,12 +1318,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,13 +1332,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>256000</v>
+        <v>6330</v>
       </c>
       <c r="F28" t="n">
-        <v>45.4873</v>
+        <v>50.5051</v>
       </c>
       <c r="G28" t="n">
-        <v>11644736.8</v>
+        <v>319697.4</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1348,27 +1350,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>91100</v>
+        <v>31700</v>
       </c>
       <c r="F29" t="n">
-        <v>19.6174</v>
+        <v>158.7408</v>
       </c>
       <c r="G29" t="n">
-        <v>1787142.1</v>
+        <v>5032084.2</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,12 +1382,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1394,13 +1396,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>130900</v>
+        <v>68700</v>
       </c>
       <c r="F30" t="n">
-        <v>89.1437</v>
+        <v>16.0386</v>
       </c>
       <c r="G30" t="n">
-        <v>11668905.3</v>
+        <v>1101852.6</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1412,27 +1414,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2400</v>
+        <v>256000</v>
       </c>
       <c r="F31" t="n">
-        <v>32820.1843</v>
+        <v>45.4873</v>
       </c>
       <c r="G31" t="n">
-        <v>78768442.40000001</v>
+        <v>11644736.8</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1444,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1458,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>41150</v>
+        <v>91100</v>
       </c>
       <c r="F32" t="n">
-        <v>38.7861</v>
+        <v>19.6174</v>
       </c>
       <c r="G32" t="n">
-        <v>1596047.4</v>
+        <v>1787142.1</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1476,12 +1478,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1490,13 +1492,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>49450</v>
+        <v>130900</v>
       </c>
       <c r="F33" t="n">
-        <v>83.90349999999999</v>
+        <v>89.1437</v>
       </c>
       <c r="G33" t="n">
-        <v>4149029</v>
+        <v>11668905.3</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1508,12 +1510,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1522,13 +1524,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>24750</v>
+        <v>2400</v>
       </c>
       <c r="F34" t="n">
-        <v>23.3799</v>
+        <v>32820.1843</v>
       </c>
       <c r="G34" t="n">
-        <v>578652.6</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1540,142 +1542,140 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5450</v>
+        <v>41150</v>
       </c>
       <c r="F35" t="n">
-        <v>220.6267</v>
+        <v>38.7861</v>
       </c>
       <c r="G35" t="n">
-        <v>1202415.4</v>
+        <v>1596047.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>327000</v>
+        <v>49450</v>
       </c>
       <c r="F36" t="n">
-        <v>54</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>4149029</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5130</v>
+        <v>24750</v>
       </c>
       <c r="F37" t="n">
-        <v>4001.7913</v>
+        <v>23.3799</v>
       </c>
       <c r="G37" t="n">
-        <v>20529189.5</v>
+        <v>578652.6</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>27100</v>
+        <v>5450</v>
       </c>
       <c r="F38" t="n">
-        <v>376</v>
+        <v>220.6267</v>
       </c>
       <c r="G38" t="n">
-        <v>10189600</v>
+        <v>1202415.4</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1684,47 +1684,47 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>67600</v>
+        <v>327000</v>
       </c>
       <c r="F39" t="n">
-        <v>998</v>
+        <v>54</v>
       </c>
       <c r="G39" t="n">
-        <v>67464800</v>
+        <v>17658000</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.57</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11900</v>
+        <v>5130</v>
       </c>
       <c r="F40" t="n">
-        <v>856</v>
+        <v>4001.7913</v>
       </c>
       <c r="G40" t="n">
-        <v>10186400</v>
+        <v>20529189.5</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,27 +1736,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>29300</v>
+        <v>27100</v>
       </c>
       <c r="F41" t="n">
-        <v>2434</v>
+        <v>376</v>
       </c>
       <c r="G41" t="n">
-        <v>71316200</v>
+        <v>10189600</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,29 +1768,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>119300</v>
+        <v>67600</v>
       </c>
       <c r="F42" t="n">
-        <v>171</v>
+        <v>998</v>
       </c>
       <c r="G42" t="n">
-        <v>20400300</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1800,44 +1802,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2445</v>
+        <v>11900</v>
       </c>
       <c r="F43" t="n">
-        <v>82456</v>
+        <v>856</v>
       </c>
       <c r="G43" t="n">
-        <v>201604920</v>
+        <v>10186400</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1846,81 +1848,79 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18910</v>
+        <v>29300</v>
       </c>
       <c r="F44" t="n">
-        <v>1068.0212</v>
+        <v>2434</v>
       </c>
       <c r="G44" t="n">
-        <v>20196280</v>
+        <v>71316200</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>32250</v>
+        <v>119300</v>
       </c>
       <c r="F45" t="n">
-        <v>626</v>
+        <v>171</v>
       </c>
       <c r="G45" t="n">
-        <v>20188500</v>
+        <v>20400300</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>82500</v>
+        <v>2445</v>
       </c>
       <c r="F46" t="n">
-        <v>204</v>
+        <v>82456</v>
       </c>
       <c r="G46" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>201604920</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1930,100 +1930,100 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>56800</v>
+        <v>18910</v>
       </c>
       <c r="F47" t="n">
-        <v>258</v>
+        <v>1068.0212</v>
       </c>
       <c r="G47" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20196280</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>83700</v>
+        <v>32250</v>
       </c>
       <c r="F48" t="n">
-        <v>120</v>
+        <v>626</v>
       </c>
       <c r="G48" t="n">
-        <v>10044000</v>
+        <v>20188500</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>43650</v>
+        <v>82500</v>
       </c>
       <c r="F49" t="n">
-        <v>462</v>
+        <v>204</v>
       </c>
       <c r="G49" t="n">
-        <v>20166300</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2038,113 +2038,115 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>59700</v>
+        <v>56800</v>
       </c>
       <c r="F50" t="n">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="G50" t="n">
-        <v>10089300</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10930</v>
+        <v>83700</v>
       </c>
       <c r="F51" t="n">
-        <v>1833</v>
+        <v>120</v>
       </c>
       <c r="G51" t="n">
-        <v>20034690</v>
+        <v>10044000</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>19850</v>
+        <v>43650</v>
       </c>
       <c r="F52" t="n">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="G52" t="n">
-        <v>10024250</v>
+        <v>20166300</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>26350</v>
+        <v>59700</v>
       </c>
       <c r="F53" t="n">
-        <v>380</v>
+        <v>169</v>
       </c>
       <c r="G53" t="n">
-        <v>10013000</v>
+        <v>10089300</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2156,31 +2158,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>23500</v>
+        <v>10930</v>
       </c>
       <c r="F54" t="n">
-        <v>833</v>
+        <v>1833</v>
       </c>
       <c r="G54" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20034690</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2190,27 +2190,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>85200</v>
+        <v>19850</v>
       </c>
       <c r="F55" t="n">
-        <v>118</v>
+        <v>505</v>
       </c>
       <c r="G55" t="n">
-        <v>10053600</v>
+        <v>10024250</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2222,27 +2222,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>63400</v>
+        <v>26350</v>
       </c>
       <c r="F56" t="n">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="G56" t="n">
-        <v>20034400</v>
+        <v>10013000</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2254,29 +2254,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>110300</v>
+        <v>23500</v>
       </c>
       <c r="F57" t="n">
-        <v>91</v>
+        <v>833</v>
       </c>
       <c r="G57" t="n">
-        <v>10037300</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2286,12 +2288,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2300,30 +2302,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>66100</v>
+        <v>85200</v>
       </c>
       <c r="F58" t="n">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="G58" t="n">
-        <v>10047200</v>
+        <v>10053600</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2332,77 +2334,77 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>25800</v>
+        <v>63400</v>
       </c>
       <c r="F59" t="n">
-        <v>2713</v>
+        <v>316</v>
       </c>
       <c r="G59" t="n">
-        <v>69995400</v>
+        <v>20034400</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>206500</v>
+        <v>110300</v>
       </c>
       <c r="F60" t="n">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="G60" t="n">
-        <v>69797000</v>
+        <v>10037300</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>70100</v>
+        <v>66100</v>
       </c>
       <c r="F61" t="n">
-        <v>998</v>
+        <v>152</v>
       </c>
       <c r="G61" t="n">
-        <v>69959800</v>
+        <v>10047200</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2414,12 +2416,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2428,13 +2430,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>93300</v>
+        <v>25800</v>
       </c>
       <c r="F62" t="n">
-        <v>214</v>
+        <v>2713</v>
       </c>
       <c r="G62" t="n">
-        <v>19966200</v>
+        <v>69995400</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2446,12 +2448,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2460,13 +2462,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>11300</v>
+        <v>206500</v>
       </c>
       <c r="F63" t="n">
-        <v>4424</v>
+        <v>338</v>
       </c>
       <c r="G63" t="n">
-        <v>49991200</v>
+        <v>69797000</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2478,12 +2480,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2492,13 +2494,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>19740</v>
+        <v>70100</v>
       </c>
       <c r="F64" t="n">
-        <v>2532</v>
+        <v>998</v>
       </c>
       <c r="G64" t="n">
-        <v>49981680</v>
+        <v>69959800</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2510,12 +2512,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2524,13 +2526,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>25150</v>
+        <v>93300</v>
       </c>
       <c r="F65" t="n">
-        <v>2385</v>
+        <v>214</v>
       </c>
       <c r="G65" t="n">
-        <v>59982750</v>
+        <v>19966200</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2542,12 +2544,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2556,13 +2558,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>22050</v>
+        <v>11300</v>
       </c>
       <c r="F66" t="n">
-        <v>2267</v>
+        <v>4424</v>
       </c>
       <c r="G66" t="n">
-        <v>49987350</v>
+        <v>49991200</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2574,12 +2576,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2588,13 +2590,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>43150</v>
+        <v>19740</v>
       </c>
       <c r="F67" t="n">
-        <v>1390</v>
+        <v>2532</v>
       </c>
       <c r="G67" t="n">
-        <v>59978500</v>
+        <v>49981680</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2606,12 +2608,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2620,13 +2622,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>310000</v>
+        <v>25150</v>
       </c>
       <c r="F68" t="n">
-        <v>225</v>
+        <v>2385</v>
       </c>
       <c r="G68" t="n">
-        <v>69750000</v>
+        <v>59982750</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2638,12 +2640,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2652,13 +2654,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6240</v>
+        <v>22050</v>
       </c>
       <c r="F69" t="n">
-        <v>3205</v>
+        <v>2267</v>
       </c>
       <c r="G69" t="n">
-        <v>19999200</v>
+        <v>49987350</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2670,12 +2672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2684,13 +2686,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>24000</v>
+        <v>43150</v>
       </c>
       <c r="F70" t="n">
-        <v>833</v>
+        <v>1390</v>
       </c>
       <c r="G70" t="n">
-        <v>19992000</v>
+        <v>59978500</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2702,12 +2704,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2716,13 +2718,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>90300</v>
+        <v>310000</v>
       </c>
       <c r="F71" t="n">
-        <v>442</v>
+        <v>225</v>
       </c>
       <c r="G71" t="n">
-        <v>39912600</v>
+        <v>69750000</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2734,12 +2736,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2748,13 +2750,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F72" t="n">
-        <v>357</v>
+        <v>3205</v>
       </c>
       <c r="G72" t="n">
-        <v>99781500</v>
+        <v>19999200</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2766,12 +2768,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2780,13 +2782,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>366000</v>
+        <v>24000</v>
       </c>
       <c r="F73" t="n">
-        <v>54</v>
+        <v>833</v>
       </c>
       <c r="G73" t="n">
-        <v>19764000</v>
+        <v>19992000</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2798,12 +2800,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2812,13 +2814,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>91000</v>
+        <v>90300</v>
       </c>
       <c r="F74" t="n">
-        <v>659</v>
+        <v>442</v>
       </c>
       <c r="G74" t="n">
-        <v>59969000</v>
+        <v>39912600</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2830,12 +2832,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2844,13 +2846,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>120100</v>
+        <v>279500</v>
       </c>
       <c r="F75" t="n">
-        <v>666</v>
+        <v>357</v>
       </c>
       <c r="G75" t="n">
-        <v>79986600</v>
+        <v>99781500</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2862,12 +2864,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2876,13 +2878,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2405</v>
+        <v>366000</v>
       </c>
       <c r="F76" t="n">
-        <v>415800</v>
+        <v>54</v>
       </c>
       <c r="G76" t="n">
-        <v>999999000</v>
+        <v>19764000</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2894,12 +2896,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2908,13 +2910,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>69000</v>
+        <v>91000</v>
       </c>
       <c r="F77" t="n">
-        <v>579</v>
+        <v>659</v>
       </c>
       <c r="G77" t="n">
-        <v>39951000</v>
+        <v>59969000</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2926,12 +2928,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2940,13 +2942,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>42300</v>
+        <v>120100</v>
       </c>
       <c r="F78" t="n">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="G78" t="n">
-        <v>29990700</v>
+        <v>79986600</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2958,29 +2960,125 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F79" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G79" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F80" t="n">
+        <v>579</v>
+      </c>
+      <c r="G80" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F81" t="n">
+        <v>709</v>
+      </c>
+      <c r="G81" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="E82" t="n">
         <v>23350</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F82" t="n">
         <v>856</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G82" t="n">
         <v>19987600</v>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,147 +473,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6080</v>
+        <v>22900</v>
       </c>
       <c r="F2" t="n">
-        <v>3255.5051</v>
+        <v>1397.6406</v>
       </c>
       <c r="G2" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>32005969</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>95200</v>
+        <v>73600</v>
       </c>
       <c r="F3" t="n">
-        <v>221.6088</v>
+        <v>299.9614</v>
       </c>
       <c r="G3" t="n">
-        <v>21097154.4</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2205</v>
+        <v>43800</v>
       </c>
       <c r="F4" t="n">
-        <v>52623.2877</v>
+        <v>504.0447</v>
       </c>
       <c r="G4" t="n">
-        <v>116034349.3</v>
+        <v>22077158.2</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58700</v>
+        <v>23650</v>
       </c>
       <c r="F5" t="n">
-        <v>357.1039</v>
+        <v>451.106</v>
       </c>
       <c r="G5" t="n">
-        <v>20961998.6</v>
+        <v>10668656.3</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,111 +622,111 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13250</v>
+        <v>5730</v>
       </c>
       <c r="F6" t="n">
-        <v>791.0188000000001</v>
+        <v>3723.7893</v>
       </c>
       <c r="G6" t="n">
-        <v>10480999.3</v>
+        <v>21337312.7</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2360</v>
+        <v>6080</v>
       </c>
       <c r="F7" t="n">
-        <v>66616.5209</v>
+        <v>3255.5051</v>
       </c>
       <c r="G7" t="n">
-        <v>157214989.3</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38300</v>
+        <v>95200</v>
       </c>
       <c r="F8" t="n">
-        <v>500.7861</v>
+        <v>221.6088</v>
       </c>
       <c r="G8" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>21097154.4</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21150</v>
+        <v>2205</v>
       </c>
       <c r="F9" t="n">
-        <v>495.5555</v>
+        <v>52623.2877</v>
       </c>
       <c r="G9" t="n">
-        <v>10480999.3</v>
+        <v>116034349.3</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -738,46 +738,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>23650</v>
+        <v>58700</v>
       </c>
       <c r="F10" t="n">
-        <v>832.6201</v>
+        <v>357.1039</v>
       </c>
       <c r="G10" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.28</v>
-      </c>
+        <v>20961998.6</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -786,94 +784,96 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12310</v>
+        <v>13250</v>
       </c>
       <c r="F11" t="n">
-        <v>2480.1654</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>30530836.4</v>
+        <v>10480999.3</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>40650</v>
+        <v>2360</v>
       </c>
       <c r="F12" t="n">
-        <v>751.0661</v>
+        <v>66616.5209</v>
       </c>
       <c r="G12" t="n">
-        <v>30530836.4</v>
+        <v>157214989.3</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283500</v>
+        <v>38300</v>
       </c>
       <c r="F13" t="n">
-        <v>71.795</v>
+        <v>500.7861</v>
       </c>
       <c r="G13" t="n">
-        <v>20353890.9</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -882,192 +882,192 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2390</v>
+        <v>21150</v>
       </c>
       <c r="F14" t="n">
-        <v>42581.3618</v>
+        <v>495.5555</v>
       </c>
       <c r="G14" t="n">
-        <v>101769454.6</v>
+        <v>10480999.3</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20450</v>
+        <v>23650</v>
       </c>
       <c r="F15" t="n">
-        <v>995.3003</v>
+        <v>832.6201</v>
       </c>
       <c r="G15" t="n">
-        <v>20353890.9</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>30200</v>
+        <v>12310</v>
       </c>
       <c r="F16" t="n">
-        <v>359.55</v>
+        <v>2480.1654</v>
       </c>
       <c r="G16" t="n">
-        <v>10858410.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208500</v>
+        <v>40650</v>
       </c>
       <c r="F17" t="n">
-        <v>338</v>
+        <v>751.0661</v>
       </c>
       <c r="G17" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.97</v>
-      </c>
+        <v>30530836.4</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>17720</v>
+        <v>283500</v>
       </c>
       <c r="F18" t="n">
-        <v>94.9217</v>
+        <v>71.795</v>
       </c>
       <c r="G18" t="n">
-        <v>1682012.5</v>
+        <v>20353890.9</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100500</v>
+        <v>2390</v>
       </c>
       <c r="F19" t="n">
-        <v>8.9518</v>
+        <v>42581.3618</v>
       </c>
       <c r="G19" t="n">
-        <v>899652.6</v>
+        <v>101769454.6</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11410</v>
+        <v>20450</v>
       </c>
       <c r="F20" t="n">
-        <v>6321.2722</v>
+        <v>995.3003</v>
       </c>
       <c r="G20" t="n">
-        <v>72125715.8</v>
+        <v>20353890.9</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>12880</v>
+        <v>30200</v>
       </c>
       <c r="F21" t="n">
-        <v>713.2027</v>
+        <v>359.55</v>
       </c>
       <c r="G21" t="n">
-        <v>9186050.6</v>
+        <v>10858410.6</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1126,29 +1126,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21200</v>
+        <v>208500</v>
       </c>
       <c r="F22" t="n">
-        <v>120.8659</v>
+        <v>338</v>
       </c>
       <c r="G22" t="n">
-        <v>2562357.9</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1158,27 +1160,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>27700</v>
+        <v>17720</v>
       </c>
       <c r="F23" t="n">
-        <v>161.1835</v>
+        <v>94.9217</v>
       </c>
       <c r="G23" t="n">
-        <v>4464784.2</v>
+        <v>1682012.5</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1190,27 +1192,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>21500</v>
+        <v>100500</v>
       </c>
       <c r="F24" t="n">
-        <v>129.2032</v>
+        <v>8.9518</v>
       </c>
       <c r="G24" t="n">
-        <v>2777868.4</v>
+        <v>899652.6</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1222,27 +1224,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>34100</v>
+        <v>11410</v>
       </c>
       <c r="F25" t="n">
-        <v>21.679</v>
+        <v>6321.2722</v>
       </c>
       <c r="G25" t="n">
-        <v>739252.6</v>
+        <v>72125715.8</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1254,27 +1256,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>40850</v>
+        <v>12880</v>
       </c>
       <c r="F26" t="n">
-        <v>123.3915</v>
+        <v>713.2027</v>
       </c>
       <c r="G26" t="n">
-        <v>5040542.1</v>
+        <v>9186050.6</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1286,27 +1288,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308000</v>
+        <v>21200</v>
       </c>
       <c r="F27" t="n">
-        <v>9.1744</v>
+        <v>120.8659</v>
       </c>
       <c r="G27" t="n">
-        <v>2825715.8</v>
+        <v>2562357.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1318,27 +1320,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6330</v>
+        <v>27700</v>
       </c>
       <c r="F28" t="n">
-        <v>50.5051</v>
+        <v>161.1835</v>
       </c>
       <c r="G28" t="n">
-        <v>319697.4</v>
+        <v>4464784.2</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1350,27 +1352,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>31700</v>
+        <v>21500</v>
       </c>
       <c r="F29" t="n">
-        <v>158.7408</v>
+        <v>129.2032</v>
       </c>
       <c r="G29" t="n">
-        <v>5032084.2</v>
+        <v>2777868.4</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1382,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1396,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>68700</v>
+        <v>34100</v>
       </c>
       <c r="F30" t="n">
-        <v>16.0386</v>
+        <v>21.679</v>
       </c>
       <c r="G30" t="n">
-        <v>1101852.6</v>
+        <v>739252.6</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,12 +1416,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1428,13 +1430,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>256000</v>
+        <v>40850</v>
       </c>
       <c r="F31" t="n">
-        <v>45.4873</v>
+        <v>123.3915</v>
       </c>
       <c r="G31" t="n">
-        <v>11644736.8</v>
+        <v>5040542.1</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,12 +1448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1462,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>91100</v>
+        <v>308000</v>
       </c>
       <c r="F32" t="n">
-        <v>19.6174</v>
+        <v>9.1744</v>
       </c>
       <c r="G32" t="n">
-        <v>1787142.1</v>
+        <v>2825715.8</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,27 +1480,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>130900</v>
+        <v>6330</v>
       </c>
       <c r="F33" t="n">
-        <v>89.1437</v>
+        <v>50.5051</v>
       </c>
       <c r="G33" t="n">
-        <v>11668905.3</v>
+        <v>319697.4</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1510,12 +1512,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1524,13 +1526,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2400</v>
+        <v>31700</v>
       </c>
       <c r="F34" t="n">
-        <v>32820.1843</v>
+        <v>158.7408</v>
       </c>
       <c r="G34" t="n">
-        <v>78768442.40000001</v>
+        <v>5032084.2</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1542,27 +1544,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>41150</v>
+        <v>68700</v>
       </c>
       <c r="F35" t="n">
-        <v>38.7861</v>
+        <v>16.0386</v>
       </c>
       <c r="G35" t="n">
-        <v>1596047.4</v>
+        <v>1101852.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1574,27 +1576,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>49450</v>
+        <v>256000</v>
       </c>
       <c r="F36" t="n">
-        <v>83.90349999999999</v>
+        <v>45.4873</v>
       </c>
       <c r="G36" t="n">
-        <v>4149029</v>
+        <v>11644736.8</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1606,27 +1608,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>24750</v>
+        <v>91100</v>
       </c>
       <c r="F37" t="n">
-        <v>23.3799</v>
+        <v>19.6174</v>
       </c>
       <c r="G37" t="n">
-        <v>578652.6</v>
+        <v>1787142.1</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1638,12 +1640,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1652,241 +1654,239 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5450</v>
+        <v>130900</v>
       </c>
       <c r="F38" t="n">
-        <v>220.6267</v>
+        <v>89.1437</v>
       </c>
       <c r="G38" t="n">
-        <v>1202415.4</v>
+        <v>11668905.3</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>327000</v>
+        <v>2400</v>
       </c>
       <c r="F39" t="n">
-        <v>54</v>
+        <v>32820.1843</v>
       </c>
       <c r="G39" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>78768442.40000001</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5130</v>
+        <v>41150</v>
       </c>
       <c r="F40" t="n">
-        <v>4001.7913</v>
+        <v>38.7861</v>
       </c>
       <c r="G40" t="n">
-        <v>20529189.5</v>
+        <v>1596047.4</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>27100</v>
+        <v>49450</v>
       </c>
       <c r="F41" t="n">
-        <v>376</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>10189600</v>
+        <v>4149029</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>67600</v>
+        <v>24750</v>
       </c>
       <c r="F42" t="n">
-        <v>998</v>
+        <v>23.3799</v>
       </c>
       <c r="G42" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>578652.6</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>11900</v>
+        <v>5450</v>
       </c>
       <c r="F43" t="n">
-        <v>856</v>
+        <v>220.6267</v>
       </c>
       <c r="G43" t="n">
-        <v>10186400</v>
+        <v>1202415.4</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>29300</v>
+        <v>327000</v>
       </c>
       <c r="F44" t="n">
-        <v>2434</v>
+        <v>54</v>
       </c>
       <c r="G44" t="n">
-        <v>71316200</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>119300</v>
+        <v>5130</v>
       </c>
       <c r="F45" t="n">
-        <v>171</v>
+        <v>4001.7913</v>
       </c>
       <c r="G45" t="n">
-        <v>20400300</v>
+        <v>20529189.5</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1898,176 +1898,174 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2445</v>
+        <v>27100</v>
       </c>
       <c r="F46" t="n">
-        <v>82456</v>
+        <v>376</v>
       </c>
       <c r="G46" t="n">
-        <v>201604920</v>
+        <v>10189600</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>18910</v>
+        <v>67600</v>
       </c>
       <c r="F47" t="n">
-        <v>1068.0212</v>
+        <v>998</v>
       </c>
       <c r="G47" t="n">
-        <v>20196280</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>32250</v>
+        <v>11900</v>
       </c>
       <c r="F48" t="n">
-        <v>626</v>
+        <v>856</v>
       </c>
       <c r="G48" t="n">
-        <v>20188500</v>
+        <v>10186400</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>82500</v>
+        <v>29300</v>
       </c>
       <c r="F49" t="n">
-        <v>204</v>
+        <v>2434</v>
       </c>
       <c r="G49" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>71316200</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>56800</v>
+        <v>119300</v>
       </c>
       <c r="F50" t="n">
-        <v>258</v>
+        <v>171</v>
       </c>
       <c r="G50" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20400300</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2076,30 +2074,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>83700</v>
+        <v>2445</v>
       </c>
       <c r="F51" t="n">
-        <v>120</v>
+        <v>82456</v>
       </c>
       <c r="G51" t="n">
-        <v>10044000</v>
+        <v>201604920</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2108,192 +2106,194 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>43650</v>
+        <v>18910</v>
       </c>
       <c r="F52" t="n">
-        <v>462</v>
+        <v>1068.0212</v>
       </c>
       <c r="G52" t="n">
-        <v>20166300</v>
+        <v>20196280</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>59700</v>
+        <v>32250</v>
       </c>
       <c r="F53" t="n">
-        <v>169</v>
+        <v>626</v>
       </c>
       <c r="G53" t="n">
-        <v>10089300</v>
+        <v>20188500</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10930</v>
+        <v>82500</v>
       </c>
       <c r="F54" t="n">
-        <v>1833</v>
+        <v>204</v>
       </c>
       <c r="G54" t="n">
-        <v>20034690</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>19850</v>
+        <v>56800</v>
       </c>
       <c r="F55" t="n">
-        <v>505</v>
+        <v>258</v>
       </c>
       <c r="G55" t="n">
-        <v>10024250</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>26350</v>
+        <v>83700</v>
       </c>
       <c r="F56" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="G56" t="n">
-        <v>10013000</v>
+        <v>10044000</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>23500</v>
+        <v>43650</v>
       </c>
       <c r="F57" t="n">
-        <v>833</v>
+        <v>462</v>
       </c>
       <c r="G57" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20166300</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>85200</v>
+        <v>59700</v>
       </c>
       <c r="F58" t="n">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="G58" t="n">
-        <v>10053600</v>
+        <v>10089300</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2320,27 +2320,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>63400</v>
+        <v>10930</v>
       </c>
       <c r="F59" t="n">
-        <v>316</v>
+        <v>1833</v>
       </c>
       <c r="G59" t="n">
-        <v>20034400</v>
+        <v>20034690</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2352,27 +2352,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>110300</v>
+        <v>19850</v>
       </c>
       <c r="F60" t="n">
-        <v>91</v>
+        <v>505</v>
       </c>
       <c r="G60" t="n">
-        <v>10037300</v>
+        <v>10024250</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2384,108 +2384,110 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>66100</v>
+        <v>26350</v>
       </c>
       <c r="F61" t="n">
-        <v>152</v>
+        <v>380</v>
       </c>
       <c r="G61" t="n">
-        <v>10047200</v>
+        <v>10013000</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>25800</v>
+        <v>23500</v>
       </c>
       <c r="F62" t="n">
-        <v>2713</v>
+        <v>833</v>
       </c>
       <c r="G62" t="n">
-        <v>69995400</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>206500</v>
+        <v>85200</v>
       </c>
       <c r="F63" t="n">
-        <v>338</v>
+        <v>118</v>
       </c>
       <c r="G63" t="n">
-        <v>69797000</v>
+        <v>10053600</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2494,77 +2496,77 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>70100</v>
+        <v>63400</v>
       </c>
       <c r="F64" t="n">
-        <v>998</v>
+        <v>316</v>
       </c>
       <c r="G64" t="n">
-        <v>69959800</v>
+        <v>20034400</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>93300</v>
+        <v>110300</v>
       </c>
       <c r="F65" t="n">
-        <v>214</v>
+        <v>91</v>
       </c>
       <c r="G65" t="n">
-        <v>19966200</v>
+        <v>10037300</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>11300</v>
+        <v>66100</v>
       </c>
       <c r="F66" t="n">
-        <v>4424</v>
+        <v>152</v>
       </c>
       <c r="G66" t="n">
-        <v>49991200</v>
+        <v>10047200</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2576,12 +2578,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2590,13 +2592,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>19740</v>
+        <v>25800</v>
       </c>
       <c r="F67" t="n">
-        <v>2532</v>
+        <v>2713</v>
       </c>
       <c r="G67" t="n">
-        <v>49981680</v>
+        <v>69995400</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2608,12 +2610,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2622,13 +2624,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>25150</v>
+        <v>206500</v>
       </c>
       <c r="F68" t="n">
-        <v>2385</v>
+        <v>338</v>
       </c>
       <c r="G68" t="n">
-        <v>59982750</v>
+        <v>69797000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2640,12 +2642,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2654,13 +2656,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>22050</v>
+        <v>70100</v>
       </c>
       <c r="F69" t="n">
-        <v>2267</v>
+        <v>998</v>
       </c>
       <c r="G69" t="n">
-        <v>49987350</v>
+        <v>69959800</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2672,12 +2674,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2686,13 +2688,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>43150</v>
+        <v>93300</v>
       </c>
       <c r="F70" t="n">
-        <v>1390</v>
+        <v>214</v>
       </c>
       <c r="G70" t="n">
-        <v>59978500</v>
+        <v>19966200</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2704,12 +2706,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2718,13 +2720,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>310000</v>
+        <v>11300</v>
       </c>
       <c r="F71" t="n">
-        <v>225</v>
+        <v>4424</v>
       </c>
       <c r="G71" t="n">
-        <v>69750000</v>
+        <v>49991200</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2736,12 +2738,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2750,13 +2752,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6240</v>
+        <v>19740</v>
       </c>
       <c r="F72" t="n">
-        <v>3205</v>
+        <v>2532</v>
       </c>
       <c r="G72" t="n">
-        <v>19999200</v>
+        <v>49981680</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2768,12 +2770,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2782,13 +2784,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>24000</v>
+        <v>25150</v>
       </c>
       <c r="F73" t="n">
-        <v>833</v>
+        <v>2385</v>
       </c>
       <c r="G73" t="n">
-        <v>19992000</v>
+        <v>59982750</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2800,12 +2802,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2814,13 +2816,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>90300</v>
+        <v>22050</v>
       </c>
       <c r="F74" t="n">
-        <v>442</v>
+        <v>2267</v>
       </c>
       <c r="G74" t="n">
-        <v>39912600</v>
+        <v>49987350</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2832,12 +2834,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2846,13 +2848,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>279500</v>
+        <v>43150</v>
       </c>
       <c r="F75" t="n">
-        <v>357</v>
+        <v>1390</v>
       </c>
       <c r="G75" t="n">
-        <v>99781500</v>
+        <v>59978500</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2864,12 +2866,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2878,13 +2880,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>366000</v>
+        <v>310000</v>
       </c>
       <c r="F76" t="n">
-        <v>54</v>
+        <v>225</v>
       </c>
       <c r="G76" t="n">
-        <v>19764000</v>
+        <v>69750000</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2896,12 +2898,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2910,13 +2912,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>91000</v>
+        <v>6240</v>
       </c>
       <c r="F77" t="n">
-        <v>659</v>
+        <v>3205</v>
       </c>
       <c r="G77" t="n">
-        <v>59969000</v>
+        <v>19999200</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2928,12 +2930,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2942,13 +2944,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>120100</v>
+        <v>24000</v>
       </c>
       <c r="F78" t="n">
-        <v>666</v>
+        <v>833</v>
       </c>
       <c r="G78" t="n">
-        <v>79986600</v>
+        <v>19992000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2960,12 +2962,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2974,13 +2976,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2405</v>
+        <v>90300</v>
       </c>
       <c r="F79" t="n">
-        <v>415800</v>
+        <v>442</v>
       </c>
       <c r="G79" t="n">
-        <v>999999000</v>
+        <v>39912600</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2992,12 +2994,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3006,13 +3008,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>69000</v>
+        <v>279500</v>
       </c>
       <c r="F80" t="n">
-        <v>579</v>
+        <v>357</v>
       </c>
       <c r="G80" t="n">
-        <v>39951000</v>
+        <v>99781500</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3024,12 +3026,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3038,13 +3040,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>42300</v>
+        <v>366000</v>
       </c>
       <c r="F81" t="n">
-        <v>709</v>
+        <v>54</v>
       </c>
       <c r="G81" t="n">
-        <v>29990700</v>
+        <v>19764000</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3056,29 +3058,189 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F82" t="n">
+        <v>659</v>
+      </c>
+      <c r="G82" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F83" t="n">
+        <v>666</v>
+      </c>
+      <c r="G83" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F84" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G84" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F85" t="n">
+        <v>579</v>
+      </c>
+      <c r="G85" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F86" t="n">
+        <v>709</v>
+      </c>
+      <c r="G86" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E87" t="n">
         <v>23350</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F87" t="n">
         <v>856</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G87" t="n">
         <v>19987600</v>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,27 +544,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>43800</v>
+        <v>2215</v>
       </c>
       <c r="F4" t="n">
-        <v>504.0447</v>
+        <v>28224.978</v>
       </c>
       <c r="G4" t="n">
-        <v>22077158.2</v>
+        <v>62518326.2</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -576,27 +576,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23650</v>
+        <v>43800</v>
       </c>
       <c r="F5" t="n">
-        <v>451.106</v>
+        <v>504.0447</v>
       </c>
       <c r="G5" t="n">
-        <v>10668656.3</v>
+        <v>22077158.2</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -608,12 +608,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,49 +622,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5730</v>
+        <v>23650</v>
       </c>
       <c r="F6" t="n">
-        <v>3723.7893</v>
+        <v>451.106</v>
       </c>
       <c r="G6" t="n">
-        <v>21337312.7</v>
+        <v>10668656.3</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6080</v>
+        <v>5730</v>
       </c>
       <c r="F7" t="n">
-        <v>3255.5051</v>
+        <v>3723.7893</v>
       </c>
       <c r="G7" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>21337312.7</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -674,29 +672,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>95200</v>
+        <v>6080</v>
       </c>
       <c r="F8" t="n">
-        <v>221.6088</v>
+        <v>3255.5051</v>
       </c>
       <c r="G8" t="n">
-        <v>21097154.4</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2205</v>
+        <v>95200</v>
       </c>
       <c r="F9" t="n">
-        <v>52623.2877</v>
+        <v>221.6088</v>
       </c>
       <c r="G9" t="n">
-        <v>116034349.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>58700</v>
+        <v>2205</v>
       </c>
       <c r="F10" t="n">
-        <v>357.1039</v>
+        <v>52623.2877</v>
       </c>
       <c r="G10" t="n">
-        <v>20961998.6</v>
+        <v>116034349.3</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,27 +770,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13250</v>
+        <v>58700</v>
       </c>
       <c r="F11" t="n">
-        <v>791.0188000000001</v>
+        <v>357.1039</v>
       </c>
       <c r="G11" t="n">
-        <v>10480999.3</v>
+        <v>20961998.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2360</v>
+        <v>13250</v>
       </c>
       <c r="F12" t="n">
-        <v>66616.5209</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>157214989.3</v>
+        <v>10480999.3</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,31 +834,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>38300</v>
+        <v>2360</v>
       </c>
       <c r="F13" t="n">
-        <v>500.7861</v>
+        <v>66616.5209</v>
       </c>
       <c r="G13" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>157214989.3</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -868,29 +866,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21150</v>
+        <v>38300</v>
       </c>
       <c r="F14" t="n">
-        <v>495.5555</v>
+        <v>500.7861</v>
       </c>
       <c r="G14" t="n">
-        <v>10480999.3</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -900,63 +900,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>23650</v>
+        <v>21150</v>
       </c>
       <c r="F15" t="n">
-        <v>832.6201</v>
+        <v>495.5555</v>
       </c>
       <c r="G15" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.28</v>
-      </c>
+        <v>10480999.3</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12310</v>
+        <v>23650</v>
       </c>
       <c r="F16" t="n">
-        <v>2480.1654</v>
+        <v>832.6201</v>
       </c>
       <c r="G16" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -966,24 +966,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40650</v>
+        <v>12310</v>
       </c>
       <c r="F17" t="n">
-        <v>751.0661</v>
+        <v>2480.1654</v>
       </c>
       <c r="G17" t="n">
         <v>30530836.4</v>
@@ -998,12 +998,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>283500</v>
+        <v>40650</v>
       </c>
       <c r="F18" t="n">
-        <v>71.795</v>
+        <v>751.0661</v>
       </c>
       <c r="G18" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1030,27 +1030,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2390</v>
+        <v>283500</v>
       </c>
       <c r="F19" t="n">
-        <v>42581.3618</v>
+        <v>71.795</v>
       </c>
       <c r="G19" t="n">
-        <v>101769454.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1062,59 +1062,59 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20450</v>
+        <v>2390</v>
       </c>
       <c r="F20" t="n">
-        <v>995.3003</v>
+        <v>42581.3618</v>
       </c>
       <c r="G20" t="n">
-        <v>20353890.9</v>
+        <v>101769454.6</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>30200</v>
+        <v>20450</v>
       </c>
       <c r="F21" t="n">
-        <v>359.55</v>
+        <v>995.3003</v>
       </c>
       <c r="G21" t="n">
-        <v>10858410.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1126,31 +1126,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208500</v>
+        <v>30200</v>
       </c>
       <c r="F22" t="n">
-        <v>338</v>
+        <v>359.55</v>
       </c>
       <c r="G22" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.97</v>
-      </c>
+        <v>10858410.6</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1160,29 +1158,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17720</v>
+        <v>208500</v>
       </c>
       <c r="F23" t="n">
-        <v>94.9217</v>
+        <v>338</v>
       </c>
       <c r="G23" t="n">
-        <v>1682012.5</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1192,27 +1192,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100500</v>
+        <v>17720</v>
       </c>
       <c r="F24" t="n">
-        <v>8.9518</v>
+        <v>94.9217</v>
       </c>
       <c r="G24" t="n">
-        <v>899652.6</v>
+        <v>1682012.5</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1224,27 +1224,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11410</v>
+        <v>100500</v>
       </c>
       <c r="F25" t="n">
-        <v>6321.2722</v>
+        <v>8.9518</v>
       </c>
       <c r="G25" t="n">
-        <v>72125715.8</v>
+        <v>899652.6</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,27 +1256,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12880</v>
+        <v>11410</v>
       </c>
       <c r="F26" t="n">
-        <v>713.2027</v>
+        <v>6321.2722</v>
       </c>
       <c r="G26" t="n">
-        <v>9186050.6</v>
+        <v>72125715.8</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>21200</v>
+        <v>12880</v>
       </c>
       <c r="F27" t="n">
-        <v>120.8659</v>
+        <v>713.2027</v>
       </c>
       <c r="G27" t="n">
-        <v>2562357.9</v>
+        <v>9186050.6</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>27700</v>
+        <v>21200</v>
       </c>
       <c r="F28" t="n">
-        <v>161.1835</v>
+        <v>120.8659</v>
       </c>
       <c r="G28" t="n">
-        <v>4464784.2</v>
+        <v>2562357.9</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,27 +1352,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>21500</v>
+        <v>27700</v>
       </c>
       <c r="F29" t="n">
-        <v>129.2032</v>
+        <v>161.1835</v>
       </c>
       <c r="G29" t="n">
-        <v>2777868.4</v>
+        <v>4464784.2</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,27 +1384,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>34100</v>
+        <v>21500</v>
       </c>
       <c r="F30" t="n">
-        <v>21.679</v>
+        <v>129.2032</v>
       </c>
       <c r="G30" t="n">
-        <v>739252.6</v>
+        <v>2777868.4</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40850</v>
+        <v>34100</v>
       </c>
       <c r="F31" t="n">
-        <v>123.3915</v>
+        <v>21.679</v>
       </c>
       <c r="G31" t="n">
-        <v>5040542.1</v>
+        <v>739252.6</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308000</v>
+        <v>40850</v>
       </c>
       <c r="F32" t="n">
-        <v>9.1744</v>
+        <v>123.3915</v>
       </c>
       <c r="G32" t="n">
-        <v>2825715.8</v>
+        <v>5040542.1</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6330</v>
+        <v>308000</v>
       </c>
       <c r="F33" t="n">
-        <v>50.5051</v>
+        <v>9.1744</v>
       </c>
       <c r="G33" t="n">
-        <v>319697.4</v>
+        <v>2825715.8</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,27 +1512,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>31700</v>
+        <v>6330</v>
       </c>
       <c r="F34" t="n">
-        <v>158.7408</v>
+        <v>50.5051</v>
       </c>
       <c r="G34" t="n">
-        <v>5032084.2</v>
+        <v>319697.4</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>68700</v>
+        <v>31700</v>
       </c>
       <c r="F35" t="n">
-        <v>16.0386</v>
+        <v>158.7408</v>
       </c>
       <c r="G35" t="n">
-        <v>1101852.6</v>
+        <v>5032084.2</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,27 +1576,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256000</v>
+        <v>68700</v>
       </c>
       <c r="F36" t="n">
-        <v>45.4873</v>
+        <v>16.0386</v>
       </c>
       <c r="G36" t="n">
-        <v>11644736.8</v>
+        <v>1101852.6</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>91100</v>
+        <v>256000</v>
       </c>
       <c r="F37" t="n">
-        <v>19.6174</v>
+        <v>45.4873</v>
       </c>
       <c r="G37" t="n">
-        <v>1787142.1</v>
+        <v>11644736.8</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,27 +1640,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>130900</v>
+        <v>91100</v>
       </c>
       <c r="F38" t="n">
-        <v>89.1437</v>
+        <v>19.6174</v>
       </c>
       <c r="G38" t="n">
-        <v>11668905.3</v>
+        <v>1787142.1</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2400</v>
+        <v>130900</v>
       </c>
       <c r="F39" t="n">
-        <v>32820.1843</v>
+        <v>89.1437</v>
       </c>
       <c r="G39" t="n">
-        <v>78768442.40000001</v>
+        <v>11668905.3</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,27 +1704,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>41150</v>
+        <v>2400</v>
       </c>
       <c r="F40" t="n">
-        <v>38.7861</v>
+        <v>32820.1843</v>
       </c>
       <c r="G40" t="n">
-        <v>1596047.4</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,27 +1736,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>49450</v>
+        <v>41150</v>
       </c>
       <c r="F41" t="n">
-        <v>83.90349999999999</v>
+        <v>38.7861</v>
       </c>
       <c r="G41" t="n">
-        <v>4149029</v>
+        <v>1596047.4</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>24750</v>
+        <v>49450</v>
       </c>
       <c r="F42" t="n">
-        <v>23.3799</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>578652.6</v>
+        <v>4149029</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1814,49 +1814,47 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5450</v>
+        <v>24750</v>
       </c>
       <c r="F43" t="n">
-        <v>220.6267</v>
+        <v>23.3799</v>
       </c>
       <c r="G43" t="n">
-        <v>1202415.4</v>
+        <v>578652.6</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>327000</v>
+        <v>5450</v>
       </c>
       <c r="F44" t="n">
-        <v>54</v>
+        <v>220.6267</v>
       </c>
       <c r="G44" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>1202415.4</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1866,59 +1864,61 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5130</v>
+        <v>327000</v>
       </c>
       <c r="F45" t="n">
-        <v>4001.7913</v>
+        <v>54</v>
       </c>
       <c r="G45" t="n">
-        <v>20529189.5</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>27100</v>
+        <v>5130</v>
       </c>
       <c r="F46" t="n">
-        <v>376</v>
+        <v>4001.7913</v>
       </c>
       <c r="G46" t="n">
-        <v>10189600</v>
+        <v>20529189.5</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1930,31 +1930,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>67600</v>
+        <v>27100</v>
       </c>
       <c r="F47" t="n">
-        <v>998</v>
+        <v>376</v>
       </c>
       <c r="G47" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>10189600</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1964,29 +1962,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>11900</v>
+        <v>67600</v>
       </c>
       <c r="F48" t="n">
-        <v>856</v>
+        <v>998</v>
       </c>
       <c r="G48" t="n">
-        <v>10186400</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1996,27 +1996,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>29300</v>
+        <v>11900</v>
       </c>
       <c r="F49" t="n">
-        <v>2434</v>
+        <v>856</v>
       </c>
       <c r="G49" t="n">
-        <v>71316200</v>
+        <v>10186400</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2028,27 +2028,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>119300</v>
+        <v>29300</v>
       </c>
       <c r="F50" t="n">
-        <v>171</v>
+        <v>2434</v>
       </c>
       <c r="G50" t="n">
-        <v>20400300</v>
+        <v>71316200</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2074,45 +2074,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2445</v>
+        <v>119300</v>
       </c>
       <c r="F51" t="n">
-        <v>82456</v>
+        <v>171</v>
       </c>
       <c r="G51" t="n">
-        <v>201604920</v>
+        <v>20400300</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>18910</v>
+        <v>2445</v>
       </c>
       <c r="F52" t="n">
-        <v>1068.0212</v>
+        <v>82456</v>
       </c>
       <c r="G52" t="n">
-        <v>20196280</v>
+        <v>201604920</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2138,13 +2138,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>32250</v>
+        <v>18910</v>
       </c>
       <c r="F53" t="n">
-        <v>626</v>
+        <v>1068.0212</v>
       </c>
       <c r="G53" t="n">
-        <v>20188500</v>
+        <v>20196280</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2156,31 +2156,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>82500</v>
+        <v>32250</v>
       </c>
       <c r="F54" t="n">
-        <v>204</v>
+        <v>626</v>
       </c>
       <c r="G54" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>20188500</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2190,12 +2188,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2204,49 +2202,51 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>56800</v>
+        <v>82500</v>
       </c>
       <c r="F55" t="n">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="G55" t="n">
-        <v>14654400</v>
+        <v>16830000</v>
       </c>
       <c r="H55" t="n">
-        <v>-17.68</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>83700</v>
+        <v>56800</v>
       </c>
       <c r="F56" t="n">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="G56" t="n">
-        <v>10044000</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2256,27 +2256,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>43650</v>
+        <v>83700</v>
       </c>
       <c r="F57" t="n">
-        <v>462</v>
+        <v>120</v>
       </c>
       <c r="G57" t="n">
-        <v>20166300</v>
+        <v>10044000</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2288,59 +2288,59 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>59700</v>
+        <v>43650</v>
       </c>
       <c r="F58" t="n">
-        <v>169</v>
+        <v>462</v>
       </c>
       <c r="G58" t="n">
-        <v>10089300</v>
+        <v>20166300</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>10930</v>
+        <v>59700</v>
       </c>
       <c r="F59" t="n">
-        <v>1833</v>
+        <v>169</v>
       </c>
       <c r="G59" t="n">
-        <v>20034690</v>
+        <v>10089300</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>19850</v>
+        <v>10930</v>
       </c>
       <c r="F60" t="n">
-        <v>505</v>
+        <v>1833</v>
       </c>
       <c r="G60" t="n">
-        <v>10024250</v>
+        <v>20034690</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>26350</v>
+        <v>19850</v>
       </c>
       <c r="F61" t="n">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="G61" t="n">
-        <v>10013000</v>
+        <v>10024250</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2416,31 +2416,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>23500</v>
+        <v>26350</v>
       </c>
       <c r="F62" t="n">
-        <v>833</v>
+        <v>380</v>
       </c>
       <c r="G62" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10013000</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2450,29 +2448,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>85200</v>
+        <v>23500</v>
       </c>
       <c r="F63" t="n">
-        <v>118</v>
+        <v>833</v>
       </c>
       <c r="G63" t="n">
-        <v>10053600</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2482,27 +2482,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>63400</v>
+        <v>85200</v>
       </c>
       <c r="F64" t="n">
-        <v>316</v>
+        <v>118</v>
       </c>
       <c r="G64" t="n">
-        <v>20034400</v>
+        <v>10053600</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2514,27 +2514,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>110300</v>
+        <v>63400</v>
       </c>
       <c r="F65" t="n">
-        <v>91</v>
+        <v>316</v>
       </c>
       <c r="G65" t="n">
-        <v>10037300</v>
+        <v>20034400</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2560,45 +2560,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>66100</v>
+        <v>110300</v>
       </c>
       <c r="F66" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="G66" t="n">
-        <v>10047200</v>
+        <v>10037300</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>25800</v>
+        <v>66100</v>
       </c>
       <c r="F67" t="n">
-        <v>2713</v>
+        <v>152</v>
       </c>
       <c r="G67" t="n">
-        <v>69995400</v>
+        <v>10047200</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,13 +2624,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>206500</v>
+        <v>25800</v>
       </c>
       <c r="F68" t="n">
-        <v>338</v>
+        <v>2713</v>
       </c>
       <c r="G68" t="n">
-        <v>69797000</v>
+        <v>69995400</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>70100</v>
+        <v>206500</v>
       </c>
       <c r="F69" t="n">
-        <v>998</v>
+        <v>338</v>
       </c>
       <c r="G69" t="n">
-        <v>69959800</v>
+        <v>69797000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>93300</v>
+        <v>70100</v>
       </c>
       <c r="F70" t="n">
-        <v>214</v>
+        <v>998</v>
       </c>
       <c r="G70" t="n">
-        <v>19966200</v>
+        <v>69959800</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>11300</v>
+        <v>93300</v>
       </c>
       <c r="F71" t="n">
-        <v>4424</v>
+        <v>214</v>
       </c>
       <c r="G71" t="n">
-        <v>49991200</v>
+        <v>19966200</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>19740</v>
+        <v>11300</v>
       </c>
       <c r="F72" t="n">
-        <v>2532</v>
+        <v>4424</v>
       </c>
       <c r="G72" t="n">
-        <v>49981680</v>
+        <v>49991200</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2784,13 +2784,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F73" t="n">
-        <v>2385</v>
+        <v>2532</v>
       </c>
       <c r="G73" t="n">
-        <v>59982750</v>
+        <v>49981680</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>22050</v>
+        <v>25150</v>
       </c>
       <c r="F74" t="n">
-        <v>2267</v>
+        <v>2385</v>
       </c>
       <c r="G74" t="n">
-        <v>49987350</v>
+        <v>59982750</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>43150</v>
+        <v>22050</v>
       </c>
       <c r="F75" t="n">
-        <v>1390</v>
+        <v>2267</v>
       </c>
       <c r="G75" t="n">
-        <v>59978500</v>
+        <v>49987350</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2866,12 +2866,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>310000</v>
+        <v>43150</v>
       </c>
       <c r="F76" t="n">
-        <v>225</v>
+        <v>1390</v>
       </c>
       <c r="G76" t="n">
-        <v>69750000</v>
+        <v>59978500</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2912,13 +2912,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6240</v>
+        <v>310000</v>
       </c>
       <c r="F77" t="n">
-        <v>3205</v>
+        <v>225</v>
       </c>
       <c r="G77" t="n">
-        <v>19999200</v>
+        <v>69750000</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>24000</v>
+        <v>6240</v>
       </c>
       <c r="F78" t="n">
-        <v>833</v>
+        <v>3205</v>
       </c>
       <c r="G78" t="n">
-        <v>19992000</v>
+        <v>19999200</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>90300</v>
+        <v>24000</v>
       </c>
       <c r="F79" t="n">
-        <v>442</v>
+        <v>833</v>
       </c>
       <c r="G79" t="n">
-        <v>39912600</v>
+        <v>19992000</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>279500</v>
+        <v>90300</v>
       </c>
       <c r="F80" t="n">
-        <v>357</v>
+        <v>442</v>
       </c>
       <c r="G80" t="n">
-        <v>99781500</v>
+        <v>39912600</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>366000</v>
+        <v>279500</v>
       </c>
       <c r="F81" t="n">
-        <v>54</v>
+        <v>357</v>
       </c>
       <c r="G81" t="n">
-        <v>19764000</v>
+        <v>99781500</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3072,13 +3072,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>91000</v>
+        <v>366000</v>
       </c>
       <c r="F82" t="n">
-        <v>659</v>
+        <v>54</v>
       </c>
       <c r="G82" t="n">
-        <v>59969000</v>
+        <v>19764000</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3090,12 +3090,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>120100</v>
+        <v>91000</v>
       </c>
       <c r="F83" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="G83" t="n">
-        <v>79986600</v>
+        <v>59969000</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2405</v>
+        <v>120100</v>
       </c>
       <c r="F84" t="n">
-        <v>415800</v>
+        <v>666</v>
       </c>
       <c r="G84" t="n">
-        <v>999999000</v>
+        <v>79986600</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3168,13 +3168,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>69000</v>
+        <v>2405</v>
       </c>
       <c r="F85" t="n">
-        <v>579</v>
+        <v>415800</v>
       </c>
       <c r="G85" t="n">
-        <v>39951000</v>
+        <v>999999000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>42300</v>
+        <v>69000</v>
       </c>
       <c r="F86" t="n">
-        <v>709</v>
+        <v>579</v>
       </c>
       <c r="G86" t="n">
-        <v>29990700</v>
+        <v>39951000</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3218,29 +3218,61 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F87" t="n">
+        <v>709</v>
+      </c>
+      <c r="G87" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="E88" t="n">
         <v>23350</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F88" t="n">
         <v>856</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G88" t="n">
         <v>19987600</v>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22900</v>
+        <v>2120</v>
       </c>
       <c r="F2" t="n">
-        <v>1397.6406</v>
+        <v>63879.7502</v>
       </c>
       <c r="G2" t="n">
-        <v>32005969</v>
+        <v>135425070.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -510,31 +510,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73600</v>
+        <v>22900</v>
       </c>
       <c r="F3" t="n">
-        <v>299.9614</v>
+        <v>1397.6406</v>
       </c>
       <c r="G3" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>16.09</v>
-      </c>
+        <v>32005969</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,29 +542,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2215</v>
+        <v>73600</v>
       </c>
       <c r="F4" t="n">
-        <v>28224.978</v>
+        <v>299.9614</v>
       </c>
       <c r="G4" t="n">
-        <v>62518326.2</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,27 +576,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43800</v>
+        <v>2215</v>
       </c>
       <c r="F5" t="n">
-        <v>504.0447</v>
+        <v>28224.978</v>
       </c>
       <c r="G5" t="n">
-        <v>22077158.2</v>
+        <v>62518326.2</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -608,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23650</v>
+        <v>43800</v>
       </c>
       <c r="F6" t="n">
-        <v>451.106</v>
+        <v>504.0447</v>
       </c>
       <c r="G6" t="n">
-        <v>10668656.3</v>
+        <v>22077158.2</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,49 +654,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5730</v>
+        <v>23650</v>
       </c>
       <c r="F7" t="n">
-        <v>3723.7893</v>
+        <v>451.106</v>
       </c>
       <c r="G7" t="n">
-        <v>21337312.7</v>
+        <v>10668656.3</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6080</v>
+        <v>5730</v>
       </c>
       <c r="F8" t="n">
-        <v>3255.5051</v>
+        <v>3723.7893</v>
       </c>
       <c r="G8" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>21337312.7</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,29 +704,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>95200</v>
+        <v>6080</v>
       </c>
       <c r="F9" t="n">
-        <v>221.6088</v>
+        <v>3255.5051</v>
       </c>
       <c r="G9" t="n">
-        <v>21097154.4</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,59 +738,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2205</v>
+        <v>95200</v>
       </c>
       <c r="F10" t="n">
-        <v>52623.2877</v>
+        <v>221.6088</v>
       </c>
       <c r="G10" t="n">
-        <v>116034349.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58700</v>
+        <v>2205</v>
       </c>
       <c r="F11" t="n">
-        <v>357.1039</v>
+        <v>52623.2877</v>
       </c>
       <c r="G11" t="n">
-        <v>20961998.6</v>
+        <v>116034349.3</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,27 +802,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13250</v>
+        <v>58700</v>
       </c>
       <c r="F12" t="n">
-        <v>791.0188000000001</v>
+        <v>357.1039</v>
       </c>
       <c r="G12" t="n">
-        <v>10480999.3</v>
+        <v>20961998.6</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2360</v>
+        <v>13250</v>
       </c>
       <c r="F13" t="n">
-        <v>66616.5209</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>157214989.3</v>
+        <v>10480999.3</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,31 +866,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>38300</v>
+        <v>2360</v>
       </c>
       <c r="F14" t="n">
-        <v>500.7861</v>
+        <v>66616.5209</v>
       </c>
       <c r="G14" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>157214989.3</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -900,29 +898,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21150</v>
+        <v>38300</v>
       </c>
       <c r="F15" t="n">
-        <v>495.5555</v>
+        <v>500.7861</v>
       </c>
       <c r="G15" t="n">
-        <v>10480999.3</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -932,63 +932,63 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>23650</v>
+        <v>21150</v>
       </c>
       <c r="F16" t="n">
-        <v>832.6201</v>
+        <v>495.5555</v>
       </c>
       <c r="G16" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.28</v>
-      </c>
+        <v>10480999.3</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12310</v>
+        <v>23650</v>
       </c>
       <c r="F17" t="n">
-        <v>2480.1654</v>
+        <v>832.6201</v>
       </c>
       <c r="G17" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -998,24 +998,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>40650</v>
+        <v>12310</v>
       </c>
       <c r="F18" t="n">
-        <v>751.0661</v>
+        <v>2480.1654</v>
       </c>
       <c r="G18" t="n">
         <v>30530836.4</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283500</v>
+        <v>40650</v>
       </c>
       <c r="F19" t="n">
-        <v>71.795</v>
+        <v>751.0661</v>
       </c>
       <c r="G19" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1062,27 +1062,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2390</v>
+        <v>283500</v>
       </c>
       <c r="F20" t="n">
-        <v>42581.3618</v>
+        <v>71.795</v>
       </c>
       <c r="G20" t="n">
-        <v>101769454.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1094,59 +1094,59 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>20450</v>
+        <v>2390</v>
       </c>
       <c r="F21" t="n">
-        <v>995.3003</v>
+        <v>42581.3618</v>
       </c>
       <c r="G21" t="n">
-        <v>20353890.9</v>
+        <v>101769454.6</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>30200</v>
+        <v>20450</v>
       </c>
       <c r="F22" t="n">
-        <v>359.55</v>
+        <v>995.3003</v>
       </c>
       <c r="G22" t="n">
-        <v>10858410.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1158,31 +1158,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208500</v>
+        <v>30200</v>
       </c>
       <c r="F23" t="n">
-        <v>338</v>
+        <v>359.55</v>
       </c>
       <c r="G23" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.97</v>
-      </c>
+        <v>10858410.6</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1192,29 +1190,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17720</v>
+        <v>208500</v>
       </c>
       <c r="F24" t="n">
-        <v>94.9217</v>
+        <v>338</v>
       </c>
       <c r="G24" t="n">
-        <v>1682012.5</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1224,27 +1224,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100500</v>
+        <v>17720</v>
       </c>
       <c r="F25" t="n">
-        <v>8.9518</v>
+        <v>94.9217</v>
       </c>
       <c r="G25" t="n">
-        <v>899652.6</v>
+        <v>1682012.5</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,27 +1256,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11410</v>
+        <v>100500</v>
       </c>
       <c r="F26" t="n">
-        <v>6321.2722</v>
+        <v>8.9518</v>
       </c>
       <c r="G26" t="n">
-        <v>72125715.8</v>
+        <v>899652.6</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,27 +1288,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12880</v>
+        <v>11410</v>
       </c>
       <c r="F27" t="n">
-        <v>713.2027</v>
+        <v>6321.2722</v>
       </c>
       <c r="G27" t="n">
-        <v>9186050.6</v>
+        <v>72125715.8</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>21200</v>
+        <v>12880</v>
       </c>
       <c r="F28" t="n">
-        <v>120.8659</v>
+        <v>713.2027</v>
       </c>
       <c r="G28" t="n">
-        <v>2562357.9</v>
+        <v>9186050.6</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>27700</v>
+        <v>21200</v>
       </c>
       <c r="F29" t="n">
-        <v>161.1835</v>
+        <v>120.8659</v>
       </c>
       <c r="G29" t="n">
-        <v>4464784.2</v>
+        <v>2562357.9</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,27 +1384,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>21500</v>
+        <v>27700</v>
       </c>
       <c r="F30" t="n">
-        <v>129.2032</v>
+        <v>161.1835</v>
       </c>
       <c r="G30" t="n">
-        <v>2777868.4</v>
+        <v>4464784.2</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>34100</v>
+        <v>21500</v>
       </c>
       <c r="F31" t="n">
-        <v>21.679</v>
+        <v>129.2032</v>
       </c>
       <c r="G31" t="n">
-        <v>739252.6</v>
+        <v>2777868.4</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>40850</v>
+        <v>34100</v>
       </c>
       <c r="F32" t="n">
-        <v>123.3915</v>
+        <v>21.679</v>
       </c>
       <c r="G32" t="n">
-        <v>5040542.1</v>
+        <v>739252.6</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308000</v>
+        <v>40850</v>
       </c>
       <c r="F33" t="n">
-        <v>9.1744</v>
+        <v>123.3915</v>
       </c>
       <c r="G33" t="n">
-        <v>2825715.8</v>
+        <v>5040542.1</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6330</v>
+        <v>308000</v>
       </c>
       <c r="F34" t="n">
-        <v>50.5051</v>
+        <v>9.1744</v>
       </c>
       <c r="G34" t="n">
-        <v>319697.4</v>
+        <v>2825715.8</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>31700</v>
+        <v>6330</v>
       </c>
       <c r="F35" t="n">
-        <v>158.7408</v>
+        <v>50.5051</v>
       </c>
       <c r="G35" t="n">
-        <v>5032084.2</v>
+        <v>319697.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>68700</v>
+        <v>31700</v>
       </c>
       <c r="F36" t="n">
-        <v>16.0386</v>
+        <v>158.7408</v>
       </c>
       <c r="G36" t="n">
-        <v>1101852.6</v>
+        <v>5032084.2</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,27 +1608,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>256000</v>
+        <v>68700</v>
       </c>
       <c r="F37" t="n">
-        <v>45.4873</v>
+        <v>16.0386</v>
       </c>
       <c r="G37" t="n">
-        <v>11644736.8</v>
+        <v>1101852.6</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>91100</v>
+        <v>256000</v>
       </c>
       <c r="F38" t="n">
-        <v>19.6174</v>
+        <v>45.4873</v>
       </c>
       <c r="G38" t="n">
-        <v>1787142.1</v>
+        <v>11644736.8</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,27 +1672,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>130900</v>
+        <v>91100</v>
       </c>
       <c r="F39" t="n">
-        <v>89.1437</v>
+        <v>19.6174</v>
       </c>
       <c r="G39" t="n">
-        <v>11668905.3</v>
+        <v>1787142.1</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2400</v>
+        <v>130900</v>
       </c>
       <c r="F40" t="n">
-        <v>32820.1843</v>
+        <v>89.1437</v>
       </c>
       <c r="G40" t="n">
-        <v>78768442.40000001</v>
+        <v>11668905.3</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,27 +1736,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>41150</v>
+        <v>2400</v>
       </c>
       <c r="F41" t="n">
-        <v>38.7861</v>
+        <v>32820.1843</v>
       </c>
       <c r="G41" t="n">
-        <v>1596047.4</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,27 +1768,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>49450</v>
+        <v>41150</v>
       </c>
       <c r="F42" t="n">
-        <v>83.90349999999999</v>
+        <v>38.7861</v>
       </c>
       <c r="G42" t="n">
-        <v>4149029</v>
+        <v>1596047.4</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>24750</v>
+        <v>49450</v>
       </c>
       <c r="F43" t="n">
-        <v>23.3799</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>578652.6</v>
+        <v>4149029</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1846,49 +1846,47 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5450</v>
+        <v>24750</v>
       </c>
       <c r="F44" t="n">
-        <v>220.6267</v>
+        <v>23.3799</v>
       </c>
       <c r="G44" t="n">
-        <v>1202415.4</v>
+        <v>578652.6</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>327000</v>
+        <v>5450</v>
       </c>
       <c r="F45" t="n">
-        <v>54</v>
+        <v>220.6267</v>
       </c>
       <c r="G45" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>1202415.4</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1898,59 +1896,61 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5130</v>
+        <v>327000</v>
       </c>
       <c r="F46" t="n">
-        <v>4001.7913</v>
+        <v>54</v>
       </c>
       <c r="G46" t="n">
-        <v>20529189.5</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>27100</v>
+        <v>5130</v>
       </c>
       <c r="F47" t="n">
-        <v>376</v>
+        <v>4001.7913</v>
       </c>
       <c r="G47" t="n">
-        <v>10189600</v>
+        <v>20529189.5</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1962,31 +1962,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>67600</v>
+        <v>27100</v>
       </c>
       <c r="F48" t="n">
-        <v>998</v>
+        <v>376</v>
       </c>
       <c r="G48" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>10189600</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1996,29 +1994,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11900</v>
+        <v>67600</v>
       </c>
       <c r="F49" t="n">
-        <v>856</v>
+        <v>998</v>
       </c>
       <c r="G49" t="n">
-        <v>10186400</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2028,27 +2028,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>29300</v>
+        <v>11900</v>
       </c>
       <c r="F50" t="n">
-        <v>2434</v>
+        <v>856</v>
       </c>
       <c r="G50" t="n">
-        <v>71316200</v>
+        <v>10186400</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2060,27 +2060,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>119300</v>
+        <v>29300</v>
       </c>
       <c r="F51" t="n">
-        <v>171</v>
+        <v>2434</v>
       </c>
       <c r="G51" t="n">
-        <v>20400300</v>
+        <v>71316200</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2106,45 +2106,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2445</v>
+        <v>119300</v>
       </c>
       <c r="F52" t="n">
-        <v>82456</v>
+        <v>171</v>
       </c>
       <c r="G52" t="n">
-        <v>201604920</v>
+        <v>20400300</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>18910</v>
+        <v>2445</v>
       </c>
       <c r="F53" t="n">
-        <v>1068.0212</v>
+        <v>82456</v>
       </c>
       <c r="G53" t="n">
-        <v>20196280</v>
+        <v>201604920</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>32250</v>
+        <v>18910</v>
       </c>
       <c r="F54" t="n">
-        <v>626</v>
+        <v>1068.0212</v>
       </c>
       <c r="G54" t="n">
-        <v>20188500</v>
+        <v>20196280</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2188,31 +2188,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>82500</v>
+        <v>32250</v>
       </c>
       <c r="F55" t="n">
-        <v>204</v>
+        <v>626</v>
       </c>
       <c r="G55" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>20188500</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2222,12 +2220,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2236,49 +2234,51 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>56800</v>
+        <v>82500</v>
       </c>
       <c r="F56" t="n">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="G56" t="n">
-        <v>14654400</v>
+        <v>16830000</v>
       </c>
       <c r="H56" t="n">
-        <v>-17.68</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>83700</v>
+        <v>56800</v>
       </c>
       <c r="F57" t="n">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="G57" t="n">
-        <v>10044000</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2288,27 +2288,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>43650</v>
+        <v>83700</v>
       </c>
       <c r="F58" t="n">
-        <v>462</v>
+        <v>120</v>
       </c>
       <c r="G58" t="n">
-        <v>20166300</v>
+        <v>10044000</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2320,59 +2320,59 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59700</v>
+        <v>43650</v>
       </c>
       <c r="F59" t="n">
-        <v>169</v>
+        <v>462</v>
       </c>
       <c r="G59" t="n">
-        <v>10089300</v>
+        <v>20166300</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>10930</v>
+        <v>59700</v>
       </c>
       <c r="F60" t="n">
-        <v>1833</v>
+        <v>169</v>
       </c>
       <c r="G60" t="n">
-        <v>20034690</v>
+        <v>10089300</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>19850</v>
+        <v>10930</v>
       </c>
       <c r="F61" t="n">
-        <v>505</v>
+        <v>1833</v>
       </c>
       <c r="G61" t="n">
-        <v>10024250</v>
+        <v>20034690</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>26350</v>
+        <v>19850</v>
       </c>
       <c r="F62" t="n">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="G62" t="n">
-        <v>10013000</v>
+        <v>10024250</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2448,31 +2448,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>23500</v>
+        <v>26350</v>
       </c>
       <c r="F63" t="n">
-        <v>833</v>
+        <v>380</v>
       </c>
       <c r="G63" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10013000</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2482,29 +2480,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>85200</v>
+        <v>23500</v>
       </c>
       <c r="F64" t="n">
-        <v>118</v>
+        <v>833</v>
       </c>
       <c r="G64" t="n">
-        <v>10053600</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2514,27 +2514,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>63400</v>
+        <v>85200</v>
       </c>
       <c r="F65" t="n">
-        <v>316</v>
+        <v>118</v>
       </c>
       <c r="G65" t="n">
-        <v>20034400</v>
+        <v>10053600</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2546,27 +2546,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>110300</v>
+        <v>63400</v>
       </c>
       <c r="F66" t="n">
-        <v>91</v>
+        <v>316</v>
       </c>
       <c r="G66" t="n">
-        <v>10037300</v>
+        <v>20034400</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2592,45 +2592,45 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>66100</v>
+        <v>110300</v>
       </c>
       <c r="F67" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="G67" t="n">
-        <v>10047200</v>
+        <v>10037300</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>25800</v>
+        <v>66100</v>
       </c>
       <c r="F68" t="n">
-        <v>2713</v>
+        <v>152</v>
       </c>
       <c r="G68" t="n">
-        <v>69995400</v>
+        <v>10047200</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>206500</v>
+        <v>25800</v>
       </c>
       <c r="F69" t="n">
-        <v>338</v>
+        <v>2713</v>
       </c>
       <c r="G69" t="n">
-        <v>69797000</v>
+        <v>69995400</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>70100</v>
+        <v>206500</v>
       </c>
       <c r="F70" t="n">
-        <v>998</v>
+        <v>338</v>
       </c>
       <c r="G70" t="n">
-        <v>69959800</v>
+        <v>69797000</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>93300</v>
+        <v>70100</v>
       </c>
       <c r="F71" t="n">
-        <v>214</v>
+        <v>998</v>
       </c>
       <c r="G71" t="n">
-        <v>19966200</v>
+        <v>69959800</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>11300</v>
+        <v>93300</v>
       </c>
       <c r="F72" t="n">
-        <v>4424</v>
+        <v>214</v>
       </c>
       <c r="G72" t="n">
-        <v>49991200</v>
+        <v>19966200</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2784,13 +2784,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>19740</v>
+        <v>11300</v>
       </c>
       <c r="F73" t="n">
-        <v>2532</v>
+        <v>4424</v>
       </c>
       <c r="G73" t="n">
-        <v>49981680</v>
+        <v>49991200</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F74" t="n">
-        <v>2385</v>
+        <v>2532</v>
       </c>
       <c r="G74" t="n">
-        <v>59982750</v>
+        <v>49981680</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>22050</v>
+        <v>25150</v>
       </c>
       <c r="F75" t="n">
-        <v>2267</v>
+        <v>2385</v>
       </c>
       <c r="G75" t="n">
-        <v>49987350</v>
+        <v>59982750</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2866,12 +2866,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>43150</v>
+        <v>22050</v>
       </c>
       <c r="F76" t="n">
-        <v>1390</v>
+        <v>2267</v>
       </c>
       <c r="G76" t="n">
-        <v>59978500</v>
+        <v>49987350</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2912,13 +2912,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>310000</v>
+        <v>43150</v>
       </c>
       <c r="F77" t="n">
-        <v>225</v>
+        <v>1390</v>
       </c>
       <c r="G77" t="n">
-        <v>69750000</v>
+        <v>59978500</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6240</v>
+        <v>310000</v>
       </c>
       <c r="F78" t="n">
-        <v>3205</v>
+        <v>225</v>
       </c>
       <c r="G78" t="n">
-        <v>19999200</v>
+        <v>69750000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>24000</v>
+        <v>6240</v>
       </c>
       <c r="F79" t="n">
-        <v>833</v>
+        <v>3205</v>
       </c>
       <c r="G79" t="n">
-        <v>19992000</v>
+        <v>19999200</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>90300</v>
+        <v>24000</v>
       </c>
       <c r="F80" t="n">
-        <v>442</v>
+        <v>833</v>
       </c>
       <c r="G80" t="n">
-        <v>39912600</v>
+        <v>19992000</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>279500</v>
+        <v>90300</v>
       </c>
       <c r="F81" t="n">
-        <v>357</v>
+        <v>442</v>
       </c>
       <c r="G81" t="n">
-        <v>99781500</v>
+        <v>39912600</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3072,13 +3072,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>366000</v>
+        <v>279500</v>
       </c>
       <c r="F82" t="n">
-        <v>54</v>
+        <v>357</v>
       </c>
       <c r="G82" t="n">
-        <v>19764000</v>
+        <v>99781500</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3090,12 +3090,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>91000</v>
+        <v>366000</v>
       </c>
       <c r="F83" t="n">
-        <v>659</v>
+        <v>54</v>
       </c>
       <c r="G83" t="n">
-        <v>59969000</v>
+        <v>19764000</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>120100</v>
+        <v>91000</v>
       </c>
       <c r="F84" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="G84" t="n">
-        <v>79986600</v>
+        <v>59969000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3168,13 +3168,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2405</v>
+        <v>120100</v>
       </c>
       <c r="F85" t="n">
-        <v>415800</v>
+        <v>666</v>
       </c>
       <c r="G85" t="n">
-        <v>999999000</v>
+        <v>79986600</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>69000</v>
+        <v>2405</v>
       </c>
       <c r="F86" t="n">
-        <v>579</v>
+        <v>415800</v>
       </c>
       <c r="G86" t="n">
-        <v>39951000</v>
+        <v>999999000</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>42300</v>
+        <v>69000</v>
       </c>
       <c r="F87" t="n">
-        <v>709</v>
+        <v>579</v>
       </c>
       <c r="G87" t="n">
-        <v>29990700</v>
+        <v>39951000</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3250,29 +3250,61 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F88" t="n">
+        <v>709</v>
+      </c>
+      <c r="G88" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E88" t="n">
+      <c r="E89" t="n">
         <v>23350</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F89" t="n">
         <v>856</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G89" t="n">
         <v>19987600</v>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,32 +505,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22900</v>
+        <v>2120</v>
       </c>
       <c r="F3" t="n">
-        <v>1397.6406</v>
+        <v>3453.9051</v>
       </c>
       <c r="G3" t="n">
-        <v>32005969</v>
+        <v>7322278.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,31 +542,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>73600</v>
+        <v>22900</v>
       </c>
       <c r="F4" t="n">
-        <v>299.9614</v>
+        <v>1397.6406</v>
       </c>
       <c r="G4" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>16.09</v>
-      </c>
+        <v>32005969</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,29 +574,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2215</v>
+        <v>73600</v>
       </c>
       <c r="F5" t="n">
-        <v>28224.978</v>
+        <v>299.9614</v>
       </c>
       <c r="G5" t="n">
-        <v>62518326.2</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>43800</v>
+        <v>2215</v>
       </c>
       <c r="F6" t="n">
-        <v>504.0447</v>
+        <v>28224.978</v>
       </c>
       <c r="G6" t="n">
-        <v>22077158.2</v>
+        <v>62518326.2</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,27 +640,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>23650</v>
+        <v>43800</v>
       </c>
       <c r="F7" t="n">
-        <v>451.106</v>
+        <v>504.0447</v>
       </c>
       <c r="G7" t="n">
-        <v>10668656.3</v>
+        <v>22077158.2</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,49 +686,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5730</v>
+        <v>23650</v>
       </c>
       <c r="F8" t="n">
-        <v>3723.7893</v>
+        <v>451.106</v>
       </c>
       <c r="G8" t="n">
-        <v>21337312.7</v>
+        <v>10668656.3</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6080</v>
+        <v>5730</v>
       </c>
       <c r="F9" t="n">
-        <v>3255.5051</v>
+        <v>3723.7893</v>
       </c>
       <c r="G9" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>21337312.7</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,29 +736,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>95200</v>
+        <v>6080</v>
       </c>
       <c r="F10" t="n">
-        <v>221.6088</v>
+        <v>3255.5051</v>
       </c>
       <c r="G10" t="n">
-        <v>21097154.4</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,59 +770,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2205</v>
+        <v>95200</v>
       </c>
       <c r="F11" t="n">
-        <v>52623.2877</v>
+        <v>221.6088</v>
       </c>
       <c r="G11" t="n">
-        <v>116034349.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58700</v>
+        <v>2205</v>
       </c>
       <c r="F12" t="n">
-        <v>357.1039</v>
+        <v>52623.2877</v>
       </c>
       <c r="G12" t="n">
-        <v>20961998.6</v>
+        <v>116034349.3</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,27 +834,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13250</v>
+        <v>58700</v>
       </c>
       <c r="F13" t="n">
-        <v>791.0188000000001</v>
+        <v>357.1039</v>
       </c>
       <c r="G13" t="n">
-        <v>10480999.3</v>
+        <v>20961998.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2360</v>
+        <v>13250</v>
       </c>
       <c r="F14" t="n">
-        <v>66616.5209</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>157214989.3</v>
+        <v>10480999.3</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,31 +898,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>38300</v>
+        <v>2360</v>
       </c>
       <c r="F15" t="n">
-        <v>500.7861</v>
+        <v>66616.5209</v>
       </c>
       <c r="G15" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>157214989.3</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -932,29 +930,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21150</v>
+        <v>38300</v>
       </c>
       <c r="F16" t="n">
-        <v>495.5555</v>
+        <v>500.7861</v>
       </c>
       <c r="G16" t="n">
-        <v>10480999.3</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -964,63 +964,63 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>23650</v>
+        <v>21150</v>
       </c>
       <c r="F17" t="n">
-        <v>832.6201</v>
+        <v>495.5555</v>
       </c>
       <c r="G17" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.28</v>
-      </c>
+        <v>10480999.3</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12310</v>
+        <v>23650</v>
       </c>
       <c r="F18" t="n">
-        <v>2480.1654</v>
+        <v>832.6201</v>
       </c>
       <c r="G18" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1030,24 +1030,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>40650</v>
+        <v>12310</v>
       </c>
       <c r="F19" t="n">
-        <v>751.0661</v>
+        <v>2480.1654</v>
       </c>
       <c r="G19" t="n">
         <v>30530836.4</v>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283500</v>
+        <v>40650</v>
       </c>
       <c r="F20" t="n">
-        <v>71.795</v>
+        <v>751.0661</v>
       </c>
       <c r="G20" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1094,27 +1094,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2390</v>
+        <v>283500</v>
       </c>
       <c r="F21" t="n">
-        <v>42581.3618</v>
+        <v>71.795</v>
       </c>
       <c r="G21" t="n">
-        <v>101769454.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1126,59 +1126,59 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>20450</v>
+        <v>2390</v>
       </c>
       <c r="F22" t="n">
-        <v>995.3003</v>
+        <v>42581.3618</v>
       </c>
       <c r="G22" t="n">
-        <v>20353890.9</v>
+        <v>101769454.6</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>30200</v>
+        <v>20450</v>
       </c>
       <c r="F23" t="n">
-        <v>359.55</v>
+        <v>995.3003</v>
       </c>
       <c r="G23" t="n">
-        <v>10858410.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1190,31 +1190,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208500</v>
+        <v>30200</v>
       </c>
       <c r="F24" t="n">
-        <v>338</v>
+        <v>359.55</v>
       </c>
       <c r="G24" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.97</v>
-      </c>
+        <v>10858410.6</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1224,29 +1222,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17720</v>
+        <v>208500</v>
       </c>
       <c r="F25" t="n">
-        <v>94.9217</v>
+        <v>338</v>
       </c>
       <c r="G25" t="n">
-        <v>1682012.5</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100500</v>
+        <v>17720</v>
       </c>
       <c r="F26" t="n">
-        <v>8.9518</v>
+        <v>94.9217</v>
       </c>
       <c r="G26" t="n">
-        <v>899652.6</v>
+        <v>1682012.5</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,27 +1288,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>11410</v>
+        <v>100500</v>
       </c>
       <c r="F27" t="n">
-        <v>6321.2722</v>
+        <v>8.9518</v>
       </c>
       <c r="G27" t="n">
-        <v>72125715.8</v>
+        <v>899652.6</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,27 +1320,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12880</v>
+        <v>11410</v>
       </c>
       <c r="F28" t="n">
-        <v>713.2027</v>
+        <v>6321.2722</v>
       </c>
       <c r="G28" t="n">
-        <v>9186050.6</v>
+        <v>72125715.8</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>21200</v>
+        <v>12880</v>
       </c>
       <c r="F29" t="n">
-        <v>120.8659</v>
+        <v>713.2027</v>
       </c>
       <c r="G29" t="n">
-        <v>2562357.9</v>
+        <v>9186050.6</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>27700</v>
+        <v>21200</v>
       </c>
       <c r="F30" t="n">
-        <v>161.1835</v>
+        <v>120.8659</v>
       </c>
       <c r="G30" t="n">
-        <v>4464784.2</v>
+        <v>2562357.9</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>21500</v>
+        <v>27700</v>
       </c>
       <c r="F31" t="n">
-        <v>129.2032</v>
+        <v>161.1835</v>
       </c>
       <c r="G31" t="n">
-        <v>2777868.4</v>
+        <v>4464784.2</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>34100</v>
+        <v>21500</v>
       </c>
       <c r="F32" t="n">
-        <v>21.679</v>
+        <v>129.2032</v>
       </c>
       <c r="G32" t="n">
-        <v>739252.6</v>
+        <v>2777868.4</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,27 +1480,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>40850</v>
+        <v>34100</v>
       </c>
       <c r="F33" t="n">
-        <v>123.3915</v>
+        <v>21.679</v>
       </c>
       <c r="G33" t="n">
-        <v>5040542.1</v>
+        <v>739252.6</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308000</v>
+        <v>40850</v>
       </c>
       <c r="F34" t="n">
-        <v>9.1744</v>
+        <v>123.3915</v>
       </c>
       <c r="G34" t="n">
-        <v>2825715.8</v>
+        <v>5040542.1</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6330</v>
+        <v>308000</v>
       </c>
       <c r="F35" t="n">
-        <v>50.5051</v>
+        <v>9.1744</v>
       </c>
       <c r="G35" t="n">
-        <v>319697.4</v>
+        <v>2825715.8</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,27 +1576,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31700</v>
+        <v>6330</v>
       </c>
       <c r="F36" t="n">
-        <v>158.7408</v>
+        <v>50.5051</v>
       </c>
       <c r="G36" t="n">
-        <v>5032084.2</v>
+        <v>319697.4</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>68700</v>
+        <v>31700</v>
       </c>
       <c r="F37" t="n">
-        <v>16.0386</v>
+        <v>158.7408</v>
       </c>
       <c r="G37" t="n">
-        <v>1101852.6</v>
+        <v>5032084.2</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,27 +1640,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>256000</v>
+        <v>68700</v>
       </c>
       <c r="F38" t="n">
-        <v>45.4873</v>
+        <v>16.0386</v>
       </c>
       <c r="G38" t="n">
-        <v>11644736.8</v>
+        <v>1101852.6</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>91100</v>
+        <v>256000</v>
       </c>
       <c r="F39" t="n">
-        <v>19.6174</v>
+        <v>45.4873</v>
       </c>
       <c r="G39" t="n">
-        <v>1787142.1</v>
+        <v>11644736.8</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,27 +1704,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>130900</v>
+        <v>91100</v>
       </c>
       <c r="F40" t="n">
-        <v>89.1437</v>
+        <v>19.6174</v>
       </c>
       <c r="G40" t="n">
-        <v>11668905.3</v>
+        <v>1787142.1</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2400</v>
+        <v>130900</v>
       </c>
       <c r="F41" t="n">
-        <v>32820.1843</v>
+        <v>89.1437</v>
       </c>
       <c r="G41" t="n">
-        <v>78768442.40000001</v>
+        <v>11668905.3</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,27 +1768,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>41150</v>
+        <v>2400</v>
       </c>
       <c r="F42" t="n">
-        <v>38.7861</v>
+        <v>32820.1843</v>
       </c>
       <c r="G42" t="n">
-        <v>1596047.4</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>49450</v>
+        <v>41150</v>
       </c>
       <c r="F43" t="n">
-        <v>83.90349999999999</v>
+        <v>38.7861</v>
       </c>
       <c r="G43" t="n">
-        <v>4149029</v>
+        <v>1596047.4</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1846,13 +1846,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>24750</v>
+        <v>49450</v>
       </c>
       <c r="F44" t="n">
-        <v>23.3799</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>578652.6</v>
+        <v>4149029</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1878,49 +1878,47 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5450</v>
+        <v>24750</v>
       </c>
       <c r="F45" t="n">
-        <v>220.6267</v>
+        <v>23.3799</v>
       </c>
       <c r="G45" t="n">
-        <v>1202415.4</v>
+        <v>578652.6</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>327000</v>
+        <v>5450</v>
       </c>
       <c r="F46" t="n">
-        <v>54</v>
+        <v>220.6267</v>
       </c>
       <c r="G46" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>1202415.4</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1930,59 +1928,61 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5130</v>
+        <v>327000</v>
       </c>
       <c r="F47" t="n">
-        <v>4001.7913</v>
+        <v>54</v>
       </c>
       <c r="G47" t="n">
-        <v>20529189.5</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>27100</v>
+        <v>5130</v>
       </c>
       <c r="F48" t="n">
-        <v>376</v>
+        <v>4001.7913</v>
       </c>
       <c r="G48" t="n">
-        <v>10189600</v>
+        <v>20529189.5</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1994,31 +1994,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>67600</v>
+        <v>27100</v>
       </c>
       <c r="F49" t="n">
-        <v>998</v>
+        <v>376</v>
       </c>
       <c r="G49" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>10189600</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2028,29 +2026,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11900</v>
+        <v>67600</v>
       </c>
       <c r="F50" t="n">
-        <v>856</v>
+        <v>998</v>
       </c>
       <c r="G50" t="n">
-        <v>10186400</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2060,27 +2060,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>29300</v>
+        <v>11900</v>
       </c>
       <c r="F51" t="n">
-        <v>2434</v>
+        <v>856</v>
       </c>
       <c r="G51" t="n">
-        <v>71316200</v>
+        <v>10186400</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2092,27 +2092,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>119300</v>
+        <v>29300</v>
       </c>
       <c r="F52" t="n">
-        <v>171</v>
+        <v>2434</v>
       </c>
       <c r="G52" t="n">
-        <v>20400300</v>
+        <v>71316200</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2138,45 +2138,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2445</v>
+        <v>119300</v>
       </c>
       <c r="F53" t="n">
-        <v>82456</v>
+        <v>171</v>
       </c>
       <c r="G53" t="n">
-        <v>201604920</v>
+        <v>20400300</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>18910</v>
+        <v>2445</v>
       </c>
       <c r="F54" t="n">
-        <v>1068.0212</v>
+        <v>82456</v>
       </c>
       <c r="G54" t="n">
-        <v>20196280</v>
+        <v>201604920</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>32250</v>
+        <v>18910</v>
       </c>
       <c r="F55" t="n">
-        <v>626</v>
+        <v>1068.0212</v>
       </c>
       <c r="G55" t="n">
-        <v>20188500</v>
+        <v>20196280</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2220,31 +2220,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>82500</v>
+        <v>32250</v>
       </c>
       <c r="F56" t="n">
-        <v>204</v>
+        <v>626</v>
       </c>
       <c r="G56" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>20188500</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2254,12 +2252,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2268,49 +2266,51 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>56800</v>
+        <v>82500</v>
       </c>
       <c r="F57" t="n">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="G57" t="n">
-        <v>14654400</v>
+        <v>16830000</v>
       </c>
       <c r="H57" t="n">
-        <v>-17.68</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>83700</v>
+        <v>56800</v>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>258</v>
       </c>
       <c r="G58" t="n">
-        <v>10044000</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2320,27 +2320,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>43650</v>
+        <v>83700</v>
       </c>
       <c r="F59" t="n">
-        <v>462</v>
+        <v>120</v>
       </c>
       <c r="G59" t="n">
-        <v>20166300</v>
+        <v>10044000</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2352,59 +2352,59 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>59700</v>
+        <v>43650</v>
       </c>
       <c r="F60" t="n">
-        <v>169</v>
+        <v>462</v>
       </c>
       <c r="G60" t="n">
-        <v>10089300</v>
+        <v>20166300</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10930</v>
+        <v>59700</v>
       </c>
       <c r="F61" t="n">
-        <v>1833</v>
+        <v>169</v>
       </c>
       <c r="G61" t="n">
-        <v>20034690</v>
+        <v>10089300</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>19850</v>
+        <v>10930</v>
       </c>
       <c r="F62" t="n">
-        <v>505</v>
+        <v>1833</v>
       </c>
       <c r="G62" t="n">
-        <v>10024250</v>
+        <v>20034690</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>26350</v>
+        <v>19850</v>
       </c>
       <c r="F63" t="n">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="G63" t="n">
-        <v>10013000</v>
+        <v>10024250</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2480,31 +2480,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>23500</v>
+        <v>26350</v>
       </c>
       <c r="F64" t="n">
-        <v>833</v>
+        <v>380</v>
       </c>
       <c r="G64" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10013000</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2514,29 +2512,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>85200</v>
+        <v>23500</v>
       </c>
       <c r="F65" t="n">
-        <v>118</v>
+        <v>833</v>
       </c>
       <c r="G65" t="n">
-        <v>10053600</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2546,27 +2546,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>63400</v>
+        <v>85200</v>
       </c>
       <c r="F66" t="n">
-        <v>316</v>
+        <v>118</v>
       </c>
       <c r="G66" t="n">
-        <v>20034400</v>
+        <v>10053600</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2578,27 +2578,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>110300</v>
+        <v>63400</v>
       </c>
       <c r="F67" t="n">
-        <v>91</v>
+        <v>316</v>
       </c>
       <c r="G67" t="n">
-        <v>10037300</v>
+        <v>20034400</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,45 +2624,45 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>66100</v>
+        <v>110300</v>
       </c>
       <c r="F68" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="G68" t="n">
-        <v>10047200</v>
+        <v>10037300</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>25800</v>
+        <v>66100</v>
       </c>
       <c r="F69" t="n">
-        <v>2713</v>
+        <v>152</v>
       </c>
       <c r="G69" t="n">
-        <v>69995400</v>
+        <v>10047200</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>206500</v>
+        <v>25800</v>
       </c>
       <c r="F70" t="n">
-        <v>338</v>
+        <v>2713</v>
       </c>
       <c r="G70" t="n">
-        <v>69797000</v>
+        <v>69995400</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>70100</v>
+        <v>206500</v>
       </c>
       <c r="F71" t="n">
-        <v>998</v>
+        <v>338</v>
       </c>
       <c r="G71" t="n">
-        <v>69959800</v>
+        <v>69797000</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>93300</v>
+        <v>70100</v>
       </c>
       <c r="F72" t="n">
-        <v>214</v>
+        <v>998</v>
       </c>
       <c r="G72" t="n">
-        <v>19966200</v>
+        <v>69959800</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2784,13 +2784,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>11300</v>
+        <v>93300</v>
       </c>
       <c r="F73" t="n">
-        <v>4424</v>
+        <v>214</v>
       </c>
       <c r="G73" t="n">
-        <v>49991200</v>
+        <v>19966200</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>19740</v>
+        <v>11300</v>
       </c>
       <c r="F74" t="n">
-        <v>2532</v>
+        <v>4424</v>
       </c>
       <c r="G74" t="n">
-        <v>49981680</v>
+        <v>49991200</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F75" t="n">
-        <v>2385</v>
+        <v>2532</v>
       </c>
       <c r="G75" t="n">
-        <v>59982750</v>
+        <v>49981680</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2866,12 +2866,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>22050</v>
+        <v>25150</v>
       </c>
       <c r="F76" t="n">
-        <v>2267</v>
+        <v>2385</v>
       </c>
       <c r="G76" t="n">
-        <v>49987350</v>
+        <v>59982750</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2912,13 +2912,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>43150</v>
+        <v>22050</v>
       </c>
       <c r="F77" t="n">
-        <v>1390</v>
+        <v>2267</v>
       </c>
       <c r="G77" t="n">
-        <v>59978500</v>
+        <v>49987350</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>310000</v>
+        <v>43150</v>
       </c>
       <c r="F78" t="n">
-        <v>225</v>
+        <v>1390</v>
       </c>
       <c r="G78" t="n">
-        <v>69750000</v>
+        <v>59978500</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6240</v>
+        <v>310000</v>
       </c>
       <c r="F79" t="n">
-        <v>3205</v>
+        <v>225</v>
       </c>
       <c r="G79" t="n">
-        <v>19999200</v>
+        <v>69750000</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3008,13 +3008,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>24000</v>
+        <v>6240</v>
       </c>
       <c r="F80" t="n">
-        <v>833</v>
+        <v>3205</v>
       </c>
       <c r="G80" t="n">
-        <v>19992000</v>
+        <v>19999200</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>90300</v>
+        <v>24000</v>
       </c>
       <c r="F81" t="n">
-        <v>442</v>
+        <v>833</v>
       </c>
       <c r="G81" t="n">
-        <v>39912600</v>
+        <v>19992000</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3072,13 +3072,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>279500</v>
+        <v>90300</v>
       </c>
       <c r="F82" t="n">
-        <v>357</v>
+        <v>442</v>
       </c>
       <c r="G82" t="n">
-        <v>99781500</v>
+        <v>39912600</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3090,12 +3090,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>366000</v>
+        <v>279500</v>
       </c>
       <c r="F83" t="n">
-        <v>54</v>
+        <v>357</v>
       </c>
       <c r="G83" t="n">
-        <v>19764000</v>
+        <v>99781500</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>91000</v>
+        <v>366000</v>
       </c>
       <c r="F84" t="n">
-        <v>659</v>
+        <v>54</v>
       </c>
       <c r="G84" t="n">
-        <v>59969000</v>
+        <v>19764000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3168,13 +3168,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>120100</v>
+        <v>91000</v>
       </c>
       <c r="F85" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="G85" t="n">
-        <v>79986600</v>
+        <v>59969000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2405</v>
+        <v>120100</v>
       </c>
       <c r="F86" t="n">
-        <v>415800</v>
+        <v>666</v>
       </c>
       <c r="G86" t="n">
-        <v>999999000</v>
+        <v>79986600</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>69000</v>
+        <v>2405</v>
       </c>
       <c r="F87" t="n">
-        <v>579</v>
+        <v>415800</v>
       </c>
       <c r="G87" t="n">
-        <v>39951000</v>
+        <v>999999000</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3250,12 +3250,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3264,13 +3264,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>42300</v>
+        <v>69000</v>
       </c>
       <c r="F88" t="n">
-        <v>709</v>
+        <v>579</v>
       </c>
       <c r="G88" t="n">
-        <v>29990700</v>
+        <v>39951000</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3282,29 +3282,61 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F89" t="n">
+        <v>709</v>
+      </c>
+      <c r="G89" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E89" t="n">
+      <c r="E90" t="n">
         <v>23350</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F90" t="n">
         <v>856</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G90" t="n">
         <v>19987600</v>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,113 +473,115 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2120</v>
+        <v>44600</v>
       </c>
       <c r="F2" t="n">
-        <v>63879.7502</v>
+        <v>1359.3974</v>
       </c>
       <c r="G2" t="n">
-        <v>135425070.4</v>
+        <v>60629123.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2120</v>
+        <v>20300</v>
       </c>
       <c r="F3" t="n">
-        <v>3453.9051</v>
+        <v>1162.9429</v>
       </c>
       <c r="G3" t="n">
-        <v>7322278.8</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>23607739.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22900</v>
+        <v>13160</v>
       </c>
       <c r="F4" t="n">
-        <v>1397.6406</v>
+        <v>767.846</v>
       </c>
       <c r="G4" t="n">
-        <v>32005969</v>
+        <v>10104853.9</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,64 +590,66 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73600</v>
+        <v>49050</v>
       </c>
       <c r="F5" t="n">
-        <v>299.9614</v>
+        <v>357.1039</v>
       </c>
       <c r="G5" t="n">
-        <v>22077158.2</v>
+        <v>17515946</v>
       </c>
       <c r="H5" t="n">
-        <v>16.09</v>
+        <v>-16.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2215</v>
+        <v>37100</v>
       </c>
       <c r="F6" t="n">
-        <v>28224.978</v>
+        <v>604.321</v>
       </c>
       <c r="G6" t="n">
-        <v>62518326.2</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,118 +658,116 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43800</v>
+        <v>123700</v>
       </c>
       <c r="F7" t="n">
-        <v>504.0447</v>
+        <v>490.1303</v>
       </c>
       <c r="G7" t="n">
-        <v>22077158.2</v>
+        <v>60629123.5</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>23650</v>
+        <v>41150</v>
       </c>
       <c r="F8" t="n">
-        <v>451.106</v>
+        <v>491.1229</v>
       </c>
       <c r="G8" t="n">
-        <v>10668656.3</v>
+        <v>20209707.8</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5730</v>
+        <v>31500</v>
       </c>
       <c r="F9" t="n">
-        <v>3723.7893</v>
+        <v>320.789</v>
       </c>
       <c r="G9" t="n">
-        <v>21337312.7</v>
+        <v>10104853.9</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6080</v>
+        <v>228500</v>
       </c>
       <c r="F10" t="n">
-        <v>3255.5051</v>
+        <v>88.4451</v>
       </c>
       <c r="G10" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>20209707.8</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -780,196 +782,198 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>95200</v>
+        <v>88500</v>
       </c>
       <c r="F11" t="n">
-        <v>221.6088</v>
+        <v>900.2261</v>
       </c>
       <c r="G11" t="n">
-        <v>21097154.4</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2205</v>
+        <v>130100</v>
       </c>
       <c r="F12" t="n">
-        <v>52623.2877</v>
+        <v>314.8563</v>
       </c>
       <c r="G12" t="n">
-        <v>116034349.3</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>58700</v>
+        <v>2325</v>
       </c>
       <c r="F13" t="n">
-        <v>357.1039</v>
+        <v>21730.8686</v>
       </c>
       <c r="G13" t="n">
-        <v>20961998.6</v>
+        <v>50524269.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13250</v>
+        <v>64700</v>
       </c>
       <c r="F14" t="n">
-        <v>791.0188000000001</v>
+        <v>468.5404</v>
       </c>
       <c r="G14" t="n">
-        <v>10480999.3</v>
+        <v>30314561.7</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2360</v>
+        <v>4670</v>
       </c>
       <c r="F15" t="n">
-        <v>66616.5209</v>
+        <v>6491.3408</v>
       </c>
       <c r="G15" t="n">
-        <v>157214989.3</v>
+        <v>30314561.7</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38300</v>
+        <v>2120</v>
       </c>
       <c r="F16" t="n">
-        <v>500.7861</v>
+        <v>63879.7502</v>
       </c>
       <c r="G16" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>135425070.4</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -978,160 +982,160 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21150</v>
+        <v>2120</v>
       </c>
       <c r="F17" t="n">
-        <v>495.5555</v>
+        <v>3453.9051</v>
       </c>
       <c r="G17" t="n">
-        <v>10480999.3</v>
+        <v>7322278.8</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>23650</v>
+        <v>22900</v>
       </c>
       <c r="F18" t="n">
-        <v>832.6201</v>
+        <v>1397.6406</v>
       </c>
       <c r="G18" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.28</v>
-      </c>
+        <v>32005969</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12310</v>
+        <v>73600</v>
       </c>
       <c r="F19" t="n">
-        <v>2480.1654</v>
+        <v>299.9614</v>
       </c>
       <c r="G19" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>40650</v>
+        <v>2215</v>
       </c>
       <c r="F20" t="n">
-        <v>751.0661</v>
+        <v>28224.978</v>
       </c>
       <c r="G20" t="n">
-        <v>30530836.4</v>
+        <v>62518326.2</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>283500</v>
+        <v>43800</v>
       </c>
       <c r="F21" t="n">
-        <v>71.795</v>
+        <v>504.0447</v>
       </c>
       <c r="G21" t="n">
-        <v>20353890.9</v>
+        <v>22077158.2</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1140,374 +1144,378 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2390</v>
+        <v>23650</v>
       </c>
       <c r="F22" t="n">
-        <v>42581.3618</v>
+        <v>451.106</v>
       </c>
       <c r="G22" t="n">
-        <v>101769454.6</v>
+        <v>10668656.3</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20450</v>
+        <v>5730</v>
       </c>
       <c r="F23" t="n">
-        <v>995.3003</v>
+        <v>3723.7893</v>
       </c>
       <c r="G23" t="n">
-        <v>20353890.9</v>
+        <v>21337312.7</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>30200</v>
+        <v>6080</v>
       </c>
       <c r="F24" t="n">
-        <v>359.55</v>
+        <v>3255.5051</v>
       </c>
       <c r="G24" t="n">
-        <v>10858410.6</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208500</v>
+        <v>95200</v>
       </c>
       <c r="F25" t="n">
-        <v>338</v>
+        <v>221.6088</v>
       </c>
       <c r="G25" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.97</v>
-      </c>
+        <v>21097154.4</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>17720</v>
+        <v>2205</v>
       </c>
       <c r="F26" t="n">
-        <v>94.9217</v>
+        <v>52623.2877</v>
       </c>
       <c r="G26" t="n">
-        <v>1682012.5</v>
+        <v>116034349.3</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100500</v>
+        <v>58700</v>
       </c>
       <c r="F27" t="n">
-        <v>8.9518</v>
+        <v>357.1039</v>
       </c>
       <c r="G27" t="n">
-        <v>899652.6</v>
+        <v>20961998.6</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>11410</v>
+        <v>13250</v>
       </c>
       <c r="F28" t="n">
-        <v>6321.2722</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>72125715.8</v>
+        <v>10480999.3</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>12880</v>
+        <v>2360</v>
       </c>
       <c r="F29" t="n">
-        <v>713.2027</v>
+        <v>66616.5209</v>
       </c>
       <c r="G29" t="n">
-        <v>9186050.6</v>
+        <v>157214989.3</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>21200</v>
+        <v>38300</v>
       </c>
       <c r="F30" t="n">
-        <v>120.8659</v>
+        <v>500.7861</v>
       </c>
       <c r="G30" t="n">
-        <v>2562357.9</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>27700</v>
+        <v>21150</v>
       </c>
       <c r="F31" t="n">
-        <v>161.1835</v>
+        <v>495.5555</v>
       </c>
       <c r="G31" t="n">
-        <v>4464784.2</v>
+        <v>10480999.3</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>21500</v>
+        <v>23650</v>
       </c>
       <c r="F32" t="n">
-        <v>129.2032</v>
+        <v>832.6201</v>
       </c>
       <c r="G32" t="n">
-        <v>2777868.4</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>34100</v>
+        <v>12310</v>
       </c>
       <c r="F33" t="n">
-        <v>21.679</v>
+        <v>2480.1654</v>
       </c>
       <c r="G33" t="n">
-        <v>739252.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1522,24 +1530,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>40850</v>
+        <v>40650</v>
       </c>
       <c r="F34" t="n">
-        <v>123.3915</v>
+        <v>751.0661</v>
       </c>
       <c r="G34" t="n">
-        <v>5040542.1</v>
+        <v>30530836.4</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1554,34 +1562,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308000</v>
+        <v>283500</v>
       </c>
       <c r="F35" t="n">
-        <v>9.1744</v>
+        <v>71.795</v>
       </c>
       <c r="G35" t="n">
-        <v>2825715.8</v>
+        <v>20353890.9</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,45 +1598,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6330</v>
+        <v>2390</v>
       </c>
       <c r="F36" t="n">
-        <v>50.5051</v>
+        <v>42581.3618</v>
       </c>
       <c r="G36" t="n">
-        <v>319697.4</v>
+        <v>101769454.6</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>31700</v>
+        <v>20450</v>
       </c>
       <c r="F37" t="n">
-        <v>158.7408</v>
+        <v>995.3003</v>
       </c>
       <c r="G37" t="n">
-        <v>5032084.2</v>
+        <v>20353890.9</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,12 +1648,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,13 +1662,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>68700</v>
+        <v>30200</v>
       </c>
       <c r="F38" t="n">
-        <v>16.0386</v>
+        <v>359.55</v>
       </c>
       <c r="G38" t="n">
-        <v>1101852.6</v>
+        <v>10858410.6</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,29 +1680,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>256000</v>
+        <v>208500</v>
       </c>
       <c r="F39" t="n">
-        <v>45.4873</v>
+        <v>338</v>
       </c>
       <c r="G39" t="n">
-        <v>11644736.8</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1704,12 +1714,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1718,13 +1728,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>91100</v>
+        <v>17720</v>
       </c>
       <c r="F40" t="n">
-        <v>19.6174</v>
+        <v>94.9217</v>
       </c>
       <c r="G40" t="n">
-        <v>1787142.1</v>
+        <v>1682012.5</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,12 +1746,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1750,13 +1760,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>130900</v>
+        <v>100500</v>
       </c>
       <c r="F41" t="n">
-        <v>89.1437</v>
+        <v>8.9518</v>
       </c>
       <c r="G41" t="n">
-        <v>11668905.3</v>
+        <v>899652.6</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,27 +1778,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2400</v>
+        <v>11410</v>
       </c>
       <c r="F42" t="n">
-        <v>32820.1843</v>
+        <v>6321.2722</v>
       </c>
       <c r="G42" t="n">
-        <v>78768442.40000001</v>
+        <v>72125715.8</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1800,27 +1810,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>41150</v>
+        <v>12880</v>
       </c>
       <c r="F43" t="n">
-        <v>38.7861</v>
+        <v>713.2027</v>
       </c>
       <c r="G43" t="n">
-        <v>1596047.4</v>
+        <v>9186050.6</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1832,12 +1842,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1846,13 +1856,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>49450</v>
+        <v>21200</v>
       </c>
       <c r="F44" t="n">
-        <v>83.90349999999999</v>
+        <v>120.8659</v>
       </c>
       <c r="G44" t="n">
-        <v>4149029</v>
+        <v>2562357.9</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1864,12 +1874,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1878,13 +1888,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>24750</v>
+        <v>27700</v>
       </c>
       <c r="F45" t="n">
-        <v>23.3799</v>
+        <v>161.1835</v>
       </c>
       <c r="G45" t="n">
-        <v>578652.6</v>
+        <v>4464784.2</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1896,110 +1906,108 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5450</v>
+        <v>21500</v>
       </c>
       <c r="F46" t="n">
-        <v>220.6267</v>
+        <v>129.2032</v>
       </c>
       <c r="G46" t="n">
-        <v>1202415.4</v>
+        <v>2777868.4</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>327000</v>
+        <v>34100</v>
       </c>
       <c r="F47" t="n">
-        <v>54</v>
+        <v>21.679</v>
       </c>
       <c r="G47" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>739252.6</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5130</v>
+        <v>40850</v>
       </c>
       <c r="F48" t="n">
-        <v>4001.7913</v>
+        <v>123.3915</v>
       </c>
       <c r="G48" t="n">
-        <v>20529189.5</v>
+        <v>5040542.1</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2008,324 +2016,318 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>27100</v>
+        <v>308000</v>
       </c>
       <c r="F49" t="n">
-        <v>376</v>
+        <v>9.1744</v>
       </c>
       <c r="G49" t="n">
-        <v>10189600</v>
+        <v>2825715.8</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>67600</v>
+        <v>6330</v>
       </c>
       <c r="F50" t="n">
-        <v>998</v>
+        <v>50.5051</v>
       </c>
       <c r="G50" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>319697.4</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11900</v>
+        <v>31700</v>
       </c>
       <c r="F51" t="n">
-        <v>856</v>
+        <v>158.7408</v>
       </c>
       <c r="G51" t="n">
-        <v>10186400</v>
+        <v>5032084.2</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>29300</v>
+        <v>68700</v>
       </c>
       <c r="F52" t="n">
-        <v>2434</v>
+        <v>16.0386</v>
       </c>
       <c r="G52" t="n">
-        <v>71316200</v>
+        <v>1101852.6</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>119300</v>
+        <v>256000</v>
       </c>
       <c r="F53" t="n">
-        <v>171</v>
+        <v>45.4873</v>
       </c>
       <c r="G53" t="n">
-        <v>20400300</v>
+        <v>11644736.8</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2445</v>
+        <v>91100</v>
       </c>
       <c r="F54" t="n">
-        <v>82456</v>
+        <v>19.6174</v>
       </c>
       <c r="G54" t="n">
-        <v>201604920</v>
+        <v>1787142.1</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>18910</v>
+        <v>130900</v>
       </c>
       <c r="F55" t="n">
-        <v>1068.0212</v>
+        <v>89.1437</v>
       </c>
       <c r="G55" t="n">
-        <v>20196280</v>
+        <v>11668905.3</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>32250</v>
+        <v>2400</v>
       </c>
       <c r="F56" t="n">
-        <v>626</v>
+        <v>32820.1843</v>
       </c>
       <c r="G56" t="n">
-        <v>20188500</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>82500</v>
+        <v>41150</v>
       </c>
       <c r="F57" t="n">
-        <v>204</v>
+        <v>38.7861</v>
       </c>
       <c r="G57" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>1596047.4</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>56800</v>
+        <v>49450</v>
       </c>
       <c r="F58" t="n">
-        <v>258</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>4149029</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2334,126 +2336,128 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>83700</v>
+        <v>24750</v>
       </c>
       <c r="F59" t="n">
-        <v>120</v>
+        <v>23.3799</v>
       </c>
       <c r="G59" t="n">
-        <v>10044000</v>
+        <v>578652.6</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>43650</v>
+        <v>5450</v>
       </c>
       <c r="F60" t="n">
-        <v>462</v>
+        <v>220.6267</v>
       </c>
       <c r="G60" t="n">
-        <v>20166300</v>
+        <v>1202415.4</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59700</v>
+        <v>327000</v>
       </c>
       <c r="F61" t="n">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="G61" t="n">
-        <v>10089300</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10930</v>
+        <v>5130</v>
       </c>
       <c r="F62" t="n">
-        <v>1833</v>
+        <v>4001.7913</v>
       </c>
       <c r="G62" t="n">
-        <v>20034690</v>
+        <v>20529189.5</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2462,160 +2466,160 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>19850</v>
+        <v>27100</v>
       </c>
       <c r="F63" t="n">
-        <v>505</v>
+        <v>376</v>
       </c>
       <c r="G63" t="n">
-        <v>10024250</v>
+        <v>10189600</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>26350</v>
+        <v>67600</v>
       </c>
       <c r="F64" t="n">
-        <v>380</v>
+        <v>998</v>
       </c>
       <c r="G64" t="n">
-        <v>10013000</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>23500</v>
+        <v>11900</v>
       </c>
       <c r="F65" t="n">
-        <v>833</v>
+        <v>856</v>
       </c>
       <c r="G65" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10186400</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>85200</v>
+        <v>29300</v>
       </c>
       <c r="F66" t="n">
-        <v>118</v>
+        <v>2434</v>
       </c>
       <c r="G66" t="n">
-        <v>10053600</v>
+        <v>71316200</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>63400</v>
+        <v>119300</v>
       </c>
       <c r="F67" t="n">
-        <v>316</v>
+        <v>171</v>
       </c>
       <c r="G67" t="n">
-        <v>20034400</v>
+        <v>20400300</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,62 +2628,62 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>110300</v>
+        <v>2445</v>
       </c>
       <c r="F68" t="n">
-        <v>91</v>
+        <v>82456</v>
       </c>
       <c r="G68" t="n">
-        <v>10037300</v>
+        <v>201604920</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>66100</v>
+        <v>18910</v>
       </c>
       <c r="F69" t="n">
-        <v>152</v>
+        <v>1068.0212</v>
       </c>
       <c r="G69" t="n">
-        <v>10047200</v>
+        <v>20196280</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2688,126 +2692,130 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>25800</v>
+        <v>32250</v>
       </c>
       <c r="F70" t="n">
-        <v>2713</v>
+        <v>626</v>
       </c>
       <c r="G70" t="n">
-        <v>69995400</v>
+        <v>20188500</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>206500</v>
+        <v>82500</v>
       </c>
       <c r="F71" t="n">
-        <v>338</v>
+        <v>204</v>
       </c>
       <c r="G71" t="n">
-        <v>69797000</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>70100</v>
+        <v>56800</v>
       </c>
       <c r="F72" t="n">
-        <v>998</v>
+        <v>258</v>
       </c>
       <c r="G72" t="n">
-        <v>69959800</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>93300</v>
+        <v>83700</v>
       </c>
       <c r="F73" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="G73" t="n">
-        <v>19966200</v>
+        <v>10044000</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2816,222 +2824,224 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>11300</v>
+        <v>43650</v>
       </c>
       <c r="F74" t="n">
-        <v>4424</v>
+        <v>462</v>
       </c>
       <c r="G74" t="n">
-        <v>49991200</v>
+        <v>20166300</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>19740</v>
+        <v>59700</v>
       </c>
       <c r="F75" t="n">
-        <v>2532</v>
+        <v>169</v>
       </c>
       <c r="G75" t="n">
-        <v>49981680</v>
+        <v>10089300</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>25150</v>
+        <v>10930</v>
       </c>
       <c r="F76" t="n">
-        <v>2385</v>
+        <v>1833</v>
       </c>
       <c r="G76" t="n">
-        <v>59982750</v>
+        <v>20034690</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>22050</v>
+        <v>19850</v>
       </c>
       <c r="F77" t="n">
-        <v>2267</v>
+        <v>505</v>
       </c>
       <c r="G77" t="n">
-        <v>49987350</v>
+        <v>10024250</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>43150</v>
+        <v>26350</v>
       </c>
       <c r="F78" t="n">
-        <v>1390</v>
+        <v>380</v>
       </c>
       <c r="G78" t="n">
-        <v>59978500</v>
+        <v>10013000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>310000</v>
+        <v>23500</v>
       </c>
       <c r="F79" t="n">
-        <v>225</v>
+        <v>833</v>
       </c>
       <c r="G79" t="n">
-        <v>69750000</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6240</v>
+        <v>85200</v>
       </c>
       <c r="F80" t="n">
-        <v>3205</v>
+        <v>118</v>
       </c>
       <c r="G80" t="n">
-        <v>19999200</v>
+        <v>10053600</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3040,77 +3050,77 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>24000</v>
+        <v>63400</v>
       </c>
       <c r="F81" t="n">
-        <v>833</v>
+        <v>316</v>
       </c>
       <c r="G81" t="n">
-        <v>19992000</v>
+        <v>20034400</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>90300</v>
+        <v>110300</v>
       </c>
       <c r="F82" t="n">
-        <v>442</v>
+        <v>91</v>
       </c>
       <c r="G82" t="n">
-        <v>39912600</v>
+        <v>10037300</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>279500</v>
+        <v>66100</v>
       </c>
       <c r="F83" t="n">
-        <v>357</v>
+        <v>152</v>
       </c>
       <c r="G83" t="n">
-        <v>99781500</v>
+        <v>10047200</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3122,12 +3132,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3136,13 +3146,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>366000</v>
+        <v>25800</v>
       </c>
       <c r="F84" t="n">
-        <v>54</v>
+        <v>2713</v>
       </c>
       <c r="G84" t="n">
-        <v>19764000</v>
+        <v>69995400</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3154,12 +3164,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3168,13 +3178,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>91000</v>
+        <v>206500</v>
       </c>
       <c r="F85" t="n">
-        <v>659</v>
+        <v>338</v>
       </c>
       <c r="G85" t="n">
-        <v>59969000</v>
+        <v>69797000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3186,12 +3196,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3200,13 +3210,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>120100</v>
+        <v>70100</v>
       </c>
       <c r="F86" t="n">
-        <v>666</v>
+        <v>998</v>
       </c>
       <c r="G86" t="n">
-        <v>79986600</v>
+        <v>69959800</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3218,12 +3228,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3232,13 +3242,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2405</v>
+        <v>93300</v>
       </c>
       <c r="F87" t="n">
-        <v>415800</v>
+        <v>214</v>
       </c>
       <c r="G87" t="n">
-        <v>999999000</v>
+        <v>19966200</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3250,12 +3260,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3264,13 +3274,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>69000</v>
+        <v>11300</v>
       </c>
       <c r="F88" t="n">
-        <v>579</v>
+        <v>4424</v>
       </c>
       <c r="G88" t="n">
-        <v>39951000</v>
+        <v>49991200</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3282,12 +3292,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3296,13 +3306,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>42300</v>
+        <v>19740</v>
       </c>
       <c r="F89" t="n">
-        <v>709</v>
+        <v>2532</v>
       </c>
       <c r="G89" t="n">
-        <v>29990700</v>
+        <v>49981680</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3314,29 +3324,477 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>25150</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2385</v>
+      </c>
+      <c r="G90" t="n">
+        <v>59982750</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>091580</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>22050</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2267</v>
+      </c>
+      <c r="G91" t="n">
+        <v>49987350</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>107640</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>43150</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G92" t="n">
+        <v>59978500</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>108490</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>310000</v>
+      </c>
+      <c r="F93" t="n">
+        <v>225</v>
+      </c>
+      <c r="G93" t="n">
+        <v>69750000</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>티씨머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>125020</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6240</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3205</v>
+      </c>
+      <c r="G94" t="n">
+        <v>19999200</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>138080</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F95" t="n">
+        <v>833</v>
+      </c>
+      <c r="G95" t="n">
+        <v>19992000</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>141080</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>90300</v>
+      </c>
+      <c r="F96" t="n">
+        <v>442</v>
+      </c>
+      <c r="G96" t="n">
+        <v>39912600</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>279500</v>
+      </c>
+      <c r="F97" t="n">
+        <v>357</v>
+      </c>
+      <c r="G97" t="n">
+        <v>99781500</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F98" t="n">
+        <v>54</v>
+      </c>
+      <c r="G98" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F99" t="n">
+        <v>659</v>
+      </c>
+      <c r="G99" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F100" t="n">
+        <v>666</v>
+      </c>
+      <c r="G100" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F101" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G101" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F102" t="n">
+        <v>579</v>
+      </c>
+      <c r="G102" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F103" t="n">
+        <v>709</v>
+      </c>
+      <c r="G103" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E90" t="n">
+      <c r="E104" t="n">
         <v>23350</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F104" t="n">
         <v>856</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G104" t="n">
         <v>19987600</v>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,83 +473,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>44600</v>
+        <v>32350</v>
       </c>
       <c r="F2" t="n">
-        <v>1359.3974</v>
+        <v>314.5779</v>
       </c>
       <c r="G2" t="n">
-        <v>60629123.5</v>
+        <v>10176595.1</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20300</v>
+        <v>13650</v>
       </c>
       <c r="F3" t="n">
-        <v>1162.9429</v>
+        <v>745.5381</v>
       </c>
       <c r="G3" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7.9</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,245 +556,241 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13160</v>
+        <v>31950</v>
       </c>
       <c r="F4" t="n">
-        <v>767.846</v>
+        <v>318.5163</v>
       </c>
       <c r="G4" t="n">
-        <v>10104853.9</v>
+        <v>10176595.1</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49050</v>
+        <v>250500</v>
       </c>
       <c r="F5" t="n">
-        <v>357.1039</v>
+        <v>81.2503</v>
       </c>
       <c r="G5" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>37100</v>
+        <v>14100</v>
       </c>
       <c r="F6" t="n">
-        <v>604.321</v>
+        <v>1443.4887</v>
       </c>
       <c r="G6" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>15.04</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>123700</v>
+        <v>31300</v>
       </c>
       <c r="F7" t="n">
-        <v>490.1303</v>
+        <v>1954.4702</v>
       </c>
       <c r="G7" t="n">
-        <v>60629123.5</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>41150</v>
+        <v>2355</v>
       </c>
       <c r="F8" t="n">
-        <v>491.1229</v>
+        <v>65496.7248</v>
       </c>
       <c r="G8" t="n">
-        <v>20209707.8</v>
+        <v>154244786.8</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31500</v>
+        <v>15810</v>
       </c>
       <c r="F9" t="n">
-        <v>320.789</v>
+        <v>5149.4473</v>
       </c>
       <c r="G9" t="n">
-        <v>10104853.9</v>
+        <v>81412761.09999999</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228500</v>
+        <v>56700</v>
       </c>
       <c r="F10" t="n">
-        <v>88.4451</v>
+        <v>179.4814</v>
       </c>
       <c r="G10" t="n">
-        <v>20209707.8</v>
+        <v>10176595.1</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>88500</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="n">
-        <v>900.2261</v>
+        <v>4367.6374</v>
       </c>
       <c r="G11" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -806,31 +800,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>130100</v>
+        <v>44600</v>
       </c>
       <c r="F12" t="n">
-        <v>314.8563</v>
+        <v>1359.3974</v>
       </c>
       <c r="G12" t="n">
-        <v>40962809.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.33</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -840,29 +832,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2325</v>
+        <v>20300</v>
       </c>
       <c r="F13" t="n">
-        <v>21730.8686</v>
+        <v>1162.9429</v>
       </c>
       <c r="G13" t="n">
-        <v>50524269.6</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>23607739.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -872,27 +866,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>64700</v>
+        <v>13160</v>
       </c>
       <c r="F14" t="n">
-        <v>468.5404</v>
+        <v>767.846</v>
       </c>
       <c r="G14" t="n">
-        <v>30314561.7</v>
+        <v>10104853.9</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -904,358 +898,362 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4670</v>
+        <v>49050</v>
       </c>
       <c r="F15" t="n">
-        <v>6491.3408</v>
+        <v>357.1039</v>
       </c>
       <c r="G15" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2120</v>
+        <v>37100</v>
       </c>
       <c r="F16" t="n">
-        <v>63879.7502</v>
+        <v>604.321</v>
       </c>
       <c r="G16" t="n">
-        <v>135425070.4</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2120</v>
+        <v>123700</v>
       </c>
       <c r="F17" t="n">
-        <v>3453.9051</v>
+        <v>490.1303</v>
       </c>
       <c r="G17" t="n">
-        <v>7322278.8</v>
+        <v>60629123.5</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>22900</v>
+        <v>41150</v>
       </c>
       <c r="F18" t="n">
-        <v>1397.6406</v>
+        <v>491.1229</v>
       </c>
       <c r="G18" t="n">
-        <v>32005969</v>
+        <v>20209707.8</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>73600</v>
+        <v>31500</v>
       </c>
       <c r="F19" t="n">
-        <v>299.9614</v>
+        <v>320.789</v>
       </c>
       <c r="G19" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16.09</v>
-      </c>
+        <v>10104853.9</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2215</v>
+        <v>228500</v>
       </c>
       <c r="F20" t="n">
-        <v>28224.978</v>
+        <v>88.4451</v>
       </c>
       <c r="G20" t="n">
-        <v>62518326.2</v>
+        <v>20209707.8</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>43800</v>
+        <v>88500</v>
       </c>
       <c r="F21" t="n">
-        <v>504.0447</v>
+        <v>900.2261</v>
       </c>
       <c r="G21" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>23650</v>
+        <v>130100</v>
       </c>
       <c r="F22" t="n">
-        <v>451.106</v>
+        <v>314.8563</v>
       </c>
       <c r="G22" t="n">
-        <v>10668656.3</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5730</v>
+        <v>2325</v>
       </c>
       <c r="F23" t="n">
-        <v>3723.7893</v>
+        <v>21730.8686</v>
       </c>
       <c r="G23" t="n">
-        <v>21337312.7</v>
+        <v>50524269.6</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6080</v>
+        <v>64700</v>
       </c>
       <c r="F24" t="n">
-        <v>3255.5051</v>
+        <v>468.5404</v>
       </c>
       <c r="G24" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>30314561.7</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>95200</v>
+        <v>4670</v>
       </c>
       <c r="F25" t="n">
-        <v>221.6088</v>
+        <v>6491.3408</v>
       </c>
       <c r="G25" t="n">
-        <v>21097154.4</v>
+        <v>30314561.7</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1274,226 +1272,224 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2205</v>
+        <v>2120</v>
       </c>
       <c r="F26" t="n">
-        <v>52623.2877</v>
+        <v>63879.7502</v>
       </c>
       <c r="G26" t="n">
-        <v>116034349.3</v>
+        <v>135425070.4</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>58700</v>
+        <v>2120</v>
       </c>
       <c r="F27" t="n">
-        <v>357.1039</v>
+        <v>3453.9051</v>
       </c>
       <c r="G27" t="n">
-        <v>20961998.6</v>
+        <v>7322278.8</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13250</v>
+        <v>22900</v>
       </c>
       <c r="F28" t="n">
-        <v>791.0188000000001</v>
+        <v>1397.6406</v>
       </c>
       <c r="G28" t="n">
-        <v>10480999.3</v>
+        <v>32005969</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2360</v>
+        <v>73600</v>
       </c>
       <c r="F29" t="n">
-        <v>66616.5209</v>
+        <v>299.9614</v>
       </c>
       <c r="G29" t="n">
-        <v>157214989.3</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>38300</v>
+        <v>2215</v>
       </c>
       <c r="F30" t="n">
-        <v>500.7861</v>
+        <v>28224.978</v>
       </c>
       <c r="G30" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>62518326.2</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>21150</v>
+        <v>43800</v>
       </c>
       <c r="F31" t="n">
-        <v>495.5555</v>
+        <v>504.0447</v>
       </c>
       <c r="G31" t="n">
-        <v>10480999.3</v>
+        <v>22077158.2</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>23650</v>
       </c>
       <c r="F32" t="n">
-        <v>832.6201</v>
+        <v>451.106</v>
       </c>
       <c r="G32" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.28</v>
-      </c>
+        <v>10668656.3</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1502,84 +1498,86 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12310</v>
+        <v>5730</v>
       </c>
       <c r="F33" t="n">
-        <v>2480.1654</v>
+        <v>3723.7893</v>
       </c>
       <c r="G33" t="n">
-        <v>30530836.4</v>
+        <v>21337312.7</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>40650</v>
+        <v>6080</v>
       </c>
       <c r="F34" t="n">
-        <v>751.0661</v>
+        <v>3255.5051</v>
       </c>
       <c r="G34" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>283500</v>
+        <v>95200</v>
       </c>
       <c r="F35" t="n">
-        <v>71.795</v>
+        <v>221.6088</v>
       </c>
       <c r="G35" t="n">
-        <v>20353890.9</v>
+        <v>21097154.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1594,34 +1592,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2390</v>
+        <v>2205</v>
       </c>
       <c r="F36" t="n">
-        <v>42581.3618</v>
+        <v>52623.2877</v>
       </c>
       <c r="G36" t="n">
-        <v>101769454.6</v>
+        <v>116034349.3</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1630,224 +1628,226 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>20450</v>
+        <v>58700</v>
       </c>
       <c r="F37" t="n">
-        <v>995.3003</v>
+        <v>357.1039</v>
       </c>
       <c r="G37" t="n">
-        <v>20353890.9</v>
+        <v>20961998.6</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>30200</v>
+        <v>13250</v>
       </c>
       <c r="F38" t="n">
-        <v>359.55</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>10858410.6</v>
+        <v>10480999.3</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208500</v>
+        <v>2360</v>
       </c>
       <c r="F39" t="n">
-        <v>338</v>
+        <v>66616.5209</v>
       </c>
       <c r="G39" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.97</v>
-      </c>
+        <v>157214989.3</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>17720</v>
+        <v>38300</v>
       </c>
       <c r="F40" t="n">
-        <v>94.9217</v>
+        <v>500.7861</v>
       </c>
       <c r="G40" t="n">
-        <v>1682012.5</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100500</v>
+        <v>21150</v>
       </c>
       <c r="F41" t="n">
-        <v>8.9518</v>
+        <v>495.5555</v>
       </c>
       <c r="G41" t="n">
-        <v>899652.6</v>
+        <v>10480999.3</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>11410</v>
+        <v>23650</v>
       </c>
       <c r="F42" t="n">
-        <v>6321.2722</v>
+        <v>832.6201</v>
       </c>
       <c r="G42" t="n">
-        <v>72125715.8</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12880</v>
+        <v>12310</v>
       </c>
       <c r="F43" t="n">
-        <v>713.2027</v>
+        <v>2480.1654</v>
       </c>
       <c r="G43" t="n">
-        <v>9186050.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1856,30 +1856,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21200</v>
+        <v>40650</v>
       </c>
       <c r="F44" t="n">
-        <v>120.8659</v>
+        <v>751.0661</v>
       </c>
       <c r="G44" t="n">
-        <v>2562357.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1888,30 +1888,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>27700</v>
+        <v>283500</v>
       </c>
       <c r="F45" t="n">
-        <v>161.1835</v>
+        <v>71.795</v>
       </c>
       <c r="G45" t="n">
-        <v>4464784.2</v>
+        <v>20353890.9</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1920,45 +1920,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>21500</v>
+        <v>2390</v>
       </c>
       <c r="F46" t="n">
-        <v>129.2032</v>
+        <v>42581.3618</v>
       </c>
       <c r="G46" t="n">
-        <v>2777868.4</v>
+        <v>101769454.6</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>34100</v>
+        <v>20450</v>
       </c>
       <c r="F47" t="n">
-        <v>21.679</v>
+        <v>995.3003</v>
       </c>
       <c r="G47" t="n">
-        <v>739252.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1970,27 +1970,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>40850</v>
+        <v>30200</v>
       </c>
       <c r="F48" t="n">
-        <v>123.3915</v>
+        <v>359.55</v>
       </c>
       <c r="G48" t="n">
-        <v>5040542.1</v>
+        <v>10858410.6</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2002,29 +2002,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308000</v>
+        <v>208500</v>
       </c>
       <c r="F49" t="n">
-        <v>9.1744</v>
+        <v>338</v>
       </c>
       <c r="G49" t="n">
-        <v>2825715.8</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2034,12 +2036,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2048,13 +2050,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6330</v>
+        <v>17720</v>
       </c>
       <c r="F50" t="n">
-        <v>50.5051</v>
+        <v>94.9217</v>
       </c>
       <c r="G50" t="n">
-        <v>319697.4</v>
+        <v>1682012.5</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2066,12 +2068,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2080,13 +2082,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>31700</v>
+        <v>100500</v>
       </c>
       <c r="F51" t="n">
-        <v>158.7408</v>
+        <v>8.9518</v>
       </c>
       <c r="G51" t="n">
-        <v>5032084.2</v>
+        <v>899652.6</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2098,27 +2100,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>68700</v>
+        <v>11410</v>
       </c>
       <c r="F52" t="n">
-        <v>16.0386</v>
+        <v>6321.2722</v>
       </c>
       <c r="G52" t="n">
-        <v>1101852.6</v>
+        <v>72125715.8</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2130,27 +2132,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>256000</v>
+        <v>12880</v>
       </c>
       <c r="F53" t="n">
-        <v>45.4873</v>
+        <v>713.2027</v>
       </c>
       <c r="G53" t="n">
-        <v>11644736.8</v>
+        <v>9186050.6</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2162,27 +2164,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>91100</v>
+        <v>21200</v>
       </c>
       <c r="F54" t="n">
-        <v>19.6174</v>
+        <v>120.8659</v>
       </c>
       <c r="G54" t="n">
-        <v>1787142.1</v>
+        <v>2562357.9</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2194,12 +2196,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2208,13 +2210,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>130900</v>
+        <v>27700</v>
       </c>
       <c r="F55" t="n">
-        <v>89.1437</v>
+        <v>161.1835</v>
       </c>
       <c r="G55" t="n">
-        <v>11668905.3</v>
+        <v>4464784.2</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2226,27 +2228,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F56" t="n">
-        <v>32820.1843</v>
+        <v>129.2032</v>
       </c>
       <c r="G56" t="n">
-        <v>78768442.40000001</v>
+        <v>2777868.4</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2258,27 +2260,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>41150</v>
+        <v>34100</v>
       </c>
       <c r="F57" t="n">
-        <v>38.7861</v>
+        <v>21.679</v>
       </c>
       <c r="G57" t="n">
-        <v>1596047.4</v>
+        <v>739252.6</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2290,27 +2292,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>49450</v>
+        <v>40850</v>
       </c>
       <c r="F58" t="n">
-        <v>83.90349999999999</v>
+        <v>123.3915</v>
       </c>
       <c r="G58" t="n">
-        <v>4149029</v>
+        <v>5040542.1</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2322,27 +2324,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>24750</v>
+        <v>308000</v>
       </c>
       <c r="F59" t="n">
-        <v>23.3799</v>
+        <v>9.1744</v>
       </c>
       <c r="G59" t="n">
-        <v>578652.6</v>
+        <v>2825715.8</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2354,110 +2356,108 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5450</v>
+        <v>6330</v>
       </c>
       <c r="F60" t="n">
-        <v>220.6267</v>
+        <v>50.5051</v>
       </c>
       <c r="G60" t="n">
-        <v>1202415.4</v>
+        <v>319697.4</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>327000</v>
+        <v>31700</v>
       </c>
       <c r="F61" t="n">
-        <v>54</v>
+        <v>158.7408</v>
       </c>
       <c r="G61" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>5032084.2</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5130</v>
+        <v>68700</v>
       </c>
       <c r="F62" t="n">
-        <v>4001.7913</v>
+        <v>16.0386</v>
       </c>
       <c r="G62" t="n">
-        <v>20529189.5</v>
+        <v>1101852.6</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2466,160 +2466,158 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>27100</v>
+        <v>256000</v>
       </c>
       <c r="F63" t="n">
-        <v>376</v>
+        <v>45.4873</v>
       </c>
       <c r="G63" t="n">
-        <v>10189600</v>
+        <v>11644736.8</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>67600</v>
+        <v>91100</v>
       </c>
       <c r="F64" t="n">
-        <v>998</v>
+        <v>19.6174</v>
       </c>
       <c r="G64" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>1787142.1</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11900</v>
+        <v>130900</v>
       </c>
       <c r="F65" t="n">
-        <v>856</v>
+        <v>89.1437</v>
       </c>
       <c r="G65" t="n">
-        <v>10186400</v>
+        <v>11668905.3</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>29300</v>
+        <v>2400</v>
       </c>
       <c r="F66" t="n">
-        <v>2434</v>
+        <v>32820.1843</v>
       </c>
       <c r="G66" t="n">
-        <v>71316200</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>119300</v>
+        <v>41150</v>
       </c>
       <c r="F67" t="n">
-        <v>171</v>
+        <v>38.7861</v>
       </c>
       <c r="G67" t="n">
-        <v>20400300</v>
+        <v>1596047.4</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2628,94 +2626,94 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2445</v>
+        <v>49450</v>
       </c>
       <c r="F68" t="n">
-        <v>82456</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>201604920</v>
+        <v>4149029</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>18910</v>
+        <v>24750</v>
       </c>
       <c r="F69" t="n">
-        <v>1068.0212</v>
+        <v>23.3799</v>
       </c>
       <c r="G69" t="n">
-        <v>20196280</v>
+        <v>578652.6</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>32250</v>
+        <v>5450</v>
       </c>
       <c r="F70" t="n">
-        <v>626</v>
+        <v>220.6267</v>
       </c>
       <c r="G70" t="n">
-        <v>20188500</v>
+        <v>1202415.4</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2724,388 +2722,390 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>82500</v>
+        <v>327000</v>
       </c>
       <c r="F71" t="n">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="G71" t="n">
-        <v>16830000</v>
+        <v>17658000</v>
       </c>
       <c r="H71" t="n">
-        <v>-8.640000000000001</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>56800</v>
+        <v>5130</v>
       </c>
       <c r="F72" t="n">
-        <v>258</v>
+        <v>4001.7913</v>
       </c>
       <c r="G72" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20529189.5</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>83700</v>
+        <v>27100</v>
       </c>
       <c r="F73" t="n">
-        <v>120</v>
+        <v>376</v>
       </c>
       <c r="G73" t="n">
-        <v>10044000</v>
+        <v>10189600</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>43650</v>
+        <v>67600</v>
       </c>
       <c r="F74" t="n">
-        <v>462</v>
+        <v>998</v>
       </c>
       <c r="G74" t="n">
-        <v>20166300</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>59700</v>
+        <v>11900</v>
       </c>
       <c r="F75" t="n">
-        <v>169</v>
+        <v>856</v>
       </c>
       <c r="G75" t="n">
-        <v>10089300</v>
+        <v>10186400</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10930</v>
+        <v>29300</v>
       </c>
       <c r="F76" t="n">
-        <v>1833</v>
+        <v>2434</v>
       </c>
       <c r="G76" t="n">
-        <v>20034690</v>
+        <v>71316200</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>19850</v>
+        <v>119300</v>
       </c>
       <c r="F77" t="n">
-        <v>505</v>
+        <v>171</v>
       </c>
       <c r="G77" t="n">
-        <v>10024250</v>
+        <v>20400300</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>26350</v>
+        <v>2445</v>
       </c>
       <c r="F78" t="n">
-        <v>380</v>
+        <v>82456</v>
       </c>
       <c r="G78" t="n">
-        <v>10013000</v>
+        <v>201604920</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>23500</v>
+        <v>18910</v>
       </c>
       <c r="F79" t="n">
-        <v>833</v>
+        <v>1068.0212</v>
       </c>
       <c r="G79" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20196280</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>85200</v>
+        <v>32250</v>
       </c>
       <c r="F80" t="n">
-        <v>118</v>
+        <v>626</v>
       </c>
       <c r="G80" t="n">
-        <v>10053600</v>
+        <v>20188500</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>63400</v>
+        <v>82500</v>
       </c>
       <c r="F81" t="n">
-        <v>316</v>
+        <v>204</v>
       </c>
       <c r="G81" t="n">
-        <v>20034400</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>110300</v>
+        <v>56800</v>
       </c>
       <c r="F82" t="n">
-        <v>91</v>
+        <v>258</v>
       </c>
       <c r="G82" t="n">
-        <v>10037300</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3114,30 +3114,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>66100</v>
+        <v>83700</v>
       </c>
       <c r="F83" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="G83" t="n">
-        <v>10047200</v>
+        <v>10044000</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3146,222 +3146,224 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>25800</v>
+        <v>43650</v>
       </c>
       <c r="F84" t="n">
-        <v>2713</v>
+        <v>462</v>
       </c>
       <c r="G84" t="n">
-        <v>69995400</v>
+        <v>20166300</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>206500</v>
+        <v>59700</v>
       </c>
       <c r="F85" t="n">
-        <v>338</v>
+        <v>169</v>
       </c>
       <c r="G85" t="n">
-        <v>69797000</v>
+        <v>10089300</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>70100</v>
+        <v>10930</v>
       </c>
       <c r="F86" t="n">
-        <v>998</v>
+        <v>1833</v>
       </c>
       <c r="G86" t="n">
-        <v>69959800</v>
+        <v>20034690</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>93300</v>
+        <v>19850</v>
       </c>
       <c r="F87" t="n">
-        <v>214</v>
+        <v>505</v>
       </c>
       <c r="G87" t="n">
-        <v>19966200</v>
+        <v>10024250</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>11300</v>
+        <v>26350</v>
       </c>
       <c r="F88" t="n">
-        <v>4424</v>
+        <v>380</v>
       </c>
       <c r="G88" t="n">
-        <v>49991200</v>
+        <v>10013000</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>19740</v>
+        <v>23500</v>
       </c>
       <c r="F89" t="n">
-        <v>2532</v>
+        <v>833</v>
       </c>
       <c r="G89" t="n">
-        <v>49981680</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>25150</v>
+        <v>85200</v>
       </c>
       <c r="F90" t="n">
-        <v>2385</v>
+        <v>118</v>
       </c>
       <c r="G90" t="n">
-        <v>59982750</v>
+        <v>10053600</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3370,77 +3372,77 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>22050</v>
+        <v>63400</v>
       </c>
       <c r="F91" t="n">
-        <v>2267</v>
+        <v>316</v>
       </c>
       <c r="G91" t="n">
-        <v>49987350</v>
+        <v>20034400</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>43150</v>
+        <v>110300</v>
       </c>
       <c r="F92" t="n">
-        <v>1390</v>
+        <v>91</v>
       </c>
       <c r="G92" t="n">
-        <v>59978500</v>
+        <v>10037300</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>310000</v>
+        <v>66100</v>
       </c>
       <c r="F93" t="n">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="G93" t="n">
-        <v>69750000</v>
+        <v>10047200</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3452,12 +3454,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3466,13 +3468,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6240</v>
+        <v>25800</v>
       </c>
       <c r="F94" t="n">
-        <v>3205</v>
+        <v>2713</v>
       </c>
       <c r="G94" t="n">
-        <v>19999200</v>
+        <v>69995400</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3484,12 +3486,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3498,13 +3500,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>24000</v>
+        <v>206500</v>
       </c>
       <c r="F95" t="n">
-        <v>833</v>
+        <v>338</v>
       </c>
       <c r="G95" t="n">
-        <v>19992000</v>
+        <v>69797000</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3516,12 +3518,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3530,13 +3532,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>90300</v>
+        <v>70100</v>
       </c>
       <c r="F96" t="n">
-        <v>442</v>
+        <v>998</v>
       </c>
       <c r="G96" t="n">
-        <v>39912600</v>
+        <v>69959800</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3548,12 +3550,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3562,13 +3564,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>279500</v>
+        <v>93300</v>
       </c>
       <c r="F97" t="n">
-        <v>357</v>
+        <v>214</v>
       </c>
       <c r="G97" t="n">
-        <v>99781500</v>
+        <v>19966200</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3580,12 +3582,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3594,13 +3596,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>366000</v>
+        <v>11300</v>
       </c>
       <c r="F98" t="n">
-        <v>54</v>
+        <v>4424</v>
       </c>
       <c r="G98" t="n">
-        <v>19764000</v>
+        <v>49991200</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3612,12 +3614,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3626,13 +3628,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>91000</v>
+        <v>19740</v>
       </c>
       <c r="F99" t="n">
-        <v>659</v>
+        <v>2532</v>
       </c>
       <c r="G99" t="n">
-        <v>59969000</v>
+        <v>49981680</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3644,12 +3646,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3658,13 +3660,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>120100</v>
+        <v>25150</v>
       </c>
       <c r="F100" t="n">
-        <v>666</v>
+        <v>2385</v>
       </c>
       <c r="G100" t="n">
-        <v>79986600</v>
+        <v>59982750</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3676,12 +3678,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3690,13 +3692,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2405</v>
+        <v>22050</v>
       </c>
       <c r="F101" t="n">
-        <v>415800</v>
+        <v>2267</v>
       </c>
       <c r="G101" t="n">
-        <v>999999000</v>
+        <v>49987350</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3708,12 +3710,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3722,13 +3724,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>69000</v>
+        <v>43150</v>
       </c>
       <c r="F102" t="n">
-        <v>579</v>
+        <v>1390</v>
       </c>
       <c r="G102" t="n">
-        <v>39951000</v>
+        <v>59978500</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3740,12 +3742,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3754,13 +3756,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>42300</v>
+        <v>310000</v>
       </c>
       <c r="F103" t="n">
-        <v>709</v>
+        <v>225</v>
       </c>
       <c r="G103" t="n">
-        <v>29990700</v>
+        <v>69750000</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3772,29 +3774,349 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>티씨머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>125020</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6240</v>
+      </c>
+      <c r="F104" t="n">
+        <v>3205</v>
+      </c>
+      <c r="G104" t="n">
+        <v>19999200</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>138080</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F105" t="n">
+        <v>833</v>
+      </c>
+      <c r="G105" t="n">
+        <v>19992000</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>141080</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>90300</v>
+      </c>
+      <c r="F106" t="n">
+        <v>442</v>
+      </c>
+      <c r="G106" t="n">
+        <v>39912600</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>279500</v>
+      </c>
+      <c r="F107" t="n">
+        <v>357</v>
+      </c>
+      <c r="G107" t="n">
+        <v>99781500</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F108" t="n">
+        <v>54</v>
+      </c>
+      <c r="G108" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F109" t="n">
+        <v>659</v>
+      </c>
+      <c r="G109" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F110" t="n">
+        <v>666</v>
+      </c>
+      <c r="G110" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F111" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G111" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F112" t="n">
+        <v>579</v>
+      </c>
+      <c r="G112" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F113" t="n">
+        <v>709</v>
+      </c>
+      <c r="G113" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E104" t="n">
+      <c r="E114" t="n">
         <v>23350</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F114" t="n">
         <v>856</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G114" t="n">
         <v>19987600</v>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,111 +492,115 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32350</v>
+        <v>12120</v>
       </c>
       <c r="F2" t="n">
-        <v>314.5779</v>
+        <v>820.878</v>
       </c>
       <c r="G2" t="n">
-        <v>10176595.1</v>
+        <v>9949041.199999999</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>13650</v>
+        <v>248000</v>
       </c>
       <c r="F3" t="n">
-        <v>745.5381</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31950</v>
+        <v>222500</v>
       </c>
       <c r="F4" t="n">
-        <v>318.5163</v>
+        <v>178.8592</v>
       </c>
       <c r="G4" t="n">
-        <v>10176595.1</v>
+        <v>39796164.7</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>250500</v>
+        <v>54500</v>
       </c>
       <c r="F5" t="n">
-        <v>81.2503</v>
+        <v>504.0447</v>
       </c>
       <c r="G5" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -606,27 +610,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14100</v>
+        <v>32350</v>
       </c>
       <c r="F6" t="n">
-        <v>1443.4887</v>
+        <v>314.5779</v>
       </c>
       <c r="G6" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,31 +642,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31300</v>
+        <v>13650</v>
       </c>
       <c r="F7" t="n">
-        <v>1954.4702</v>
+        <v>745.5381</v>
       </c>
       <c r="G7" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6.83</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -672,27 +674,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2355</v>
+        <v>31950</v>
       </c>
       <c r="F8" t="n">
-        <v>65496.7248</v>
+        <v>318.5163</v>
       </c>
       <c r="G8" t="n">
-        <v>154244786.8</v>
+        <v>10176595.1</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -704,27 +706,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15810</v>
+        <v>250500</v>
       </c>
       <c r="F9" t="n">
-        <v>5149.4473</v>
+        <v>81.2503</v>
       </c>
       <c r="G9" t="n">
-        <v>81412761.09999999</v>
+        <v>20353190.3</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,27 +738,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>56700</v>
+        <v>14100</v>
       </c>
       <c r="F10" t="n">
-        <v>179.4814</v>
+        <v>1443.4887</v>
       </c>
       <c r="G10" t="n">
-        <v>10176595.1</v>
+        <v>20353190.3</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,110 +770,110 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>31300</v>
       </c>
       <c r="F11" t="n">
-        <v>4367.6374</v>
+        <v>1954.4702</v>
       </c>
       <c r="G11" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>44600</v>
+        <v>2355</v>
       </c>
       <c r="F12" t="n">
-        <v>1359.3974</v>
+        <v>65496.7248</v>
       </c>
       <c r="G12" t="n">
-        <v>60629123.5</v>
+        <v>154244786.8</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20300</v>
+        <v>15810</v>
       </c>
       <c r="F13" t="n">
-        <v>1162.9429</v>
+        <v>5149.4473</v>
       </c>
       <c r="G13" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>7.9</v>
-      </c>
+        <v>81412761.09999999</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,49 +882,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13160</v>
+        <v>56700</v>
       </c>
       <c r="F14" t="n">
-        <v>767.846</v>
+        <v>179.4814</v>
       </c>
       <c r="G14" t="n">
-        <v>10104853.9</v>
+        <v>10176595.1</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49050</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="n">
-        <v>357.1039</v>
+        <v>4367.6374</v>
       </c>
       <c r="G15" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -932,31 +932,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37100</v>
+        <v>44600</v>
       </c>
       <c r="F16" t="n">
-        <v>604.321</v>
+        <v>1359.3974</v>
       </c>
       <c r="G16" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>15.04</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -966,29 +964,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>123700</v>
+        <v>20300</v>
       </c>
       <c r="F17" t="n">
-        <v>490.1303</v>
+        <v>1162.9429</v>
       </c>
       <c r="G17" t="n">
-        <v>60629123.5</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>23607739.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -998,27 +998,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>41150</v>
+        <v>13160</v>
       </c>
       <c r="F18" t="n">
-        <v>491.1229</v>
+        <v>767.846</v>
       </c>
       <c r="G18" t="n">
-        <v>20209707.8</v>
+        <v>10104853.9</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1030,29 +1030,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>31500</v>
+        <v>49050</v>
       </c>
       <c r="F19" t="n">
-        <v>320.789</v>
+        <v>357.1039</v>
       </c>
       <c r="G19" t="n">
-        <v>10104853.9</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1062,29 +1064,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228500</v>
+        <v>37100</v>
       </c>
       <c r="F20" t="n">
-        <v>88.4451</v>
+        <v>604.321</v>
       </c>
       <c r="G20" t="n">
-        <v>20209707.8</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1094,31 +1098,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>88500</v>
+        <v>123700</v>
       </c>
       <c r="F21" t="n">
-        <v>900.2261</v>
+        <v>490.1303</v>
       </c>
       <c r="G21" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1128,31 +1130,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>130100</v>
+        <v>41150</v>
       </c>
       <c r="F22" t="n">
-        <v>314.8563</v>
+        <v>491.1229</v>
       </c>
       <c r="G22" t="n">
-        <v>40962809.6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>8.33</v>
-      </c>
+        <v>20209707.8</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2325</v>
+        <v>31500</v>
       </c>
       <c r="F23" t="n">
-        <v>21730.8686</v>
+        <v>320.789</v>
       </c>
       <c r="G23" t="n">
-        <v>50524269.6</v>
+        <v>10104853.9</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1194,27 +1194,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>64700</v>
+        <v>228500</v>
       </c>
       <c r="F24" t="n">
-        <v>468.5404</v>
+        <v>88.4451</v>
       </c>
       <c r="G24" t="n">
-        <v>30314561.7</v>
+        <v>20209707.8</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1226,66 +1226,70 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4670</v>
+        <v>88500</v>
       </c>
       <c r="F25" t="n">
-        <v>6491.3408</v>
+        <v>900.2261</v>
       </c>
       <c r="G25" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2120</v>
+        <v>130100</v>
       </c>
       <c r="F26" t="n">
-        <v>63879.7502</v>
+        <v>314.8563</v>
       </c>
       <c r="G26" t="n">
-        <v>135425070.4</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1300,90 +1304,88 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2120</v>
+        <v>2325</v>
       </c>
       <c r="F27" t="n">
-        <v>3453.9051</v>
+        <v>21730.8686</v>
       </c>
       <c r="G27" t="n">
-        <v>7322278.8</v>
+        <v>50524269.6</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>22900</v>
+        <v>64700</v>
       </c>
       <c r="F28" t="n">
-        <v>1397.6406</v>
+        <v>468.5404</v>
       </c>
       <c r="G28" t="n">
-        <v>32005969</v>
+        <v>30314561.7</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>73600</v>
+        <v>4670</v>
       </c>
       <c r="F29" t="n">
-        <v>299.9614</v>
+        <v>6491.3408</v>
       </c>
       <c r="G29" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>16.09</v>
-      </c>
+        <v>30314561.7</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1398,49 +1400,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2215</v>
+        <v>2120</v>
       </c>
       <c r="F30" t="n">
-        <v>28224.978</v>
+        <v>63879.7502</v>
       </c>
       <c r="G30" t="n">
-        <v>62518326.2</v>
+        <v>135425070.4</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>43800</v>
+        <v>2120</v>
       </c>
       <c r="F31" t="n">
-        <v>504.0447</v>
+        <v>3453.9051</v>
       </c>
       <c r="G31" t="n">
-        <v>22077158.2</v>
+        <v>7322278.8</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1452,27 +1454,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>23650</v>
+        <v>22900</v>
       </c>
       <c r="F32" t="n">
-        <v>451.106</v>
+        <v>1397.6406</v>
       </c>
       <c r="G32" t="n">
-        <v>10668656.3</v>
+        <v>32005969</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1484,206 +1486,208 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5730</v>
+        <v>73600</v>
       </c>
       <c r="F33" t="n">
-        <v>3723.7893</v>
+        <v>299.9614</v>
       </c>
       <c r="G33" t="n">
-        <v>21337312.7</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6080</v>
+        <v>2215</v>
       </c>
       <c r="F34" t="n">
-        <v>3255.5051</v>
+        <v>28224.978</v>
       </c>
       <c r="G34" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>62518326.2</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>95200</v>
+        <v>43800</v>
       </c>
       <c r="F35" t="n">
-        <v>221.6088</v>
+        <v>504.0447</v>
       </c>
       <c r="G35" t="n">
-        <v>21097154.4</v>
+        <v>22077158.2</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2205</v>
+        <v>23650</v>
       </c>
       <c r="F36" t="n">
-        <v>52623.2877</v>
+        <v>451.106</v>
       </c>
       <c r="G36" t="n">
-        <v>116034349.3</v>
+        <v>10668656.3</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>58700</v>
+        <v>5730</v>
       </c>
       <c r="F37" t="n">
-        <v>357.1039</v>
+        <v>3723.7893</v>
       </c>
       <c r="G37" t="n">
-        <v>20961998.6</v>
+        <v>21337312.7</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>13250</v>
+        <v>6080</v>
       </c>
       <c r="F38" t="n">
-        <v>791.0188000000001</v>
+        <v>3255.5051</v>
       </c>
       <c r="G38" t="n">
-        <v>10480999.3</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1692,49 +1696,47 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2360</v>
+        <v>95200</v>
       </c>
       <c r="F39" t="n">
-        <v>66616.5209</v>
+        <v>221.6088</v>
       </c>
       <c r="G39" t="n">
-        <v>157214989.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>38300</v>
+        <v>2205</v>
       </c>
       <c r="F40" t="n">
-        <v>500.7861</v>
+        <v>52623.2877</v>
       </c>
       <c r="G40" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>116034349.3</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1744,27 +1746,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21150</v>
+        <v>58700</v>
       </c>
       <c r="F41" t="n">
-        <v>495.5555</v>
+        <v>357.1039</v>
       </c>
       <c r="G41" t="n">
-        <v>10480999.3</v>
+        <v>20961998.6</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1776,46 +1778,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23650</v>
+        <v>13250</v>
       </c>
       <c r="F42" t="n">
-        <v>832.6201</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1.28</v>
-      </c>
+        <v>10480999.3</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1824,111 +1824,115 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12310</v>
+        <v>2360</v>
       </c>
       <c r="F43" t="n">
-        <v>2480.1654</v>
+        <v>66616.5209</v>
       </c>
       <c r="G43" t="n">
-        <v>30530836.4</v>
+        <v>157214989.3</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>40650</v>
+        <v>38300</v>
       </c>
       <c r="F44" t="n">
-        <v>751.0661</v>
+        <v>500.7861</v>
       </c>
       <c r="G44" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>283500</v>
+        <v>21150</v>
       </c>
       <c r="F45" t="n">
-        <v>71.795</v>
+        <v>495.5555</v>
       </c>
       <c r="G45" t="n">
-        <v>20353890.9</v>
+        <v>10480999.3</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2390</v>
+        <v>23650</v>
       </c>
       <c r="F46" t="n">
-        <v>42581.3618</v>
+        <v>832.6201</v>
       </c>
       <c r="G46" t="n">
-        <v>101769454.6</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1938,44 +1942,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>20450</v>
+        <v>12310</v>
       </c>
       <c r="F47" t="n">
-        <v>995.3003</v>
+        <v>2480.1654</v>
       </c>
       <c r="G47" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1984,64 +1988,62 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>30200</v>
+        <v>40650</v>
       </c>
       <c r="F48" t="n">
-        <v>359.55</v>
+        <v>751.0661</v>
       </c>
       <c r="G48" t="n">
-        <v>10858410.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>208500</v>
+        <v>283500</v>
       </c>
       <c r="F49" t="n">
-        <v>338</v>
+        <v>71.795</v>
       </c>
       <c r="G49" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.97</v>
-      </c>
+        <v>20353890.9</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2050,45 +2052,45 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>17720</v>
+        <v>2390</v>
       </c>
       <c r="F50" t="n">
-        <v>94.9217</v>
+        <v>42581.3618</v>
       </c>
       <c r="G50" t="n">
-        <v>1682012.5</v>
+        <v>101769454.6</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100500</v>
+        <v>20450</v>
       </c>
       <c r="F51" t="n">
-        <v>8.9518</v>
+        <v>995.3003</v>
       </c>
       <c r="G51" t="n">
-        <v>899652.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2100,27 +2102,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>11410</v>
+        <v>30200</v>
       </c>
       <c r="F52" t="n">
-        <v>6321.2722</v>
+        <v>359.55</v>
       </c>
       <c r="G52" t="n">
-        <v>72125715.8</v>
+        <v>10858410.6</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2132,29 +2134,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>12880</v>
+        <v>208500</v>
       </c>
       <c r="F53" t="n">
-        <v>713.2027</v>
+        <v>338</v>
       </c>
       <c r="G53" t="n">
-        <v>9186050.6</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2164,27 +2168,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21200</v>
+        <v>17720</v>
       </c>
       <c r="F54" t="n">
-        <v>120.8659</v>
+        <v>94.9217</v>
       </c>
       <c r="G54" t="n">
-        <v>2562357.9</v>
+        <v>1682012.5</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2196,12 +2200,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2210,13 +2214,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>27700</v>
+        <v>100500</v>
       </c>
       <c r="F55" t="n">
-        <v>161.1835</v>
+        <v>8.9518</v>
       </c>
       <c r="G55" t="n">
-        <v>4464784.2</v>
+        <v>899652.6</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2228,27 +2232,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>21500</v>
+        <v>11410</v>
       </c>
       <c r="F56" t="n">
-        <v>129.2032</v>
+        <v>6321.2722</v>
       </c>
       <c r="G56" t="n">
-        <v>2777868.4</v>
+        <v>72125715.8</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2260,12 +2264,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2274,13 +2278,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>34100</v>
+        <v>12880</v>
       </c>
       <c r="F57" t="n">
-        <v>21.679</v>
+        <v>713.2027</v>
       </c>
       <c r="G57" t="n">
-        <v>739252.6</v>
+        <v>9186050.6</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2292,27 +2296,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>40850</v>
+        <v>21200</v>
       </c>
       <c r="F58" t="n">
-        <v>123.3915</v>
+        <v>120.8659</v>
       </c>
       <c r="G58" t="n">
-        <v>5040542.1</v>
+        <v>2562357.9</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2324,27 +2328,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308000</v>
+        <v>27700</v>
       </c>
       <c r="F59" t="n">
-        <v>9.1744</v>
+        <v>161.1835</v>
       </c>
       <c r="G59" t="n">
-        <v>2825715.8</v>
+        <v>4464784.2</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2356,12 +2360,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2370,13 +2374,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6330</v>
+        <v>21500</v>
       </c>
       <c r="F60" t="n">
-        <v>50.5051</v>
+        <v>129.2032</v>
       </c>
       <c r="G60" t="n">
-        <v>319697.4</v>
+        <v>2777868.4</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2388,12 +2392,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2402,13 +2406,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>31700</v>
+        <v>34100</v>
       </c>
       <c r="F61" t="n">
-        <v>158.7408</v>
+        <v>21.679</v>
       </c>
       <c r="G61" t="n">
-        <v>5032084.2</v>
+        <v>739252.6</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2420,27 +2424,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>68700</v>
+        <v>40850</v>
       </c>
       <c r="F62" t="n">
-        <v>16.0386</v>
+        <v>123.3915</v>
       </c>
       <c r="G62" t="n">
-        <v>1101852.6</v>
+        <v>5040542.1</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2452,12 +2456,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2466,13 +2470,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>256000</v>
+        <v>308000</v>
       </c>
       <c r="F63" t="n">
-        <v>45.4873</v>
+        <v>9.1744</v>
       </c>
       <c r="G63" t="n">
-        <v>11644736.8</v>
+        <v>2825715.8</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2484,12 +2488,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2498,13 +2502,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>91100</v>
+        <v>6330</v>
       </c>
       <c r="F64" t="n">
-        <v>19.6174</v>
+        <v>50.5051</v>
       </c>
       <c r="G64" t="n">
-        <v>1787142.1</v>
+        <v>319697.4</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2516,12 +2520,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2530,13 +2534,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>130900</v>
+        <v>31700</v>
       </c>
       <c r="F65" t="n">
-        <v>89.1437</v>
+        <v>158.7408</v>
       </c>
       <c r="G65" t="n">
-        <v>11668905.3</v>
+        <v>5032084.2</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2548,12 +2552,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2562,13 +2566,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2400</v>
+        <v>68700</v>
       </c>
       <c r="F66" t="n">
-        <v>32820.1843</v>
+        <v>16.0386</v>
       </c>
       <c r="G66" t="n">
-        <v>78768442.40000001</v>
+        <v>1101852.6</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2580,12 +2584,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2594,13 +2598,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>41150</v>
+        <v>256000</v>
       </c>
       <c r="F67" t="n">
-        <v>38.7861</v>
+        <v>45.4873</v>
       </c>
       <c r="G67" t="n">
-        <v>1596047.4</v>
+        <v>11644736.8</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2612,27 +2616,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>49450</v>
+        <v>91100</v>
       </c>
       <c r="F68" t="n">
-        <v>83.90349999999999</v>
+        <v>19.6174</v>
       </c>
       <c r="G68" t="n">
-        <v>4149029</v>
+        <v>1787142.1</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2644,12 +2648,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2658,13 +2662,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>24750</v>
+        <v>130900</v>
       </c>
       <c r="F69" t="n">
-        <v>23.3799</v>
+        <v>89.1437</v>
       </c>
       <c r="G69" t="n">
-        <v>578652.6</v>
+        <v>11668905.3</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2676,12 +2680,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2690,194 +2694,192 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5450</v>
+        <v>2400</v>
       </c>
       <c r="F70" t="n">
-        <v>220.6267</v>
+        <v>32820.1843</v>
       </c>
       <c r="G70" t="n">
-        <v>1202415.4</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>327000</v>
+        <v>41150</v>
       </c>
       <c r="F71" t="n">
-        <v>54</v>
+        <v>38.7861</v>
       </c>
       <c r="G71" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>1596047.4</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5130</v>
+        <v>49450</v>
       </c>
       <c r="F72" t="n">
-        <v>4001.7913</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>20529189.5</v>
+        <v>4149029</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>27100</v>
+        <v>24750</v>
       </c>
       <c r="F73" t="n">
-        <v>376</v>
+        <v>23.3799</v>
       </c>
       <c r="G73" t="n">
-        <v>10189600</v>
+        <v>578652.6</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>67600</v>
+        <v>5450</v>
       </c>
       <c r="F74" t="n">
-        <v>998</v>
+        <v>220.6267</v>
       </c>
       <c r="G74" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>1202415.4</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>11900</v>
+        <v>327000</v>
       </c>
       <c r="F75" t="n">
-        <v>856</v>
+        <v>54</v>
       </c>
       <c r="G75" t="n">
-        <v>10186400</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2886,13 +2888,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>29300</v>
+        <v>5130</v>
       </c>
       <c r="F76" t="n">
-        <v>2434</v>
+        <v>4001.7913</v>
       </c>
       <c r="G76" t="n">
-        <v>71316200</v>
+        <v>20529189.5</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2904,27 +2906,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>119300</v>
+        <v>27100</v>
       </c>
       <c r="F77" t="n">
-        <v>171</v>
+        <v>376</v>
       </c>
       <c r="G77" t="n">
-        <v>20400300</v>
+        <v>10189600</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2936,76 +2938,78 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2445</v>
+        <v>67600</v>
       </c>
       <c r="F78" t="n">
-        <v>82456</v>
+        <v>998</v>
       </c>
       <c r="G78" t="n">
-        <v>201604920</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>18910</v>
+        <v>11900</v>
       </c>
       <c r="F79" t="n">
-        <v>1068.0212</v>
+        <v>856</v>
       </c>
       <c r="G79" t="n">
-        <v>20196280</v>
+        <v>10186400</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3014,130 +3018,126 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>32250</v>
+        <v>29300</v>
       </c>
       <c r="F80" t="n">
-        <v>626</v>
+        <v>2434</v>
       </c>
       <c r="G80" t="n">
-        <v>20188500</v>
+        <v>71316200</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>82500</v>
+        <v>119300</v>
       </c>
       <c r="F81" t="n">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="G81" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>20400300</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>56800</v>
+        <v>2445</v>
       </c>
       <c r="F82" t="n">
-        <v>258</v>
+        <v>82456</v>
       </c>
       <c r="G82" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>201604920</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>83700</v>
+        <v>18910</v>
       </c>
       <c r="F83" t="n">
-        <v>120</v>
+        <v>1068.0212</v>
       </c>
       <c r="G83" t="n">
-        <v>10044000</v>
+        <v>20196280</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3146,177 +3146,179 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>43650</v>
+        <v>32250</v>
       </c>
       <c r="F84" t="n">
-        <v>462</v>
+        <v>626</v>
       </c>
       <c r="G84" t="n">
-        <v>20166300</v>
+        <v>20188500</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>59700</v>
+        <v>82500</v>
       </c>
       <c r="F85" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="G85" t="n">
-        <v>10089300</v>
-      </c>
-      <c r="H85" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10930</v>
+        <v>56800</v>
       </c>
       <c r="F86" t="n">
-        <v>1833</v>
+        <v>258</v>
       </c>
       <c r="G86" t="n">
-        <v>20034690</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>19850</v>
+        <v>83700</v>
       </c>
       <c r="F87" t="n">
-        <v>505</v>
+        <v>120</v>
       </c>
       <c r="G87" t="n">
-        <v>10024250</v>
+        <v>10044000</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>26350</v>
+        <v>43650</v>
       </c>
       <c r="F88" t="n">
-        <v>380</v>
+        <v>462</v>
       </c>
       <c r="G88" t="n">
-        <v>10013000</v>
+        <v>20166300</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>23500</v>
+        <v>59700</v>
       </c>
       <c r="F89" t="n">
-        <v>833</v>
+        <v>169</v>
       </c>
       <c r="G89" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10089300</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3326,27 +3328,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>85200</v>
+        <v>10930</v>
       </c>
       <c r="F90" t="n">
-        <v>118</v>
+        <v>1833</v>
       </c>
       <c r="G90" t="n">
-        <v>10053600</v>
+        <v>20034690</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3358,27 +3360,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>63400</v>
+        <v>19850</v>
       </c>
       <c r="F91" t="n">
-        <v>316</v>
+        <v>505</v>
       </c>
       <c r="G91" t="n">
-        <v>20034400</v>
+        <v>10024250</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3390,27 +3392,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>110300</v>
+        <v>26350</v>
       </c>
       <c r="F92" t="n">
-        <v>91</v>
+        <v>380</v>
       </c>
       <c r="G92" t="n">
-        <v>10037300</v>
+        <v>10013000</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3422,76 +3424,78 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>66100</v>
+        <v>23500</v>
       </c>
       <c r="F93" t="n">
-        <v>152</v>
+        <v>833</v>
       </c>
       <c r="G93" t="n">
-        <v>10047200</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>25800</v>
+        <v>85200</v>
       </c>
       <c r="F94" t="n">
-        <v>2713</v>
+        <v>118</v>
       </c>
       <c r="G94" t="n">
-        <v>69995400</v>
+        <v>10053600</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3500,77 +3504,77 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>206500</v>
+        <v>63400</v>
       </c>
       <c r="F95" t="n">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="G95" t="n">
-        <v>69797000</v>
+        <v>20034400</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>70100</v>
+        <v>110300</v>
       </c>
       <c r="F96" t="n">
-        <v>998</v>
+        <v>91</v>
       </c>
       <c r="G96" t="n">
-        <v>69959800</v>
+        <v>10037300</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>93300</v>
+        <v>66100</v>
       </c>
       <c r="F97" t="n">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="G97" t="n">
-        <v>19966200</v>
+        <v>10047200</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3582,12 +3586,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3596,13 +3600,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>11300</v>
+        <v>25800</v>
       </c>
       <c r="F98" t="n">
-        <v>4424</v>
+        <v>2713</v>
       </c>
       <c r="G98" t="n">
-        <v>49991200</v>
+        <v>69995400</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3614,12 +3618,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3628,13 +3632,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>19740</v>
+        <v>206500</v>
       </c>
       <c r="F99" t="n">
-        <v>2532</v>
+        <v>338</v>
       </c>
       <c r="G99" t="n">
-        <v>49981680</v>
+        <v>69797000</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3646,12 +3650,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3660,13 +3664,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>25150</v>
+        <v>70100</v>
       </c>
       <c r="F100" t="n">
-        <v>2385</v>
+        <v>998</v>
       </c>
       <c r="G100" t="n">
-        <v>59982750</v>
+        <v>69959800</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3678,12 +3682,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3692,13 +3696,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>22050</v>
+        <v>93300</v>
       </c>
       <c r="F101" t="n">
-        <v>2267</v>
+        <v>214</v>
       </c>
       <c r="G101" t="n">
-        <v>49987350</v>
+        <v>19966200</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3710,12 +3714,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3724,13 +3728,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>43150</v>
+        <v>11300</v>
       </c>
       <c r="F102" t="n">
-        <v>1390</v>
+        <v>4424</v>
       </c>
       <c r="G102" t="n">
-        <v>59978500</v>
+        <v>49991200</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3742,12 +3746,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3756,13 +3760,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>310000</v>
+        <v>19740</v>
       </c>
       <c r="F103" t="n">
-        <v>225</v>
+        <v>2532</v>
       </c>
       <c r="G103" t="n">
-        <v>69750000</v>
+        <v>49981680</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3774,12 +3778,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3788,13 +3792,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6240</v>
+        <v>25150</v>
       </c>
       <c r="F104" t="n">
-        <v>3205</v>
+        <v>2385</v>
       </c>
       <c r="G104" t="n">
-        <v>19999200</v>
+        <v>59982750</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3806,12 +3810,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3820,13 +3824,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>24000</v>
+        <v>22050</v>
       </c>
       <c r="F105" t="n">
-        <v>833</v>
+        <v>2267</v>
       </c>
       <c r="G105" t="n">
-        <v>19992000</v>
+        <v>49987350</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3838,12 +3842,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3852,13 +3856,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>90300</v>
+        <v>43150</v>
       </c>
       <c r="F106" t="n">
-        <v>442</v>
+        <v>1390</v>
       </c>
       <c r="G106" t="n">
-        <v>39912600</v>
+        <v>59978500</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3870,12 +3874,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3884,13 +3888,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>279500</v>
+        <v>310000</v>
       </c>
       <c r="F107" t="n">
-        <v>357</v>
+        <v>225</v>
       </c>
       <c r="G107" t="n">
-        <v>99781500</v>
+        <v>69750000</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3902,12 +3906,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3916,13 +3920,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>366000</v>
+        <v>6240</v>
       </c>
       <c r="F108" t="n">
-        <v>54</v>
+        <v>3205</v>
       </c>
       <c r="G108" t="n">
-        <v>19764000</v>
+        <v>19999200</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3934,12 +3938,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3948,13 +3952,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>91000</v>
+        <v>24000</v>
       </c>
       <c r="F109" t="n">
-        <v>659</v>
+        <v>833</v>
       </c>
       <c r="G109" t="n">
-        <v>59969000</v>
+        <v>19992000</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3966,12 +3970,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3980,13 +3984,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>120100</v>
+        <v>90300</v>
       </c>
       <c r="F110" t="n">
-        <v>666</v>
+        <v>442</v>
       </c>
       <c r="G110" t="n">
-        <v>79986600</v>
+        <v>39912600</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3998,12 +4002,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4012,13 +4016,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2405</v>
+        <v>279500</v>
       </c>
       <c r="F111" t="n">
-        <v>415800</v>
+        <v>357</v>
       </c>
       <c r="G111" t="n">
-        <v>999999000</v>
+        <v>99781500</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4030,12 +4034,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4044,13 +4048,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>69000</v>
+        <v>366000</v>
       </c>
       <c r="F112" t="n">
-        <v>579</v>
+        <v>54</v>
       </c>
       <c r="G112" t="n">
-        <v>39951000</v>
+        <v>19764000</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4062,12 +4066,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4076,13 +4080,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>42300</v>
+        <v>91000</v>
       </c>
       <c r="F113" t="n">
-        <v>709</v>
+        <v>659</v>
       </c>
       <c r="G113" t="n">
-        <v>29990700</v>
+        <v>59969000</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4094,29 +4098,157 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F114" t="n">
+        <v>666</v>
+      </c>
+      <c r="G114" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F115" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G115" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F116" t="n">
+        <v>579</v>
+      </c>
+      <c r="G116" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F117" t="n">
+        <v>709</v>
+      </c>
+      <c r="G117" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E114" t="n">
+      <c r="E118" t="n">
         <v>23350</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F118" t="n">
         <v>856</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G118" t="n">
         <v>19987600</v>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,149 +473,149 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12120</v>
+        <v>79100</v>
       </c>
       <c r="F2" t="n">
-        <v>820.878</v>
+        <v>205.0482</v>
       </c>
       <c r="G2" t="n">
-        <v>9949041.199999999</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>16219315.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-15.22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>248000</v>
+        <v>25250</v>
       </c>
       <c r="F3" t="n">
-        <v>81.12909999999999</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>20120019.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-19.98</v>
-      </c>
+        <v>19409469.1</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222500</v>
+        <v>12510</v>
       </c>
       <c r="F4" t="n">
-        <v>178.8592</v>
+        <v>1443.4887</v>
       </c>
       <c r="G4" t="n">
-        <v>39796164.7</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>18058043.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-11.28</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54500</v>
+        <v>126500</v>
       </c>
       <c r="F5" t="n">
-        <v>504.0447</v>
+        <v>383.5863</v>
       </c>
       <c r="G5" t="n">
-        <v>27470436.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>24.43</v>
-      </c>
+        <v>48523672.7</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,30 +624,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32350</v>
+        <v>2485</v>
       </c>
       <c r="F6" t="n">
-        <v>314.5779</v>
+        <v>42403.6617</v>
       </c>
       <c r="G6" t="n">
-        <v>10176595.1</v>
+        <v>105373099.3</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,94 +656,96 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13650</v>
+        <v>45500</v>
       </c>
       <c r="F7" t="n">
-        <v>745.5381</v>
+        <v>213.2909</v>
       </c>
       <c r="G7" t="n">
-        <v>10176595.1</v>
+        <v>9704734.5</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31950</v>
+        <v>17880</v>
       </c>
       <c r="F8" t="n">
-        <v>318.5163</v>
+        <v>1085.5408</v>
       </c>
       <c r="G8" t="n">
-        <v>10176595.1</v>
+        <v>19409469.1</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>250500</v>
+        <v>4460</v>
       </c>
       <c r="F9" t="n">
-        <v>81.2503</v>
+        <v>3137.3165</v>
       </c>
       <c r="G9" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>13992431.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-17.83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,145 +754,147 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14100</v>
+        <v>3345</v>
       </c>
       <c r="F10" t="n">
-        <v>1443.4887</v>
+        <v>11605.0637</v>
       </c>
       <c r="G10" t="n">
-        <v>20353190.3</v>
+        <v>38818938.1</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>31300</v>
+        <v>12120</v>
       </c>
       <c r="F11" t="n">
-        <v>1954.4702</v>
+        <v>820.878</v>
       </c>
       <c r="G11" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H11" t="n">
-        <v>6.83</v>
-      </c>
+        <v>9949041.199999999</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2355</v>
+        <v>248000</v>
       </c>
       <c r="F12" t="n">
-        <v>65496.7248</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>154244786.8</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15810</v>
+        <v>222500</v>
       </c>
       <c r="F13" t="n">
-        <v>5149.4473</v>
+        <v>178.8592</v>
       </c>
       <c r="G13" t="n">
-        <v>81412761.09999999</v>
+        <v>39796164.7</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>56700</v>
+        <v>54500</v>
       </c>
       <c r="F14" t="n">
-        <v>179.4814</v>
+        <v>504.0447</v>
       </c>
       <c r="G14" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -900,12 +904,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -914,162 +918,158 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4660</v>
+        <v>32350</v>
       </c>
       <c r="F15" t="n">
-        <v>4367.6374</v>
+        <v>314.5779</v>
       </c>
       <c r="G15" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>44600</v>
+        <v>13650</v>
       </c>
       <c r="F16" t="n">
-        <v>1359.3974</v>
+        <v>745.5381</v>
       </c>
       <c r="G16" t="n">
-        <v>60629123.5</v>
+        <v>10176595.1</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20300</v>
+        <v>31950</v>
       </c>
       <c r="F17" t="n">
-        <v>1162.9429</v>
+        <v>318.5163</v>
       </c>
       <c r="G17" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7.9</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13160</v>
+        <v>250500</v>
       </c>
       <c r="F18" t="n">
-        <v>767.846</v>
+        <v>81.2503</v>
       </c>
       <c r="G18" t="n">
-        <v>10104853.9</v>
+        <v>20353190.3</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49050</v>
+        <v>14100</v>
       </c>
       <c r="F19" t="n">
-        <v>357.1039</v>
+        <v>1443.4887</v>
       </c>
       <c r="G19" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1078,64 +1078,64 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37100</v>
+        <v>31300</v>
       </c>
       <c r="F20" t="n">
-        <v>604.321</v>
+        <v>1954.4702</v>
       </c>
       <c r="G20" t="n">
-        <v>22420310.5</v>
+        <v>61174916</v>
       </c>
       <c r="H20" t="n">
-        <v>15.04</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>123700</v>
+        <v>2355</v>
       </c>
       <c r="F21" t="n">
-        <v>490.1303</v>
+        <v>65496.7248</v>
       </c>
       <c r="G21" t="n">
-        <v>60629123.5</v>
+        <v>154244786.8</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1144,62 +1144,62 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>41150</v>
+        <v>15810</v>
       </c>
       <c r="F22" t="n">
-        <v>491.1229</v>
+        <v>5149.4473</v>
       </c>
       <c r="G22" t="n">
-        <v>20209707.8</v>
+        <v>81412761.09999999</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>31500</v>
+        <v>56700</v>
       </c>
       <c r="F23" t="n">
-        <v>320.789</v>
+        <v>179.4814</v>
       </c>
       <c r="G23" t="n">
-        <v>10104853.9</v>
+        <v>10176595.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228500</v>
+        <v>4660</v>
       </c>
       <c r="F24" t="n">
-        <v>88.4451</v>
+        <v>4367.6374</v>
       </c>
       <c r="G24" t="n">
-        <v>20209707.8</v>
+        <v>20353190.3</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1226,31 +1226,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>88500</v>
+        <v>44600</v>
       </c>
       <c r="F25" t="n">
-        <v>900.2261</v>
+        <v>1359.3974</v>
       </c>
       <c r="G25" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1260,12 +1258,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1274,16 +1272,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>130100</v>
+        <v>20300</v>
       </c>
       <c r="F26" t="n">
-        <v>314.8563</v>
+        <v>1162.9429</v>
       </c>
       <c r="G26" t="n">
-        <v>40962809.6</v>
+        <v>23607739.9</v>
       </c>
       <c r="H26" t="n">
-        <v>8.33</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="27">
@@ -1294,27 +1292,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2325</v>
+        <v>13160</v>
       </c>
       <c r="F27" t="n">
-        <v>21730.8686</v>
+        <v>767.846</v>
       </c>
       <c r="G27" t="n">
-        <v>50524269.6</v>
+        <v>10104853.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1326,29 +1324,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>64700</v>
+        <v>49050</v>
       </c>
       <c r="F28" t="n">
-        <v>468.5404</v>
+        <v>357.1039</v>
       </c>
       <c r="G28" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1358,108 +1358,110 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4670</v>
+        <v>37100</v>
       </c>
       <c r="F29" t="n">
-        <v>6491.3408</v>
+        <v>604.321</v>
       </c>
       <c r="G29" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2120</v>
+        <v>123700</v>
       </c>
       <c r="F30" t="n">
-        <v>63879.7502</v>
+        <v>490.1303</v>
       </c>
       <c r="G30" t="n">
-        <v>135425070.4</v>
+        <v>60629123.5</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2120</v>
+        <v>41150</v>
       </c>
       <c r="F31" t="n">
-        <v>3453.9051</v>
+        <v>491.1229</v>
       </c>
       <c r="G31" t="n">
-        <v>7322278.8</v>
+        <v>20209707.8</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1468,248 +1470,248 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22900</v>
+        <v>31500</v>
       </c>
       <c r="F32" t="n">
-        <v>1397.6406</v>
+        <v>320.789</v>
       </c>
       <c r="G32" t="n">
-        <v>32005969</v>
+        <v>10104853.9</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>73600</v>
+        <v>228500</v>
       </c>
       <c r="F33" t="n">
-        <v>299.9614</v>
+        <v>88.4451</v>
       </c>
       <c r="G33" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H33" t="n">
-        <v>16.09</v>
-      </c>
+        <v>20209707.8</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2215</v>
+        <v>88500</v>
       </c>
       <c r="F34" t="n">
-        <v>28224.978</v>
+        <v>900.2261</v>
       </c>
       <c r="G34" t="n">
-        <v>62518326.2</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>43800</v>
+        <v>130100</v>
       </c>
       <c r="F35" t="n">
-        <v>504.0447</v>
+        <v>314.8563</v>
       </c>
       <c r="G35" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>23650</v>
+        <v>2325</v>
       </c>
       <c r="F36" t="n">
-        <v>451.106</v>
+        <v>21730.8686</v>
       </c>
       <c r="G36" t="n">
-        <v>10668656.3</v>
+        <v>50524269.6</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5730</v>
+        <v>64700</v>
       </c>
       <c r="F37" t="n">
-        <v>3723.7893</v>
+        <v>468.5404</v>
       </c>
       <c r="G37" t="n">
-        <v>21337312.7</v>
+        <v>30314561.7</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6080</v>
+        <v>4670</v>
       </c>
       <c r="F38" t="n">
-        <v>3255.5051</v>
+        <v>6491.3408</v>
       </c>
       <c r="G38" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>30314561.7</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>95200</v>
+        <v>2120</v>
       </c>
       <c r="F39" t="n">
-        <v>221.6088</v>
+        <v>63879.7502</v>
       </c>
       <c r="G39" t="n">
-        <v>21097154.4</v>
+        <v>135425070.4</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1724,88 +1726,90 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2205</v>
+        <v>2120</v>
       </c>
       <c r="F40" t="n">
-        <v>52623.2877</v>
+        <v>3453.9051</v>
       </c>
       <c r="G40" t="n">
-        <v>116034349.3</v>
+        <v>7322278.8</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>58700</v>
+        <v>22900</v>
       </c>
       <c r="F41" t="n">
-        <v>357.1039</v>
+        <v>1397.6406</v>
       </c>
       <c r="G41" t="n">
-        <v>20961998.6</v>
+        <v>32005969</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13250</v>
+        <v>73600</v>
       </c>
       <c r="F42" t="n">
-        <v>791.0188000000001</v>
+        <v>299.9614</v>
       </c>
       <c r="G42" t="n">
-        <v>10480999.3</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1824,54 +1828,52 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2360</v>
+        <v>2215</v>
       </c>
       <c r="F43" t="n">
-        <v>66616.5209</v>
+        <v>28224.978</v>
       </c>
       <c r="G43" t="n">
-        <v>157214989.3</v>
+        <v>62518326.2</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>38300</v>
+        <v>43800</v>
       </c>
       <c r="F44" t="n">
-        <v>500.7861</v>
+        <v>504.0447</v>
       </c>
       <c r="G44" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>22077158.2</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1890,128 +1892,128 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>21150</v>
+        <v>23650</v>
       </c>
       <c r="F45" t="n">
-        <v>495.5555</v>
+        <v>451.106</v>
       </c>
       <c r="G45" t="n">
-        <v>10480999.3</v>
+        <v>10668656.3</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>23650</v>
+        <v>5730</v>
       </c>
       <c r="F46" t="n">
-        <v>832.6201</v>
+        <v>3723.7893</v>
       </c>
       <c r="G46" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.28</v>
-      </c>
+        <v>21337312.7</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>12310</v>
+        <v>6080</v>
       </c>
       <c r="F47" t="n">
-        <v>2480.1654</v>
+        <v>3255.5051</v>
       </c>
       <c r="G47" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>40650</v>
+        <v>95200</v>
       </c>
       <c r="F48" t="n">
-        <v>751.0661</v>
+        <v>221.6088</v>
       </c>
       <c r="G48" t="n">
-        <v>30530836.4</v>
+        <v>21097154.4</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2020,126 +2022,126 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>283500</v>
+        <v>2205</v>
       </c>
       <c r="F49" t="n">
-        <v>71.795</v>
+        <v>52623.2877</v>
       </c>
       <c r="G49" t="n">
-        <v>20353890.9</v>
+        <v>116034349.3</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2390</v>
+        <v>58700</v>
       </c>
       <c r="F50" t="n">
-        <v>42581.3618</v>
+        <v>357.1039</v>
       </c>
       <c r="G50" t="n">
-        <v>101769454.6</v>
+        <v>20961998.6</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>20450</v>
+        <v>13250</v>
       </c>
       <c r="F51" t="n">
-        <v>995.3003</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>20353890.9</v>
+        <v>10480999.3</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>30200</v>
+        <v>2360</v>
       </c>
       <c r="F52" t="n">
-        <v>359.55</v>
+        <v>66616.5209</v>
       </c>
       <c r="G52" t="n">
-        <v>10858410.6</v>
+        <v>157214989.3</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2148,32 +2150,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>208500</v>
+        <v>38300</v>
       </c>
       <c r="F53" t="n">
-        <v>338</v>
+        <v>500.7861</v>
       </c>
       <c r="G53" t="n">
-        <v>70473000</v>
+        <v>19180107.1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.97</v>
+        <v>-11.87</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2182,52 +2184,54 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>17720</v>
+        <v>21150</v>
       </c>
       <c r="F54" t="n">
-        <v>94.9217</v>
+        <v>495.5555</v>
       </c>
       <c r="G54" t="n">
-        <v>1682012.5</v>
+        <v>10480999.3</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100500</v>
+        <v>23650</v>
       </c>
       <c r="F55" t="n">
-        <v>8.9518</v>
+        <v>832.6201</v>
       </c>
       <c r="G55" t="n">
-        <v>899652.6</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2242,34 +2246,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>11410</v>
+        <v>12310</v>
       </c>
       <c r="F56" t="n">
-        <v>6321.2722</v>
+        <v>2480.1654</v>
       </c>
       <c r="G56" t="n">
-        <v>72125715.8</v>
+        <v>30530836.4</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2278,30 +2282,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>12880</v>
+        <v>40650</v>
       </c>
       <c r="F57" t="n">
-        <v>713.2027</v>
+        <v>751.0661</v>
       </c>
       <c r="G57" t="n">
-        <v>9186050.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2310,77 +2314,77 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>21200</v>
+        <v>283500</v>
       </c>
       <c r="F58" t="n">
-        <v>120.8659</v>
+        <v>71.795</v>
       </c>
       <c r="G58" t="n">
-        <v>2562357.9</v>
+        <v>20353890.9</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>27700</v>
+        <v>2390</v>
       </c>
       <c r="F59" t="n">
-        <v>161.1835</v>
+        <v>42581.3618</v>
       </c>
       <c r="G59" t="n">
-        <v>4464784.2</v>
+        <v>101769454.6</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>21500</v>
+        <v>20450</v>
       </c>
       <c r="F60" t="n">
-        <v>129.2032</v>
+        <v>995.3003</v>
       </c>
       <c r="G60" t="n">
-        <v>2777868.4</v>
+        <v>20353890.9</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2392,12 +2396,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2406,13 +2410,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>34100</v>
+        <v>30200</v>
       </c>
       <c r="F61" t="n">
-        <v>21.679</v>
+        <v>359.55</v>
       </c>
       <c r="G61" t="n">
-        <v>739252.6</v>
+        <v>10858410.6</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2424,29 +2428,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>40850</v>
+        <v>208500</v>
       </c>
       <c r="F62" t="n">
-        <v>123.3915</v>
+        <v>338</v>
       </c>
       <c r="G62" t="n">
-        <v>5040542.1</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2456,12 +2462,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2470,13 +2476,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308000</v>
+        <v>17720</v>
       </c>
       <c r="F63" t="n">
-        <v>9.1744</v>
+        <v>94.9217</v>
       </c>
       <c r="G63" t="n">
-        <v>2825715.8</v>
+        <v>1682012.5</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2488,27 +2494,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6330</v>
+        <v>100500</v>
       </c>
       <c r="F64" t="n">
-        <v>50.5051</v>
+        <v>8.9518</v>
       </c>
       <c r="G64" t="n">
-        <v>319697.4</v>
+        <v>899652.6</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2520,27 +2526,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>31700</v>
+        <v>11410</v>
       </c>
       <c r="F65" t="n">
-        <v>158.7408</v>
+        <v>6321.2722</v>
       </c>
       <c r="G65" t="n">
-        <v>5032084.2</v>
+        <v>72125715.8</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2552,12 +2558,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2566,13 +2572,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>68700</v>
+        <v>12880</v>
       </c>
       <c r="F66" t="n">
-        <v>16.0386</v>
+        <v>713.2027</v>
       </c>
       <c r="G66" t="n">
-        <v>1101852.6</v>
+        <v>9186050.6</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2584,27 +2590,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>256000</v>
+        <v>21200</v>
       </c>
       <c r="F67" t="n">
-        <v>45.4873</v>
+        <v>120.8659</v>
       </c>
       <c r="G67" t="n">
-        <v>11644736.8</v>
+        <v>2562357.9</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2616,27 +2622,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>91100</v>
+        <v>27700</v>
       </c>
       <c r="F68" t="n">
-        <v>19.6174</v>
+        <v>161.1835</v>
       </c>
       <c r="G68" t="n">
-        <v>1787142.1</v>
+        <v>4464784.2</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2648,27 +2654,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>130900</v>
+        <v>21500</v>
       </c>
       <c r="F69" t="n">
-        <v>89.1437</v>
+        <v>129.2032</v>
       </c>
       <c r="G69" t="n">
-        <v>11668905.3</v>
+        <v>2777868.4</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2680,12 +2686,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2694,13 +2700,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2400</v>
+        <v>34100</v>
       </c>
       <c r="F70" t="n">
-        <v>32820.1843</v>
+        <v>21.679</v>
       </c>
       <c r="G70" t="n">
-        <v>78768442.40000001</v>
+        <v>739252.6</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2712,12 +2718,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2726,13 +2732,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>41150</v>
+        <v>40850</v>
       </c>
       <c r="F71" t="n">
-        <v>38.7861</v>
+        <v>123.3915</v>
       </c>
       <c r="G71" t="n">
-        <v>1596047.4</v>
+        <v>5040542.1</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2744,27 +2750,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>49450</v>
+        <v>308000</v>
       </c>
       <c r="F72" t="n">
-        <v>83.90349999999999</v>
+        <v>9.1744</v>
       </c>
       <c r="G72" t="n">
-        <v>4149029</v>
+        <v>2825715.8</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2776,27 +2782,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>24750</v>
+        <v>6330</v>
       </c>
       <c r="F73" t="n">
-        <v>23.3799</v>
+        <v>50.5051</v>
       </c>
       <c r="G73" t="n">
-        <v>578652.6</v>
+        <v>319697.4</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2808,12 +2814,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2822,96 +2828,94 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5450</v>
+        <v>31700</v>
       </c>
       <c r="F74" t="n">
-        <v>220.6267</v>
+        <v>158.7408</v>
       </c>
       <c r="G74" t="n">
-        <v>1202415.4</v>
+        <v>5032084.2</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>327000</v>
+        <v>68700</v>
       </c>
       <c r="F75" t="n">
-        <v>54</v>
+        <v>16.0386</v>
       </c>
       <c r="G75" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>1101852.6</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5130</v>
+        <v>256000</v>
       </c>
       <c r="F76" t="n">
-        <v>4001.7913</v>
+        <v>45.4873</v>
       </c>
       <c r="G76" t="n">
-        <v>20529189.5</v>
+        <v>11644736.8</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2920,128 +2924,126 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>27100</v>
+        <v>91100</v>
       </c>
       <c r="F77" t="n">
-        <v>376</v>
+        <v>19.6174</v>
       </c>
       <c r="G77" t="n">
-        <v>10189600</v>
+        <v>1787142.1</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>67600</v>
+        <v>130900</v>
       </c>
       <c r="F78" t="n">
-        <v>998</v>
+        <v>89.1437</v>
       </c>
       <c r="G78" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>11668905.3</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>11900</v>
+        <v>2400</v>
       </c>
       <c r="F79" t="n">
-        <v>856</v>
+        <v>32820.1843</v>
       </c>
       <c r="G79" t="n">
-        <v>10186400</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>29300</v>
+        <v>41150</v>
       </c>
       <c r="F80" t="n">
-        <v>2434</v>
+        <v>38.7861</v>
       </c>
       <c r="G80" t="n">
-        <v>71316200</v>
+        <v>1596047.4</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3050,30 +3052,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>119300</v>
+        <v>49450</v>
       </c>
       <c r="F81" t="n">
-        <v>171</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>20400300</v>
+        <v>4149029</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3082,378 +3084,376 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2445</v>
+        <v>24750</v>
       </c>
       <c r="F82" t="n">
-        <v>82456</v>
+        <v>23.3799</v>
       </c>
       <c r="G82" t="n">
-        <v>201604920</v>
+        <v>578652.6</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>18910</v>
+        <v>5450</v>
       </c>
       <c r="F83" t="n">
-        <v>1068.0212</v>
+        <v>220.6267</v>
       </c>
       <c r="G83" t="n">
-        <v>20196280</v>
+        <v>1202415.4</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>32250</v>
+        <v>327000</v>
       </c>
       <c r="F84" t="n">
-        <v>626</v>
+        <v>54</v>
       </c>
       <c r="G84" t="n">
-        <v>20188500</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>82500</v>
+        <v>5130</v>
       </c>
       <c r="F85" t="n">
-        <v>204</v>
+        <v>4001.7913</v>
       </c>
       <c r="G85" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>20529189.5</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>56800</v>
+        <v>27100</v>
       </c>
       <c r="F86" t="n">
-        <v>258</v>
+        <v>376</v>
       </c>
       <c r="G86" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>10189600</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>83700</v>
+        <v>67600</v>
       </c>
       <c r="F87" t="n">
-        <v>120</v>
+        <v>998</v>
       </c>
       <c r="G87" t="n">
-        <v>10044000</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>43650</v>
+        <v>11900</v>
       </c>
       <c r="F88" t="n">
-        <v>462</v>
+        <v>856</v>
       </c>
       <c r="G88" t="n">
-        <v>20166300</v>
+        <v>10186400</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>59700</v>
+        <v>29300</v>
       </c>
       <c r="F89" t="n">
-        <v>169</v>
+        <v>2434</v>
       </c>
       <c r="G89" t="n">
-        <v>10089300</v>
+        <v>71316200</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>10930</v>
+        <v>119300</v>
       </c>
       <c r="F90" t="n">
-        <v>1833</v>
+        <v>171</v>
       </c>
       <c r="G90" t="n">
-        <v>20034690</v>
+        <v>20400300</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>19850</v>
+        <v>2445</v>
       </c>
       <c r="F91" t="n">
-        <v>505</v>
+        <v>82456</v>
       </c>
       <c r="G91" t="n">
-        <v>10024250</v>
+        <v>201604920</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>26350</v>
+        <v>18910</v>
       </c>
       <c r="F92" t="n">
-        <v>380</v>
+        <v>1068.0212</v>
       </c>
       <c r="G92" t="n">
-        <v>10013000</v>
+        <v>20196280</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>23500</v>
+        <v>32250</v>
       </c>
       <c r="F93" t="n">
-        <v>833</v>
+        <v>626</v>
       </c>
       <c r="G93" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20188500</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3468,66 +3468,70 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>85200</v>
+        <v>82500</v>
       </c>
       <c r="F94" t="n">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="G94" t="n">
-        <v>10053600</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>63400</v>
+        <v>56800</v>
       </c>
       <c r="F95" t="n">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="G95" t="n">
-        <v>20034400</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3536,254 +3540,256 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>110300</v>
+        <v>83700</v>
       </c>
       <c r="F96" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="G96" t="n">
-        <v>10037300</v>
+        <v>10044000</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>66100</v>
+        <v>43650</v>
       </c>
       <c r="F97" t="n">
-        <v>152</v>
+        <v>462</v>
       </c>
       <c r="G97" t="n">
-        <v>10047200</v>
+        <v>20166300</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>25800</v>
+        <v>59700</v>
       </c>
       <c r="F98" t="n">
-        <v>2713</v>
+        <v>169</v>
       </c>
       <c r="G98" t="n">
-        <v>69995400</v>
+        <v>10089300</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>206500</v>
+        <v>10930</v>
       </c>
       <c r="F99" t="n">
-        <v>338</v>
+        <v>1833</v>
       </c>
       <c r="G99" t="n">
-        <v>69797000</v>
+        <v>20034690</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>70100</v>
+        <v>19850</v>
       </c>
       <c r="F100" t="n">
-        <v>998</v>
+        <v>505</v>
       </c>
       <c r="G100" t="n">
-        <v>69959800</v>
+        <v>10024250</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>93300</v>
+        <v>26350</v>
       </c>
       <c r="F101" t="n">
-        <v>214</v>
+        <v>380</v>
       </c>
       <c r="G101" t="n">
-        <v>19966200</v>
+        <v>10013000</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>11300</v>
+        <v>23500</v>
       </c>
       <c r="F102" t="n">
-        <v>4424</v>
+        <v>833</v>
       </c>
       <c r="G102" t="n">
-        <v>49991200</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>19740</v>
+        <v>85200</v>
       </c>
       <c r="F103" t="n">
-        <v>2532</v>
+        <v>118</v>
       </c>
       <c r="G103" t="n">
-        <v>49981680</v>
+        <v>10053600</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3792,77 +3798,77 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>25150</v>
+        <v>63400</v>
       </c>
       <c r="F104" t="n">
-        <v>2385</v>
+        <v>316</v>
       </c>
       <c r="G104" t="n">
-        <v>59982750</v>
+        <v>20034400</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>22050</v>
+        <v>110300</v>
       </c>
       <c r="F105" t="n">
-        <v>2267</v>
+        <v>91</v>
       </c>
       <c r="G105" t="n">
-        <v>49987350</v>
+        <v>10037300</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>43150</v>
+        <v>66100</v>
       </c>
       <c r="F106" t="n">
-        <v>1390</v>
+        <v>152</v>
       </c>
       <c r="G106" t="n">
-        <v>59978500</v>
+        <v>10047200</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3874,12 +3880,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3888,13 +3894,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>310000</v>
+        <v>25800</v>
       </c>
       <c r="F107" t="n">
-        <v>225</v>
+        <v>2713</v>
       </c>
       <c r="G107" t="n">
-        <v>69750000</v>
+        <v>69995400</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3906,12 +3912,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3920,13 +3926,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6240</v>
+        <v>206500</v>
       </c>
       <c r="F108" t="n">
-        <v>3205</v>
+        <v>338</v>
       </c>
       <c r="G108" t="n">
-        <v>19999200</v>
+        <v>69797000</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3938,12 +3944,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3952,13 +3958,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>24000</v>
+        <v>70100</v>
       </c>
       <c r="F109" t="n">
-        <v>833</v>
+        <v>998</v>
       </c>
       <c r="G109" t="n">
-        <v>19992000</v>
+        <v>69959800</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3970,12 +3976,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3984,13 +3990,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>90300</v>
+        <v>93300</v>
       </c>
       <c r="F110" t="n">
-        <v>442</v>
+        <v>214</v>
       </c>
       <c r="G110" t="n">
-        <v>39912600</v>
+        <v>19966200</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -4002,12 +4008,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4016,13 +4022,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>279500</v>
+        <v>11300</v>
       </c>
       <c r="F111" t="n">
-        <v>357</v>
+        <v>4424</v>
       </c>
       <c r="G111" t="n">
-        <v>99781500</v>
+        <v>49991200</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4034,12 +4040,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4048,13 +4054,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>366000</v>
+        <v>19740</v>
       </c>
       <c r="F112" t="n">
-        <v>54</v>
+        <v>2532</v>
       </c>
       <c r="G112" t="n">
-        <v>19764000</v>
+        <v>49981680</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4066,12 +4072,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4080,13 +4086,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>91000</v>
+        <v>25150</v>
       </c>
       <c r="F113" t="n">
-        <v>659</v>
+        <v>2385</v>
       </c>
       <c r="G113" t="n">
-        <v>59969000</v>
+        <v>59982750</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4098,12 +4104,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4112,13 +4118,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>120100</v>
+        <v>22050</v>
       </c>
       <c r="F114" t="n">
-        <v>666</v>
+        <v>2267</v>
       </c>
       <c r="G114" t="n">
-        <v>79986600</v>
+        <v>49987350</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4130,12 +4136,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4144,13 +4150,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2405</v>
+        <v>43150</v>
       </c>
       <c r="F115" t="n">
-        <v>415800</v>
+        <v>1390</v>
       </c>
       <c r="G115" t="n">
-        <v>999999000</v>
+        <v>59978500</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4162,12 +4168,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4176,13 +4182,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>69000</v>
+        <v>310000</v>
       </c>
       <c r="F116" t="n">
-        <v>579</v>
+        <v>225</v>
       </c>
       <c r="G116" t="n">
-        <v>39951000</v>
+        <v>69750000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4194,12 +4200,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4208,13 +4214,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>42300</v>
+        <v>6240</v>
       </c>
       <c r="F117" t="n">
-        <v>709</v>
+        <v>3205</v>
       </c>
       <c r="G117" t="n">
-        <v>29990700</v>
+        <v>19999200</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4226,29 +4232,317 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>138080</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F118" t="n">
+        <v>833</v>
+      </c>
+      <c r="G118" t="n">
+        <v>19992000</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>141080</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>90300</v>
+      </c>
+      <c r="F119" t="n">
+        <v>442</v>
+      </c>
+      <c r="G119" t="n">
+        <v>39912600</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>279500</v>
+      </c>
+      <c r="F120" t="n">
+        <v>357</v>
+      </c>
+      <c r="G120" t="n">
+        <v>99781500</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F121" t="n">
+        <v>54</v>
+      </c>
+      <c r="G121" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F122" t="n">
+        <v>659</v>
+      </c>
+      <c r="G122" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F123" t="n">
+        <v>666</v>
+      </c>
+      <c r="G123" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F124" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G124" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F125" t="n">
+        <v>579</v>
+      </c>
+      <c r="G125" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F126" t="n">
+        <v>709</v>
+      </c>
+      <c r="G126" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E118" t="n">
+      <c r="E127" t="n">
         <v>23350</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F127" t="n">
         <v>856</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G127" t="n">
         <v>19987600</v>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,196 +473,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>79100</v>
+        <v>28650</v>
       </c>
       <c r="F2" t="n">
-        <v>205.0482</v>
+        <v>345.7839</v>
       </c>
       <c r="G2" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25250</v>
+        <v>11600</v>
       </c>
       <c r="F3" t="n">
-        <v>768.6917999999999</v>
+        <v>854.0266</v>
       </c>
       <c r="G3" t="n">
-        <v>19409469.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12510</v>
+        <v>131000</v>
       </c>
       <c r="F4" t="n">
-        <v>1443.4887</v>
+        <v>75.6237</v>
       </c>
       <c r="G4" t="n">
-        <v>18058043.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-11.28</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>126500</v>
+        <v>67100</v>
       </c>
       <c r="F5" t="n">
-        <v>383.5863</v>
+        <v>147.641</v>
       </c>
       <c r="G5" t="n">
-        <v>48523672.7</v>
+        <v>9906708.4</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2485</v>
+        <v>4830</v>
       </c>
       <c r="F6" t="n">
-        <v>42403.6617</v>
+        <v>2051.0783</v>
       </c>
       <c r="G6" t="n">
-        <v>105373099.3</v>
+        <v>9906708.4</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>45500</v>
+        <v>9430</v>
       </c>
       <c r="F7" t="n">
-        <v>213.2909</v>
+        <v>2101.1046</v>
       </c>
       <c r="G7" t="n">
-        <v>9704734.5</v>
+        <v>19813416.7</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -674,29 +670,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17880</v>
+        <v>79100</v>
       </c>
       <c r="F8" t="n">
-        <v>1085.5408</v>
+        <v>205.0482</v>
       </c>
       <c r="G8" t="n">
-        <v>19409469.1</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>16219315.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-15.22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,31 +704,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4460</v>
+        <v>25250</v>
       </c>
       <c r="F9" t="n">
-        <v>3137.3165</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>13992431.8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-17.83</v>
-      </c>
+        <v>19409469.1</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -740,110 +736,110 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3345</v>
+        <v>12510</v>
       </c>
       <c r="F10" t="n">
-        <v>11605.0637</v>
+        <v>1443.4887</v>
       </c>
       <c r="G10" t="n">
-        <v>38818938.1</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>18058043.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-11.28</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12120</v>
+        <v>126500</v>
       </c>
       <c r="F11" t="n">
-        <v>820.878</v>
+        <v>383.5863</v>
       </c>
       <c r="G11" t="n">
-        <v>9949041.199999999</v>
+        <v>48523672.7</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248000</v>
+        <v>2485</v>
       </c>
       <c r="F12" t="n">
-        <v>81.12909999999999</v>
+        <v>42403.6617</v>
       </c>
       <c r="G12" t="n">
-        <v>20120019.7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-19.98</v>
-      </c>
+        <v>105373099.3</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -852,150 +848,150 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222500</v>
+        <v>45500</v>
       </c>
       <c r="F13" t="n">
-        <v>178.8592</v>
+        <v>213.2909</v>
       </c>
       <c r="G13" t="n">
-        <v>39796164.7</v>
+        <v>9704734.5</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54500</v>
+        <v>17880</v>
       </c>
       <c r="F14" t="n">
-        <v>504.0447</v>
+        <v>1085.5408</v>
       </c>
       <c r="G14" t="n">
-        <v>27470436.6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>24.43</v>
-      </c>
+        <v>19409469.1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>32350</v>
+        <v>4460</v>
       </c>
       <c r="F15" t="n">
-        <v>314.5779</v>
+        <v>3137.3165</v>
       </c>
       <c r="G15" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>13992431.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-17.83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13650</v>
+        <v>3345</v>
       </c>
       <c r="F16" t="n">
-        <v>745.5381</v>
+        <v>11605.0637</v>
       </c>
       <c r="G16" t="n">
-        <v>10176595.1</v>
+        <v>38818938.1</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>31950</v>
+        <v>12120</v>
       </c>
       <c r="F17" t="n">
-        <v>318.5163</v>
+        <v>820.878</v>
       </c>
       <c r="G17" t="n">
-        <v>10176595.1</v>
+        <v>9949041.199999999</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1010,66 +1006,68 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>250500</v>
+        <v>248000</v>
       </c>
       <c r="F18" t="n">
-        <v>81.2503</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14100</v>
+        <v>222500</v>
       </c>
       <c r="F19" t="n">
-        <v>1443.4887</v>
+        <v>178.8592</v>
       </c>
       <c r="G19" t="n">
-        <v>20353190.3</v>
+        <v>39796164.7</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1078,16 +1076,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31300</v>
+        <v>54500</v>
       </c>
       <c r="F20" t="n">
-        <v>1954.4702</v>
+        <v>504.0447</v>
       </c>
       <c r="G20" t="n">
-        <v>61174916</v>
+        <v>27470436.6</v>
       </c>
       <c r="H20" t="n">
-        <v>6.83</v>
+        <v>24.43</v>
       </c>
     </row>
     <row r="21">
@@ -1098,12 +1096,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1112,13 +1110,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2355</v>
+        <v>32350</v>
       </c>
       <c r="F21" t="n">
-        <v>65496.7248</v>
+        <v>314.5779</v>
       </c>
       <c r="G21" t="n">
-        <v>154244786.8</v>
+        <v>10176595.1</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1130,27 +1128,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>15810</v>
+        <v>13650</v>
       </c>
       <c r="F22" t="n">
-        <v>5149.4473</v>
+        <v>745.5381</v>
       </c>
       <c r="G22" t="n">
-        <v>81412761.09999999</v>
+        <v>10176595.1</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1162,12 +1160,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1176,10 +1174,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>56700</v>
+        <v>31950</v>
       </c>
       <c r="F23" t="n">
-        <v>179.4814</v>
+        <v>318.5163</v>
       </c>
       <c r="G23" t="n">
         <v>10176595.1</v>
@@ -1194,12 +1192,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1208,10 +1206,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4660</v>
+        <v>250500</v>
       </c>
       <c r="F24" t="n">
-        <v>4367.6374</v>
+        <v>81.2503</v>
       </c>
       <c r="G24" t="n">
         <v>20353190.3</v>
@@ -1221,17 +1219,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1240,30 +1238,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>44600</v>
+        <v>14100</v>
       </c>
       <c r="F25" t="n">
-        <v>1359.3974</v>
+        <v>1443.4887</v>
       </c>
       <c r="G25" t="n">
-        <v>60629123.5</v>
+        <v>20353190.3</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1272,147 +1270,143 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>20300</v>
+        <v>31300</v>
       </c>
       <c r="F26" t="n">
-        <v>1162.9429</v>
+        <v>1954.4702</v>
       </c>
       <c r="G26" t="n">
-        <v>23607739.9</v>
+        <v>61174916</v>
       </c>
       <c r="H26" t="n">
-        <v>7.9</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>13160</v>
+        <v>2355</v>
       </c>
       <c r="F27" t="n">
-        <v>767.846</v>
+        <v>65496.7248</v>
       </c>
       <c r="G27" t="n">
-        <v>10104853.9</v>
+        <v>154244786.8</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49050</v>
+        <v>15810</v>
       </c>
       <c r="F28" t="n">
-        <v>357.1039</v>
+        <v>5149.4473</v>
       </c>
       <c r="G28" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>81412761.09999999</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>37100</v>
+        <v>56700</v>
       </c>
       <c r="F29" t="n">
-        <v>604.321</v>
+        <v>179.4814</v>
       </c>
       <c r="G29" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>15.04</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>123700</v>
+        <v>4660</v>
       </c>
       <c r="F30" t="n">
-        <v>490.1303</v>
+        <v>4367.6374</v>
       </c>
       <c r="G30" t="n">
-        <v>60629123.5</v>
+        <v>20353190.3</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1424,12 +1418,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1438,13 +1432,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>41150</v>
+        <v>44600</v>
       </c>
       <c r="F31" t="n">
-        <v>491.1229</v>
+        <v>1359.3974</v>
       </c>
       <c r="G31" t="n">
-        <v>20209707.8</v>
+        <v>60629123.5</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1456,29 +1450,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>31500</v>
+        <v>20300</v>
       </c>
       <c r="F32" t="n">
-        <v>320.789</v>
+        <v>1162.9429</v>
       </c>
       <c r="G32" t="n">
-        <v>10104853.9</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>23607739.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1488,27 +1484,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228500</v>
+        <v>13160</v>
       </c>
       <c r="F33" t="n">
-        <v>88.4451</v>
+        <v>767.846</v>
       </c>
       <c r="G33" t="n">
-        <v>20209707.8</v>
+        <v>10104853.9</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1520,12 +1516,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1534,16 +1530,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>88500</v>
+        <v>49050</v>
       </c>
       <c r="F34" t="n">
-        <v>900.2261</v>
+        <v>357.1039</v>
       </c>
       <c r="G34" t="n">
-        <v>79670012.59999999</v>
+        <v>17515946</v>
       </c>
       <c r="H34" t="n">
-        <v>-3.84</v>
+        <v>-16.44</v>
       </c>
     </row>
     <row r="35">
@@ -1554,12 +1550,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1568,16 +1564,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>130100</v>
+        <v>37100</v>
       </c>
       <c r="F35" t="n">
-        <v>314.8563</v>
+        <v>604.321</v>
       </c>
       <c r="G35" t="n">
-        <v>40962809.6</v>
+        <v>22420310.5</v>
       </c>
       <c r="H35" t="n">
-        <v>8.33</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="36">
@@ -1588,27 +1584,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2325</v>
+        <v>123700</v>
       </c>
       <c r="F36" t="n">
-        <v>21730.8686</v>
+        <v>490.1303</v>
       </c>
       <c r="G36" t="n">
-        <v>50524269.6</v>
+        <v>60629123.5</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1620,12 +1616,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1634,13 +1630,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>64700</v>
+        <v>41150</v>
       </c>
       <c r="F37" t="n">
-        <v>468.5404</v>
+        <v>491.1229</v>
       </c>
       <c r="G37" t="n">
-        <v>30314561.7</v>
+        <v>20209707.8</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1652,44 +1648,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4670</v>
+        <v>31500</v>
       </c>
       <c r="F38" t="n">
-        <v>6491.3408</v>
+        <v>320.789</v>
       </c>
       <c r="G38" t="n">
-        <v>30314561.7</v>
+        <v>10104853.9</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1698,160 +1694,162 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2120</v>
+        <v>228500</v>
       </c>
       <c r="F39" t="n">
-        <v>63879.7502</v>
+        <v>88.4451</v>
       </c>
       <c r="G39" t="n">
-        <v>135425070.4</v>
+        <v>20209707.8</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2120</v>
+        <v>88500</v>
       </c>
       <c r="F40" t="n">
-        <v>3453.9051</v>
+        <v>900.2261</v>
       </c>
       <c r="G40" t="n">
-        <v>7322278.8</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>22900</v>
+        <v>130100</v>
       </c>
       <c r="F41" t="n">
-        <v>1397.6406</v>
+        <v>314.8563</v>
       </c>
       <c r="G41" t="n">
-        <v>32005969</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>73600</v>
+        <v>2325</v>
       </c>
       <c r="F42" t="n">
-        <v>299.9614</v>
+        <v>21730.8686</v>
       </c>
       <c r="G42" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H42" t="n">
-        <v>16.09</v>
-      </c>
+        <v>50524269.6</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2215</v>
+        <v>64700</v>
       </c>
       <c r="F43" t="n">
-        <v>28224.978</v>
+        <v>468.5404</v>
       </c>
       <c r="G43" t="n">
-        <v>62518326.2</v>
+        <v>30314561.7</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1860,62 +1858,62 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>43800</v>
+        <v>4670</v>
       </c>
       <c r="F44" t="n">
-        <v>504.0447</v>
+        <v>6491.3408</v>
       </c>
       <c r="G44" t="n">
-        <v>22077158.2</v>
+        <v>30314561.7</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>23650</v>
+        <v>2120</v>
       </c>
       <c r="F45" t="n">
-        <v>451.106</v>
+        <v>63879.7502</v>
       </c>
       <c r="G45" t="n">
-        <v>10668656.3</v>
+        <v>135425070.4</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1924,86 +1922,86 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5730</v>
+        <v>2120</v>
       </c>
       <c r="F46" t="n">
-        <v>3723.7893</v>
+        <v>3453.9051</v>
       </c>
       <c r="G46" t="n">
-        <v>21337312.7</v>
+        <v>7322278.8</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6080</v>
+        <v>22900</v>
       </c>
       <c r="F47" t="n">
-        <v>3255.5051</v>
+        <v>1397.6406</v>
       </c>
       <c r="G47" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>32005969</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>95200</v>
+        <v>73600</v>
       </c>
       <c r="F48" t="n">
-        <v>221.6088</v>
+        <v>299.9614</v>
       </c>
       <c r="G48" t="n">
-        <v>21097154.4</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2018,34 +2016,34 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2205</v>
+        <v>2215</v>
       </c>
       <c r="F49" t="n">
-        <v>52623.2877</v>
+        <v>28224.978</v>
       </c>
       <c r="G49" t="n">
-        <v>116034349.3</v>
+        <v>62518326.2</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2054,30 +2052,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>58700</v>
+        <v>43800</v>
       </c>
       <c r="F50" t="n">
-        <v>357.1039</v>
+        <v>504.0447</v>
       </c>
       <c r="G50" t="n">
-        <v>20961998.6</v>
+        <v>22077158.2</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2086,30 +2084,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>13250</v>
+        <v>23650</v>
       </c>
       <c r="F51" t="n">
-        <v>791.0188000000001</v>
+        <v>451.106</v>
       </c>
       <c r="G51" t="n">
-        <v>10480999.3</v>
+        <v>10668656.3</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2118,30 +2116,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2360</v>
+        <v>5730</v>
       </c>
       <c r="F52" t="n">
-        <v>66616.5209</v>
+        <v>3723.7893</v>
       </c>
       <c r="G52" t="n">
-        <v>157214989.3</v>
+        <v>21337312.7</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2150,32 +2148,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>38300</v>
+        <v>6080</v>
       </c>
       <c r="F53" t="n">
-        <v>500.7861</v>
+        <v>3255.5051</v>
       </c>
       <c r="G53" t="n">
-        <v>19180107.1</v>
+        <v>19793471.1</v>
       </c>
       <c r="H53" t="n">
-        <v>-11.87</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2184,182 +2182,182 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21150</v>
+        <v>95200</v>
       </c>
       <c r="F54" t="n">
-        <v>495.5555</v>
+        <v>221.6088</v>
       </c>
       <c r="G54" t="n">
-        <v>10480999.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>23650</v>
+        <v>2205</v>
       </c>
       <c r="F55" t="n">
-        <v>832.6201</v>
+        <v>52623.2877</v>
       </c>
       <c r="G55" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1.28</v>
-      </c>
+        <v>116034349.3</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>12310</v>
+        <v>58700</v>
       </c>
       <c r="F56" t="n">
-        <v>2480.1654</v>
+        <v>357.1039</v>
       </c>
       <c r="G56" t="n">
-        <v>30530836.4</v>
+        <v>20961998.6</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>40650</v>
+        <v>13250</v>
       </c>
       <c r="F57" t="n">
-        <v>751.0661</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>30530836.4</v>
+        <v>10480999.3</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>283500</v>
+        <v>2360</v>
       </c>
       <c r="F58" t="n">
-        <v>71.795</v>
+        <v>66616.5209</v>
       </c>
       <c r="G58" t="n">
-        <v>20353890.9</v>
+        <v>157214989.3</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2390</v>
+        <v>38300</v>
       </c>
       <c r="F59" t="n">
-        <v>42581.3618</v>
+        <v>500.7861</v>
       </c>
       <c r="G59" t="n">
-        <v>101769454.6</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2374,132 +2372,132 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>20450</v>
+        <v>21150</v>
       </c>
       <c r="F60" t="n">
-        <v>995.3003</v>
+        <v>495.5555</v>
       </c>
       <c r="G60" t="n">
-        <v>20353890.9</v>
+        <v>10480999.3</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>30200</v>
+        <v>23650</v>
       </c>
       <c r="F61" t="n">
-        <v>359.55</v>
+        <v>832.6201</v>
       </c>
       <c r="G61" t="n">
-        <v>10858410.6</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>208500</v>
+        <v>12310</v>
       </c>
       <c r="F62" t="n">
-        <v>338</v>
+        <v>2480.1654</v>
       </c>
       <c r="G62" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.97</v>
-      </c>
+        <v>30530836.4</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>17720</v>
+        <v>40650</v>
       </c>
       <c r="F63" t="n">
-        <v>94.9217</v>
+        <v>751.0661</v>
       </c>
       <c r="G63" t="n">
-        <v>1682012.5</v>
+        <v>30530836.4</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2508,77 +2506,77 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100500</v>
+        <v>283500</v>
       </c>
       <c r="F64" t="n">
-        <v>8.9518</v>
+        <v>71.795</v>
       </c>
       <c r="G64" t="n">
-        <v>899652.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11410</v>
+        <v>2390</v>
       </c>
       <c r="F65" t="n">
-        <v>6321.2722</v>
+        <v>42581.3618</v>
       </c>
       <c r="G65" t="n">
-        <v>72125715.8</v>
+        <v>101769454.6</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12880</v>
+        <v>20450</v>
       </c>
       <c r="F66" t="n">
-        <v>713.2027</v>
+        <v>995.3003</v>
       </c>
       <c r="G66" t="n">
-        <v>9186050.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2590,12 +2588,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2604,13 +2602,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>21200</v>
+        <v>30200</v>
       </c>
       <c r="F67" t="n">
-        <v>120.8659</v>
+        <v>359.55</v>
       </c>
       <c r="G67" t="n">
-        <v>2562357.9</v>
+        <v>10858410.6</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2622,29 +2620,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>27700</v>
+        <v>208500</v>
       </c>
       <c r="F68" t="n">
-        <v>161.1835</v>
+        <v>338</v>
       </c>
       <c r="G68" t="n">
-        <v>4464784.2</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2668,13 +2668,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>21500</v>
+        <v>17720</v>
       </c>
       <c r="F69" t="n">
-        <v>129.2032</v>
+        <v>94.9217</v>
       </c>
       <c r="G69" t="n">
-        <v>2777868.4</v>
+        <v>1682012.5</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>34100</v>
+        <v>100500</v>
       </c>
       <c r="F70" t="n">
-        <v>21.679</v>
+        <v>8.9518</v>
       </c>
       <c r="G70" t="n">
-        <v>739252.6</v>
+        <v>899652.6</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2718,27 +2718,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>40850</v>
+        <v>11410</v>
       </c>
       <c r="F71" t="n">
-        <v>123.3915</v>
+        <v>6321.2722</v>
       </c>
       <c r="G71" t="n">
-        <v>5040542.1</v>
+        <v>72125715.8</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2750,27 +2750,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308000</v>
+        <v>12880</v>
       </c>
       <c r="F72" t="n">
-        <v>9.1744</v>
+        <v>713.2027</v>
       </c>
       <c r="G72" t="n">
-        <v>2825715.8</v>
+        <v>9186050.6</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2782,27 +2782,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6330</v>
+        <v>21200</v>
       </c>
       <c r="F73" t="n">
-        <v>50.5051</v>
+        <v>120.8659</v>
       </c>
       <c r="G73" t="n">
-        <v>319697.4</v>
+        <v>2562357.9</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2828,13 +2828,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>31700</v>
+        <v>27700</v>
       </c>
       <c r="F74" t="n">
-        <v>158.7408</v>
+        <v>161.1835</v>
       </c>
       <c r="G74" t="n">
-        <v>5032084.2</v>
+        <v>4464784.2</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2846,27 +2846,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>68700</v>
+        <v>21500</v>
       </c>
       <c r="F75" t="n">
-        <v>16.0386</v>
+        <v>129.2032</v>
       </c>
       <c r="G75" t="n">
-        <v>1101852.6</v>
+        <v>2777868.4</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2878,27 +2878,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>256000</v>
+        <v>34100</v>
       </c>
       <c r="F76" t="n">
-        <v>45.4873</v>
+        <v>21.679</v>
       </c>
       <c r="G76" t="n">
-        <v>11644736.8</v>
+        <v>739252.6</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2924,13 +2924,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>91100</v>
+        <v>40850</v>
       </c>
       <c r="F77" t="n">
-        <v>19.6174</v>
+        <v>123.3915</v>
       </c>
       <c r="G77" t="n">
-        <v>1787142.1</v>
+        <v>5040542.1</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2942,27 +2942,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>130900</v>
+        <v>308000</v>
       </c>
       <c r="F78" t="n">
-        <v>89.1437</v>
+        <v>9.1744</v>
       </c>
       <c r="G78" t="n">
-        <v>11668905.3</v>
+        <v>2825715.8</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2974,27 +2974,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2400</v>
+        <v>6330</v>
       </c>
       <c r="F79" t="n">
-        <v>32820.1843</v>
+        <v>50.5051</v>
       </c>
       <c r="G79" t="n">
-        <v>78768442.40000001</v>
+        <v>319697.4</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3006,27 +3006,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>41150</v>
+        <v>31700</v>
       </c>
       <c r="F80" t="n">
-        <v>38.7861</v>
+        <v>158.7408</v>
       </c>
       <c r="G80" t="n">
-        <v>1596047.4</v>
+        <v>5032084.2</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>49450</v>
+        <v>68700</v>
       </c>
       <c r="F81" t="n">
-        <v>83.90349999999999</v>
+        <v>16.0386</v>
       </c>
       <c r="G81" t="n">
-        <v>4149029</v>
+        <v>1101852.6</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3070,27 +3070,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>24750</v>
+        <v>256000</v>
       </c>
       <c r="F82" t="n">
-        <v>23.3799</v>
+        <v>45.4873</v>
       </c>
       <c r="G82" t="n">
-        <v>578652.6</v>
+        <v>11644736.8</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3102,110 +3102,108 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5450</v>
+        <v>91100</v>
       </c>
       <c r="F83" t="n">
-        <v>220.6267</v>
+        <v>19.6174</v>
       </c>
       <c r="G83" t="n">
-        <v>1202415.4</v>
+        <v>1787142.1</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>327000</v>
+        <v>130900</v>
       </c>
       <c r="F84" t="n">
-        <v>54</v>
+        <v>89.1437</v>
       </c>
       <c r="G84" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>11668905.3</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5130</v>
+        <v>2400</v>
       </c>
       <c r="F85" t="n">
-        <v>4001.7913</v>
+        <v>32820.1843</v>
       </c>
       <c r="G85" t="n">
-        <v>20529189.5</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3214,324 +3212,322 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>27100</v>
+        <v>41150</v>
       </c>
       <c r="F86" t="n">
-        <v>376</v>
+        <v>38.7861</v>
       </c>
       <c r="G86" t="n">
-        <v>10189600</v>
+        <v>1596047.4</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>67600</v>
+        <v>49450</v>
       </c>
       <c r="F87" t="n">
-        <v>998</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>4149029</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>11900</v>
+        <v>24750</v>
       </c>
       <c r="F88" t="n">
-        <v>856</v>
+        <v>23.3799</v>
       </c>
       <c r="G88" t="n">
-        <v>10186400</v>
+        <v>578652.6</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>29300</v>
+        <v>5450</v>
       </c>
       <c r="F89" t="n">
-        <v>2434</v>
+        <v>220.6267</v>
       </c>
       <c r="G89" t="n">
-        <v>71316200</v>
+        <v>1202415.4</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>119300</v>
+        <v>327000</v>
       </c>
       <c r="F90" t="n">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="G90" t="n">
-        <v>20400300</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2445</v>
+        <v>5130</v>
       </c>
       <c r="F91" t="n">
-        <v>82456</v>
+        <v>4001.7913</v>
       </c>
       <c r="G91" t="n">
-        <v>201604920</v>
+        <v>20529189.5</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>18910</v>
+        <v>27100</v>
       </c>
       <c r="F92" t="n">
-        <v>1068.0212</v>
+        <v>376</v>
       </c>
       <c r="G92" t="n">
-        <v>20196280</v>
+        <v>10189600</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>32250</v>
+        <v>67600</v>
       </c>
       <c r="F93" t="n">
-        <v>626</v>
+        <v>998</v>
       </c>
       <c r="G93" t="n">
-        <v>20188500</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>82500</v>
+        <v>11900</v>
       </c>
       <c r="F94" t="n">
-        <v>204</v>
+        <v>856</v>
       </c>
       <c r="G94" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>10186400</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>56800</v>
+        <v>29300</v>
       </c>
       <c r="F95" t="n">
-        <v>258</v>
+        <v>2434</v>
       </c>
       <c r="G95" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>71316200</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3540,271 +3536,273 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>83700</v>
+        <v>119300</v>
       </c>
       <c r="F96" t="n">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="G96" t="n">
-        <v>10044000</v>
+        <v>20400300</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>43650</v>
+        <v>2445</v>
       </c>
       <c r="F97" t="n">
-        <v>462</v>
+        <v>82456</v>
       </c>
       <c r="G97" t="n">
-        <v>20166300</v>
+        <v>201604920</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>59700</v>
+        <v>18910</v>
       </c>
       <c r="F98" t="n">
-        <v>169</v>
+        <v>1068.0212</v>
       </c>
       <c r="G98" t="n">
-        <v>10089300</v>
+        <v>20196280</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>10930</v>
+        <v>32250</v>
       </c>
       <c r="F99" t="n">
-        <v>1833</v>
+        <v>626</v>
       </c>
       <c r="G99" t="n">
-        <v>20034690</v>
+        <v>20188500</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>19850</v>
+        <v>82500</v>
       </c>
       <c r="F100" t="n">
-        <v>505</v>
+        <v>204</v>
       </c>
       <c r="G100" t="n">
-        <v>10024250</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>26350</v>
+        <v>56800</v>
       </c>
       <c r="F101" t="n">
-        <v>380</v>
+        <v>258</v>
       </c>
       <c r="G101" t="n">
-        <v>10013000</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>23500</v>
+        <v>83700</v>
       </c>
       <c r="F102" t="n">
-        <v>833</v>
+        <v>120</v>
       </c>
       <c r="G102" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10044000</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>85200</v>
+        <v>43650</v>
       </c>
       <c r="F103" t="n">
-        <v>118</v>
+        <v>462</v>
       </c>
       <c r="G103" t="n">
-        <v>10053600</v>
+        <v>20166300</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>63400</v>
+        <v>59700</v>
       </c>
       <c r="F104" t="n">
-        <v>316</v>
+        <v>169</v>
       </c>
       <c r="G104" t="n">
-        <v>20034400</v>
+        <v>10089300</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3816,27 +3814,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>110300</v>
+        <v>10930</v>
       </c>
       <c r="F105" t="n">
-        <v>91</v>
+        <v>1833</v>
       </c>
       <c r="G105" t="n">
-        <v>10037300</v>
+        <v>20034690</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3848,140 +3846,142 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>66100</v>
+        <v>19850</v>
       </c>
       <c r="F106" t="n">
-        <v>152</v>
+        <v>505</v>
       </c>
       <c r="G106" t="n">
-        <v>10047200</v>
+        <v>10024250</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>25800</v>
+        <v>26350</v>
       </c>
       <c r="F107" t="n">
-        <v>2713</v>
+        <v>380</v>
       </c>
       <c r="G107" t="n">
-        <v>69995400</v>
+        <v>10013000</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>206500</v>
+        <v>23500</v>
       </c>
       <c r="F108" t="n">
-        <v>338</v>
+        <v>833</v>
       </c>
       <c r="G108" t="n">
-        <v>69797000</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>70100</v>
+        <v>85200</v>
       </c>
       <c r="F109" t="n">
-        <v>998</v>
+        <v>118</v>
       </c>
       <c r="G109" t="n">
-        <v>69959800</v>
+        <v>10053600</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3990,77 +3990,77 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>93300</v>
+        <v>63400</v>
       </c>
       <c r="F110" t="n">
-        <v>214</v>
+        <v>316</v>
       </c>
       <c r="G110" t="n">
-        <v>19966200</v>
+        <v>20034400</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>11300</v>
+        <v>110300</v>
       </c>
       <c r="F111" t="n">
-        <v>4424</v>
+        <v>91</v>
       </c>
       <c r="G111" t="n">
-        <v>49991200</v>
+        <v>10037300</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>19740</v>
+        <v>66100</v>
       </c>
       <c r="F112" t="n">
-        <v>2532</v>
+        <v>152</v>
       </c>
       <c r="G112" t="n">
-        <v>49981680</v>
+        <v>10047200</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4072,12 +4072,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4086,13 +4086,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F113" t="n">
-        <v>2385</v>
+        <v>2713</v>
       </c>
       <c r="G113" t="n">
-        <v>59982750</v>
+        <v>69995400</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4104,12 +4104,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4118,13 +4118,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>22050</v>
+        <v>206500</v>
       </c>
       <c r="F114" t="n">
-        <v>2267</v>
+        <v>338</v>
       </c>
       <c r="G114" t="n">
-        <v>49987350</v>
+        <v>69797000</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>43150</v>
+        <v>70100</v>
       </c>
       <c r="F115" t="n">
-        <v>1390</v>
+        <v>998</v>
       </c>
       <c r="G115" t="n">
-        <v>59978500</v>
+        <v>69959800</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4182,13 +4182,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>310000</v>
+        <v>93300</v>
       </c>
       <c r="F116" t="n">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G116" t="n">
-        <v>69750000</v>
+        <v>19966200</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4200,12 +4200,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6240</v>
+        <v>11300</v>
       </c>
       <c r="F117" t="n">
-        <v>3205</v>
+        <v>4424</v>
       </c>
       <c r="G117" t="n">
-        <v>19999200</v>
+        <v>49991200</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4246,13 +4246,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>24000</v>
+        <v>19740</v>
       </c>
       <c r="F118" t="n">
-        <v>833</v>
+        <v>2532</v>
       </c>
       <c r="G118" t="n">
-        <v>19992000</v>
+        <v>49981680</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>90300</v>
+        <v>25150</v>
       </c>
       <c r="F119" t="n">
-        <v>442</v>
+        <v>2385</v>
       </c>
       <c r="G119" t="n">
-        <v>39912600</v>
+        <v>59982750</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4296,12 +4296,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>279500</v>
+        <v>22050</v>
       </c>
       <c r="F120" t="n">
-        <v>357</v>
+        <v>2267</v>
       </c>
       <c r="G120" t="n">
-        <v>99781500</v>
+        <v>49987350</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>366000</v>
+        <v>43150</v>
       </c>
       <c r="F121" t="n">
-        <v>54</v>
+        <v>1390</v>
       </c>
       <c r="G121" t="n">
-        <v>19764000</v>
+        <v>59978500</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4360,12 +4360,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4374,13 +4374,13 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>91000</v>
+        <v>310000</v>
       </c>
       <c r="F122" t="n">
-        <v>659</v>
+        <v>225</v>
       </c>
       <c r="G122" t="n">
-        <v>59969000</v>
+        <v>69750000</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4392,12 +4392,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4406,13 +4406,13 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>120100</v>
+        <v>6240</v>
       </c>
       <c r="F123" t="n">
-        <v>666</v>
+        <v>3205</v>
       </c>
       <c r="G123" t="n">
-        <v>79986600</v>
+        <v>19999200</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2405</v>
+        <v>24000</v>
       </c>
       <c r="F124" t="n">
-        <v>415800</v>
+        <v>833</v>
       </c>
       <c r="G124" t="n">
-        <v>999999000</v>
+        <v>19992000</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4470,13 +4470,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>69000</v>
+        <v>90300</v>
       </c>
       <c r="F125" t="n">
-        <v>579</v>
+        <v>442</v>
       </c>
       <c r="G125" t="n">
-        <v>39951000</v>
+        <v>39912600</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>42300</v>
+        <v>279500</v>
       </c>
       <c r="F126" t="n">
-        <v>709</v>
+        <v>357</v>
       </c>
       <c r="G126" t="n">
-        <v>29990700</v>
+        <v>99781500</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4520,29 +4520,221 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F127" t="n">
+        <v>54</v>
+      </c>
+      <c r="G127" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F128" t="n">
+        <v>659</v>
+      </c>
+      <c r="G128" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F129" t="n">
+        <v>666</v>
+      </c>
+      <c r="G129" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F130" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G130" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F131" t="n">
+        <v>579</v>
+      </c>
+      <c r="G131" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F132" t="n">
+        <v>709</v>
+      </c>
+      <c r="G132" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E127" t="n">
+      <c r="E133" t="n">
         <v>23350</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F133" t="n">
         <v>856</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G133" t="n">
         <v>19987600</v>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,20 +492,20 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28650</v>
+        <v>26600</v>
       </c>
       <c r="F2" t="n">
-        <v>345.7839</v>
+        <v>361.0017</v>
       </c>
       <c r="G2" t="n">
-        <v>9906708.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,290 +524,290 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11600</v>
+        <v>10740</v>
       </c>
       <c r="F3" t="n">
-        <v>854.0266</v>
+        <v>894.1011</v>
       </c>
       <c r="G3" t="n">
-        <v>9906708.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>131000</v>
+        <v>16180</v>
       </c>
       <c r="F4" t="n">
-        <v>75.6237</v>
+        <v>1186.9772</v>
       </c>
       <c r="G4" t="n">
-        <v>9906708.4</v>
+        <v>19205291.4</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67100</v>
+        <v>88400</v>
       </c>
       <c r="F5" t="n">
-        <v>147.641</v>
+        <v>217.2544</v>
       </c>
       <c r="G5" t="n">
-        <v>9906708.4</v>
+        <v>19205291.4</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4830</v>
+        <v>99100</v>
       </c>
       <c r="F6" t="n">
-        <v>2051.0783</v>
+        <v>290.6956</v>
       </c>
       <c r="G6" t="n">
-        <v>9906708.4</v>
+        <v>28807937.1</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9430</v>
+        <v>37350</v>
       </c>
       <c r="F7" t="n">
-        <v>2101.1046</v>
+        <v>491.1229</v>
       </c>
       <c r="G7" t="n">
-        <v>19813416.7</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>18343440.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-9.23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79100</v>
+        <v>2520</v>
       </c>
       <c r="F8" t="n">
-        <v>205.0482</v>
+        <v>33368.1327</v>
       </c>
       <c r="G8" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>84087694.5</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25250</v>
+        <v>16500</v>
       </c>
       <c r="F9" t="n">
-        <v>768.6917999999999</v>
+        <v>856.421</v>
       </c>
       <c r="G9" t="n">
-        <v>19409469.1</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>14130946.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-22.8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12510</v>
+        <v>27650</v>
       </c>
       <c r="F10" t="n">
-        <v>1443.4887</v>
+        <v>1041.8784</v>
       </c>
       <c r="G10" t="n">
-        <v>18058043.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-11.28</v>
-      </c>
+        <v>28807937.1</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>126500</v>
+        <v>9350</v>
       </c>
       <c r="F11" t="n">
-        <v>383.5863</v>
+        <v>1027.0209</v>
       </c>
       <c r="G11" t="n">
-        <v>48523672.7</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -816,30 +816,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2485</v>
+        <v>28650</v>
       </c>
       <c r="F12" t="n">
-        <v>42403.6617</v>
+        <v>345.7839</v>
       </c>
       <c r="G12" t="n">
-        <v>105373099.3</v>
+        <v>9906708.4</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,160 +848,158 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45500</v>
+        <v>11600</v>
       </c>
       <c r="F13" t="n">
-        <v>213.2909</v>
+        <v>854.0266</v>
       </c>
       <c r="G13" t="n">
-        <v>9704734.5</v>
+        <v>9906708.4</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17880</v>
+        <v>131000</v>
       </c>
       <c r="F14" t="n">
-        <v>1085.5408</v>
+        <v>75.6237</v>
       </c>
       <c r="G14" t="n">
-        <v>19409469.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4460</v>
+        <v>67100</v>
       </c>
       <c r="F15" t="n">
-        <v>3137.3165</v>
+        <v>147.641</v>
       </c>
       <c r="G15" t="n">
-        <v>13992431.8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-17.83</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3345</v>
+        <v>4830</v>
       </c>
       <c r="F16" t="n">
-        <v>11605.0637</v>
+        <v>2051.0783</v>
       </c>
       <c r="G16" t="n">
-        <v>38818938.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12120</v>
+        <v>9430</v>
       </c>
       <c r="F17" t="n">
-        <v>820.878</v>
+        <v>2101.1046</v>
       </c>
       <c r="G17" t="n">
-        <v>9949041.199999999</v>
+        <v>19813416.7</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1010,64 +1008,64 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>248000</v>
+        <v>79100</v>
       </c>
       <c r="F18" t="n">
-        <v>81.12909999999999</v>
+        <v>205.0482</v>
       </c>
       <c r="G18" t="n">
-        <v>20120019.7</v>
+        <v>16219315.2</v>
       </c>
       <c r="H18" t="n">
-        <v>-19.98</v>
+        <v>-15.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222500</v>
+        <v>25250</v>
       </c>
       <c r="F19" t="n">
-        <v>178.8592</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>39796164.7</v>
+        <v>19409469.1</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1076,64 +1074,64 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>54500</v>
+        <v>12510</v>
       </c>
       <c r="F20" t="n">
-        <v>504.0447</v>
+        <v>1443.4887</v>
       </c>
       <c r="G20" t="n">
-        <v>27470436.6</v>
+        <v>18058043.3</v>
       </c>
       <c r="H20" t="n">
-        <v>24.43</v>
+        <v>-11.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32350</v>
+        <v>126500</v>
       </c>
       <c r="F21" t="n">
-        <v>314.5779</v>
+        <v>383.5863</v>
       </c>
       <c r="G21" t="n">
-        <v>10176595.1</v>
+        <v>48523672.7</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1142,62 +1140,62 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>13650</v>
+        <v>2485</v>
       </c>
       <c r="F22" t="n">
-        <v>745.5381</v>
+        <v>42403.6617</v>
       </c>
       <c r="G22" t="n">
-        <v>10176595.1</v>
+        <v>105373099.3</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>31950</v>
+        <v>45500</v>
       </c>
       <c r="F23" t="n">
-        <v>318.5163</v>
+        <v>213.2909</v>
       </c>
       <c r="G23" t="n">
-        <v>10176595.1</v>
+        <v>9704734.5</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,96 +1204,96 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>250500</v>
+        <v>17880</v>
       </c>
       <c r="F24" t="n">
-        <v>81.2503</v>
+        <v>1085.5408</v>
       </c>
       <c r="G24" t="n">
-        <v>20353190.3</v>
+        <v>19409469.1</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>14100</v>
+        <v>4460</v>
       </c>
       <c r="F25" t="n">
-        <v>1443.4887</v>
+        <v>3137.3165</v>
       </c>
       <c r="G25" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>13992431.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-17.83</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31300</v>
+        <v>3345</v>
       </c>
       <c r="F26" t="n">
-        <v>1954.4702</v>
+        <v>11605.0637</v>
       </c>
       <c r="G26" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H26" t="n">
-        <v>6.83</v>
-      </c>
+        <v>38818938.1</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1304,192 +1302,194 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2355</v>
+        <v>12120</v>
       </c>
       <c r="F27" t="n">
-        <v>65496.7248</v>
+        <v>820.878</v>
       </c>
       <c r="G27" t="n">
-        <v>154244786.8</v>
+        <v>9949041.199999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>15810</v>
+        <v>248000</v>
       </c>
       <c r="F28" t="n">
-        <v>5149.4473</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>81412761.09999999</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>56700</v>
+        <v>222500</v>
       </c>
       <c r="F29" t="n">
-        <v>179.4814</v>
+        <v>178.8592</v>
       </c>
       <c r="G29" t="n">
-        <v>10176595.1</v>
+        <v>39796164.7</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4660</v>
+        <v>54500</v>
       </c>
       <c r="F30" t="n">
-        <v>4367.6374</v>
+        <v>504.0447</v>
       </c>
       <c r="G30" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>44600</v>
+        <v>32350</v>
       </c>
       <c r="F31" t="n">
-        <v>1359.3974</v>
+        <v>314.5779</v>
       </c>
       <c r="G31" t="n">
-        <v>60629123.5</v>
+        <v>10176595.1</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>20300</v>
+        <v>13650</v>
       </c>
       <c r="F32" t="n">
-        <v>1162.9429</v>
+        <v>745.5381</v>
       </c>
       <c r="G32" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H32" t="n">
-        <v>7.9</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1498,245 +1498,241 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>13160</v>
+        <v>31950</v>
       </c>
       <c r="F33" t="n">
-        <v>767.846</v>
+        <v>318.5163</v>
       </c>
       <c r="G33" t="n">
-        <v>10104853.9</v>
+        <v>10176595.1</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>49050</v>
+        <v>250500</v>
       </c>
       <c r="F34" t="n">
-        <v>357.1039</v>
+        <v>81.2503</v>
       </c>
       <c r="G34" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>37100</v>
+        <v>14100</v>
       </c>
       <c r="F35" t="n">
-        <v>604.321</v>
+        <v>1443.4887</v>
       </c>
       <c r="G35" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H35" t="n">
-        <v>15.04</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>123700</v>
+        <v>31300</v>
       </c>
       <c r="F36" t="n">
-        <v>490.1303</v>
+        <v>1954.4702</v>
       </c>
       <c r="G36" t="n">
-        <v>60629123.5</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>41150</v>
+        <v>2355</v>
       </c>
       <c r="F37" t="n">
-        <v>491.1229</v>
+        <v>65496.7248</v>
       </c>
       <c r="G37" t="n">
-        <v>20209707.8</v>
+        <v>154244786.8</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>31500</v>
+        <v>15810</v>
       </c>
       <c r="F38" t="n">
-        <v>320.789</v>
+        <v>5149.4473</v>
       </c>
       <c r="G38" t="n">
-        <v>10104853.9</v>
+        <v>81412761.09999999</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228500</v>
+        <v>56700</v>
       </c>
       <c r="F39" t="n">
-        <v>88.4451</v>
+        <v>179.4814</v>
       </c>
       <c r="G39" t="n">
-        <v>20209707.8</v>
+        <v>10176595.1</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>88500</v>
+        <v>4660</v>
       </c>
       <c r="F40" t="n">
-        <v>900.2261</v>
+        <v>4367.6374</v>
       </c>
       <c r="G40" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1746,31 +1742,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>130100</v>
+        <v>44600</v>
       </c>
       <c r="F41" t="n">
-        <v>314.8563</v>
+        <v>1359.3974</v>
       </c>
       <c r="G41" t="n">
-        <v>40962809.6</v>
-      </c>
-      <c r="H41" t="n">
-        <v>8.33</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1780,29 +1774,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2325</v>
+        <v>20300</v>
       </c>
       <c r="F42" t="n">
-        <v>21730.8686</v>
+        <v>1162.9429</v>
       </c>
       <c r="G42" t="n">
-        <v>50524269.6</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>23607739.9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1812,27 +1808,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>64700</v>
+        <v>13160</v>
       </c>
       <c r="F43" t="n">
-        <v>468.5404</v>
+        <v>767.846</v>
       </c>
       <c r="G43" t="n">
-        <v>30314561.7</v>
+        <v>10104853.9</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1844,358 +1840,362 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4670</v>
+        <v>49050</v>
       </c>
       <c r="F44" t="n">
-        <v>6491.3408</v>
+        <v>357.1039</v>
       </c>
       <c r="G44" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2120</v>
+        <v>37100</v>
       </c>
       <c r="F45" t="n">
-        <v>63879.7502</v>
+        <v>604.321</v>
       </c>
       <c r="G45" t="n">
-        <v>135425070.4</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2120</v>
+        <v>123700</v>
       </c>
       <c r="F46" t="n">
-        <v>3453.9051</v>
+        <v>490.1303</v>
       </c>
       <c r="G46" t="n">
-        <v>7322278.8</v>
+        <v>60629123.5</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>22900</v>
+        <v>41150</v>
       </c>
       <c r="F47" t="n">
-        <v>1397.6406</v>
+        <v>491.1229</v>
       </c>
       <c r="G47" t="n">
-        <v>32005969</v>
+        <v>20209707.8</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>73600</v>
+        <v>31500</v>
       </c>
       <c r="F48" t="n">
-        <v>299.9614</v>
+        <v>320.789</v>
       </c>
       <c r="G48" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H48" t="n">
-        <v>16.09</v>
-      </c>
+        <v>10104853.9</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2215</v>
+        <v>228500</v>
       </c>
       <c r="F49" t="n">
-        <v>28224.978</v>
+        <v>88.4451</v>
       </c>
       <c r="G49" t="n">
-        <v>62518326.2</v>
+        <v>20209707.8</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>43800</v>
+        <v>88500</v>
       </c>
       <c r="F50" t="n">
-        <v>504.0447</v>
+        <v>900.2261</v>
       </c>
       <c r="G50" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>23650</v>
+        <v>130100</v>
       </c>
       <c r="F51" t="n">
-        <v>451.106</v>
+        <v>314.8563</v>
       </c>
       <c r="G51" t="n">
-        <v>10668656.3</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5730</v>
+        <v>2325</v>
       </c>
       <c r="F52" t="n">
-        <v>3723.7893</v>
+        <v>21730.8686</v>
       </c>
       <c r="G52" t="n">
-        <v>21337312.7</v>
+        <v>50524269.6</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6080</v>
+        <v>64700</v>
       </c>
       <c r="F53" t="n">
-        <v>3255.5051</v>
+        <v>468.5404</v>
       </c>
       <c r="G53" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>30314561.7</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>95200</v>
+        <v>4670</v>
       </c>
       <c r="F54" t="n">
-        <v>221.6088</v>
+        <v>6491.3408</v>
       </c>
       <c r="G54" t="n">
-        <v>21097154.4</v>
+        <v>30314561.7</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2214,226 +2214,224 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2205</v>
+        <v>2120</v>
       </c>
       <c r="F55" t="n">
-        <v>52623.2877</v>
+        <v>63879.7502</v>
       </c>
       <c r="G55" t="n">
-        <v>116034349.3</v>
+        <v>135425070.4</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58700</v>
+        <v>2120</v>
       </c>
       <c r="F56" t="n">
-        <v>357.1039</v>
+        <v>3453.9051</v>
       </c>
       <c r="G56" t="n">
-        <v>20961998.6</v>
+        <v>7322278.8</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>13250</v>
+        <v>22900</v>
       </c>
       <c r="F57" t="n">
-        <v>791.0188000000001</v>
+        <v>1397.6406</v>
       </c>
       <c r="G57" t="n">
-        <v>10480999.3</v>
+        <v>32005969</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2360</v>
+        <v>73600</v>
       </c>
       <c r="F58" t="n">
-        <v>66616.5209</v>
+        <v>299.9614</v>
       </c>
       <c r="G58" t="n">
-        <v>157214989.3</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>38300</v>
+        <v>2215</v>
       </c>
       <c r="F59" t="n">
-        <v>500.7861</v>
+        <v>28224.978</v>
       </c>
       <c r="G59" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>62518326.2</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>21150</v>
+        <v>43800</v>
       </c>
       <c r="F60" t="n">
-        <v>495.5555</v>
+        <v>504.0447</v>
       </c>
       <c r="G60" t="n">
-        <v>10480999.3</v>
+        <v>22077158.2</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>23650</v>
       </c>
       <c r="F61" t="n">
-        <v>832.6201</v>
+        <v>451.106</v>
       </c>
       <c r="G61" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H61" t="n">
-        <v>1.28</v>
-      </c>
+        <v>10668656.3</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2442,84 +2440,86 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>12310</v>
+        <v>5730</v>
       </c>
       <c r="F62" t="n">
-        <v>2480.1654</v>
+        <v>3723.7893</v>
       </c>
       <c r="G62" t="n">
-        <v>30530836.4</v>
+        <v>21337312.7</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>40650</v>
+        <v>6080</v>
       </c>
       <c r="F63" t="n">
-        <v>751.0661</v>
+        <v>3255.5051</v>
       </c>
       <c r="G63" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>283500</v>
+        <v>95200</v>
       </c>
       <c r="F64" t="n">
-        <v>71.795</v>
+        <v>221.6088</v>
       </c>
       <c r="G64" t="n">
-        <v>20353890.9</v>
+        <v>21097154.4</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2534,34 +2534,34 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2390</v>
+        <v>2205</v>
       </c>
       <c r="F65" t="n">
-        <v>42581.3618</v>
+        <v>52623.2877</v>
       </c>
       <c r="G65" t="n">
-        <v>101769454.6</v>
+        <v>116034349.3</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2570,224 +2570,226 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>20450</v>
+        <v>58700</v>
       </c>
       <c r="F66" t="n">
-        <v>995.3003</v>
+        <v>357.1039</v>
       </c>
       <c r="G66" t="n">
-        <v>20353890.9</v>
+        <v>20961998.6</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>30200</v>
+        <v>13250</v>
       </c>
       <c r="F67" t="n">
-        <v>359.55</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>10858410.6</v>
+        <v>10480999.3</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>208500</v>
+        <v>2360</v>
       </c>
       <c r="F68" t="n">
-        <v>338</v>
+        <v>66616.5209</v>
       </c>
       <c r="G68" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.97</v>
-      </c>
+        <v>157214989.3</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>17720</v>
+        <v>38300</v>
       </c>
       <c r="F69" t="n">
-        <v>94.9217</v>
+        <v>500.7861</v>
       </c>
       <c r="G69" t="n">
-        <v>1682012.5</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100500</v>
+        <v>21150</v>
       </c>
       <c r="F70" t="n">
-        <v>8.9518</v>
+        <v>495.5555</v>
       </c>
       <c r="G70" t="n">
-        <v>899652.6</v>
+        <v>10480999.3</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>11410</v>
+        <v>23650</v>
       </c>
       <c r="F71" t="n">
-        <v>6321.2722</v>
+        <v>832.6201</v>
       </c>
       <c r="G71" t="n">
-        <v>72125715.8</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12880</v>
+        <v>12310</v>
       </c>
       <c r="F72" t="n">
-        <v>713.2027</v>
+        <v>2480.1654</v>
       </c>
       <c r="G72" t="n">
-        <v>9186050.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2796,30 +2798,30 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21200</v>
+        <v>40650</v>
       </c>
       <c r="F73" t="n">
-        <v>120.8659</v>
+        <v>751.0661</v>
       </c>
       <c r="G73" t="n">
-        <v>2562357.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2828,30 +2830,30 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>27700</v>
+        <v>283500</v>
       </c>
       <c r="F74" t="n">
-        <v>161.1835</v>
+        <v>71.795</v>
       </c>
       <c r="G74" t="n">
-        <v>4464784.2</v>
+        <v>20353890.9</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2860,45 +2862,45 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>21500</v>
+        <v>2390</v>
       </c>
       <c r="F75" t="n">
-        <v>129.2032</v>
+        <v>42581.3618</v>
       </c>
       <c r="G75" t="n">
-        <v>2777868.4</v>
+        <v>101769454.6</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>34100</v>
+        <v>20450</v>
       </c>
       <c r="F76" t="n">
-        <v>21.679</v>
+        <v>995.3003</v>
       </c>
       <c r="G76" t="n">
-        <v>739252.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2910,27 +2912,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>40850</v>
+        <v>30200</v>
       </c>
       <c r="F77" t="n">
-        <v>123.3915</v>
+        <v>359.55</v>
       </c>
       <c r="G77" t="n">
-        <v>5040542.1</v>
+        <v>10858410.6</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2942,29 +2944,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>308000</v>
+        <v>208500</v>
       </c>
       <c r="F78" t="n">
-        <v>9.1744</v>
+        <v>338</v>
       </c>
       <c r="G78" t="n">
-        <v>2825715.8</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2974,12 +2978,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2988,13 +2992,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6330</v>
+        <v>17720</v>
       </c>
       <c r="F79" t="n">
-        <v>50.5051</v>
+        <v>94.9217</v>
       </c>
       <c r="G79" t="n">
-        <v>319697.4</v>
+        <v>1682012.5</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3006,12 +3010,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3020,13 +3024,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>31700</v>
+        <v>100500</v>
       </c>
       <c r="F80" t="n">
-        <v>158.7408</v>
+        <v>8.9518</v>
       </c>
       <c r="G80" t="n">
-        <v>5032084.2</v>
+        <v>899652.6</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3038,27 +3042,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>68700</v>
+        <v>11410</v>
       </c>
       <c r="F81" t="n">
-        <v>16.0386</v>
+        <v>6321.2722</v>
       </c>
       <c r="G81" t="n">
-        <v>1101852.6</v>
+        <v>72125715.8</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3070,27 +3074,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>256000</v>
+        <v>12880</v>
       </c>
       <c r="F82" t="n">
-        <v>45.4873</v>
+        <v>713.2027</v>
       </c>
       <c r="G82" t="n">
-        <v>11644736.8</v>
+        <v>9186050.6</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3102,27 +3106,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>91100</v>
+        <v>21200</v>
       </c>
       <c r="F83" t="n">
-        <v>19.6174</v>
+        <v>120.8659</v>
       </c>
       <c r="G83" t="n">
-        <v>1787142.1</v>
+        <v>2562357.9</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3134,12 +3138,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3148,13 +3152,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>130900</v>
+        <v>27700</v>
       </c>
       <c r="F84" t="n">
-        <v>89.1437</v>
+        <v>161.1835</v>
       </c>
       <c r="G84" t="n">
-        <v>11668905.3</v>
+        <v>4464784.2</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3166,27 +3170,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F85" t="n">
-        <v>32820.1843</v>
+        <v>129.2032</v>
       </c>
       <c r="G85" t="n">
-        <v>78768442.40000001</v>
+        <v>2777868.4</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3198,27 +3202,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>41150</v>
+        <v>34100</v>
       </c>
       <c r="F86" t="n">
-        <v>38.7861</v>
+        <v>21.679</v>
       </c>
       <c r="G86" t="n">
-        <v>1596047.4</v>
+        <v>739252.6</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3230,27 +3234,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>49450</v>
+        <v>40850</v>
       </c>
       <c r="F87" t="n">
-        <v>83.90349999999999</v>
+        <v>123.3915</v>
       </c>
       <c r="G87" t="n">
-        <v>4149029</v>
+        <v>5040542.1</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3262,27 +3266,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>24750</v>
+        <v>308000</v>
       </c>
       <c r="F88" t="n">
-        <v>23.3799</v>
+        <v>9.1744</v>
       </c>
       <c r="G88" t="n">
-        <v>578652.6</v>
+        <v>2825715.8</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3294,110 +3298,108 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5450</v>
+        <v>6330</v>
       </c>
       <c r="F89" t="n">
-        <v>220.6267</v>
+        <v>50.5051</v>
       </c>
       <c r="G89" t="n">
-        <v>1202415.4</v>
+        <v>319697.4</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>327000</v>
+        <v>31700</v>
       </c>
       <c r="F90" t="n">
-        <v>54</v>
+        <v>158.7408</v>
       </c>
       <c r="G90" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>5032084.2</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5130</v>
+        <v>68700</v>
       </c>
       <c r="F91" t="n">
-        <v>4001.7913</v>
+        <v>16.0386</v>
       </c>
       <c r="G91" t="n">
-        <v>20529189.5</v>
+        <v>1101852.6</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3406,160 +3408,158 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>27100</v>
+        <v>256000</v>
       </c>
       <c r="F92" t="n">
-        <v>376</v>
+        <v>45.4873</v>
       </c>
       <c r="G92" t="n">
-        <v>10189600</v>
+        <v>11644736.8</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>67600</v>
+        <v>91100</v>
       </c>
       <c r="F93" t="n">
-        <v>998</v>
+        <v>19.6174</v>
       </c>
       <c r="G93" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>1787142.1</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>11900</v>
+        <v>130900</v>
       </c>
       <c r="F94" t="n">
-        <v>856</v>
+        <v>89.1437</v>
       </c>
       <c r="G94" t="n">
-        <v>10186400</v>
+        <v>11668905.3</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>29300</v>
+        <v>2400</v>
       </c>
       <c r="F95" t="n">
-        <v>2434</v>
+        <v>32820.1843</v>
       </c>
       <c r="G95" t="n">
-        <v>71316200</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>119300</v>
+        <v>41150</v>
       </c>
       <c r="F96" t="n">
-        <v>171</v>
+        <v>38.7861</v>
       </c>
       <c r="G96" t="n">
-        <v>20400300</v>
+        <v>1596047.4</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3568,94 +3568,94 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2445</v>
+        <v>49450</v>
       </c>
       <c r="F97" t="n">
-        <v>82456</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G97" t="n">
-        <v>201604920</v>
+        <v>4149029</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>18910</v>
+        <v>24750</v>
       </c>
       <c r="F98" t="n">
-        <v>1068.0212</v>
+        <v>23.3799</v>
       </c>
       <c r="G98" t="n">
-        <v>20196280</v>
+        <v>578652.6</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>32250</v>
+        <v>5450</v>
       </c>
       <c r="F99" t="n">
-        <v>626</v>
+        <v>220.6267</v>
       </c>
       <c r="G99" t="n">
-        <v>20188500</v>
+        <v>1202415.4</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3664,388 +3664,390 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>82500</v>
+        <v>327000</v>
       </c>
       <c r="F100" t="n">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="G100" t="n">
-        <v>16830000</v>
+        <v>17658000</v>
       </c>
       <c r="H100" t="n">
-        <v>-8.640000000000001</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>56800</v>
+        <v>5130</v>
       </c>
       <c r="F101" t="n">
-        <v>258</v>
+        <v>4001.7913</v>
       </c>
       <c r="G101" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20529189.5</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>83700</v>
+        <v>27100</v>
       </c>
       <c r="F102" t="n">
-        <v>120</v>
+        <v>376</v>
       </c>
       <c r="G102" t="n">
-        <v>10044000</v>
+        <v>10189600</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>43650</v>
+        <v>67600</v>
       </c>
       <c r="F103" t="n">
-        <v>462</v>
+        <v>998</v>
       </c>
       <c r="G103" t="n">
-        <v>20166300</v>
-      </c>
-      <c r="H103" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>59700</v>
+        <v>11900</v>
       </c>
       <c r="F104" t="n">
-        <v>169</v>
+        <v>856</v>
       </c>
       <c r="G104" t="n">
-        <v>10089300</v>
+        <v>10186400</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>10930</v>
+        <v>29300</v>
       </c>
       <c r="F105" t="n">
-        <v>1833</v>
+        <v>2434</v>
       </c>
       <c r="G105" t="n">
-        <v>20034690</v>
+        <v>71316200</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>19850</v>
+        <v>119300</v>
       </c>
       <c r="F106" t="n">
-        <v>505</v>
+        <v>171</v>
       </c>
       <c r="G106" t="n">
-        <v>10024250</v>
+        <v>20400300</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>26350</v>
+        <v>2445</v>
       </c>
       <c r="F107" t="n">
-        <v>380</v>
+        <v>82456</v>
       </c>
       <c r="G107" t="n">
-        <v>10013000</v>
+        <v>201604920</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>23500</v>
+        <v>18910</v>
       </c>
       <c r="F108" t="n">
-        <v>833</v>
+        <v>1068.0212</v>
       </c>
       <c r="G108" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20196280</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>85200</v>
+        <v>32250</v>
       </c>
       <c r="F109" t="n">
-        <v>118</v>
+        <v>626</v>
       </c>
       <c r="G109" t="n">
-        <v>10053600</v>
+        <v>20188500</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>63400</v>
+        <v>82500</v>
       </c>
       <c r="F110" t="n">
-        <v>316</v>
+        <v>204</v>
       </c>
       <c r="G110" t="n">
-        <v>20034400</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>110300</v>
+        <v>56800</v>
       </c>
       <c r="F111" t="n">
-        <v>91</v>
+        <v>258</v>
       </c>
       <c r="G111" t="n">
-        <v>10037300</v>
-      </c>
-      <c r="H111" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4054,30 +4056,30 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>66100</v>
+        <v>83700</v>
       </c>
       <c r="F112" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="G112" t="n">
-        <v>10047200</v>
+        <v>10044000</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4086,222 +4088,224 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>25800</v>
+        <v>43650</v>
       </c>
       <c r="F113" t="n">
-        <v>2713</v>
+        <v>462</v>
       </c>
       <c r="G113" t="n">
-        <v>69995400</v>
+        <v>20166300</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>206500</v>
+        <v>59700</v>
       </c>
       <c r="F114" t="n">
-        <v>338</v>
+        <v>169</v>
       </c>
       <c r="G114" t="n">
-        <v>69797000</v>
+        <v>10089300</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>70100</v>
+        <v>10930</v>
       </c>
       <c r="F115" t="n">
-        <v>998</v>
+        <v>1833</v>
       </c>
       <c r="G115" t="n">
-        <v>69959800</v>
+        <v>20034690</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>93300</v>
+        <v>19850</v>
       </c>
       <c r="F116" t="n">
-        <v>214</v>
+        <v>505</v>
       </c>
       <c r="G116" t="n">
-        <v>19966200</v>
+        <v>10024250</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>11300</v>
+        <v>26350</v>
       </c>
       <c r="F117" t="n">
-        <v>4424</v>
+        <v>380</v>
       </c>
       <c r="G117" t="n">
-        <v>49991200</v>
+        <v>10013000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>19740</v>
+        <v>23500</v>
       </c>
       <c r="F118" t="n">
-        <v>2532</v>
+        <v>833</v>
       </c>
       <c r="G118" t="n">
-        <v>49981680</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>25150</v>
+        <v>85200</v>
       </c>
       <c r="F119" t="n">
-        <v>2385</v>
+        <v>118</v>
       </c>
       <c r="G119" t="n">
-        <v>59982750</v>
+        <v>10053600</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4310,77 +4314,77 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>22050</v>
+        <v>63400</v>
       </c>
       <c r="F120" t="n">
-        <v>2267</v>
+        <v>316</v>
       </c>
       <c r="G120" t="n">
-        <v>49987350</v>
+        <v>20034400</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>43150</v>
+        <v>110300</v>
       </c>
       <c r="F121" t="n">
-        <v>1390</v>
+        <v>91</v>
       </c>
       <c r="G121" t="n">
-        <v>59978500</v>
+        <v>10037300</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>310000</v>
+        <v>66100</v>
       </c>
       <c r="F122" t="n">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="G122" t="n">
-        <v>69750000</v>
+        <v>10047200</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4392,12 +4396,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4406,13 +4410,13 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6240</v>
+        <v>25800</v>
       </c>
       <c r="F123" t="n">
-        <v>3205</v>
+        <v>2713</v>
       </c>
       <c r="G123" t="n">
-        <v>19999200</v>
+        <v>69995400</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4424,12 +4428,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4438,13 +4442,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>24000</v>
+        <v>206500</v>
       </c>
       <c r="F124" t="n">
-        <v>833</v>
+        <v>338</v>
       </c>
       <c r="G124" t="n">
-        <v>19992000</v>
+        <v>69797000</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4456,12 +4460,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4470,13 +4474,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>90300</v>
+        <v>70100</v>
       </c>
       <c r="F125" t="n">
-        <v>442</v>
+        <v>998</v>
       </c>
       <c r="G125" t="n">
-        <v>39912600</v>
+        <v>69959800</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4488,12 +4492,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4502,13 +4506,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>279500</v>
+        <v>93300</v>
       </c>
       <c r="F126" t="n">
-        <v>357</v>
+        <v>214</v>
       </c>
       <c r="G126" t="n">
-        <v>99781500</v>
+        <v>19966200</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4520,12 +4524,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4534,13 +4538,13 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>366000</v>
+        <v>11300</v>
       </c>
       <c r="F127" t="n">
-        <v>54</v>
+        <v>4424</v>
       </c>
       <c r="G127" t="n">
-        <v>19764000</v>
+        <v>49991200</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -4552,12 +4556,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4566,13 +4570,13 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>91000</v>
+        <v>19740</v>
       </c>
       <c r="F128" t="n">
-        <v>659</v>
+        <v>2532</v>
       </c>
       <c r="G128" t="n">
-        <v>59969000</v>
+        <v>49981680</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -4584,12 +4588,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4598,13 +4602,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>120100</v>
+        <v>25150</v>
       </c>
       <c r="F129" t="n">
-        <v>666</v>
+        <v>2385</v>
       </c>
       <c r="G129" t="n">
-        <v>79986600</v>
+        <v>59982750</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4616,12 +4620,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4630,13 +4634,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2405</v>
+        <v>22050</v>
       </c>
       <c r="F130" t="n">
-        <v>415800</v>
+        <v>2267</v>
       </c>
       <c r="G130" t="n">
-        <v>999999000</v>
+        <v>49987350</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4648,12 +4652,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4662,13 +4666,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>69000</v>
+        <v>43150</v>
       </c>
       <c r="F131" t="n">
-        <v>579</v>
+        <v>1390</v>
       </c>
       <c r="G131" t="n">
-        <v>39951000</v>
+        <v>59978500</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4680,12 +4684,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4694,13 +4698,13 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>42300</v>
+        <v>310000</v>
       </c>
       <c r="F132" t="n">
-        <v>709</v>
+        <v>225</v>
       </c>
       <c r="G132" t="n">
-        <v>29990700</v>
+        <v>69750000</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -4712,29 +4716,349 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
+          <t>티씨머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>125020</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6240</v>
+      </c>
+      <c r="F133" t="n">
+        <v>3205</v>
+      </c>
+      <c r="G133" t="n">
+        <v>19999200</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>138080</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F134" t="n">
+        <v>833</v>
+      </c>
+      <c r="G134" t="n">
+        <v>19992000</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>141080</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>90300</v>
+      </c>
+      <c r="F135" t="n">
+        <v>442</v>
+      </c>
+      <c r="G135" t="n">
+        <v>39912600</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>279500</v>
+      </c>
+      <c r="F136" t="n">
+        <v>357</v>
+      </c>
+      <c r="G136" t="n">
+        <v>99781500</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F137" t="n">
+        <v>54</v>
+      </c>
+      <c r="G137" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F138" t="n">
+        <v>659</v>
+      </c>
+      <c r="G138" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F139" t="n">
+        <v>666</v>
+      </c>
+      <c r="G139" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F140" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G140" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F141" t="n">
+        <v>579</v>
+      </c>
+      <c r="G141" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F142" t="n">
+        <v>709</v>
+      </c>
+      <c r="G142" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E133" t="n">
+      <c r="E143" t="n">
         <v>23350</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F143" t="n">
         <v>856</v>
       </c>
-      <c r="G133" t="n">
+      <c r="G143" t="n">
         <v>19987600</v>
       </c>
-      <c r="H133" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,62 +492,62 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26600</v>
+        <v>26200</v>
       </c>
       <c r="F2" t="n">
-        <v>361.0017</v>
+        <v>382.0025</v>
       </c>
       <c r="G2" t="n">
-        <v>9602645.699999999</v>
+        <v>10008466.3</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10740</v>
+        <v>94700</v>
       </c>
       <c r="F3" t="n">
-        <v>894.1011</v>
+        <v>105.686</v>
       </c>
       <c r="G3" t="n">
-        <v>9602645.699999999</v>
+        <v>10008466.3</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,13 +556,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16180</v>
+        <v>42500</v>
       </c>
       <c r="F4" t="n">
-        <v>1186.9772</v>
+        <v>470.9867</v>
       </c>
       <c r="G4" t="n">
-        <v>19205291.4</v>
+        <v>20016932.7</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,27 +574,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>88400</v>
+        <v>26600</v>
       </c>
       <c r="F5" t="n">
-        <v>217.2544</v>
+        <v>361.0017</v>
       </c>
       <c r="G5" t="n">
-        <v>19205291.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>99100</v>
+        <v>10740</v>
       </c>
       <c r="F6" t="n">
-        <v>290.6956</v>
+        <v>894.1011</v>
       </c>
       <c r="G6" t="n">
-        <v>28807937.1</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,31 +638,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>37350</v>
+        <v>16180</v>
       </c>
       <c r="F7" t="n">
-        <v>491.1229</v>
+        <v>1186.9772</v>
       </c>
       <c r="G7" t="n">
-        <v>18343440.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-9.23</v>
-      </c>
+        <v>19205291.4</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -672,27 +670,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2520</v>
+        <v>88400</v>
       </c>
       <c r="F8" t="n">
-        <v>33368.1327</v>
+        <v>217.2544</v>
       </c>
       <c r="G8" t="n">
-        <v>84087694.5</v>
+        <v>19205291.4</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -704,31 +702,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16500</v>
+        <v>99100</v>
       </c>
       <c r="F9" t="n">
-        <v>856.421</v>
+        <v>290.6956</v>
       </c>
       <c r="G9" t="n">
-        <v>14130946.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-22.8</v>
-      </c>
+        <v>28807937.1</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,29 +734,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27650</v>
+        <v>37350</v>
       </c>
       <c r="F10" t="n">
-        <v>1041.8784</v>
+        <v>491.1229</v>
       </c>
       <c r="G10" t="n">
-        <v>28807937.1</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>18343440.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-9.23</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,12 +768,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,94 +782,96 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9350</v>
+        <v>2520</v>
       </c>
       <c r="F11" t="n">
-        <v>1027.0209</v>
+        <v>33368.1327</v>
       </c>
       <c r="G11" t="n">
-        <v>9602645.699999999</v>
+        <v>84087694.5</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>28650</v>
+        <v>16500</v>
       </c>
       <c r="F12" t="n">
-        <v>345.7839</v>
+        <v>856.421</v>
       </c>
       <c r="G12" t="n">
-        <v>9906708.4</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>14130946.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-22.8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11600</v>
+        <v>27650</v>
       </c>
       <c r="F13" t="n">
-        <v>854.0266</v>
+        <v>1041.8784</v>
       </c>
       <c r="G13" t="n">
-        <v>9906708.4</v>
+        <v>28807937.1</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>131000</v>
+        <v>9350</v>
       </c>
       <c r="F14" t="n">
-        <v>75.6237</v>
+        <v>1027.0209</v>
       </c>
       <c r="G14" t="n">
-        <v>9906708.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,24 +898,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67100</v>
+        <v>28650</v>
       </c>
       <c r="F15" t="n">
-        <v>147.641</v>
+        <v>345.7839</v>
       </c>
       <c r="G15" t="n">
         <v>9906708.4</v>
@@ -930,24 +930,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4830</v>
+        <v>11600</v>
       </c>
       <c r="F16" t="n">
-        <v>2051.0783</v>
+        <v>854.0266</v>
       </c>
       <c r="G16" t="n">
         <v>9906708.4</v>
@@ -962,78 +962,76 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9430</v>
+        <v>131000</v>
       </c>
       <c r="F17" t="n">
-        <v>2101.1046</v>
+        <v>75.6237</v>
       </c>
       <c r="G17" t="n">
-        <v>19813416.7</v>
+        <v>9906708.4</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>79100</v>
+        <v>67100</v>
       </c>
       <c r="F18" t="n">
-        <v>205.0482</v>
+        <v>147.641</v>
       </c>
       <c r="G18" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1042,49 +1040,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>25250</v>
+        <v>4830</v>
       </c>
       <c r="F19" t="n">
-        <v>768.6917999999999</v>
+        <v>2051.0783</v>
       </c>
       <c r="G19" t="n">
-        <v>19409469.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>12510</v>
+        <v>9430</v>
       </c>
       <c r="F20" t="n">
-        <v>1443.4887</v>
+        <v>2101.1046</v>
       </c>
       <c r="G20" t="n">
-        <v>18058043.3</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-11.28</v>
-      </c>
+        <v>19813416.7</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1094,29 +1090,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>126500</v>
+        <v>79100</v>
       </c>
       <c r="F21" t="n">
-        <v>383.5863</v>
+        <v>205.0482</v>
       </c>
       <c r="G21" t="n">
-        <v>48523672.7</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>16219315.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-15.22</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1126,27 +1124,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2485</v>
+        <v>25250</v>
       </c>
       <c r="F22" t="n">
-        <v>42403.6617</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>105373099.3</v>
+        <v>19409469.1</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1158,29 +1156,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>45500</v>
+        <v>12510</v>
       </c>
       <c r="F23" t="n">
-        <v>213.2909</v>
+        <v>1443.4887</v>
       </c>
       <c r="G23" t="n">
-        <v>9704734.5</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>18058043.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-11.28</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1190,27 +1190,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17880</v>
+        <v>126500</v>
       </c>
       <c r="F24" t="n">
-        <v>1085.5408</v>
+        <v>383.5863</v>
       </c>
       <c r="G24" t="n">
-        <v>19409469.1</v>
+        <v>48523672.7</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1222,31 +1222,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4460</v>
+        <v>2485</v>
       </c>
       <c r="F25" t="n">
-        <v>3137.3165</v>
+        <v>42403.6617</v>
       </c>
       <c r="G25" t="n">
-        <v>13992431.8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-17.83</v>
-      </c>
+        <v>105373099.3</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1256,44 +1254,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3345</v>
+        <v>45500</v>
       </c>
       <c r="F26" t="n">
-        <v>11605.0637</v>
+        <v>213.2909</v>
       </c>
       <c r="G26" t="n">
-        <v>38818938.1</v>
+        <v>9704734.5</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,30 +1300,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12120</v>
+        <v>17880</v>
       </c>
       <c r="F27" t="n">
-        <v>820.878</v>
+        <v>1085.5408</v>
       </c>
       <c r="G27" t="n">
-        <v>9949041.199999999</v>
+        <v>19409469.1</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,47 +1332,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>248000</v>
+        <v>4460</v>
       </c>
       <c r="F28" t="n">
-        <v>81.12909999999999</v>
+        <v>3137.3165</v>
       </c>
       <c r="G28" t="n">
-        <v>20120019.7</v>
+        <v>13992431.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-19.98</v>
+        <v>-17.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222500</v>
+        <v>3345</v>
       </c>
       <c r="F29" t="n">
-        <v>178.8592</v>
+        <v>11605.0637</v>
       </c>
       <c r="G29" t="n">
-        <v>39796164.7</v>
+        <v>38818938.1</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1386,78 +1384,78 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>54500</v>
+        <v>12120</v>
       </c>
       <c r="F30" t="n">
-        <v>504.0447</v>
+        <v>820.878</v>
       </c>
       <c r="G30" t="n">
-        <v>27470436.6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>24.43</v>
-      </c>
+        <v>9949041.199999999</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>32350</v>
+        <v>248000</v>
       </c>
       <c r="F31" t="n">
-        <v>314.5779</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1466,47 +1464,49 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>13650</v>
+        <v>222500</v>
       </c>
       <c r="F32" t="n">
-        <v>745.5381</v>
+        <v>178.8592</v>
       </c>
       <c r="G32" t="n">
-        <v>10176595.1</v>
+        <v>39796164.7</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>31950</v>
+        <v>54500</v>
       </c>
       <c r="F33" t="n">
-        <v>318.5163</v>
+        <v>504.0447</v>
       </c>
       <c r="G33" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1530,13 +1530,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>250500</v>
+        <v>32350</v>
       </c>
       <c r="F34" t="n">
-        <v>81.2503</v>
+        <v>314.5779</v>
       </c>
       <c r="G34" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1548,27 +1548,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>14100</v>
+        <v>13650</v>
       </c>
       <c r="F35" t="n">
-        <v>1443.4887</v>
+        <v>745.5381</v>
       </c>
       <c r="G35" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1580,31 +1580,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31300</v>
+        <v>31950</v>
       </c>
       <c r="F36" t="n">
-        <v>1954.4702</v>
+        <v>318.5163</v>
       </c>
       <c r="G36" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H36" t="n">
-        <v>6.83</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1614,12 +1612,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1628,13 +1626,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2355</v>
+        <v>250500</v>
       </c>
       <c r="F37" t="n">
-        <v>65496.7248</v>
+        <v>81.2503</v>
       </c>
       <c r="G37" t="n">
-        <v>154244786.8</v>
+        <v>20353190.3</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1646,12 +1644,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1660,13 +1658,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15810</v>
+        <v>14100</v>
       </c>
       <c r="F38" t="n">
-        <v>5149.4473</v>
+        <v>1443.4887</v>
       </c>
       <c r="G38" t="n">
-        <v>81412761.09999999</v>
+        <v>20353190.3</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1678,29 +1676,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>56700</v>
+        <v>31300</v>
       </c>
       <c r="F39" t="n">
-        <v>179.4814</v>
+        <v>1954.4702</v>
       </c>
       <c r="G39" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1724,30 +1724,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4660</v>
+        <v>2355</v>
       </c>
       <c r="F40" t="n">
-        <v>4367.6374</v>
+        <v>65496.7248</v>
       </c>
       <c r="G40" t="n">
-        <v>20353190.3</v>
+        <v>154244786.8</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1756,79 +1756,77 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>44600</v>
+        <v>15810</v>
       </c>
       <c r="F41" t="n">
-        <v>1359.3974</v>
+        <v>5149.4473</v>
       </c>
       <c r="G41" t="n">
-        <v>60629123.5</v>
+        <v>81412761.09999999</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>20300</v>
+        <v>56700</v>
       </c>
       <c r="F42" t="n">
-        <v>1162.9429</v>
+        <v>179.4814</v>
       </c>
       <c r="G42" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H42" t="n">
-        <v>7.9</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>13160</v>
+        <v>4660</v>
       </c>
       <c r="F43" t="n">
-        <v>767.846</v>
+        <v>4367.6374</v>
       </c>
       <c r="G43" t="n">
-        <v>10104853.9</v>
+        <v>20353190.3</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1840,31 +1838,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>49050</v>
+        <v>44600</v>
       </c>
       <c r="F44" t="n">
-        <v>357.1039</v>
+        <v>1359.3974</v>
       </c>
       <c r="G44" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1874,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1888,16 +1884,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>37100</v>
+        <v>20300</v>
       </c>
       <c r="F45" t="n">
-        <v>604.321</v>
+        <v>1162.9429</v>
       </c>
       <c r="G45" t="n">
-        <v>22420310.5</v>
+        <v>23607739.9</v>
       </c>
       <c r="H45" t="n">
-        <v>15.04</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="46">
@@ -1908,27 +1904,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>123700</v>
+        <v>13160</v>
       </c>
       <c r="F46" t="n">
-        <v>490.1303</v>
+        <v>767.846</v>
       </c>
       <c r="G46" t="n">
-        <v>60629123.5</v>
+        <v>10104853.9</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1940,29 +1936,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>41150</v>
+        <v>49050</v>
       </c>
       <c r="F47" t="n">
-        <v>491.1229</v>
+        <v>357.1039</v>
       </c>
       <c r="G47" t="n">
-        <v>20209707.8</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1972,29 +1970,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>31500</v>
+        <v>37100</v>
       </c>
       <c r="F48" t="n">
-        <v>320.789</v>
+        <v>604.321</v>
       </c>
       <c r="G48" t="n">
-        <v>10104853.9</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2004,27 +2004,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228500</v>
+        <v>123700</v>
       </c>
       <c r="F49" t="n">
-        <v>88.4451</v>
+        <v>490.1303</v>
       </c>
       <c r="G49" t="n">
-        <v>20209707.8</v>
+        <v>60629123.5</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2036,31 +2036,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>88500</v>
+        <v>41150</v>
       </c>
       <c r="F50" t="n">
-        <v>900.2261</v>
+        <v>491.1229</v>
       </c>
       <c r="G50" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>20209707.8</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2070,31 +2068,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>130100</v>
+        <v>31500</v>
       </c>
       <c r="F51" t="n">
-        <v>314.8563</v>
+        <v>320.789</v>
       </c>
       <c r="G51" t="n">
-        <v>40962809.6</v>
-      </c>
-      <c r="H51" t="n">
-        <v>8.33</v>
-      </c>
+        <v>10104853.9</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2104,12 +2100,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2118,13 +2114,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2325</v>
+        <v>228500</v>
       </c>
       <c r="F52" t="n">
-        <v>21730.8686</v>
+        <v>88.4451</v>
       </c>
       <c r="G52" t="n">
-        <v>50524269.6</v>
+        <v>20209707.8</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2136,29 +2132,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>64700</v>
+        <v>88500</v>
       </c>
       <c r="F53" t="n">
-        <v>468.5404</v>
+        <v>900.2261</v>
       </c>
       <c r="G53" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2168,34 +2166,36 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4670</v>
+        <v>130100</v>
       </c>
       <c r="F54" t="n">
-        <v>6491.3408</v>
+        <v>314.8563</v>
       </c>
       <c r="G54" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2214,118 +2214,116 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2120</v>
+        <v>2325</v>
       </c>
       <c r="F55" t="n">
-        <v>63879.7502</v>
+        <v>21730.8686</v>
       </c>
       <c r="G55" t="n">
-        <v>135425070.4</v>
+        <v>50524269.6</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2120</v>
+        <v>64700</v>
       </c>
       <c r="F56" t="n">
-        <v>3453.9051</v>
+        <v>468.5404</v>
       </c>
       <c r="G56" t="n">
-        <v>7322278.8</v>
+        <v>30314561.7</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>22900</v>
+        <v>4670</v>
       </c>
       <c r="F57" t="n">
-        <v>1397.6406</v>
+        <v>6491.3408</v>
       </c>
       <c r="G57" t="n">
-        <v>32005969</v>
+        <v>30314561.7</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>73600</v>
+        <v>2120</v>
       </c>
       <c r="F58" t="n">
-        <v>299.9614</v>
+        <v>63879.7502</v>
       </c>
       <c r="G58" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H58" t="n">
-        <v>16.09</v>
-      </c>
+        <v>135425070.4</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2344,13 +2342,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2215</v>
+        <v>2120</v>
       </c>
       <c r="F59" t="n">
-        <v>28224.978</v>
+        <v>3453.9051</v>
       </c>
       <c r="G59" t="n">
-        <v>62518326.2</v>
+        <v>7322278.8</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2362,27 +2360,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>43800</v>
+        <v>22900</v>
       </c>
       <c r="F60" t="n">
-        <v>504.0447</v>
+        <v>1397.6406</v>
       </c>
       <c r="G60" t="n">
-        <v>22077158.2</v>
+        <v>32005969</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2394,29 +2392,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>23650</v>
+        <v>73600</v>
       </c>
       <c r="F61" t="n">
-        <v>451.106</v>
+        <v>299.9614</v>
       </c>
       <c r="G61" t="n">
-        <v>10668656.3</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2440,64 +2440,62 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5730</v>
+        <v>2215</v>
       </c>
       <c r="F62" t="n">
-        <v>3723.7893</v>
+        <v>28224.978</v>
       </c>
       <c r="G62" t="n">
-        <v>21337312.7</v>
+        <v>62518326.2</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6080</v>
+        <v>43800</v>
       </c>
       <c r="F63" t="n">
-        <v>3255.5051</v>
+        <v>504.0447</v>
       </c>
       <c r="G63" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>22077158.2</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2506,94 +2504,96 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>95200</v>
+        <v>23650</v>
       </c>
       <c r="F64" t="n">
-        <v>221.6088</v>
+        <v>451.106</v>
       </c>
       <c r="G64" t="n">
-        <v>21097154.4</v>
+        <v>10668656.3</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2205</v>
+        <v>5730</v>
       </c>
       <c r="F65" t="n">
-        <v>52623.2877</v>
+        <v>3723.7893</v>
       </c>
       <c r="G65" t="n">
-        <v>116034349.3</v>
+        <v>21337312.7</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>58700</v>
+        <v>6080</v>
       </c>
       <c r="F66" t="n">
-        <v>357.1039</v>
+        <v>3255.5051</v>
       </c>
       <c r="G66" t="n">
-        <v>20961998.6</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2602,20 +2602,20 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>13250</v>
+        <v>95200</v>
       </c>
       <c r="F67" t="n">
-        <v>791.0188000000001</v>
+        <v>221.6088</v>
       </c>
       <c r="G67" t="n">
-        <v>10480999.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2360</v>
+        <v>2205</v>
       </c>
       <c r="F68" t="n">
-        <v>66616.5209</v>
+        <v>52623.2877</v>
       </c>
       <c r="G68" t="n">
-        <v>157214989.3</v>
+        <v>116034349.3</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2652,31 +2652,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>38300</v>
+        <v>58700</v>
       </c>
       <c r="F69" t="n">
-        <v>500.7861</v>
+        <v>357.1039</v>
       </c>
       <c r="G69" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>20961998.6</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2686,12 +2684,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2700,10 +2698,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>21150</v>
+        <v>13250</v>
       </c>
       <c r="F70" t="n">
-        <v>495.5555</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G70" t="n">
         <v>10480999.3</v>
@@ -2718,127 +2716,129 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>23650</v>
+        <v>2360</v>
       </c>
       <c r="F71" t="n">
-        <v>832.6201</v>
+        <v>66616.5209</v>
       </c>
       <c r="G71" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H71" t="n">
-        <v>1.28</v>
-      </c>
+        <v>157214989.3</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12310</v>
+        <v>38300</v>
       </c>
       <c r="F72" t="n">
-        <v>2480.1654</v>
+        <v>500.7861</v>
       </c>
       <c r="G72" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>40650</v>
+        <v>21150</v>
       </c>
       <c r="F73" t="n">
-        <v>751.0661</v>
+        <v>495.5555</v>
       </c>
       <c r="G73" t="n">
-        <v>30530836.4</v>
+        <v>10480999.3</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>283500</v>
+        <v>23650</v>
       </c>
       <c r="F74" t="n">
-        <v>71.795</v>
+        <v>832.6201</v>
       </c>
       <c r="G74" t="n">
-        <v>20353890.9</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2390</v>
+        <v>12310</v>
       </c>
       <c r="F75" t="n">
-        <v>42581.3618</v>
+        <v>2480.1654</v>
       </c>
       <c r="G75" t="n">
-        <v>101769454.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2880,44 +2880,44 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>20450</v>
+        <v>40650</v>
       </c>
       <c r="F76" t="n">
-        <v>995.3003</v>
+        <v>751.0661</v>
       </c>
       <c r="G76" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2926,79 +2926,77 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>30200</v>
+        <v>283500</v>
       </c>
       <c r="F77" t="n">
-        <v>359.55</v>
+        <v>71.795</v>
       </c>
       <c r="G77" t="n">
-        <v>10858410.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>208500</v>
+        <v>2390</v>
       </c>
       <c r="F78" t="n">
-        <v>338</v>
+        <v>42581.3618</v>
       </c>
       <c r="G78" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.97</v>
-      </c>
+        <v>101769454.6</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>17720</v>
+        <v>20450</v>
       </c>
       <c r="F79" t="n">
-        <v>94.9217</v>
+        <v>995.3003</v>
       </c>
       <c r="G79" t="n">
-        <v>1682012.5</v>
+        <v>20353890.9</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3010,12 +3008,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3024,13 +3022,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100500</v>
+        <v>30200</v>
       </c>
       <c r="F80" t="n">
-        <v>8.9518</v>
+        <v>359.55</v>
       </c>
       <c r="G80" t="n">
-        <v>899652.6</v>
+        <v>10858410.6</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3042,29 +3040,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>11410</v>
+        <v>208500</v>
       </c>
       <c r="F81" t="n">
-        <v>6321.2722</v>
+        <v>338</v>
       </c>
       <c r="G81" t="n">
-        <v>72125715.8</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3074,27 +3074,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>12880</v>
+        <v>17720</v>
       </c>
       <c r="F82" t="n">
-        <v>713.2027</v>
+        <v>94.9217</v>
       </c>
       <c r="G82" t="n">
-        <v>9186050.6</v>
+        <v>1682012.5</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3106,12 +3106,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>21200</v>
+        <v>100500</v>
       </c>
       <c r="F83" t="n">
-        <v>120.8659</v>
+        <v>8.9518</v>
       </c>
       <c r="G83" t="n">
-        <v>2562357.9</v>
+        <v>899652.6</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3138,27 +3138,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>27700</v>
+        <v>11410</v>
       </c>
       <c r="F84" t="n">
-        <v>161.1835</v>
+        <v>6321.2722</v>
       </c>
       <c r="G84" t="n">
-        <v>4464784.2</v>
+        <v>72125715.8</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3170,27 +3170,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>21500</v>
+        <v>12880</v>
       </c>
       <c r="F85" t="n">
-        <v>129.2032</v>
+        <v>713.2027</v>
       </c>
       <c r="G85" t="n">
-        <v>2777868.4</v>
+        <v>9186050.6</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>34100</v>
+        <v>21200</v>
       </c>
       <c r="F86" t="n">
-        <v>21.679</v>
+        <v>120.8659</v>
       </c>
       <c r="G86" t="n">
-        <v>739252.6</v>
+        <v>2562357.9</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3234,27 +3234,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>40850</v>
+        <v>27700</v>
       </c>
       <c r="F87" t="n">
-        <v>123.3915</v>
+        <v>161.1835</v>
       </c>
       <c r="G87" t="n">
-        <v>5040542.1</v>
+        <v>4464784.2</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3280,13 +3280,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>308000</v>
+        <v>21500</v>
       </c>
       <c r="F88" t="n">
-        <v>9.1744</v>
+        <v>129.2032</v>
       </c>
       <c r="G88" t="n">
-        <v>2825715.8</v>
+        <v>2777868.4</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3298,27 +3298,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6330</v>
+        <v>34100</v>
       </c>
       <c r="F89" t="n">
-        <v>50.5051</v>
+        <v>21.679</v>
       </c>
       <c r="G89" t="n">
-        <v>319697.4</v>
+        <v>739252.6</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3330,27 +3330,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>31700</v>
+        <v>40850</v>
       </c>
       <c r="F90" t="n">
-        <v>158.7408</v>
+        <v>123.3915</v>
       </c>
       <c r="G90" t="n">
-        <v>5032084.2</v>
+        <v>5040542.1</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3362,27 +3362,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>68700</v>
+        <v>308000</v>
       </c>
       <c r="F91" t="n">
-        <v>16.0386</v>
+        <v>9.1744</v>
       </c>
       <c r="G91" t="n">
-        <v>1101852.6</v>
+        <v>2825715.8</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3394,12 +3394,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3408,13 +3408,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>256000</v>
+        <v>6330</v>
       </c>
       <c r="F92" t="n">
-        <v>45.4873</v>
+        <v>50.5051</v>
       </c>
       <c r="G92" t="n">
-        <v>11644736.8</v>
+        <v>319697.4</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3426,27 +3426,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>91100</v>
+        <v>31700</v>
       </c>
       <c r="F93" t="n">
-        <v>19.6174</v>
+        <v>158.7408</v>
       </c>
       <c r="G93" t="n">
-        <v>1787142.1</v>
+        <v>5032084.2</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>130900</v>
+        <v>68700</v>
       </c>
       <c r="F94" t="n">
-        <v>89.1437</v>
+        <v>16.0386</v>
       </c>
       <c r="G94" t="n">
-        <v>11668905.3</v>
+        <v>1101852.6</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3490,27 +3490,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2400</v>
+        <v>256000</v>
       </c>
       <c r="F95" t="n">
-        <v>32820.1843</v>
+        <v>45.4873</v>
       </c>
       <c r="G95" t="n">
-        <v>78768442.40000001</v>
+        <v>11644736.8</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3536,13 +3536,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>41150</v>
+        <v>91100</v>
       </c>
       <c r="F96" t="n">
-        <v>38.7861</v>
+        <v>19.6174</v>
       </c>
       <c r="G96" t="n">
-        <v>1596047.4</v>
+        <v>1787142.1</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3568,13 +3568,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>49450</v>
+        <v>130900</v>
       </c>
       <c r="F97" t="n">
-        <v>83.90349999999999</v>
+        <v>89.1437</v>
       </c>
       <c r="G97" t="n">
-        <v>4149029</v>
+        <v>11668905.3</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3600,13 +3600,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>24750</v>
+        <v>2400</v>
       </c>
       <c r="F98" t="n">
-        <v>23.3799</v>
+        <v>32820.1843</v>
       </c>
       <c r="G98" t="n">
-        <v>578652.6</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3618,142 +3618,140 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5450</v>
+        <v>41150</v>
       </c>
       <c r="F99" t="n">
-        <v>220.6267</v>
+        <v>38.7861</v>
       </c>
       <c r="G99" t="n">
-        <v>1202415.4</v>
+        <v>1596047.4</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>327000</v>
+        <v>49450</v>
       </c>
       <c r="F100" t="n">
-        <v>54</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>4149029</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5130</v>
+        <v>24750</v>
       </c>
       <c r="F101" t="n">
-        <v>4001.7913</v>
+        <v>23.3799</v>
       </c>
       <c r="G101" t="n">
-        <v>20529189.5</v>
+        <v>578652.6</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>27100</v>
+        <v>5450</v>
       </c>
       <c r="F102" t="n">
-        <v>376</v>
+        <v>220.6267</v>
       </c>
       <c r="G102" t="n">
-        <v>10189600</v>
+        <v>1202415.4</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3762,47 +3760,47 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>67600</v>
+        <v>327000</v>
       </c>
       <c r="F103" t="n">
-        <v>998</v>
+        <v>54</v>
       </c>
       <c r="G103" t="n">
-        <v>67464800</v>
+        <v>17658000</v>
       </c>
       <c r="H103" t="n">
-        <v>-3.57</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>11900</v>
+        <v>5130</v>
       </c>
       <c r="F104" t="n">
-        <v>856</v>
+        <v>4001.7913</v>
       </c>
       <c r="G104" t="n">
-        <v>10186400</v>
+        <v>20529189.5</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3814,27 +3812,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>29300</v>
+        <v>27100</v>
       </c>
       <c r="F105" t="n">
-        <v>2434</v>
+        <v>376</v>
       </c>
       <c r="G105" t="n">
-        <v>71316200</v>
+        <v>10189600</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3846,29 +3844,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>119300</v>
+        <v>67600</v>
       </c>
       <c r="F106" t="n">
-        <v>171</v>
+        <v>998</v>
       </c>
       <c r="G106" t="n">
-        <v>20400300</v>
-      </c>
-      <c r="H106" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3878,44 +3878,44 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2445</v>
+        <v>11900</v>
       </c>
       <c r="F107" t="n">
-        <v>82456</v>
+        <v>856</v>
       </c>
       <c r="G107" t="n">
-        <v>201604920</v>
+        <v>10186400</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3924,81 +3924,79 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>18910</v>
+        <v>29300</v>
       </c>
       <c r="F108" t="n">
-        <v>1068.0212</v>
+        <v>2434</v>
       </c>
       <c r="G108" t="n">
-        <v>20196280</v>
+        <v>71316200</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>32250</v>
+        <v>119300</v>
       </c>
       <c r="F109" t="n">
-        <v>626</v>
+        <v>171</v>
       </c>
       <c r="G109" t="n">
-        <v>20188500</v>
+        <v>20400300</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>82500</v>
+        <v>2445</v>
       </c>
       <c r="F110" t="n">
-        <v>204</v>
+        <v>82456</v>
       </c>
       <c r="G110" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>201604920</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4008,100 +4006,100 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>56800</v>
+        <v>18910</v>
       </c>
       <c r="F111" t="n">
-        <v>258</v>
+        <v>1068.0212</v>
       </c>
       <c r="G111" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20196280</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>83700</v>
+        <v>32250</v>
       </c>
       <c r="F112" t="n">
-        <v>120</v>
+        <v>626</v>
       </c>
       <c r="G112" t="n">
-        <v>10044000</v>
+        <v>20188500</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>43650</v>
+        <v>82500</v>
       </c>
       <c r="F113" t="n">
-        <v>462</v>
+        <v>204</v>
       </c>
       <c r="G113" t="n">
-        <v>20166300</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4116,113 +4114,115 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>59700</v>
+        <v>56800</v>
       </c>
       <c r="F114" t="n">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="G114" t="n">
-        <v>10089300</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>10930</v>
+        <v>83700</v>
       </c>
       <c r="F115" t="n">
-        <v>1833</v>
+        <v>120</v>
       </c>
       <c r="G115" t="n">
-        <v>20034690</v>
+        <v>10044000</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>19850</v>
+        <v>43650</v>
       </c>
       <c r="F116" t="n">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="G116" t="n">
-        <v>10024250</v>
+        <v>20166300</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>26350</v>
+        <v>59700</v>
       </c>
       <c r="F117" t="n">
-        <v>380</v>
+        <v>169</v>
       </c>
       <c r="G117" t="n">
-        <v>10013000</v>
+        <v>10089300</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4234,31 +4234,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>23500</v>
+        <v>10930</v>
       </c>
       <c r="F118" t="n">
-        <v>833</v>
+        <v>1833</v>
       </c>
       <c r="G118" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20034690</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4268,27 +4266,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>85200</v>
+        <v>19850</v>
       </c>
       <c r="F119" t="n">
-        <v>118</v>
+        <v>505</v>
       </c>
       <c r="G119" t="n">
-        <v>10053600</v>
+        <v>10024250</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4300,27 +4298,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>63400</v>
+        <v>26350</v>
       </c>
       <c r="F120" t="n">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="G120" t="n">
-        <v>20034400</v>
+        <v>10013000</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4332,29 +4330,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>110300</v>
+        <v>23500</v>
       </c>
       <c r="F121" t="n">
-        <v>91</v>
+        <v>833</v>
       </c>
       <c r="G121" t="n">
-        <v>10037300</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4378,30 +4378,30 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>66100</v>
+        <v>85200</v>
       </c>
       <c r="F122" t="n">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="G122" t="n">
-        <v>10047200</v>
+        <v>10053600</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>25800</v>
+        <v>63400</v>
       </c>
       <c r="F123" t="n">
-        <v>2713</v>
+        <v>316</v>
       </c>
       <c r="G123" t="n">
-        <v>69995400</v>
+        <v>20034400</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>206500</v>
+        <v>110300</v>
       </c>
       <c r="F124" t="n">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="G124" t="n">
-        <v>69797000</v>
+        <v>10037300</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>70100</v>
+        <v>66100</v>
       </c>
       <c r="F125" t="n">
-        <v>998</v>
+        <v>152</v>
       </c>
       <c r="G125" t="n">
-        <v>69959800</v>
+        <v>10047200</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4506,13 +4506,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>93300</v>
+        <v>25800</v>
       </c>
       <c r="F126" t="n">
-        <v>214</v>
+        <v>2713</v>
       </c>
       <c r="G126" t="n">
-        <v>19966200</v>
+        <v>69995400</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4524,12 +4524,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>11300</v>
+        <v>206500</v>
       </c>
       <c r="F127" t="n">
-        <v>4424</v>
+        <v>338</v>
       </c>
       <c r="G127" t="n">
-        <v>49991200</v>
+        <v>69797000</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4570,13 +4570,13 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>19740</v>
+        <v>70100</v>
       </c>
       <c r="F128" t="n">
-        <v>2532</v>
+        <v>998</v>
       </c>
       <c r="G128" t="n">
-        <v>49981680</v>
+        <v>69959800</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>25150</v>
+        <v>93300</v>
       </c>
       <c r="F129" t="n">
-        <v>2385</v>
+        <v>214</v>
       </c>
       <c r="G129" t="n">
-        <v>59982750</v>
+        <v>19966200</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>22050</v>
+        <v>11300</v>
       </c>
       <c r="F130" t="n">
-        <v>2267</v>
+        <v>4424</v>
       </c>
       <c r="G130" t="n">
-        <v>49987350</v>
+        <v>49991200</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4652,12 +4652,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4666,13 +4666,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>43150</v>
+        <v>19740</v>
       </c>
       <c r="F131" t="n">
-        <v>1390</v>
+        <v>2532</v>
       </c>
       <c r="G131" t="n">
-        <v>59978500</v>
+        <v>49981680</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4684,12 +4684,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4698,13 +4698,13 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>310000</v>
+        <v>25150</v>
       </c>
       <c r="F132" t="n">
-        <v>225</v>
+        <v>2385</v>
       </c>
       <c r="G132" t="n">
-        <v>69750000</v>
+        <v>59982750</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6240</v>
+        <v>22050</v>
       </c>
       <c r="F133" t="n">
-        <v>3205</v>
+        <v>2267</v>
       </c>
       <c r="G133" t="n">
-        <v>19999200</v>
+        <v>49987350</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>24000</v>
+        <v>43150</v>
       </c>
       <c r="F134" t="n">
-        <v>833</v>
+        <v>1390</v>
       </c>
       <c r="G134" t="n">
-        <v>19992000</v>
+        <v>59978500</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -4780,12 +4780,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4794,13 +4794,13 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>90300</v>
+        <v>310000</v>
       </c>
       <c r="F135" t="n">
-        <v>442</v>
+        <v>225</v>
       </c>
       <c r="G135" t="n">
-        <v>39912600</v>
+        <v>69750000</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4826,13 +4826,13 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F136" t="n">
-        <v>357</v>
+        <v>3205</v>
       </c>
       <c r="G136" t="n">
-        <v>99781500</v>
+        <v>19999200</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4858,13 +4858,13 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>366000</v>
+        <v>24000</v>
       </c>
       <c r="F137" t="n">
-        <v>54</v>
+        <v>833</v>
       </c>
       <c r="G137" t="n">
-        <v>19764000</v>
+        <v>19992000</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4890,13 +4890,13 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>91000</v>
+        <v>90300</v>
       </c>
       <c r="F138" t="n">
-        <v>659</v>
+        <v>442</v>
       </c>
       <c r="G138" t="n">
-        <v>59969000</v>
+        <v>39912600</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4922,13 +4922,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>120100</v>
+        <v>279500</v>
       </c>
       <c r="F139" t="n">
-        <v>666</v>
+        <v>357</v>
       </c>
       <c r="G139" t="n">
-        <v>79986600</v>
+        <v>99781500</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4954,13 +4954,13 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2405</v>
+        <v>366000</v>
       </c>
       <c r="F140" t="n">
-        <v>415800</v>
+        <v>54</v>
       </c>
       <c r="G140" t="n">
-        <v>999999000</v>
+        <v>19764000</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4986,13 +4986,13 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>69000</v>
+        <v>91000</v>
       </c>
       <c r="F141" t="n">
-        <v>579</v>
+        <v>659</v>
       </c>
       <c r="G141" t="n">
-        <v>39951000</v>
+        <v>59969000</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>42300</v>
+        <v>120100</v>
       </c>
       <c r="F142" t="n">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="G142" t="n">
-        <v>29990700</v>
+        <v>79986600</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -5036,29 +5036,125 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F143" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G143" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F144" t="n">
+        <v>579</v>
+      </c>
+      <c r="G144" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F145" t="n">
+        <v>709</v>
+      </c>
+      <c r="G145" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E143" t="n">
+      <c r="E146" t="n">
         <v>23350</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F146" t="n">
         <v>856</v>
       </c>
-      <c r="G143" t="n">
+      <c r="G146" t="n">
         <v>19987600</v>
       </c>
-      <c r="H143" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,94 +492,96 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26200</v>
+        <v>41050</v>
       </c>
       <c r="F2" t="n">
-        <v>382.0025</v>
+        <v>490.4266</v>
       </c>
       <c r="G2" t="n">
-        <v>10008466.3</v>
+        <v>20132010.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>94700</v>
+        <v>230000</v>
       </c>
       <c r="F3" t="n">
-        <v>105.686</v>
+        <v>135.183</v>
       </c>
       <c r="G3" t="n">
-        <v>10008466.3</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>31092084.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-16.92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42500</v>
+        <v>2595</v>
       </c>
       <c r="F4" t="n">
-        <v>470.9867</v>
+        <v>42895.584</v>
       </c>
       <c r="G4" t="n">
-        <v>20016932.7</v>
+        <v>111314040.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,30 +590,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26600</v>
+        <v>15870</v>
       </c>
       <c r="F5" t="n">
-        <v>361.0017</v>
+        <v>634.2788</v>
       </c>
       <c r="G5" t="n">
-        <v>9602645.699999999</v>
+        <v>10066005.2</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,62 +622,62 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10740</v>
+        <v>59000</v>
       </c>
       <c r="F6" t="n">
-        <v>894.1011</v>
+        <v>170.6103</v>
       </c>
       <c r="G6" t="n">
-        <v>9602645.699999999</v>
+        <v>10066005.2</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16180</v>
+        <v>9960</v>
       </c>
       <c r="F7" t="n">
-        <v>1186.9772</v>
+        <v>1010.6431</v>
       </c>
       <c r="G7" t="n">
-        <v>19205291.4</v>
+        <v>10066005.2</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,96 +686,94 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>88400</v>
+        <v>59100</v>
       </c>
       <c r="F8" t="n">
-        <v>217.2544</v>
+        <v>681.2863</v>
       </c>
       <c r="G8" t="n">
-        <v>19205291.4</v>
+        <v>40264020.8</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>99100</v>
+        <v>3385</v>
       </c>
       <c r="F9" t="n">
-        <v>290.6956</v>
+        <v>2973.7091</v>
       </c>
       <c r="G9" t="n">
-        <v>28807937.1</v>
+        <v>10066005.2</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37350</v>
+        <v>26200</v>
       </c>
       <c r="F10" t="n">
-        <v>491.1229</v>
+        <v>382.0025</v>
       </c>
       <c r="G10" t="n">
-        <v>18343440.7</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-9.23</v>
-      </c>
+        <v>10008466.3</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,49 +782,47 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2520</v>
+        <v>94700</v>
       </c>
       <c r="F11" t="n">
-        <v>33368.1327</v>
+        <v>105.686</v>
       </c>
       <c r="G11" t="n">
-        <v>84087694.5</v>
+        <v>10008466.3</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>16500</v>
+        <v>42500</v>
       </c>
       <c r="F12" t="n">
-        <v>856.421</v>
+        <v>470.9867</v>
       </c>
       <c r="G12" t="n">
-        <v>14130946.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-22.8</v>
-      </c>
+        <v>20016932.7</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -834,27 +832,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>27650</v>
+        <v>26600</v>
       </c>
       <c r="F13" t="n">
-        <v>1041.8784</v>
+        <v>361.0017</v>
       </c>
       <c r="G13" t="n">
-        <v>28807937.1</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,24 +864,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9350</v>
+        <v>10740</v>
       </c>
       <c r="F14" t="n">
-        <v>1027.0209</v>
+        <v>894.1011</v>
       </c>
       <c r="G14" t="n">
         <v>9602645.699999999</v>
@@ -893,145 +891,147 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>28650</v>
+        <v>16180</v>
       </c>
       <c r="F15" t="n">
-        <v>345.7839</v>
+        <v>1186.9772</v>
       </c>
       <c r="G15" t="n">
-        <v>9906708.4</v>
+        <v>19205291.4</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11600</v>
+        <v>88400</v>
       </c>
       <c r="F16" t="n">
-        <v>854.0266</v>
+        <v>217.2544</v>
       </c>
       <c r="G16" t="n">
-        <v>9906708.4</v>
+        <v>19205291.4</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>131000</v>
+        <v>99100</v>
       </c>
       <c r="F17" t="n">
-        <v>75.6237</v>
+        <v>290.6956</v>
       </c>
       <c r="G17" t="n">
-        <v>9906708.4</v>
+        <v>28807937.1</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>67100</v>
+        <v>37350</v>
       </c>
       <c r="F18" t="n">
-        <v>147.641</v>
+        <v>491.1229</v>
       </c>
       <c r="G18" t="n">
-        <v>9906708.4</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>18343440.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-9.23</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,96 +1040,96 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4830</v>
+        <v>2520</v>
       </c>
       <c r="F19" t="n">
-        <v>2051.0783</v>
+        <v>33368.1327</v>
       </c>
       <c r="G19" t="n">
-        <v>9906708.4</v>
+        <v>84087694.5</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9430</v>
+        <v>16500</v>
       </c>
       <c r="F20" t="n">
-        <v>2101.1046</v>
+        <v>856.421</v>
       </c>
       <c r="G20" t="n">
-        <v>19813416.7</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>14130946.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-22.8</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>79100</v>
+        <v>27650</v>
       </c>
       <c r="F21" t="n">
-        <v>205.0482</v>
+        <v>1041.8784</v>
       </c>
       <c r="G21" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>28807937.1</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,211 +1138,207 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>25250</v>
+        <v>9350</v>
       </c>
       <c r="F22" t="n">
-        <v>768.6917999999999</v>
+        <v>1027.0209</v>
       </c>
       <c r="G22" t="n">
-        <v>19409469.1</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12510</v>
+        <v>28650</v>
       </c>
       <c r="F23" t="n">
-        <v>1443.4887</v>
+        <v>345.7839</v>
       </c>
       <c r="G23" t="n">
-        <v>18058043.3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-11.28</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>126500</v>
+        <v>11600</v>
       </c>
       <c r="F24" t="n">
-        <v>383.5863</v>
+        <v>854.0266</v>
       </c>
       <c r="G24" t="n">
-        <v>48523672.7</v>
+        <v>9906708.4</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2485</v>
+        <v>131000</v>
       </c>
       <c r="F25" t="n">
-        <v>42403.6617</v>
+        <v>75.6237</v>
       </c>
       <c r="G25" t="n">
-        <v>105373099.3</v>
+        <v>9906708.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>45500</v>
+        <v>67100</v>
       </c>
       <c r="F26" t="n">
-        <v>213.2909</v>
+        <v>147.641</v>
       </c>
       <c r="G26" t="n">
-        <v>9704734.5</v>
+        <v>9906708.4</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>17880</v>
+        <v>4830</v>
       </c>
       <c r="F27" t="n">
-        <v>1085.5408</v>
+        <v>2051.0783</v>
       </c>
       <c r="G27" t="n">
-        <v>19409469.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4460</v>
+        <v>9430</v>
       </c>
       <c r="F28" t="n">
-        <v>3137.3165</v>
+        <v>2101.1046</v>
       </c>
       <c r="G28" t="n">
-        <v>13992431.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-17.83</v>
-      </c>
+        <v>19813416.7</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1352,76 +1348,78 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3345</v>
+        <v>79100</v>
       </c>
       <c r="F29" t="n">
-        <v>11605.0637</v>
+        <v>205.0482</v>
       </c>
       <c r="G29" t="n">
-        <v>38818938.1</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>16219315.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-15.22</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>12120</v>
+        <v>25250</v>
       </c>
       <c r="F30" t="n">
-        <v>820.878</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>9949041.199999999</v>
+        <v>19409469.1</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1430,98 +1428,96 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248000</v>
+        <v>12510</v>
       </c>
       <c r="F31" t="n">
-        <v>81.12909999999999</v>
+        <v>1443.4887</v>
       </c>
       <c r="G31" t="n">
-        <v>20120019.7</v>
+        <v>18058043.3</v>
       </c>
       <c r="H31" t="n">
-        <v>-19.98</v>
+        <v>-11.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222500</v>
+        <v>126500</v>
       </c>
       <c r="F32" t="n">
-        <v>178.8592</v>
+        <v>383.5863</v>
       </c>
       <c r="G32" t="n">
-        <v>39796164.7</v>
+        <v>48523672.7</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>54500</v>
+        <v>2485</v>
       </c>
       <c r="F33" t="n">
-        <v>504.0447</v>
+        <v>42403.6617</v>
       </c>
       <c r="G33" t="n">
-        <v>27470436.6</v>
-      </c>
-      <c r="H33" t="n">
-        <v>24.43</v>
-      </c>
+        <v>105373099.3</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1530,30 +1526,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>32350</v>
+        <v>45500</v>
       </c>
       <c r="F34" t="n">
-        <v>314.5779</v>
+        <v>213.2909</v>
       </c>
       <c r="G34" t="n">
-        <v>10176595.1</v>
+        <v>9704734.5</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1562,126 +1558,128 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>13650</v>
+        <v>17880</v>
       </c>
       <c r="F35" t="n">
-        <v>745.5381</v>
+        <v>1085.5408</v>
       </c>
       <c r="G35" t="n">
-        <v>10176595.1</v>
+        <v>19409469.1</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31950</v>
+        <v>4460</v>
       </c>
       <c r="F36" t="n">
-        <v>318.5163</v>
+        <v>3137.3165</v>
       </c>
       <c r="G36" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>13992431.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-17.83</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>250500</v>
+        <v>3345</v>
       </c>
       <c r="F37" t="n">
-        <v>81.2503</v>
+        <v>11605.0637</v>
       </c>
       <c r="G37" t="n">
-        <v>20353190.3</v>
+        <v>38818938.1</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>14100</v>
+        <v>12120</v>
       </c>
       <c r="F38" t="n">
-        <v>1443.4887</v>
+        <v>820.878</v>
       </c>
       <c r="G38" t="n">
-        <v>20353190.3</v>
+        <v>9949041.199999999</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1690,32 +1688,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31300</v>
+        <v>248000</v>
       </c>
       <c r="F39" t="n">
-        <v>1954.4702</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>61174916</v>
+        <v>20120019.7</v>
       </c>
       <c r="H39" t="n">
-        <v>6.83</v>
+        <v>-19.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1724,47 +1722,49 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2355</v>
+        <v>222500</v>
       </c>
       <c r="F40" t="n">
-        <v>65496.7248</v>
+        <v>178.8592</v>
       </c>
       <c r="G40" t="n">
-        <v>154244786.8</v>
+        <v>39796164.7</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>15810</v>
+        <v>54500</v>
       </c>
       <c r="F41" t="n">
-        <v>5149.4473</v>
+        <v>504.0447</v>
       </c>
       <c r="G41" t="n">
-        <v>81412761.09999999</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1774,24 +1774,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>56700</v>
+        <v>32350</v>
       </c>
       <c r="F42" t="n">
-        <v>179.4814</v>
+        <v>314.5779</v>
       </c>
       <c r="G42" t="n">
         <v>10176595.1</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1820,128 +1820,126 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4660</v>
+        <v>13650</v>
       </c>
       <c r="F43" t="n">
-        <v>4367.6374</v>
+        <v>745.5381</v>
       </c>
       <c r="G43" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>44600</v>
+        <v>31950</v>
       </c>
       <c r="F44" t="n">
-        <v>1359.3974</v>
+        <v>318.5163</v>
       </c>
       <c r="G44" t="n">
-        <v>60629123.5</v>
+        <v>10176595.1</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>20300</v>
+        <v>250500</v>
       </c>
       <c r="F45" t="n">
-        <v>1162.9429</v>
+        <v>81.2503</v>
       </c>
       <c r="G45" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H45" t="n">
-        <v>7.9</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>13160</v>
+        <v>14100</v>
       </c>
       <c r="F46" t="n">
-        <v>767.846</v>
+        <v>1443.4887</v>
       </c>
       <c r="G46" t="n">
-        <v>10104853.9</v>
+        <v>20353190.3</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1950,66 +1948,64 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>49050</v>
+        <v>31300</v>
       </c>
       <c r="F47" t="n">
-        <v>357.1039</v>
+        <v>1954.4702</v>
       </c>
       <c r="G47" t="n">
-        <v>17515946</v>
+        <v>61174916</v>
       </c>
       <c r="H47" t="n">
-        <v>-16.44</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>37100</v>
+        <v>2355</v>
       </c>
       <c r="F48" t="n">
-        <v>604.321</v>
+        <v>65496.7248</v>
       </c>
       <c r="G48" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>15.04</v>
-      </c>
+        <v>154244786.8</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2018,62 +2014,62 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>123700</v>
+        <v>15810</v>
       </c>
       <c r="F49" t="n">
-        <v>490.1303</v>
+        <v>5149.4473</v>
       </c>
       <c r="G49" t="n">
-        <v>60629123.5</v>
+        <v>81412761.09999999</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>41150</v>
+        <v>56700</v>
       </c>
       <c r="F50" t="n">
-        <v>491.1229</v>
+        <v>179.4814</v>
       </c>
       <c r="G50" t="n">
-        <v>20209707.8</v>
+        <v>10176595.1</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2082,13 +2078,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>31500</v>
+        <v>4660</v>
       </c>
       <c r="F51" t="n">
-        <v>320.789</v>
+        <v>4367.6374</v>
       </c>
       <c r="G51" t="n">
-        <v>10104853.9</v>
+        <v>20353190.3</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2100,27 +2096,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228500</v>
+        <v>44600</v>
       </c>
       <c r="F52" t="n">
-        <v>88.4451</v>
+        <v>1359.3974</v>
       </c>
       <c r="G52" t="n">
-        <v>20209707.8</v>
+        <v>60629123.5</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2132,12 +2128,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2146,16 +2142,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>88500</v>
+        <v>20300</v>
       </c>
       <c r="F53" t="n">
-        <v>900.2261</v>
+        <v>1162.9429</v>
       </c>
       <c r="G53" t="n">
-        <v>79670012.59999999</v>
+        <v>23607739.9</v>
       </c>
       <c r="H53" t="n">
-        <v>-3.84</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="54">
@@ -2166,31 +2162,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>130100</v>
+        <v>13160</v>
       </c>
       <c r="F54" t="n">
-        <v>314.8563</v>
+        <v>767.846</v>
       </c>
       <c r="G54" t="n">
-        <v>40962809.6</v>
-      </c>
-      <c r="H54" t="n">
-        <v>8.33</v>
-      </c>
+        <v>10104853.9</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2200,29 +2194,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2325</v>
+        <v>49050</v>
       </c>
       <c r="F55" t="n">
-        <v>21730.8686</v>
+        <v>357.1039</v>
       </c>
       <c r="G55" t="n">
-        <v>50524269.6</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2232,29 +2228,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>64700</v>
+        <v>37100</v>
       </c>
       <c r="F56" t="n">
-        <v>468.5404</v>
+        <v>604.321</v>
       </c>
       <c r="G56" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2264,12 +2262,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2278,94 +2276,94 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4670</v>
+        <v>123700</v>
       </c>
       <c r="F57" t="n">
-        <v>6491.3408</v>
+        <v>490.1303</v>
       </c>
       <c r="G57" t="n">
-        <v>30314561.7</v>
+        <v>60629123.5</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2120</v>
+        <v>41150</v>
       </c>
       <c r="F58" t="n">
-        <v>63879.7502</v>
+        <v>491.1229</v>
       </c>
       <c r="G58" t="n">
-        <v>135425070.4</v>
+        <v>20209707.8</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2120</v>
+        <v>31500</v>
       </c>
       <c r="F59" t="n">
-        <v>3453.9051</v>
+        <v>320.789</v>
       </c>
       <c r="G59" t="n">
-        <v>7322278.8</v>
+        <v>10104853.9</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2374,30 +2372,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>22900</v>
+        <v>228500</v>
       </c>
       <c r="F60" t="n">
-        <v>1397.6406</v>
+        <v>88.4451</v>
       </c>
       <c r="G60" t="n">
-        <v>32005969</v>
+        <v>20209707.8</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2406,194 +2404,194 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>73600</v>
+        <v>88500</v>
       </c>
       <c r="F61" t="n">
-        <v>299.9614</v>
+        <v>900.2261</v>
       </c>
       <c r="G61" t="n">
-        <v>22077158.2</v>
+        <v>79670012.59999999</v>
       </c>
       <c r="H61" t="n">
-        <v>16.09</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2215</v>
+        <v>130100</v>
       </c>
       <c r="F62" t="n">
-        <v>28224.978</v>
+        <v>314.8563</v>
       </c>
       <c r="G62" t="n">
-        <v>62518326.2</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H62" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43800</v>
+        <v>2325</v>
       </c>
       <c r="F63" t="n">
-        <v>504.0447</v>
+        <v>21730.8686</v>
       </c>
       <c r="G63" t="n">
-        <v>22077158.2</v>
+        <v>50524269.6</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>23650</v>
+        <v>64700</v>
       </c>
       <c r="F64" t="n">
-        <v>451.106</v>
+        <v>468.5404</v>
       </c>
       <c r="G64" t="n">
-        <v>10668656.3</v>
+        <v>30314561.7</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5730</v>
+        <v>4670</v>
       </c>
       <c r="F65" t="n">
-        <v>3723.7893</v>
+        <v>6491.3408</v>
       </c>
       <c r="G65" t="n">
-        <v>21337312.7</v>
+        <v>30314561.7</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6080</v>
+        <v>2120</v>
       </c>
       <c r="F66" t="n">
-        <v>3255.5051</v>
+        <v>63879.7502</v>
       </c>
       <c r="G66" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>135425070.4</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2602,30 +2600,30 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>95200</v>
+        <v>2120</v>
       </c>
       <c r="F67" t="n">
-        <v>221.6088</v>
+        <v>3453.9051</v>
       </c>
       <c r="G67" t="n">
-        <v>21097154.4</v>
+        <v>7322278.8</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2634,62 +2632,64 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2205</v>
+        <v>22900</v>
       </c>
       <c r="F68" t="n">
-        <v>52623.2877</v>
+        <v>1397.6406</v>
       </c>
       <c r="G68" t="n">
-        <v>116034349.3</v>
+        <v>32005969</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>58700</v>
+        <v>73600</v>
       </c>
       <c r="F69" t="n">
-        <v>357.1039</v>
+        <v>299.9614</v>
       </c>
       <c r="G69" t="n">
-        <v>20961998.6</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2698,96 +2698,94 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>13250</v>
+        <v>2215</v>
       </c>
       <c r="F70" t="n">
-        <v>791.0188000000001</v>
+        <v>28224.978</v>
       </c>
       <c r="G70" t="n">
-        <v>10480999.3</v>
+        <v>62518326.2</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2360</v>
+        <v>43800</v>
       </c>
       <c r="F71" t="n">
-        <v>66616.5209</v>
+        <v>504.0447</v>
       </c>
       <c r="G71" t="n">
-        <v>157214989.3</v>
+        <v>22077158.2</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>38300</v>
+        <v>23650</v>
       </c>
       <c r="F72" t="n">
-        <v>500.7861</v>
+        <v>451.106</v>
       </c>
       <c r="G72" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>10668656.3</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2796,30 +2794,30 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21150</v>
+        <v>5730</v>
       </c>
       <c r="F73" t="n">
-        <v>495.5555</v>
+        <v>3723.7893</v>
       </c>
       <c r="G73" t="n">
-        <v>10480999.3</v>
+        <v>21337312.7</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2828,32 +2826,32 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>23650</v>
+        <v>6080</v>
       </c>
       <c r="F74" t="n">
-        <v>832.6201</v>
+        <v>3255.5051</v>
       </c>
       <c r="G74" t="n">
-        <v>19691465.3</v>
+        <v>19793471.1</v>
       </c>
       <c r="H74" t="n">
-        <v>1.28</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2862,30 +2860,30 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>12310</v>
+        <v>95200</v>
       </c>
       <c r="F75" t="n">
-        <v>2480.1654</v>
+        <v>221.6088</v>
       </c>
       <c r="G75" t="n">
-        <v>30530836.4</v>
+        <v>21097154.4</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2894,62 +2892,62 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>40650</v>
+        <v>2205</v>
       </c>
       <c r="F76" t="n">
-        <v>751.0661</v>
+        <v>52623.2877</v>
       </c>
       <c r="G76" t="n">
-        <v>30530836.4</v>
+        <v>116034349.3</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>283500</v>
+        <v>58700</v>
       </c>
       <c r="F77" t="n">
-        <v>71.795</v>
+        <v>357.1039</v>
       </c>
       <c r="G77" t="n">
-        <v>20353890.9</v>
+        <v>20961998.6</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2958,224 +2956,226 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2390</v>
+        <v>13250</v>
       </c>
       <c r="F78" t="n">
-        <v>42581.3618</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>101769454.6</v>
+        <v>10480999.3</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>20450</v>
+        <v>2360</v>
       </c>
       <c r="F79" t="n">
-        <v>995.3003</v>
+        <v>66616.5209</v>
       </c>
       <c r="G79" t="n">
-        <v>20353890.9</v>
+        <v>157214989.3</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>30200</v>
+        <v>38300</v>
       </c>
       <c r="F80" t="n">
-        <v>359.55</v>
+        <v>500.7861</v>
       </c>
       <c r="G80" t="n">
-        <v>10858410.6</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>208500</v>
+        <v>21150</v>
       </c>
       <c r="F81" t="n">
-        <v>338</v>
+        <v>495.5555</v>
       </c>
       <c r="G81" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.97</v>
-      </c>
+        <v>10480999.3</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>17720</v>
+        <v>23650</v>
       </c>
       <c r="F82" t="n">
-        <v>94.9217</v>
+        <v>832.6201</v>
       </c>
       <c r="G82" t="n">
-        <v>1682012.5</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100500</v>
+        <v>12310</v>
       </c>
       <c r="F83" t="n">
-        <v>8.9518</v>
+        <v>2480.1654</v>
       </c>
       <c r="G83" t="n">
-        <v>899652.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>11410</v>
+        <v>40650</v>
       </c>
       <c r="F84" t="n">
-        <v>6321.2722</v>
+        <v>751.0661</v>
       </c>
       <c r="G84" t="n">
-        <v>72125715.8</v>
+        <v>30530836.4</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3184,77 +3184,77 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>12880</v>
+        <v>283500</v>
       </c>
       <c r="F85" t="n">
-        <v>713.2027</v>
+        <v>71.795</v>
       </c>
       <c r="G85" t="n">
-        <v>9186050.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>21200</v>
+        <v>2390</v>
       </c>
       <c r="F86" t="n">
-        <v>120.8659</v>
+        <v>42581.3618</v>
       </c>
       <c r="G86" t="n">
-        <v>2562357.9</v>
+        <v>101769454.6</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>27700</v>
+        <v>20450</v>
       </c>
       <c r="F87" t="n">
-        <v>161.1835</v>
+        <v>995.3003</v>
       </c>
       <c r="G87" t="n">
-        <v>4464784.2</v>
+        <v>20353890.9</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3266,27 +3266,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>21500</v>
+        <v>30200</v>
       </c>
       <c r="F88" t="n">
-        <v>129.2032</v>
+        <v>359.55</v>
       </c>
       <c r="G88" t="n">
-        <v>2777868.4</v>
+        <v>10858410.6</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3298,29 +3298,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>34100</v>
+        <v>208500</v>
       </c>
       <c r="F89" t="n">
-        <v>21.679</v>
+        <v>338</v>
       </c>
       <c r="G89" t="n">
-        <v>739252.6</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3330,12 +3332,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3344,13 +3346,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>40850</v>
+        <v>17720</v>
       </c>
       <c r="F90" t="n">
-        <v>123.3915</v>
+        <v>94.9217</v>
       </c>
       <c r="G90" t="n">
-        <v>5040542.1</v>
+        <v>1682012.5</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3362,27 +3364,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>308000</v>
+        <v>100500</v>
       </c>
       <c r="F91" t="n">
-        <v>9.1744</v>
+        <v>8.9518</v>
       </c>
       <c r="G91" t="n">
-        <v>2825715.8</v>
+        <v>899652.6</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3394,27 +3396,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6330</v>
+        <v>11410</v>
       </c>
       <c r="F92" t="n">
-        <v>50.5051</v>
+        <v>6321.2722</v>
       </c>
       <c r="G92" t="n">
-        <v>319697.4</v>
+        <v>72125715.8</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3426,12 +3428,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3440,13 +3442,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>31700</v>
+        <v>12880</v>
       </c>
       <c r="F93" t="n">
-        <v>158.7408</v>
+        <v>713.2027</v>
       </c>
       <c r="G93" t="n">
-        <v>5032084.2</v>
+        <v>9186050.6</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3458,12 +3460,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3472,13 +3474,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>68700</v>
+        <v>21200</v>
       </c>
       <c r="F94" t="n">
-        <v>16.0386</v>
+        <v>120.8659</v>
       </c>
       <c r="G94" t="n">
-        <v>1101852.6</v>
+        <v>2562357.9</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3490,27 +3492,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>256000</v>
+        <v>27700</v>
       </c>
       <c r="F95" t="n">
-        <v>45.4873</v>
+        <v>161.1835</v>
       </c>
       <c r="G95" t="n">
-        <v>11644736.8</v>
+        <v>4464784.2</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3522,12 +3524,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3536,13 +3538,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>91100</v>
+        <v>21500</v>
       </c>
       <c r="F96" t="n">
-        <v>19.6174</v>
+        <v>129.2032</v>
       </c>
       <c r="G96" t="n">
-        <v>1787142.1</v>
+        <v>2777868.4</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3554,12 +3556,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3568,13 +3570,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>130900</v>
+        <v>34100</v>
       </c>
       <c r="F97" t="n">
-        <v>89.1437</v>
+        <v>21.679</v>
       </c>
       <c r="G97" t="n">
-        <v>11668905.3</v>
+        <v>739252.6</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3586,27 +3588,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2400</v>
+        <v>40850</v>
       </c>
       <c r="F98" t="n">
-        <v>32820.1843</v>
+        <v>123.3915</v>
       </c>
       <c r="G98" t="n">
-        <v>78768442.40000001</v>
+        <v>5040542.1</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3618,12 +3620,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3632,13 +3634,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>41150</v>
+        <v>308000</v>
       </c>
       <c r="F99" t="n">
-        <v>38.7861</v>
+        <v>9.1744</v>
       </c>
       <c r="G99" t="n">
-        <v>1596047.4</v>
+        <v>2825715.8</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3650,27 +3652,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>49450</v>
+        <v>6330</v>
       </c>
       <c r="F100" t="n">
-        <v>83.90349999999999</v>
+        <v>50.5051</v>
       </c>
       <c r="G100" t="n">
-        <v>4149029</v>
+        <v>319697.4</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3682,12 +3684,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3696,13 +3698,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>24750</v>
+        <v>31700</v>
       </c>
       <c r="F101" t="n">
-        <v>23.3799</v>
+        <v>158.7408</v>
       </c>
       <c r="G101" t="n">
-        <v>578652.6</v>
+        <v>5032084.2</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3714,12 +3716,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3728,162 +3730,158 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5450</v>
+        <v>68700</v>
       </c>
       <c r="F102" t="n">
-        <v>220.6267</v>
+        <v>16.0386</v>
       </c>
       <c r="G102" t="n">
-        <v>1202415.4</v>
+        <v>1101852.6</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>327000</v>
+        <v>256000</v>
       </c>
       <c r="F103" t="n">
-        <v>54</v>
+        <v>45.4873</v>
       </c>
       <c r="G103" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>11644736.8</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5130</v>
+        <v>91100</v>
       </c>
       <c r="F104" t="n">
-        <v>4001.7913</v>
+        <v>19.6174</v>
       </c>
       <c r="G104" t="n">
-        <v>20529189.5</v>
+        <v>1787142.1</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>27100</v>
+        <v>130900</v>
       </c>
       <c r="F105" t="n">
-        <v>376</v>
+        <v>89.1437</v>
       </c>
       <c r="G105" t="n">
-        <v>10189600</v>
+        <v>11668905.3</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>67600</v>
+        <v>2400</v>
       </c>
       <c r="F106" t="n">
-        <v>998</v>
+        <v>32820.1843</v>
       </c>
       <c r="G106" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>78768442.40000001</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3892,62 +3890,62 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>11900</v>
+        <v>41150</v>
       </c>
       <c r="F107" t="n">
-        <v>856</v>
+        <v>38.7861</v>
       </c>
       <c r="G107" t="n">
-        <v>10186400</v>
+        <v>1596047.4</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>29300</v>
+        <v>49450</v>
       </c>
       <c r="F108" t="n">
-        <v>2434</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>71316200</v>
+        <v>4149029</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3956,30 +3954,30 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>119300</v>
+        <v>24750</v>
       </c>
       <c r="F109" t="n">
-        <v>171</v>
+        <v>23.3799</v>
       </c>
       <c r="G109" t="n">
-        <v>20400300</v>
+        <v>578652.6</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3988,62 +3986,64 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2445</v>
+        <v>5450</v>
       </c>
       <c r="F110" t="n">
-        <v>82456</v>
+        <v>220.6267</v>
       </c>
       <c r="G110" t="n">
-        <v>201604920</v>
+        <v>1202415.4</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>18910</v>
+        <v>327000</v>
       </c>
       <c r="F111" t="n">
-        <v>1068.0212</v>
+        <v>54</v>
       </c>
       <c r="G111" t="n">
-        <v>20196280</v>
-      </c>
-      <c r="H111" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4052,64 +4052,62 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>32250</v>
+        <v>5130</v>
       </c>
       <c r="F112" t="n">
-        <v>626</v>
+        <v>4001.7913</v>
       </c>
       <c r="G112" t="n">
-        <v>20188500</v>
+        <v>20529189.5</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>82500</v>
+        <v>27100</v>
       </c>
       <c r="F113" t="n">
-        <v>204</v>
+        <v>376</v>
       </c>
       <c r="G113" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>10189600</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4118,64 +4116,64 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>56800</v>
+        <v>67600</v>
       </c>
       <c r="F114" t="n">
-        <v>258</v>
+        <v>998</v>
       </c>
       <c r="G114" t="n">
-        <v>14654400</v>
+        <v>67464800</v>
       </c>
       <c r="H114" t="n">
-        <v>-17.68</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>83700</v>
+        <v>11900</v>
       </c>
       <c r="F115" t="n">
-        <v>120</v>
+        <v>856</v>
       </c>
       <c r="G115" t="n">
-        <v>10044000</v>
+        <v>10186400</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4184,30 +4182,30 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>43650</v>
+        <v>29300</v>
       </c>
       <c r="F116" t="n">
-        <v>462</v>
+        <v>2434</v>
       </c>
       <c r="G116" t="n">
-        <v>20166300</v>
+        <v>71316200</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4216,126 +4214,126 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>59700</v>
+        <v>119300</v>
       </c>
       <c r="F117" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G117" t="n">
-        <v>10089300</v>
+        <v>20400300</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>10930</v>
+        <v>2445</v>
       </c>
       <c r="F118" t="n">
-        <v>1833</v>
+        <v>82456</v>
       </c>
       <c r="G118" t="n">
-        <v>20034690</v>
+        <v>201604920</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>19850</v>
+        <v>18910</v>
       </c>
       <c r="F119" t="n">
-        <v>505</v>
+        <v>1068.0212</v>
       </c>
       <c r="G119" t="n">
-        <v>10024250</v>
+        <v>20196280</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>26350</v>
+        <v>32250</v>
       </c>
       <c r="F120" t="n">
-        <v>380</v>
+        <v>626</v>
       </c>
       <c r="G120" t="n">
-        <v>10013000</v>
+        <v>20188500</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4344,118 +4342,120 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>23500</v>
+        <v>82500</v>
       </c>
       <c r="F121" t="n">
-        <v>833</v>
+        <v>204</v>
       </c>
       <c r="G121" t="n">
-        <v>19575500</v>
+        <v>16830000</v>
       </c>
       <c r="H121" t="n">
-        <v>-2.08</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>85200</v>
+        <v>56800</v>
       </c>
       <c r="F122" t="n">
-        <v>118</v>
+        <v>258</v>
       </c>
       <c r="G122" t="n">
-        <v>10053600</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>63400</v>
+        <v>83700</v>
       </c>
       <c r="F123" t="n">
-        <v>316</v>
+        <v>120</v>
       </c>
       <c r="G123" t="n">
-        <v>20034400</v>
+        <v>10044000</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>110300</v>
+        <v>43650</v>
       </c>
       <c r="F124" t="n">
-        <v>91</v>
+        <v>462</v>
       </c>
       <c r="G124" t="n">
-        <v>10037300</v>
+        <v>20166300</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4474,190 +4474,192 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>66100</v>
+        <v>59700</v>
       </c>
       <c r="F125" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="G125" t="n">
-        <v>10047200</v>
+        <v>10089300</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>25800</v>
+        <v>10930</v>
       </c>
       <c r="F126" t="n">
-        <v>2713</v>
+        <v>1833</v>
       </c>
       <c r="G126" t="n">
-        <v>69995400</v>
+        <v>20034690</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>206500</v>
+        <v>19850</v>
       </c>
       <c r="F127" t="n">
-        <v>338</v>
+        <v>505</v>
       </c>
       <c r="G127" t="n">
-        <v>69797000</v>
+        <v>10024250</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>70100</v>
+        <v>26350</v>
       </c>
       <c r="F128" t="n">
-        <v>998</v>
+        <v>380</v>
       </c>
       <c r="G128" t="n">
-        <v>69959800</v>
+        <v>10013000</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>93300</v>
+        <v>23500</v>
       </c>
       <c r="F129" t="n">
-        <v>214</v>
+        <v>833</v>
       </c>
       <c r="G129" t="n">
-        <v>19966200</v>
-      </c>
-      <c r="H129" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>11300</v>
+        <v>85200</v>
       </c>
       <c r="F130" t="n">
-        <v>4424</v>
+        <v>118</v>
       </c>
       <c r="G130" t="n">
-        <v>49991200</v>
+        <v>10053600</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4666,77 +4668,77 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>19740</v>
+        <v>63400</v>
       </c>
       <c r="F131" t="n">
-        <v>2532</v>
+        <v>316</v>
       </c>
       <c r="G131" t="n">
-        <v>49981680</v>
+        <v>20034400</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>25150</v>
+        <v>110300</v>
       </c>
       <c r="F132" t="n">
-        <v>2385</v>
+        <v>91</v>
       </c>
       <c r="G132" t="n">
-        <v>59982750</v>
+        <v>10037300</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>22050</v>
+        <v>66100</v>
       </c>
       <c r="F133" t="n">
-        <v>2267</v>
+        <v>152</v>
       </c>
       <c r="G133" t="n">
-        <v>49987350</v>
+        <v>10047200</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
@@ -4748,12 +4750,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4762,13 +4764,13 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>43150</v>
+        <v>25800</v>
       </c>
       <c r="F134" t="n">
-        <v>1390</v>
+        <v>2713</v>
       </c>
       <c r="G134" t="n">
-        <v>59978500</v>
+        <v>69995400</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -4780,12 +4782,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4794,13 +4796,13 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>310000</v>
+        <v>206500</v>
       </c>
       <c r="F135" t="n">
-        <v>225</v>
+        <v>338</v>
       </c>
       <c r="G135" t="n">
-        <v>69750000</v>
+        <v>69797000</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -4812,12 +4814,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4826,13 +4828,13 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6240</v>
+        <v>70100</v>
       </c>
       <c r="F136" t="n">
-        <v>3205</v>
+        <v>998</v>
       </c>
       <c r="G136" t="n">
-        <v>19999200</v>
+        <v>69959800</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -4844,12 +4846,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4858,13 +4860,13 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>24000</v>
+        <v>93300</v>
       </c>
       <c r="F137" t="n">
-        <v>833</v>
+        <v>214</v>
       </c>
       <c r="G137" t="n">
-        <v>19992000</v>
+        <v>19966200</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -4876,12 +4878,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4890,13 +4892,13 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>90300</v>
+        <v>11300</v>
       </c>
       <c r="F138" t="n">
-        <v>442</v>
+        <v>4424</v>
       </c>
       <c r="G138" t="n">
-        <v>39912600</v>
+        <v>49991200</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -4908,12 +4910,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4922,13 +4924,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>279500</v>
+        <v>19740</v>
       </c>
       <c r="F139" t="n">
-        <v>357</v>
+        <v>2532</v>
       </c>
       <c r="G139" t="n">
-        <v>99781500</v>
+        <v>49981680</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -4940,12 +4942,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4954,13 +4956,13 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>366000</v>
+        <v>25150</v>
       </c>
       <c r="F140" t="n">
-        <v>54</v>
+        <v>2385</v>
       </c>
       <c r="G140" t="n">
-        <v>19764000</v>
+        <v>59982750</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -4972,12 +4974,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4986,13 +4988,13 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>91000</v>
+        <v>22050</v>
       </c>
       <c r="F141" t="n">
-        <v>659</v>
+        <v>2267</v>
       </c>
       <c r="G141" t="n">
-        <v>59969000</v>
+        <v>49987350</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -5004,12 +5006,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5018,13 +5020,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>120100</v>
+        <v>43150</v>
       </c>
       <c r="F142" t="n">
-        <v>666</v>
+        <v>1390</v>
       </c>
       <c r="G142" t="n">
-        <v>79986600</v>
+        <v>59978500</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -5036,12 +5038,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5050,13 +5052,13 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2405</v>
+        <v>310000</v>
       </c>
       <c r="F143" t="n">
-        <v>415800</v>
+        <v>225</v>
       </c>
       <c r="G143" t="n">
-        <v>999999000</v>
+        <v>69750000</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -5068,12 +5070,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5082,13 +5084,13 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>69000</v>
+        <v>6240</v>
       </c>
       <c r="F144" t="n">
-        <v>579</v>
+        <v>3205</v>
       </c>
       <c r="G144" t="n">
-        <v>39951000</v>
+        <v>19999200</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -5100,12 +5102,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5114,13 +5116,13 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>42300</v>
+        <v>24000</v>
       </c>
       <c r="F145" t="n">
-        <v>709</v>
+        <v>833</v>
       </c>
       <c r="G145" t="n">
-        <v>29990700</v>
+        <v>19992000</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -5132,29 +5134,285 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>141080</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>90300</v>
+      </c>
+      <c r="F146" t="n">
+        <v>442</v>
+      </c>
+      <c r="G146" t="n">
+        <v>39912600</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>279500</v>
+      </c>
+      <c r="F147" t="n">
+        <v>357</v>
+      </c>
+      <c r="G147" t="n">
+        <v>99781500</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F148" t="n">
+        <v>54</v>
+      </c>
+      <c r="G148" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F149" t="n">
+        <v>659</v>
+      </c>
+      <c r="G149" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F150" t="n">
+        <v>666</v>
+      </c>
+      <c r="G150" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F151" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G151" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F152" t="n">
+        <v>579</v>
+      </c>
+      <c r="G152" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F153" t="n">
+        <v>709</v>
+      </c>
+      <c r="G153" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E146" t="n">
+      <c r="E154" t="n">
         <v>23350</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F154" t="n">
         <v>856</v>
       </c>
-      <c r="G146" t="n">
+      <c r="G154" t="n">
         <v>19987600</v>
       </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,96 +492,96 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>41050</v>
+        <v>23850</v>
       </c>
       <c r="F2" t="n">
-        <v>490.4266</v>
+        <v>433.5542</v>
       </c>
       <c r="G2" t="n">
-        <v>20132010.4</v>
+        <v>10340268.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230000</v>
+        <v>45450</v>
       </c>
       <c r="F3" t="n">
-        <v>135.183</v>
+        <v>227.5087</v>
       </c>
       <c r="G3" t="n">
-        <v>31092084.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-16.92</v>
-      </c>
+        <v>10340268.5</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2595</v>
+        <v>15230</v>
       </c>
       <c r="F4" t="n">
-        <v>42895.584</v>
+        <v>1186.9772</v>
       </c>
       <c r="G4" t="n">
-        <v>111314040.6</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>18077663</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-5.87</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,20 +590,20 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15870</v>
+        <v>2655</v>
       </c>
       <c r="F5" t="n">
-        <v>634.2788</v>
+        <v>76798.0178</v>
       </c>
       <c r="G5" t="n">
-        <v>10066005.2</v>
+        <v>203898737.2</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,56 +618,56 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59000</v>
+        <v>60200</v>
       </c>
       <c r="F6" t="n">
-        <v>170.6103</v>
+        <v>171.7653</v>
       </c>
       <c r="G6" t="n">
-        <v>10066005.2</v>
+        <v>10340268.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9960</v>
+        <v>25550</v>
       </c>
       <c r="F7" t="n">
-        <v>1010.6431</v>
+        <v>404.7072</v>
       </c>
       <c r="G7" t="n">
-        <v>10066005.2</v>
+        <v>10340268.5</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -682,17 +682,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59100</v>
+        <v>59900</v>
       </c>
       <c r="F8" t="n">
-        <v>681.2863</v>
+        <v>172.6255</v>
       </c>
       <c r="G8" t="n">
-        <v>40264020.8</v>
+        <v>10340268.5</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -704,76 +704,78 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3385</v>
+        <v>41050</v>
       </c>
       <c r="F9" t="n">
-        <v>2973.7091</v>
+        <v>490.4266</v>
       </c>
       <c r="G9" t="n">
-        <v>10066005.2</v>
+        <v>20132010.4</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>26200</v>
+        <v>230000</v>
       </c>
       <c r="F10" t="n">
-        <v>382.0025</v>
+        <v>135.183</v>
       </c>
       <c r="G10" t="n">
-        <v>10008466.3</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>31092084.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-16.92</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,62 +784,62 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>94700</v>
+        <v>2595</v>
       </c>
       <c r="F11" t="n">
-        <v>105.686</v>
+        <v>42895.584</v>
       </c>
       <c r="G11" t="n">
-        <v>10008466.3</v>
+        <v>111314040.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>42500</v>
+        <v>15870</v>
       </c>
       <c r="F12" t="n">
-        <v>470.9867</v>
+        <v>634.2788</v>
       </c>
       <c r="G12" t="n">
-        <v>20016932.7</v>
+        <v>10066005.2</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,62 +848,62 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>26600</v>
+        <v>59000</v>
       </c>
       <c r="F13" t="n">
-        <v>361.0017</v>
+        <v>170.6103</v>
       </c>
       <c r="G13" t="n">
-        <v>9602645.699999999</v>
+        <v>10066005.2</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10740</v>
+        <v>9960</v>
       </c>
       <c r="F14" t="n">
-        <v>894.1011</v>
+        <v>1010.6431</v>
       </c>
       <c r="G14" t="n">
-        <v>9602645.699999999</v>
+        <v>10066005.2</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -910,62 +912,62 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16180</v>
+        <v>59100</v>
       </c>
       <c r="F15" t="n">
-        <v>1186.9772</v>
+        <v>681.2863</v>
       </c>
       <c r="G15" t="n">
-        <v>19205291.4</v>
+        <v>40264020.8</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>88400</v>
+        <v>3385</v>
       </c>
       <c r="F16" t="n">
-        <v>217.2544</v>
+        <v>2973.7091</v>
       </c>
       <c r="G16" t="n">
-        <v>19205291.4</v>
+        <v>10066005.2</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,79 +976,77 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99100</v>
+        <v>26200</v>
       </c>
       <c r="F17" t="n">
-        <v>290.6956</v>
+        <v>382.0025</v>
       </c>
       <c r="G17" t="n">
-        <v>28807937.1</v>
+        <v>10008466.3</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37350</v>
+        <v>94700</v>
       </c>
       <c r="F18" t="n">
-        <v>491.1229</v>
+        <v>105.686</v>
       </c>
       <c r="G18" t="n">
-        <v>18343440.7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-9.23</v>
-      </c>
+        <v>10008466.3</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2520</v>
+        <v>42500</v>
       </c>
       <c r="F19" t="n">
-        <v>33368.1327</v>
+        <v>470.9867</v>
       </c>
       <c r="G19" t="n">
-        <v>84087694.5</v>
+        <v>20016932.7</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,31 +1058,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>16500</v>
+        <v>26600</v>
       </c>
       <c r="F20" t="n">
-        <v>856.421</v>
+        <v>361.0017</v>
       </c>
       <c r="G20" t="n">
-        <v>14130946.6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-22.8</v>
-      </c>
+        <v>9602645.699999999</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1092,27 +1090,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>27650</v>
+        <v>10740</v>
       </c>
       <c r="F21" t="n">
-        <v>1041.8784</v>
+        <v>894.1011</v>
       </c>
       <c r="G21" t="n">
-        <v>28807937.1</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1124,76 +1122,76 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9350</v>
+        <v>16180</v>
       </c>
       <c r="F22" t="n">
-        <v>1027.0209</v>
+        <v>1186.9772</v>
       </c>
       <c r="G22" t="n">
-        <v>9602645.699999999</v>
+        <v>19205291.4</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>28650</v>
+        <v>88400</v>
       </c>
       <c r="F23" t="n">
-        <v>345.7839</v>
+        <v>217.2544</v>
       </c>
       <c r="G23" t="n">
-        <v>9906708.4</v>
+        <v>19205291.4</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,62 +1200,64 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11600</v>
+        <v>99100</v>
       </c>
       <c r="F24" t="n">
-        <v>854.0266</v>
+        <v>290.6956</v>
       </c>
       <c r="G24" t="n">
-        <v>9906708.4</v>
+        <v>28807937.1</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>131000</v>
+        <v>37350</v>
       </c>
       <c r="F25" t="n">
-        <v>75.6237</v>
+        <v>491.1229</v>
       </c>
       <c r="G25" t="n">
-        <v>9906708.4</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>18343440.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-9.23</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,62 +1266,64 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>67100</v>
+        <v>2520</v>
       </c>
       <c r="F26" t="n">
-        <v>147.641</v>
+        <v>33368.1327</v>
       </c>
       <c r="G26" t="n">
-        <v>9906708.4</v>
+        <v>84087694.5</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4830</v>
+        <v>16500</v>
       </c>
       <c r="F27" t="n">
-        <v>2051.0783</v>
+        <v>856.421</v>
       </c>
       <c r="G27" t="n">
-        <v>9906708.4</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>14130946.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-22.8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,120 +1332,116 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9430</v>
+        <v>27650</v>
       </c>
       <c r="F28" t="n">
-        <v>2101.1046</v>
+        <v>1041.8784</v>
       </c>
       <c r="G28" t="n">
-        <v>19813416.7</v>
+        <v>28807937.1</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>79100</v>
+        <v>9350</v>
       </c>
       <c r="F29" t="n">
-        <v>205.0482</v>
+        <v>1027.0209</v>
       </c>
       <c r="G29" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>9602645.699999999</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>25250</v>
+        <v>28650</v>
       </c>
       <c r="F30" t="n">
-        <v>768.6917999999999</v>
+        <v>345.7839</v>
       </c>
       <c r="G30" t="n">
-        <v>19409469.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12510</v>
+        <v>11600</v>
       </c>
       <c r="F31" t="n">
-        <v>1443.4887</v>
+        <v>854.0266</v>
       </c>
       <c r="G31" t="n">
-        <v>18058043.3</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-11.28</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1458,113 +1456,113 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>126500</v>
+        <v>131000</v>
       </c>
       <c r="F32" t="n">
-        <v>383.5863</v>
+        <v>75.6237</v>
       </c>
       <c r="G32" t="n">
-        <v>48523672.7</v>
+        <v>9906708.4</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2485</v>
+        <v>67100</v>
       </c>
       <c r="F33" t="n">
-        <v>42403.6617</v>
+        <v>147.641</v>
       </c>
       <c r="G33" t="n">
-        <v>105373099.3</v>
+        <v>9906708.4</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>45500</v>
+        <v>4830</v>
       </c>
       <c r="F34" t="n">
-        <v>213.2909</v>
+        <v>2051.0783</v>
       </c>
       <c r="G34" t="n">
-        <v>9704734.5</v>
+        <v>9906708.4</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>17880</v>
+        <v>9430</v>
       </c>
       <c r="F35" t="n">
-        <v>1085.5408</v>
+        <v>2101.1046</v>
       </c>
       <c r="G35" t="n">
-        <v>19409469.1</v>
+        <v>19813416.7</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,12 +1574,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,16 +1588,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4460</v>
+        <v>79100</v>
       </c>
       <c r="F36" t="n">
-        <v>3137.3165</v>
+        <v>205.0482</v>
       </c>
       <c r="G36" t="n">
-        <v>13992431.8</v>
+        <v>16219315.2</v>
       </c>
       <c r="H36" t="n">
-        <v>-17.83</v>
+        <v>-15.22</v>
       </c>
     </row>
     <row r="37">
@@ -1610,110 +1608,110 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3345</v>
+        <v>25250</v>
       </c>
       <c r="F37" t="n">
-        <v>11605.0637</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>38818938.1</v>
+        <v>19409469.1</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>12120</v>
+        <v>12510</v>
       </c>
       <c r="F38" t="n">
-        <v>820.878</v>
+        <v>1443.4887</v>
       </c>
       <c r="G38" t="n">
-        <v>9949041.199999999</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>18058043.3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-11.28</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248000</v>
+        <v>126500</v>
       </c>
       <c r="F39" t="n">
-        <v>81.12909999999999</v>
+        <v>383.5863</v>
       </c>
       <c r="G39" t="n">
-        <v>20120019.7</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-19.98</v>
-      </c>
+        <v>48523672.7</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1722,64 +1720,62 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222500</v>
+        <v>2485</v>
       </c>
       <c r="F40" t="n">
-        <v>178.8592</v>
+        <v>42403.6617</v>
       </c>
       <c r="G40" t="n">
-        <v>39796164.7</v>
+        <v>105373099.3</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>54500</v>
+        <v>45500</v>
       </c>
       <c r="F41" t="n">
-        <v>504.0447</v>
+        <v>213.2909</v>
       </c>
       <c r="G41" t="n">
-        <v>27470436.6</v>
-      </c>
-      <c r="H41" t="n">
-        <v>24.43</v>
-      </c>
+        <v>9704734.5</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1788,94 +1784,96 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>32350</v>
+        <v>17880</v>
       </c>
       <c r="F42" t="n">
-        <v>314.5779</v>
+        <v>1085.5408</v>
       </c>
       <c r="G42" t="n">
-        <v>10176595.1</v>
+        <v>19409469.1</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>13650</v>
+        <v>4460</v>
       </c>
       <c r="F43" t="n">
-        <v>745.5381</v>
+        <v>3137.3165</v>
       </c>
       <c r="G43" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>13992431.8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-17.83</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>31950</v>
+        <v>3345</v>
       </c>
       <c r="F44" t="n">
-        <v>318.5163</v>
+        <v>11605.0637</v>
       </c>
       <c r="G44" t="n">
-        <v>10176595.1</v>
+        <v>38818938.1</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1884,113 +1882,115 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>250500</v>
+        <v>12120</v>
       </c>
       <c r="F45" t="n">
-        <v>81.2503</v>
+        <v>820.878</v>
       </c>
       <c r="G45" t="n">
-        <v>20353190.3</v>
+        <v>9949041.199999999</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>14100</v>
+        <v>248000</v>
       </c>
       <c r="F46" t="n">
-        <v>1443.4887</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>31300</v>
+        <v>222500</v>
       </c>
       <c r="F47" t="n">
-        <v>1954.4702</v>
+        <v>178.8592</v>
       </c>
       <c r="G47" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H47" t="n">
-        <v>6.83</v>
-      </c>
+        <v>39796164.7</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2355</v>
+        <v>54500</v>
       </c>
       <c r="F48" t="n">
-        <v>65496.7248</v>
+        <v>504.0447</v>
       </c>
       <c r="G48" t="n">
-        <v>154244786.8</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2000,27 +2000,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>15810</v>
+        <v>32350</v>
       </c>
       <c r="F49" t="n">
-        <v>5149.4473</v>
+        <v>314.5779</v>
       </c>
       <c r="G49" t="n">
-        <v>81412761.09999999</v>
+        <v>10176595.1</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2032,24 +2032,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>56700</v>
+        <v>13650</v>
       </c>
       <c r="F50" t="n">
-        <v>179.4814</v>
+        <v>745.5381</v>
       </c>
       <c r="G50" t="n">
         <v>10176595.1</v>
@@ -2064,257 +2064,253 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4660</v>
+        <v>31950</v>
       </c>
       <c r="F51" t="n">
-        <v>4367.6374</v>
+        <v>318.5163</v>
       </c>
       <c r="G51" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>44600</v>
+        <v>250500</v>
       </c>
       <c r="F52" t="n">
-        <v>1359.3974</v>
+        <v>81.2503</v>
       </c>
       <c r="G52" t="n">
-        <v>60629123.5</v>
+        <v>20353190.3</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>20300</v>
+        <v>14100</v>
       </c>
       <c r="F53" t="n">
-        <v>1162.9429</v>
+        <v>1443.4887</v>
       </c>
       <c r="G53" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H53" t="n">
-        <v>7.9</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>13160</v>
+        <v>31300</v>
       </c>
       <c r="F54" t="n">
-        <v>767.846</v>
+        <v>1954.4702</v>
       </c>
       <c r="G54" t="n">
-        <v>10104853.9</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H54" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>49050</v>
+        <v>2355</v>
       </c>
       <c r="F55" t="n">
-        <v>357.1039</v>
+        <v>65496.7248</v>
       </c>
       <c r="G55" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>154244786.8</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>37100</v>
+        <v>15810</v>
       </c>
       <c r="F56" t="n">
-        <v>604.321</v>
+        <v>5149.4473</v>
       </c>
       <c r="G56" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>15.04</v>
-      </c>
+        <v>81412761.09999999</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>123700</v>
+        <v>56700</v>
       </c>
       <c r="F57" t="n">
-        <v>490.1303</v>
+        <v>179.4814</v>
       </c>
       <c r="G57" t="n">
-        <v>60629123.5</v>
+        <v>10176595.1</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>41150</v>
+        <v>4660</v>
       </c>
       <c r="F58" t="n">
-        <v>491.1229</v>
+        <v>4367.6374</v>
       </c>
       <c r="G58" t="n">
-        <v>20209707.8</v>
+        <v>20353190.3</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2326,27 +2322,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>31500</v>
+        <v>44600</v>
       </c>
       <c r="F59" t="n">
-        <v>320.789</v>
+        <v>1359.3974</v>
       </c>
       <c r="G59" t="n">
-        <v>10104853.9</v>
+        <v>60629123.5</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2358,29 +2354,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228500</v>
+        <v>20300</v>
       </c>
       <c r="F60" t="n">
-        <v>88.4451</v>
+        <v>1162.9429</v>
       </c>
       <c r="G60" t="n">
-        <v>20209707.8</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>23607739.9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2390,31 +2388,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>88500</v>
+        <v>13160</v>
       </c>
       <c r="F61" t="n">
-        <v>900.2261</v>
+        <v>767.846</v>
       </c>
       <c r="G61" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>10104853.9</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2424,12 +2420,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2438,16 +2434,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>130100</v>
+        <v>49050</v>
       </c>
       <c r="F62" t="n">
-        <v>314.8563</v>
+        <v>357.1039</v>
       </c>
       <c r="G62" t="n">
-        <v>40962809.6</v>
+        <v>17515946</v>
       </c>
       <c r="H62" t="n">
-        <v>8.33</v>
+        <v>-16.44</v>
       </c>
     </row>
     <row r="63">
@@ -2458,29 +2454,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2325</v>
+        <v>37100</v>
       </c>
       <c r="F63" t="n">
-        <v>21730.8686</v>
+        <v>604.321</v>
       </c>
       <c r="G63" t="n">
-        <v>50524269.6</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2490,12 +2488,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2504,13 +2502,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>64700</v>
+        <v>123700</v>
       </c>
       <c r="F64" t="n">
-        <v>468.5404</v>
+        <v>490.1303</v>
       </c>
       <c r="G64" t="n">
-        <v>30314561.7</v>
+        <v>60629123.5</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2522,12 +2520,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2536,30 +2534,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4670</v>
+        <v>41150</v>
       </c>
       <c r="F65" t="n">
-        <v>6491.3408</v>
+        <v>491.1229</v>
       </c>
       <c r="G65" t="n">
-        <v>30314561.7</v>
+        <v>20209707.8</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2568,94 +2566,96 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2120</v>
+        <v>31500</v>
       </c>
       <c r="F66" t="n">
-        <v>63879.7502</v>
+        <v>320.789</v>
       </c>
       <c r="G66" t="n">
-        <v>135425070.4</v>
+        <v>10104853.9</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2120</v>
+        <v>228500</v>
       </c>
       <c r="F67" t="n">
-        <v>3453.9051</v>
+        <v>88.4451</v>
       </c>
       <c r="G67" t="n">
-        <v>7322278.8</v>
+        <v>20209707.8</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>22900</v>
+        <v>88500</v>
       </c>
       <c r="F68" t="n">
-        <v>1397.6406</v>
+        <v>900.2261</v>
       </c>
       <c r="G68" t="n">
-        <v>32005969</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2664,22 +2664,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>73600</v>
+        <v>130100</v>
       </c>
       <c r="F69" t="n">
-        <v>299.9614</v>
+        <v>314.8563</v>
       </c>
       <c r="G69" t="n">
-        <v>22077158.2</v>
+        <v>40962809.6</v>
       </c>
       <c r="H69" t="n">
-        <v>16.09</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2694,34 +2694,34 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2215</v>
+        <v>2325</v>
       </c>
       <c r="F70" t="n">
-        <v>28224.978</v>
+        <v>21730.8686</v>
       </c>
       <c r="G70" t="n">
-        <v>62518326.2</v>
+        <v>50524269.6</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2730,256 +2730,256 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>43800</v>
+        <v>64700</v>
       </c>
       <c r="F71" t="n">
-        <v>504.0447</v>
+        <v>468.5404</v>
       </c>
       <c r="G71" t="n">
-        <v>22077158.2</v>
+        <v>30314561.7</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>23650</v>
+        <v>4670</v>
       </c>
       <c r="F72" t="n">
-        <v>451.106</v>
+        <v>6491.3408</v>
       </c>
       <c r="G72" t="n">
-        <v>10668656.3</v>
+        <v>30314561.7</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5730</v>
+        <v>2120</v>
       </c>
       <c r="F73" t="n">
-        <v>3723.7893</v>
+        <v>63879.7502</v>
       </c>
       <c r="G73" t="n">
-        <v>21337312.7</v>
+        <v>135425070.4</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6080</v>
+        <v>2120</v>
       </c>
       <c r="F74" t="n">
-        <v>3255.5051</v>
+        <v>3453.9051</v>
       </c>
       <c r="G74" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>7322278.8</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>95200</v>
+        <v>22900</v>
       </c>
       <c r="F75" t="n">
-        <v>221.6088</v>
+        <v>1397.6406</v>
       </c>
       <c r="G75" t="n">
-        <v>21097154.4</v>
+        <v>32005969</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2205</v>
+        <v>73600</v>
       </c>
       <c r="F76" t="n">
-        <v>52623.2877</v>
+        <v>299.9614</v>
       </c>
       <c r="G76" t="n">
-        <v>116034349.3</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>58700</v>
+        <v>2215</v>
       </c>
       <c r="F77" t="n">
-        <v>357.1039</v>
+        <v>28224.978</v>
       </c>
       <c r="G77" t="n">
-        <v>20961998.6</v>
+        <v>62518326.2</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>13250</v>
+        <v>43800</v>
       </c>
       <c r="F78" t="n">
-        <v>791.0188000000001</v>
+        <v>504.0447</v>
       </c>
       <c r="G78" t="n">
-        <v>10480999.3</v>
+        <v>22077158.2</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2988,216 +2988,214 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2360</v>
+        <v>23650</v>
       </c>
       <c r="F79" t="n">
-        <v>66616.5209</v>
+        <v>451.106</v>
       </c>
       <c r="G79" t="n">
-        <v>157214989.3</v>
+        <v>10668656.3</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>38300</v>
+        <v>5730</v>
       </c>
       <c r="F80" t="n">
-        <v>500.7861</v>
+        <v>3723.7893</v>
       </c>
       <c r="G80" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>21337312.7</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>21150</v>
+        <v>6080</v>
       </c>
       <c r="F81" t="n">
-        <v>495.5555</v>
+        <v>3255.5051</v>
       </c>
       <c r="G81" t="n">
-        <v>10480999.3</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>23650</v>
+        <v>95200</v>
       </c>
       <c r="F82" t="n">
-        <v>832.6201</v>
+        <v>221.6088</v>
       </c>
       <c r="G82" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H82" t="n">
-        <v>1.28</v>
-      </c>
+        <v>21097154.4</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>12310</v>
+        <v>2205</v>
       </c>
       <c r="F83" t="n">
-        <v>2480.1654</v>
+        <v>52623.2877</v>
       </c>
       <c r="G83" t="n">
-        <v>30530836.4</v>
+        <v>116034349.3</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>40650</v>
+        <v>58700</v>
       </c>
       <c r="F84" t="n">
-        <v>751.0661</v>
+        <v>357.1039</v>
       </c>
       <c r="G84" t="n">
-        <v>30530836.4</v>
+        <v>20961998.6</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>283500</v>
+        <v>13250</v>
       </c>
       <c r="F85" t="n">
-        <v>71.795</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>20353890.9</v>
+        <v>10480999.3</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3216,94 +3214,96 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2390</v>
+        <v>2360</v>
       </c>
       <c r="F86" t="n">
-        <v>42581.3618</v>
+        <v>66616.5209</v>
       </c>
       <c r="G86" t="n">
-        <v>101769454.6</v>
+        <v>157214989.3</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>20450</v>
+        <v>38300</v>
       </c>
       <c r="F87" t="n">
-        <v>995.3003</v>
+        <v>500.7861</v>
       </c>
       <c r="G87" t="n">
-        <v>20353890.9</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>30200</v>
+        <v>21150</v>
       </c>
       <c r="F88" t="n">
-        <v>359.55</v>
+        <v>495.5555</v>
       </c>
       <c r="G88" t="n">
-        <v>10858410.6</v>
+        <v>10480999.3</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3312,32 +3312,32 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>208500</v>
+        <v>23650</v>
       </c>
       <c r="F89" t="n">
-        <v>338</v>
+        <v>832.6201</v>
       </c>
       <c r="G89" t="n">
-        <v>70473000</v>
+        <v>19691465.3</v>
       </c>
       <c r="H89" t="n">
-        <v>0.97</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3346,30 +3346,30 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>17720</v>
+        <v>12310</v>
       </c>
       <c r="F90" t="n">
-        <v>94.9217</v>
+        <v>2480.1654</v>
       </c>
       <c r="G90" t="n">
-        <v>1682012.5</v>
+        <v>30530836.4</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3378,109 +3378,109 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100500</v>
+        <v>40650</v>
       </c>
       <c r="F91" t="n">
-        <v>8.9518</v>
+        <v>751.0661</v>
       </c>
       <c r="G91" t="n">
-        <v>899652.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>11410</v>
+        <v>283500</v>
       </c>
       <c r="F92" t="n">
-        <v>6321.2722</v>
+        <v>71.795</v>
       </c>
       <c r="G92" t="n">
-        <v>72125715.8</v>
+        <v>20353890.9</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>12880</v>
+        <v>2390</v>
       </c>
       <c r="F93" t="n">
-        <v>713.2027</v>
+        <v>42581.3618</v>
       </c>
       <c r="G93" t="n">
-        <v>9186050.6</v>
+        <v>101769454.6</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>21200</v>
+        <v>20450</v>
       </c>
       <c r="F94" t="n">
-        <v>120.8659</v>
+        <v>995.3003</v>
       </c>
       <c r="G94" t="n">
-        <v>2562357.9</v>
+        <v>20353890.9</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3506,13 +3506,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>27700</v>
+        <v>30200</v>
       </c>
       <c r="F95" t="n">
-        <v>161.1835</v>
+        <v>359.55</v>
       </c>
       <c r="G95" t="n">
-        <v>4464784.2</v>
+        <v>10858410.6</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3524,29 +3524,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>21500</v>
+        <v>208500</v>
       </c>
       <c r="F96" t="n">
-        <v>129.2032</v>
+        <v>338</v>
       </c>
       <c r="G96" t="n">
-        <v>2777868.4</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3556,27 +3558,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>34100</v>
+        <v>17720</v>
       </c>
       <c r="F97" t="n">
-        <v>21.679</v>
+        <v>94.9217</v>
       </c>
       <c r="G97" t="n">
-        <v>739252.6</v>
+        <v>1682012.5</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3588,27 +3590,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>40850</v>
+        <v>100500</v>
       </c>
       <c r="F98" t="n">
-        <v>123.3915</v>
+        <v>8.9518</v>
       </c>
       <c r="G98" t="n">
-        <v>5040542.1</v>
+        <v>899652.6</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3620,27 +3622,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>308000</v>
+        <v>11410</v>
       </c>
       <c r="F99" t="n">
-        <v>9.1744</v>
+        <v>6321.2722</v>
       </c>
       <c r="G99" t="n">
-        <v>2825715.8</v>
+        <v>72125715.8</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3652,27 +3654,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6330</v>
+        <v>12880</v>
       </c>
       <c r="F100" t="n">
-        <v>50.5051</v>
+        <v>713.2027</v>
       </c>
       <c r="G100" t="n">
-        <v>319697.4</v>
+        <v>9186050.6</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3684,12 +3686,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3698,13 +3700,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>31700</v>
+        <v>21200</v>
       </c>
       <c r="F101" t="n">
-        <v>158.7408</v>
+        <v>120.8659</v>
       </c>
       <c r="G101" t="n">
-        <v>5032084.2</v>
+        <v>2562357.9</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3716,12 +3718,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3730,13 +3732,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>68700</v>
+        <v>27700</v>
       </c>
       <c r="F102" t="n">
-        <v>16.0386</v>
+        <v>161.1835</v>
       </c>
       <c r="G102" t="n">
-        <v>1101852.6</v>
+        <v>4464784.2</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3748,12 +3750,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3762,13 +3764,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>256000</v>
+        <v>21500</v>
       </c>
       <c r="F103" t="n">
-        <v>45.4873</v>
+        <v>129.2032</v>
       </c>
       <c r="G103" t="n">
-        <v>11644736.8</v>
+        <v>2777868.4</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3780,27 +3782,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>91100</v>
+        <v>34100</v>
       </c>
       <c r="F104" t="n">
-        <v>19.6174</v>
+        <v>21.679</v>
       </c>
       <c r="G104" t="n">
-        <v>1787142.1</v>
+        <v>739252.6</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3812,27 +3814,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>130900</v>
+        <v>40850</v>
       </c>
       <c r="F105" t="n">
-        <v>89.1437</v>
+        <v>123.3915</v>
       </c>
       <c r="G105" t="n">
-        <v>11668905.3</v>
+        <v>5040542.1</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3844,27 +3846,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2400</v>
+        <v>308000</v>
       </c>
       <c r="F106" t="n">
-        <v>32820.1843</v>
+        <v>9.1744</v>
       </c>
       <c r="G106" t="n">
-        <v>78768442.40000001</v>
+        <v>2825715.8</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3876,12 +3878,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3890,13 +3892,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>41150</v>
+        <v>6330</v>
       </c>
       <c r="F107" t="n">
-        <v>38.7861</v>
+        <v>50.5051</v>
       </c>
       <c r="G107" t="n">
-        <v>1596047.4</v>
+        <v>319697.4</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3908,12 +3910,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3922,13 +3924,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>49450</v>
+        <v>31700</v>
       </c>
       <c r="F108" t="n">
-        <v>83.90349999999999</v>
+        <v>158.7408</v>
       </c>
       <c r="G108" t="n">
-        <v>4149029</v>
+        <v>5032084.2</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3940,12 +3942,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3954,13 +3956,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>24750</v>
+        <v>68700</v>
       </c>
       <c r="F109" t="n">
-        <v>23.3799</v>
+        <v>16.0386</v>
       </c>
       <c r="G109" t="n">
-        <v>578652.6</v>
+        <v>1101852.6</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3972,240 +3974,236 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5450</v>
+        <v>256000</v>
       </c>
       <c r="F110" t="n">
-        <v>220.6267</v>
+        <v>45.4873</v>
       </c>
       <c r="G110" t="n">
-        <v>1202415.4</v>
+        <v>11644736.8</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>327000</v>
+        <v>91100</v>
       </c>
       <c r="F111" t="n">
-        <v>54</v>
+        <v>19.6174</v>
       </c>
       <c r="G111" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>1787142.1</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5130</v>
+        <v>130900</v>
       </c>
       <c r="F112" t="n">
-        <v>4001.7913</v>
+        <v>89.1437</v>
       </c>
       <c r="G112" t="n">
-        <v>20529189.5</v>
+        <v>11668905.3</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>27100</v>
+        <v>2400</v>
       </c>
       <c r="F113" t="n">
-        <v>376</v>
+        <v>32820.1843</v>
       </c>
       <c r="G113" t="n">
-        <v>10189600</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>67600</v>
+        <v>41150</v>
       </c>
       <c r="F114" t="n">
-        <v>998</v>
+        <v>38.7861</v>
       </c>
       <c r="G114" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>1596047.4</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>11900</v>
+        <v>49450</v>
       </c>
       <c r="F115" t="n">
-        <v>856</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G115" t="n">
-        <v>10186400</v>
+        <v>4149029</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>29300</v>
+        <v>24750</v>
       </c>
       <c r="F116" t="n">
-        <v>2434</v>
+        <v>23.3799</v>
       </c>
       <c r="G116" t="n">
-        <v>71316200</v>
+        <v>578652.6</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4214,62 +4212,64 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>119300</v>
+        <v>5450</v>
       </c>
       <c r="F117" t="n">
-        <v>171</v>
+        <v>220.6267</v>
       </c>
       <c r="G117" t="n">
-        <v>20400300</v>
+        <v>1202415.4</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2445</v>
+        <v>327000</v>
       </c>
       <c r="F118" t="n">
-        <v>82456</v>
+        <v>54</v>
       </c>
       <c r="G118" t="n">
-        <v>201604920</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4278,62 +4278,62 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>18910</v>
+        <v>5130</v>
       </c>
       <c r="F119" t="n">
-        <v>1068.0212</v>
+        <v>4001.7913</v>
       </c>
       <c r="G119" t="n">
-        <v>20196280</v>
+        <v>20529189.5</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>32250</v>
+        <v>27100</v>
       </c>
       <c r="F120" t="n">
-        <v>626</v>
+        <v>376</v>
       </c>
       <c r="G120" t="n">
-        <v>20188500</v>
+        <v>10189600</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4342,130 +4342,128 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>82500</v>
+        <v>67600</v>
       </c>
       <c r="F121" t="n">
-        <v>204</v>
+        <v>998</v>
       </c>
       <c r="G121" t="n">
-        <v>16830000</v>
+        <v>67464800</v>
       </c>
       <c r="H121" t="n">
-        <v>-8.640000000000001</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>56800</v>
+        <v>11900</v>
       </c>
       <c r="F122" t="n">
-        <v>258</v>
+        <v>856</v>
       </c>
       <c r="G122" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>10186400</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>83700</v>
+        <v>29300</v>
       </c>
       <c r="F123" t="n">
-        <v>120</v>
+        <v>2434</v>
       </c>
       <c r="G123" t="n">
-        <v>10044000</v>
+        <v>71316200</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>43650</v>
+        <v>119300</v>
       </c>
       <c r="F124" t="n">
-        <v>462</v>
+        <v>171</v>
       </c>
       <c r="G124" t="n">
-        <v>20166300</v>
+        <v>20400300</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4474,126 +4472,128 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>59700</v>
+        <v>2445</v>
       </c>
       <c r="F125" t="n">
-        <v>169</v>
+        <v>82456</v>
       </c>
       <c r="G125" t="n">
-        <v>10089300</v>
+        <v>201604920</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>10930</v>
+        <v>18910</v>
       </c>
       <c r="F126" t="n">
-        <v>1833</v>
+        <v>1068.0212</v>
       </c>
       <c r="G126" t="n">
-        <v>20034690</v>
+        <v>20196280</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>19850</v>
+        <v>32250</v>
       </c>
       <c r="F127" t="n">
-        <v>505</v>
+        <v>626</v>
       </c>
       <c r="G127" t="n">
-        <v>10024250</v>
+        <v>20188500</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>26350</v>
+        <v>82500</v>
       </c>
       <c r="F128" t="n">
-        <v>380</v>
+        <v>204</v>
       </c>
       <c r="G128" t="n">
-        <v>10013000</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4602,22 +4602,22 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>23500</v>
+        <v>56800</v>
       </c>
       <c r="F129" t="n">
-        <v>833</v>
+        <v>258</v>
       </c>
       <c r="G129" t="n">
-        <v>19575500</v>
+        <v>14654400</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.08</v>
+        <v>-17.68</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4636,30 +4636,30 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>85200</v>
+        <v>83700</v>
       </c>
       <c r="F130" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G130" t="n">
-        <v>10053600</v>
+        <v>10044000</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4668,30 +4668,30 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>63400</v>
+        <v>43650</v>
       </c>
       <c r="F131" t="n">
-        <v>316</v>
+        <v>462</v>
       </c>
       <c r="G131" t="n">
-        <v>20034400</v>
+        <v>20166300</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>110300</v>
+        <v>59700</v>
       </c>
       <c r="F132" t="n">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="G132" t="n">
-        <v>10037300</v>
+        <v>10089300</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -4718,172 +4718,174 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>66100</v>
+        <v>10930</v>
       </c>
       <c r="F133" t="n">
-        <v>152</v>
+        <v>1833</v>
       </c>
       <c r="G133" t="n">
-        <v>10047200</v>
+        <v>20034690</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>25800</v>
+        <v>19850</v>
       </c>
       <c r="F134" t="n">
-        <v>2713</v>
+        <v>505</v>
       </c>
       <c r="G134" t="n">
-        <v>69995400</v>
+        <v>10024250</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>206500</v>
+        <v>26350</v>
       </c>
       <c r="F135" t="n">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="G135" t="n">
-        <v>69797000</v>
+        <v>10013000</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>70100</v>
+        <v>23500</v>
       </c>
       <c r="F136" t="n">
-        <v>998</v>
+        <v>833</v>
       </c>
       <c r="G136" t="n">
-        <v>69959800</v>
-      </c>
-      <c r="H136" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>93300</v>
+        <v>85200</v>
       </c>
       <c r="F137" t="n">
-        <v>214</v>
+        <v>118</v>
       </c>
       <c r="G137" t="n">
-        <v>19966200</v>
+        <v>10053600</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4892,77 +4894,77 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>11300</v>
+        <v>63400</v>
       </c>
       <c r="F138" t="n">
-        <v>4424</v>
+        <v>316</v>
       </c>
       <c r="G138" t="n">
-        <v>49991200</v>
+        <v>20034400</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>19740</v>
+        <v>110300</v>
       </c>
       <c r="F139" t="n">
-        <v>2532</v>
+        <v>91</v>
       </c>
       <c r="G139" t="n">
-        <v>49981680</v>
+        <v>10037300</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>25150</v>
+        <v>66100</v>
       </c>
       <c r="F140" t="n">
-        <v>2385</v>
+        <v>152</v>
       </c>
       <c r="G140" t="n">
-        <v>59982750</v>
+        <v>10047200</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -4974,12 +4976,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4988,13 +4990,13 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>22050</v>
+        <v>25800</v>
       </c>
       <c r="F141" t="n">
-        <v>2267</v>
+        <v>2713</v>
       </c>
       <c r="G141" t="n">
-        <v>49987350</v>
+        <v>69995400</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -5006,12 +5008,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5020,13 +5022,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>43150</v>
+        <v>206500</v>
       </c>
       <c r="F142" t="n">
-        <v>1390</v>
+        <v>338</v>
       </c>
       <c r="G142" t="n">
-        <v>59978500</v>
+        <v>69797000</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -5038,12 +5040,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5052,13 +5054,13 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>310000</v>
+        <v>70100</v>
       </c>
       <c r="F143" t="n">
-        <v>225</v>
+        <v>998</v>
       </c>
       <c r="G143" t="n">
-        <v>69750000</v>
+        <v>69959800</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -5070,12 +5072,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5084,13 +5086,13 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6240</v>
+        <v>93300</v>
       </c>
       <c r="F144" t="n">
-        <v>3205</v>
+        <v>214</v>
       </c>
       <c r="G144" t="n">
-        <v>19999200</v>
+        <v>19966200</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -5102,12 +5104,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5116,13 +5118,13 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>24000</v>
+        <v>11300</v>
       </c>
       <c r="F145" t="n">
-        <v>833</v>
+        <v>4424</v>
       </c>
       <c r="G145" t="n">
-        <v>19992000</v>
+        <v>49991200</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -5134,12 +5136,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5148,13 +5150,13 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>90300</v>
+        <v>19740</v>
       </c>
       <c r="F146" t="n">
-        <v>442</v>
+        <v>2532</v>
       </c>
       <c r="G146" t="n">
-        <v>39912600</v>
+        <v>49981680</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -5166,12 +5168,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5180,13 +5182,13 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>279500</v>
+        <v>25150</v>
       </c>
       <c r="F147" t="n">
-        <v>357</v>
+        <v>2385</v>
       </c>
       <c r="G147" t="n">
-        <v>99781500</v>
+        <v>59982750</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -5198,12 +5200,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5212,13 +5214,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>366000</v>
+        <v>22050</v>
       </c>
       <c r="F148" t="n">
-        <v>54</v>
+        <v>2267</v>
       </c>
       <c r="G148" t="n">
-        <v>19764000</v>
+        <v>49987350</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -5230,12 +5232,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5244,13 +5246,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>91000</v>
+        <v>43150</v>
       </c>
       <c r="F149" t="n">
-        <v>659</v>
+        <v>1390</v>
       </c>
       <c r="G149" t="n">
-        <v>59969000</v>
+        <v>59978500</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5262,12 +5264,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5276,13 +5278,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>120100</v>
+        <v>310000</v>
       </c>
       <c r="F150" t="n">
-        <v>666</v>
+        <v>225</v>
       </c>
       <c r="G150" t="n">
-        <v>79986600</v>
+        <v>69750000</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5294,12 +5296,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5308,13 +5310,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2405</v>
+        <v>6240</v>
       </c>
       <c r="F151" t="n">
-        <v>415800</v>
+        <v>3205</v>
       </c>
       <c r="G151" t="n">
-        <v>999999000</v>
+        <v>19999200</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5326,12 +5328,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5340,13 +5342,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>69000</v>
+        <v>24000</v>
       </c>
       <c r="F152" t="n">
-        <v>579</v>
+        <v>833</v>
       </c>
       <c r="G152" t="n">
-        <v>39951000</v>
+        <v>19992000</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5358,12 +5360,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5372,13 +5374,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>42300</v>
+        <v>90300</v>
       </c>
       <c r="F153" t="n">
-        <v>709</v>
+        <v>442</v>
       </c>
       <c r="G153" t="n">
-        <v>29990700</v>
+        <v>39912600</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5390,29 +5392,253 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>279500</v>
+      </c>
+      <c r="F154" t="n">
+        <v>357</v>
+      </c>
+      <c r="G154" t="n">
+        <v>99781500</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>366000</v>
+      </c>
+      <c r="F155" t="n">
+        <v>54</v>
+      </c>
+      <c r="G155" t="n">
+        <v>19764000</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>237690</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F156" t="n">
+        <v>659</v>
+      </c>
+      <c r="G156" t="n">
+        <v>59969000</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F157" t="n">
+        <v>666</v>
+      </c>
+      <c r="G157" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F158" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G158" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F159" t="n">
+        <v>579</v>
+      </c>
+      <c r="G159" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F160" t="n">
+        <v>709</v>
+      </c>
+      <c r="G160" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E154" t="n">
+      <c r="E161" t="n">
         <v>23350</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F161" t="n">
         <v>856</v>
       </c>
-      <c r="G154" t="n">
+      <c r="G161" t="n">
         <v>19987600</v>
       </c>
-      <c r="H154" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60200</v>
+        <v>30249.84</v>
       </c>
       <c r="F6" t="n">
-        <v>171.7653</v>
+        <v>341.8289</v>
       </c>
       <c r="G6" t="n">
         <v>10340268.5</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>59000</v>
+        <v>29646.86</v>
       </c>
       <c r="F13" t="n">
-        <v>170.6103</v>
+        <v>339.5302</v>
       </c>
       <c r="G13" t="n">
         <v>10066005.2</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67100</v>
+        <v>33717.02</v>
       </c>
       <c r="F33" t="n">
-        <v>147.641</v>
+        <v>293.8192</v>
       </c>
       <c r="G33" t="n">
         <v>9906708.4</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>56700</v>
+        <v>28491.13</v>
       </c>
       <c r="F57" t="n">
-        <v>179.4814</v>
+        <v>357.1847</v>
       </c>
       <c r="G57" t="n">
         <v>10176595.1</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>64700</v>
+        <v>32511.04</v>
       </c>
       <c r="F71" t="n">
-        <v>468.5404</v>
+        <v>932.439</v>
       </c>
       <c r="G71" t="n">
         <v>30314561.7</v>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,100 +473,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23850</v>
+        <v>33300</v>
       </c>
       <c r="F2" t="n">
-        <v>433.5542</v>
+        <v>296.1438</v>
       </c>
       <c r="G2" t="n">
-        <v>10340268.5</v>
+        <v>9861590.1</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>45450</v>
+        <v>9540</v>
       </c>
       <c r="F3" t="n">
-        <v>227.5087</v>
+        <v>1033.7097</v>
       </c>
       <c r="G3" t="n">
-        <v>10340268.5</v>
+        <v>9861590.1</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15230</v>
+        <v>58500</v>
       </c>
       <c r="F4" t="n">
-        <v>1186.9772</v>
+        <v>168.5742</v>
       </c>
       <c r="G4" t="n">
-        <v>18077663</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-5.87</v>
-      </c>
+        <v>9861590.1</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,13 +588,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2655</v>
+        <v>23850</v>
       </c>
       <c r="F5" t="n">
-        <v>76798.0178</v>
+        <v>433.5542</v>
       </c>
       <c r="G5" t="n">
-        <v>203898737.2</v>
+        <v>10340268.5</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -608,24 +606,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30249.84</v>
+        <v>45450</v>
       </c>
       <c r="F6" t="n">
-        <v>341.8289</v>
+        <v>227.5087</v>
       </c>
       <c r="G6" t="n">
         <v>10340268.5</v>
@@ -640,29 +638,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25550</v>
+        <v>15230</v>
       </c>
       <c r="F7" t="n">
-        <v>404.7072</v>
+        <v>1186.9772</v>
       </c>
       <c r="G7" t="n">
-        <v>10340268.5</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>18077663</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-5.87</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -672,110 +672,108 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59900</v>
+        <v>2655</v>
       </c>
       <c r="F8" t="n">
-        <v>172.6255</v>
+        <v>76798.0178</v>
       </c>
       <c r="G8" t="n">
-        <v>10340268.5</v>
+        <v>203898737.2</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>41050</v>
+        <v>30249.84</v>
       </c>
       <c r="F9" t="n">
-        <v>490.4266</v>
+        <v>341.8289</v>
       </c>
       <c r="G9" t="n">
-        <v>20132010.4</v>
+        <v>10340268.5</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230000</v>
+        <v>25550</v>
       </c>
       <c r="F10" t="n">
-        <v>135.183</v>
+        <v>404.7072</v>
       </c>
       <c r="G10" t="n">
-        <v>31092084.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-16.92</v>
-      </c>
+        <v>10340268.5</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,13 +782,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2595</v>
+        <v>59900</v>
       </c>
       <c r="F11" t="n">
-        <v>42895.584</v>
+        <v>172.6255</v>
       </c>
       <c r="G11" t="n">
-        <v>111314040.6</v>
+        <v>10340268.5</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,12 +800,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -816,13 +814,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15870</v>
+        <v>41050</v>
       </c>
       <c r="F12" t="n">
-        <v>634.2788</v>
+        <v>490.4266</v>
       </c>
       <c r="G12" t="n">
-        <v>10066005.2</v>
+        <v>20132010.4</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,29 +832,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>29646.86</v>
+        <v>230000</v>
       </c>
       <c r="F13" t="n">
-        <v>339.5302</v>
+        <v>135.183</v>
       </c>
       <c r="G13" t="n">
-        <v>10066005.2</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>31092084.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-16.92</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9960</v>
+        <v>2595</v>
       </c>
       <c r="F14" t="n">
-        <v>1010.6431</v>
+        <v>42895.584</v>
       </c>
       <c r="G14" t="n">
-        <v>10066005.2</v>
+        <v>111314040.6</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>59100</v>
+        <v>15870</v>
       </c>
       <c r="F15" t="n">
-        <v>681.2863</v>
+        <v>634.2788</v>
       </c>
       <c r="G15" t="n">
-        <v>40264020.8</v>
+        <v>10066005.2</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3385</v>
+        <v>29646.86</v>
       </c>
       <c r="F16" t="n">
-        <v>2973.7091</v>
+        <v>339.5302</v>
       </c>
       <c r="G16" t="n">
         <v>10066005.2</v>
@@ -957,113 +957,113 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>26200</v>
+        <v>9960</v>
       </c>
       <c r="F17" t="n">
-        <v>382.0025</v>
+        <v>1010.6431</v>
       </c>
       <c r="G17" t="n">
-        <v>10008466.3</v>
+        <v>10066005.2</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>94700</v>
+        <v>59100</v>
       </c>
       <c r="F18" t="n">
-        <v>105.686</v>
+        <v>681.2863</v>
       </c>
       <c r="G18" t="n">
-        <v>10008466.3</v>
+        <v>40264020.8</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>42500</v>
+        <v>3385</v>
       </c>
       <c r="F19" t="n">
-        <v>470.9867</v>
+        <v>2973.7091</v>
       </c>
       <c r="G19" t="n">
-        <v>20016932.7</v>
+        <v>10066005.2</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,62 +1072,62 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26600</v>
+        <v>26200</v>
       </c>
       <c r="F20" t="n">
-        <v>361.0017</v>
+        <v>382.0025</v>
       </c>
       <c r="G20" t="n">
-        <v>9602645.699999999</v>
+        <v>10008466.3</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>10740</v>
+        <v>94700</v>
       </c>
       <c r="F21" t="n">
-        <v>894.1011</v>
+        <v>105.686</v>
       </c>
       <c r="G21" t="n">
-        <v>9602645.699999999</v>
+        <v>10008466.3</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1136,13 +1136,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>16180</v>
+        <v>42500</v>
       </c>
       <c r="F22" t="n">
-        <v>1186.9772</v>
+        <v>470.9867</v>
       </c>
       <c r="G22" t="n">
-        <v>19205291.4</v>
+        <v>20016932.7</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,27 +1154,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>88400</v>
+        <v>26600</v>
       </c>
       <c r="F23" t="n">
-        <v>217.2544</v>
+        <v>361.0017</v>
       </c>
       <c r="G23" t="n">
-        <v>19205291.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>99100</v>
+        <v>10740</v>
       </c>
       <c r="F24" t="n">
-        <v>290.6956</v>
+        <v>894.1011</v>
       </c>
       <c r="G24" t="n">
-        <v>28807937.1</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1218,31 +1218,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37350</v>
+        <v>16180</v>
       </c>
       <c r="F25" t="n">
-        <v>491.1229</v>
+        <v>1186.9772</v>
       </c>
       <c r="G25" t="n">
-        <v>18343440.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-9.23</v>
-      </c>
+        <v>19205291.4</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1252,27 +1250,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2520</v>
+        <v>88400</v>
       </c>
       <c r="F26" t="n">
-        <v>33368.1327</v>
+        <v>217.2544</v>
       </c>
       <c r="G26" t="n">
-        <v>84087694.5</v>
+        <v>19205291.4</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,31 +1282,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>16500</v>
+        <v>99100</v>
       </c>
       <c r="F27" t="n">
-        <v>856.421</v>
+        <v>290.6956</v>
       </c>
       <c r="G27" t="n">
-        <v>14130946.6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-22.8</v>
-      </c>
+        <v>28807937.1</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1318,29 +1314,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>27650</v>
+        <v>37350</v>
       </c>
       <c r="F28" t="n">
-        <v>1041.8784</v>
+        <v>491.1229</v>
       </c>
       <c r="G28" t="n">
-        <v>28807937.1</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>18343440.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-9.23</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1350,12 +1348,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1364,94 +1362,96 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>9350</v>
+        <v>2520</v>
       </c>
       <c r="F29" t="n">
-        <v>1027.0209</v>
+        <v>33368.1327</v>
       </c>
       <c r="G29" t="n">
-        <v>9602645.699999999</v>
+        <v>84087694.5</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>28650</v>
+        <v>16500</v>
       </c>
       <c r="F30" t="n">
-        <v>345.7839</v>
+        <v>856.421</v>
       </c>
       <c r="G30" t="n">
-        <v>9906708.4</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>14130946.6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-22.8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>11600</v>
+        <v>27650</v>
       </c>
       <c r="F31" t="n">
-        <v>854.0266</v>
+        <v>1041.8784</v>
       </c>
       <c r="G31" t="n">
-        <v>9906708.4</v>
+        <v>28807937.1</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>131000</v>
+        <v>9350</v>
       </c>
       <c r="F32" t="n">
-        <v>75.6237</v>
+        <v>1027.0209</v>
       </c>
       <c r="G32" t="n">
-        <v>9906708.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,24 +1478,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>33717.02</v>
+        <v>28650</v>
       </c>
       <c r="F33" t="n">
-        <v>293.8192</v>
+        <v>345.7839</v>
       </c>
       <c r="G33" t="n">
         <v>9906708.4</v>
@@ -1510,24 +1510,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4830</v>
+        <v>11600</v>
       </c>
       <c r="F34" t="n">
-        <v>2051.0783</v>
+        <v>854.0266</v>
       </c>
       <c r="G34" t="n">
         <v>9906708.4</v>
@@ -1542,78 +1542,76 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>9430</v>
+        <v>131000</v>
       </c>
       <c r="F35" t="n">
-        <v>2101.1046</v>
+        <v>75.6237</v>
       </c>
       <c r="G35" t="n">
-        <v>19813416.7</v>
+        <v>9906708.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>79100</v>
+        <v>33717.02</v>
       </c>
       <c r="F36" t="n">
-        <v>205.0482</v>
+        <v>293.8192</v>
       </c>
       <c r="G36" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1622,49 +1620,47 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25250</v>
+        <v>4830</v>
       </c>
       <c r="F37" t="n">
-        <v>768.6917999999999</v>
+        <v>2051.0783</v>
       </c>
       <c r="G37" t="n">
-        <v>19409469.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>12510</v>
+        <v>9430</v>
       </c>
       <c r="F38" t="n">
-        <v>1443.4887</v>
+        <v>2101.1046</v>
       </c>
       <c r="G38" t="n">
-        <v>18058043.3</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-11.28</v>
-      </c>
+        <v>19813416.7</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1674,29 +1670,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>126500</v>
+        <v>79100</v>
       </c>
       <c r="F39" t="n">
-        <v>383.5863</v>
+        <v>205.0482</v>
       </c>
       <c r="G39" t="n">
-        <v>48523672.7</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>16219315.2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-15.22</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1706,27 +1704,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2485</v>
+        <v>25250</v>
       </c>
       <c r="F40" t="n">
-        <v>42403.6617</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>105373099.3</v>
+        <v>19409469.1</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1738,29 +1736,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>45500</v>
+        <v>12510</v>
       </c>
       <c r="F41" t="n">
-        <v>213.2909</v>
+        <v>1443.4887</v>
       </c>
       <c r="G41" t="n">
-        <v>9704734.5</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>18058043.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-11.28</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1770,27 +1770,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>17880</v>
+        <v>126500</v>
       </c>
       <c r="F42" t="n">
-        <v>1085.5408</v>
+        <v>383.5863</v>
       </c>
       <c r="G42" t="n">
-        <v>19409469.1</v>
+        <v>48523672.7</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1802,31 +1802,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4460</v>
+        <v>2485</v>
       </c>
       <c r="F43" t="n">
-        <v>3137.3165</v>
+        <v>42403.6617</v>
       </c>
       <c r="G43" t="n">
-        <v>13992431.8</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-17.83</v>
-      </c>
+        <v>105373099.3</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1836,44 +1834,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3345</v>
+        <v>45500</v>
       </c>
       <c r="F44" t="n">
-        <v>11605.0637</v>
+        <v>213.2909</v>
       </c>
       <c r="G44" t="n">
-        <v>38818938.1</v>
+        <v>9704734.5</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1882,30 +1880,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12120</v>
+        <v>17880</v>
       </c>
       <c r="F45" t="n">
-        <v>820.878</v>
+        <v>1085.5408</v>
       </c>
       <c r="G45" t="n">
-        <v>9949041.199999999</v>
+        <v>19409469.1</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1914,47 +1912,47 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>248000</v>
+        <v>4460</v>
       </c>
       <c r="F46" t="n">
-        <v>81.12909999999999</v>
+        <v>3137.3165</v>
       </c>
       <c r="G46" t="n">
-        <v>20120019.7</v>
+        <v>13992431.8</v>
       </c>
       <c r="H46" t="n">
-        <v>-19.98</v>
+        <v>-17.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222500</v>
+        <v>3345</v>
       </c>
       <c r="F47" t="n">
-        <v>178.8592</v>
+        <v>11605.0637</v>
       </c>
       <c r="G47" t="n">
-        <v>39796164.7</v>
+        <v>38818938.1</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1966,78 +1964,78 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>54500</v>
+        <v>12120</v>
       </c>
       <c r="F48" t="n">
-        <v>504.0447</v>
+        <v>820.878</v>
       </c>
       <c r="G48" t="n">
-        <v>27470436.6</v>
-      </c>
-      <c r="H48" t="n">
-        <v>24.43</v>
-      </c>
+        <v>9949041.199999999</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>32350</v>
+        <v>248000</v>
       </c>
       <c r="F49" t="n">
-        <v>314.5779</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2046,47 +2044,49 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13650</v>
+        <v>222500</v>
       </c>
       <c r="F50" t="n">
-        <v>745.5381</v>
+        <v>178.8592</v>
       </c>
       <c r="G50" t="n">
-        <v>10176595.1</v>
+        <v>39796164.7</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>31950</v>
+        <v>54500</v>
       </c>
       <c r="F51" t="n">
-        <v>318.5163</v>
+        <v>504.0447</v>
       </c>
       <c r="G51" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>250500</v>
+        <v>32350</v>
       </c>
       <c r="F52" t="n">
-        <v>81.2503</v>
+        <v>314.5779</v>
       </c>
       <c r="G52" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2128,27 +2128,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>14100</v>
+        <v>13650</v>
       </c>
       <c r="F53" t="n">
-        <v>1443.4887</v>
+        <v>745.5381</v>
       </c>
       <c r="G53" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2160,31 +2160,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>31300</v>
+        <v>31950</v>
       </c>
       <c r="F54" t="n">
-        <v>1954.4702</v>
+        <v>318.5163</v>
       </c>
       <c r="G54" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H54" t="n">
-        <v>6.83</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2194,12 +2192,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2208,13 +2206,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2355</v>
+        <v>250500</v>
       </c>
       <c r="F55" t="n">
-        <v>65496.7248</v>
+        <v>81.2503</v>
       </c>
       <c r="G55" t="n">
-        <v>154244786.8</v>
+        <v>20353190.3</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2226,12 +2224,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2240,13 +2238,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>15810</v>
+        <v>14100</v>
       </c>
       <c r="F56" t="n">
-        <v>5149.4473</v>
+        <v>1443.4887</v>
       </c>
       <c r="G56" t="n">
-        <v>81412761.09999999</v>
+        <v>20353190.3</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2258,29 +2256,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>28491.13</v>
+        <v>31300</v>
       </c>
       <c r="F57" t="n">
-        <v>357.1847</v>
+        <v>1954.4702</v>
       </c>
       <c r="G57" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H57" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2304,30 +2304,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4660</v>
+        <v>2355</v>
       </c>
       <c r="F58" t="n">
-        <v>4367.6374</v>
+        <v>65496.7248</v>
       </c>
       <c r="G58" t="n">
-        <v>20353190.3</v>
+        <v>154244786.8</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2336,79 +2336,77 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44600</v>
+        <v>15810</v>
       </c>
       <c r="F59" t="n">
-        <v>1359.3974</v>
+        <v>5149.4473</v>
       </c>
       <c r="G59" t="n">
-        <v>60629123.5</v>
+        <v>81412761.09999999</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>20300</v>
+        <v>28491.13</v>
       </c>
       <c r="F60" t="n">
-        <v>1162.9429</v>
+        <v>357.1847</v>
       </c>
       <c r="G60" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H60" t="n">
-        <v>7.9</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>13160</v>
+        <v>4660</v>
       </c>
       <c r="F61" t="n">
-        <v>767.846</v>
+        <v>4367.6374</v>
       </c>
       <c r="G61" t="n">
-        <v>10104853.9</v>
+        <v>20353190.3</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2420,31 +2418,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>49050</v>
+        <v>44600</v>
       </c>
       <c r="F62" t="n">
-        <v>357.1039</v>
+        <v>1359.3974</v>
       </c>
       <c r="G62" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2454,12 +2450,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2468,16 +2464,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>37100</v>
+        <v>20300</v>
       </c>
       <c r="F63" t="n">
-        <v>604.321</v>
+        <v>1162.9429</v>
       </c>
       <c r="G63" t="n">
-        <v>22420310.5</v>
+        <v>23607739.9</v>
       </c>
       <c r="H63" t="n">
-        <v>15.04</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="64">
@@ -2488,27 +2484,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>123700</v>
+        <v>13160</v>
       </c>
       <c r="F64" t="n">
-        <v>490.1303</v>
+        <v>767.846</v>
       </c>
       <c r="G64" t="n">
-        <v>60629123.5</v>
+        <v>10104853.9</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2520,29 +2516,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>41150</v>
+        <v>49050</v>
       </c>
       <c r="F65" t="n">
-        <v>491.1229</v>
+        <v>357.1039</v>
       </c>
       <c r="G65" t="n">
-        <v>20209707.8</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2552,29 +2550,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>31500</v>
+        <v>37100</v>
       </c>
       <c r="F66" t="n">
-        <v>320.789</v>
+        <v>604.321</v>
       </c>
       <c r="G66" t="n">
-        <v>10104853.9</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2584,27 +2584,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228500</v>
+        <v>123700</v>
       </c>
       <c r="F67" t="n">
-        <v>88.4451</v>
+        <v>490.1303</v>
       </c>
       <c r="G67" t="n">
-        <v>20209707.8</v>
+        <v>60629123.5</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2616,31 +2616,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>88500</v>
+        <v>41150</v>
       </c>
       <c r="F68" t="n">
-        <v>900.2261</v>
+        <v>491.1229</v>
       </c>
       <c r="G68" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>20209707.8</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2650,31 +2648,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>130100</v>
+        <v>31500</v>
       </c>
       <c r="F69" t="n">
-        <v>314.8563</v>
+        <v>320.789</v>
       </c>
       <c r="G69" t="n">
-        <v>40962809.6</v>
-      </c>
-      <c r="H69" t="n">
-        <v>8.33</v>
-      </c>
+        <v>10104853.9</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2684,12 +2680,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2698,13 +2694,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2325</v>
+        <v>228500</v>
       </c>
       <c r="F70" t="n">
-        <v>21730.8686</v>
+        <v>88.4451</v>
       </c>
       <c r="G70" t="n">
-        <v>50524269.6</v>
+        <v>20209707.8</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2716,29 +2712,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>32511.04</v>
+        <v>88500</v>
       </c>
       <c r="F71" t="n">
-        <v>932.439</v>
+        <v>900.2261</v>
       </c>
       <c r="G71" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2748,34 +2746,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4670</v>
+        <v>130100</v>
       </c>
       <c r="F72" t="n">
-        <v>6491.3408</v>
+        <v>314.8563</v>
       </c>
       <c r="G72" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H72" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2794,118 +2794,116 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2120</v>
+        <v>2325</v>
       </c>
       <c r="F73" t="n">
-        <v>63879.7502</v>
+        <v>21730.8686</v>
       </c>
       <c r="G73" t="n">
-        <v>135425070.4</v>
+        <v>50524269.6</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2120</v>
+        <v>32511.04</v>
       </c>
       <c r="F74" t="n">
-        <v>3453.9051</v>
+        <v>932.439</v>
       </c>
       <c r="G74" t="n">
-        <v>7322278.8</v>
+        <v>30314561.7</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>22900</v>
+        <v>4670</v>
       </c>
       <c r="F75" t="n">
-        <v>1397.6406</v>
+        <v>6491.3408</v>
       </c>
       <c r="G75" t="n">
-        <v>32005969</v>
+        <v>30314561.7</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>73600</v>
+        <v>2120</v>
       </c>
       <c r="F76" t="n">
-        <v>299.9614</v>
+        <v>63879.7502</v>
       </c>
       <c r="G76" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H76" t="n">
-        <v>16.09</v>
-      </c>
+        <v>135425070.4</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2924,13 +2922,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2215</v>
+        <v>2120</v>
       </c>
       <c r="F77" t="n">
-        <v>28224.978</v>
+        <v>3453.9051</v>
       </c>
       <c r="G77" t="n">
-        <v>62518326.2</v>
+        <v>7322278.8</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2942,27 +2940,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>43800</v>
+        <v>22900</v>
       </c>
       <c r="F78" t="n">
-        <v>504.0447</v>
+        <v>1397.6406</v>
       </c>
       <c r="G78" t="n">
-        <v>22077158.2</v>
+        <v>32005969</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2974,29 +2972,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>23650</v>
+        <v>73600</v>
       </c>
       <c r="F79" t="n">
-        <v>451.106</v>
+        <v>299.9614</v>
       </c>
       <c r="G79" t="n">
-        <v>10668656.3</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3020,64 +3020,62 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5730</v>
+        <v>2215</v>
       </c>
       <c r="F80" t="n">
-        <v>3723.7893</v>
+        <v>28224.978</v>
       </c>
       <c r="G80" t="n">
-        <v>21337312.7</v>
+        <v>62518326.2</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6080</v>
+        <v>43800</v>
       </c>
       <c r="F81" t="n">
-        <v>3255.5051</v>
+        <v>504.0447</v>
       </c>
       <c r="G81" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>22077158.2</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3086,94 +3084,96 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>95200</v>
+        <v>23650</v>
       </c>
       <c r="F82" t="n">
-        <v>221.6088</v>
+        <v>451.106</v>
       </c>
       <c r="G82" t="n">
-        <v>21097154.4</v>
+        <v>10668656.3</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2205</v>
+        <v>5730</v>
       </c>
       <c r="F83" t="n">
-        <v>52623.2877</v>
+        <v>3723.7893</v>
       </c>
       <c r="G83" t="n">
-        <v>116034349.3</v>
+        <v>21337312.7</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>58700</v>
+        <v>6080</v>
       </c>
       <c r="F84" t="n">
-        <v>357.1039</v>
+        <v>3255.5051</v>
       </c>
       <c r="G84" t="n">
-        <v>20961998.6</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3182,20 +3182,20 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>13250</v>
+        <v>95200</v>
       </c>
       <c r="F85" t="n">
-        <v>791.0188000000001</v>
+        <v>221.6088</v>
       </c>
       <c r="G85" t="n">
-        <v>10480999.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2360</v>
+        <v>2205</v>
       </c>
       <c r="F86" t="n">
-        <v>66616.5209</v>
+        <v>52623.2877</v>
       </c>
       <c r="G86" t="n">
-        <v>157214989.3</v>
+        <v>116034349.3</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3232,31 +3232,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>38300</v>
+        <v>58700</v>
       </c>
       <c r="F87" t="n">
-        <v>500.7861</v>
+        <v>357.1039</v>
       </c>
       <c r="G87" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>20961998.6</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3266,12 +3264,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3280,10 +3278,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>21150</v>
+        <v>13250</v>
       </c>
       <c r="F88" t="n">
-        <v>495.5555</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G88" t="n">
         <v>10480999.3</v>
@@ -3298,127 +3296,129 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>23650</v>
+        <v>2360</v>
       </c>
       <c r="F89" t="n">
-        <v>832.6201</v>
+        <v>66616.5209</v>
       </c>
       <c r="G89" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H89" t="n">
-        <v>1.28</v>
-      </c>
+        <v>157214989.3</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>12310</v>
+        <v>38300</v>
       </c>
       <c r="F90" t="n">
-        <v>2480.1654</v>
+        <v>500.7861</v>
       </c>
       <c r="G90" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>40650</v>
+        <v>21150</v>
       </c>
       <c r="F91" t="n">
-        <v>751.0661</v>
+        <v>495.5555</v>
       </c>
       <c r="G91" t="n">
-        <v>30530836.4</v>
+        <v>10480999.3</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>283500</v>
+        <v>23650</v>
       </c>
       <c r="F92" t="n">
-        <v>71.795</v>
+        <v>832.6201</v>
       </c>
       <c r="G92" t="n">
-        <v>20353890.9</v>
-      </c>
-      <c r="H92" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2390</v>
+        <v>12310</v>
       </c>
       <c r="F93" t="n">
-        <v>42581.3618</v>
+        <v>2480.1654</v>
       </c>
       <c r="G93" t="n">
-        <v>101769454.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3460,44 +3460,44 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>20450</v>
+        <v>40650</v>
       </c>
       <c r="F94" t="n">
-        <v>995.3003</v>
+        <v>751.0661</v>
       </c>
       <c r="G94" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3506,79 +3506,77 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>30200</v>
+        <v>283500</v>
       </c>
       <c r="F95" t="n">
-        <v>359.55</v>
+        <v>71.795</v>
       </c>
       <c r="G95" t="n">
-        <v>10858410.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>208500</v>
+        <v>2390</v>
       </c>
       <c r="F96" t="n">
-        <v>338</v>
+        <v>42581.3618</v>
       </c>
       <c r="G96" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.97</v>
-      </c>
+        <v>101769454.6</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>17720</v>
+        <v>20450</v>
       </c>
       <c r="F97" t="n">
-        <v>94.9217</v>
+        <v>995.3003</v>
       </c>
       <c r="G97" t="n">
-        <v>1682012.5</v>
+        <v>20353890.9</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3590,12 +3588,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3604,13 +3602,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100500</v>
+        <v>30200</v>
       </c>
       <c r="F98" t="n">
-        <v>8.9518</v>
+        <v>359.55</v>
       </c>
       <c r="G98" t="n">
-        <v>899652.6</v>
+        <v>10858410.6</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3622,29 +3620,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>11410</v>
+        <v>208500</v>
       </c>
       <c r="F99" t="n">
-        <v>6321.2722</v>
+        <v>338</v>
       </c>
       <c r="G99" t="n">
-        <v>72125715.8</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3654,27 +3654,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>12880</v>
+        <v>17720</v>
       </c>
       <c r="F100" t="n">
-        <v>713.2027</v>
+        <v>94.9217</v>
       </c>
       <c r="G100" t="n">
-        <v>9186050.6</v>
+        <v>1682012.5</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>21200</v>
+        <v>100500</v>
       </c>
       <c r="F101" t="n">
-        <v>120.8659</v>
+        <v>8.9518</v>
       </c>
       <c r="G101" t="n">
-        <v>2562357.9</v>
+        <v>899652.6</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3718,27 +3718,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>27700</v>
+        <v>11410</v>
       </c>
       <c r="F102" t="n">
-        <v>161.1835</v>
+        <v>6321.2722</v>
       </c>
       <c r="G102" t="n">
-        <v>4464784.2</v>
+        <v>72125715.8</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3750,27 +3750,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>21500</v>
+        <v>12880</v>
       </c>
       <c r="F103" t="n">
-        <v>129.2032</v>
+        <v>713.2027</v>
       </c>
       <c r="G103" t="n">
-        <v>2777868.4</v>
+        <v>9186050.6</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3796,13 +3796,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>34100</v>
+        <v>21200</v>
       </c>
       <c r="F104" t="n">
-        <v>21.679</v>
+        <v>120.8659</v>
       </c>
       <c r="G104" t="n">
-        <v>739252.6</v>
+        <v>2562357.9</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3814,27 +3814,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>40850</v>
+        <v>27700</v>
       </c>
       <c r="F105" t="n">
-        <v>123.3915</v>
+        <v>161.1835</v>
       </c>
       <c r="G105" t="n">
-        <v>5040542.1</v>
+        <v>4464784.2</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>308000</v>
+        <v>21500</v>
       </c>
       <c r="F106" t="n">
-        <v>9.1744</v>
+        <v>129.2032</v>
       </c>
       <c r="G106" t="n">
-        <v>2825715.8</v>
+        <v>2777868.4</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3878,27 +3878,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6330</v>
+        <v>34100</v>
       </c>
       <c r="F107" t="n">
-        <v>50.5051</v>
+        <v>21.679</v>
       </c>
       <c r="G107" t="n">
-        <v>319697.4</v>
+        <v>739252.6</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3910,27 +3910,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>31700</v>
+        <v>40850</v>
       </c>
       <c r="F108" t="n">
-        <v>158.7408</v>
+        <v>123.3915</v>
       </c>
       <c r="G108" t="n">
-        <v>5032084.2</v>
+        <v>5040542.1</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3942,27 +3942,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>68700</v>
+        <v>308000</v>
       </c>
       <c r="F109" t="n">
-        <v>16.0386</v>
+        <v>9.1744</v>
       </c>
       <c r="G109" t="n">
-        <v>1101852.6</v>
+        <v>2825715.8</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3988,13 +3988,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>256000</v>
+        <v>6330</v>
       </c>
       <c r="F110" t="n">
-        <v>45.4873</v>
+        <v>50.5051</v>
       </c>
       <c r="G110" t="n">
-        <v>11644736.8</v>
+        <v>319697.4</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -4006,27 +4006,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>91100</v>
+        <v>31700</v>
       </c>
       <c r="F111" t="n">
-        <v>19.6174</v>
+        <v>158.7408</v>
       </c>
       <c r="G111" t="n">
-        <v>1787142.1</v>
+        <v>5032084.2</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>130900</v>
+        <v>68700</v>
       </c>
       <c r="F112" t="n">
-        <v>89.1437</v>
+        <v>16.0386</v>
       </c>
       <c r="G112" t="n">
-        <v>11668905.3</v>
+        <v>1101852.6</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4070,27 +4070,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2400</v>
+        <v>256000</v>
       </c>
       <c r="F113" t="n">
-        <v>32820.1843</v>
+        <v>45.4873</v>
       </c>
       <c r="G113" t="n">
-        <v>78768442.40000001</v>
+        <v>11644736.8</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4102,12 +4102,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>41150</v>
+        <v>91100</v>
       </c>
       <c r="F114" t="n">
-        <v>38.7861</v>
+        <v>19.6174</v>
       </c>
       <c r="G114" t="n">
-        <v>1596047.4</v>
+        <v>1787142.1</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>49450</v>
+        <v>130900</v>
       </c>
       <c r="F115" t="n">
-        <v>83.90349999999999</v>
+        <v>89.1437</v>
       </c>
       <c r="G115" t="n">
-        <v>4149029</v>
+        <v>11668905.3</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4180,13 +4180,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>24750</v>
+        <v>2400</v>
       </c>
       <c r="F116" t="n">
-        <v>23.3799</v>
+        <v>32820.1843</v>
       </c>
       <c r="G116" t="n">
-        <v>578652.6</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4198,142 +4198,140 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5450</v>
+        <v>41150</v>
       </c>
       <c r="F117" t="n">
-        <v>220.6267</v>
+        <v>38.7861</v>
       </c>
       <c r="G117" t="n">
-        <v>1202415.4</v>
+        <v>1596047.4</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>327000</v>
+        <v>49450</v>
       </c>
       <c r="F118" t="n">
-        <v>54</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>4149029</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5130</v>
+        <v>24750</v>
       </c>
       <c r="F119" t="n">
-        <v>4001.7913</v>
+        <v>23.3799</v>
       </c>
       <c r="G119" t="n">
-        <v>20529189.5</v>
+        <v>578652.6</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>27100</v>
+        <v>5450</v>
       </c>
       <c r="F120" t="n">
-        <v>376</v>
+        <v>220.6267</v>
       </c>
       <c r="G120" t="n">
-        <v>10189600</v>
+        <v>1202415.4</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4342,47 +4340,47 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>67600</v>
+        <v>327000</v>
       </c>
       <c r="F121" t="n">
-        <v>998</v>
+        <v>54</v>
       </c>
       <c r="G121" t="n">
-        <v>67464800</v>
+        <v>17658000</v>
       </c>
       <c r="H121" t="n">
-        <v>-3.57</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>11900</v>
+        <v>5130</v>
       </c>
       <c r="F122" t="n">
-        <v>856</v>
+        <v>4001.7913</v>
       </c>
       <c r="G122" t="n">
-        <v>10186400</v>
+        <v>20529189.5</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4394,27 +4392,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>29300</v>
+        <v>27100</v>
       </c>
       <c r="F123" t="n">
-        <v>2434</v>
+        <v>376</v>
       </c>
       <c r="G123" t="n">
-        <v>71316200</v>
+        <v>10189600</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4426,29 +4424,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>119300</v>
+        <v>67600</v>
       </c>
       <c r="F124" t="n">
-        <v>171</v>
+        <v>998</v>
       </c>
       <c r="G124" t="n">
-        <v>20400300</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4458,44 +4458,44 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2445</v>
+        <v>11900</v>
       </c>
       <c r="F125" t="n">
-        <v>82456</v>
+        <v>856</v>
       </c>
       <c r="G125" t="n">
-        <v>201604920</v>
+        <v>10186400</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4504,81 +4504,79 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>18910</v>
+        <v>29300</v>
       </c>
       <c r="F126" t="n">
-        <v>1068.0212</v>
+        <v>2434</v>
       </c>
       <c r="G126" t="n">
-        <v>20196280</v>
+        <v>71316200</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>32250</v>
+        <v>119300</v>
       </c>
       <c r="F127" t="n">
-        <v>626</v>
+        <v>171</v>
       </c>
       <c r="G127" t="n">
-        <v>20188500</v>
+        <v>20400300</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>82500</v>
+        <v>2445</v>
       </c>
       <c r="F128" t="n">
-        <v>204</v>
+        <v>82456</v>
       </c>
       <c r="G128" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>201604920</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4588,100 +4586,100 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>56800</v>
+        <v>18910</v>
       </c>
       <c r="F129" t="n">
-        <v>258</v>
+        <v>1068.0212</v>
       </c>
       <c r="G129" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H129" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20196280</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>83700</v>
+        <v>32250</v>
       </c>
       <c r="F130" t="n">
-        <v>120</v>
+        <v>626</v>
       </c>
       <c r="G130" t="n">
-        <v>10044000</v>
+        <v>20188500</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>43650</v>
+        <v>82500</v>
       </c>
       <c r="F131" t="n">
-        <v>462</v>
+        <v>204</v>
       </c>
       <c r="G131" t="n">
-        <v>20166300</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4696,113 +4694,115 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>59700</v>
+        <v>56800</v>
       </c>
       <c r="F132" t="n">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="G132" t="n">
-        <v>10089300</v>
-      </c>
-      <c r="H132" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>10930</v>
+        <v>83700</v>
       </c>
       <c r="F133" t="n">
-        <v>1833</v>
+        <v>120</v>
       </c>
       <c r="G133" t="n">
-        <v>20034690</v>
+        <v>10044000</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>19850</v>
+        <v>43650</v>
       </c>
       <c r="F134" t="n">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="G134" t="n">
-        <v>10024250</v>
+        <v>20166300</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>26350</v>
+        <v>59700</v>
       </c>
       <c r="F135" t="n">
-        <v>380</v>
+        <v>169</v>
       </c>
       <c r="G135" t="n">
-        <v>10013000</v>
+        <v>10089300</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -4814,31 +4814,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>23500</v>
+        <v>10930</v>
       </c>
       <c r="F136" t="n">
-        <v>833</v>
+        <v>1833</v>
       </c>
       <c r="G136" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>20034690</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4848,27 +4846,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>85200</v>
+        <v>19850</v>
       </c>
       <c r="F137" t="n">
-        <v>118</v>
+        <v>505</v>
       </c>
       <c r="G137" t="n">
-        <v>10053600</v>
+        <v>10024250</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -4880,27 +4878,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>63400</v>
+        <v>26350</v>
       </c>
       <c r="F138" t="n">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="G138" t="n">
-        <v>20034400</v>
+        <v>10013000</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -4912,29 +4910,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>110300</v>
+        <v>23500</v>
       </c>
       <c r="F139" t="n">
-        <v>91</v>
+        <v>833</v>
       </c>
       <c r="G139" t="n">
-        <v>10037300</v>
-      </c>
-      <c r="H139" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4958,30 +4958,30 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>66100</v>
+        <v>85200</v>
       </c>
       <c r="F140" t="n">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="G140" t="n">
-        <v>10047200</v>
+        <v>10053600</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4990,77 +4990,77 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>25800</v>
+        <v>63400</v>
       </c>
       <c r="F141" t="n">
-        <v>2713</v>
+        <v>316</v>
       </c>
       <c r="G141" t="n">
-        <v>69995400</v>
+        <v>20034400</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>206500</v>
+        <v>110300</v>
       </c>
       <c r="F142" t="n">
-        <v>338</v>
+        <v>91</v>
       </c>
       <c r="G142" t="n">
-        <v>69797000</v>
+        <v>10037300</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>70100</v>
+        <v>66100</v>
       </c>
       <c r="F143" t="n">
-        <v>998</v>
+        <v>152</v>
       </c>
       <c r="G143" t="n">
-        <v>69959800</v>
+        <v>10047200</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5086,13 +5086,13 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>93300</v>
+        <v>25800</v>
       </c>
       <c r="F144" t="n">
-        <v>214</v>
+        <v>2713</v>
       </c>
       <c r="G144" t="n">
-        <v>19966200</v>
+        <v>69995400</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>11300</v>
+        <v>206500</v>
       </c>
       <c r="F145" t="n">
-        <v>4424</v>
+        <v>338</v>
       </c>
       <c r="G145" t="n">
-        <v>49991200</v>
+        <v>69797000</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5150,13 +5150,13 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>19740</v>
+        <v>70100</v>
       </c>
       <c r="F146" t="n">
-        <v>2532</v>
+        <v>998</v>
       </c>
       <c r="G146" t="n">
-        <v>49981680</v>
+        <v>69959800</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5182,13 +5182,13 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>25150</v>
+        <v>93300</v>
       </c>
       <c r="F147" t="n">
-        <v>2385</v>
+        <v>214</v>
       </c>
       <c r="G147" t="n">
-        <v>59982750</v>
+        <v>19966200</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -5200,12 +5200,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5214,13 +5214,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>22050</v>
+        <v>11300</v>
       </c>
       <c r="F148" t="n">
-        <v>2267</v>
+        <v>4424</v>
       </c>
       <c r="G148" t="n">
-        <v>49987350</v>
+        <v>49991200</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -5232,12 +5232,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5246,13 +5246,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>43150</v>
+        <v>19740</v>
       </c>
       <c r="F149" t="n">
-        <v>1390</v>
+        <v>2532</v>
       </c>
       <c r="G149" t="n">
-        <v>59978500</v>
+        <v>49981680</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5278,13 +5278,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>310000</v>
+        <v>25150</v>
       </c>
       <c r="F150" t="n">
-        <v>225</v>
+        <v>2385</v>
       </c>
       <c r="G150" t="n">
-        <v>69750000</v>
+        <v>59982750</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5310,13 +5310,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6240</v>
+        <v>22050</v>
       </c>
       <c r="F151" t="n">
-        <v>3205</v>
+        <v>2267</v>
       </c>
       <c r="G151" t="n">
-        <v>19999200</v>
+        <v>49987350</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5328,12 +5328,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>24000</v>
+        <v>43150</v>
       </c>
       <c r="F152" t="n">
-        <v>833</v>
+        <v>1390</v>
       </c>
       <c r="G152" t="n">
-        <v>19992000</v>
+        <v>59978500</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5360,12 +5360,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5374,13 +5374,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>90300</v>
+        <v>310000</v>
       </c>
       <c r="F153" t="n">
-        <v>442</v>
+        <v>225</v>
       </c>
       <c r="G153" t="n">
-        <v>39912600</v>
+        <v>69750000</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5406,13 +5406,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F154" t="n">
-        <v>357</v>
+        <v>3205</v>
       </c>
       <c r="G154" t="n">
-        <v>99781500</v>
+        <v>19999200</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5438,13 +5438,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>366000</v>
+        <v>24000</v>
       </c>
       <c r="F155" t="n">
-        <v>54</v>
+        <v>833</v>
       </c>
       <c r="G155" t="n">
-        <v>19764000</v>
+        <v>19992000</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5470,13 +5470,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>91000</v>
+        <v>90300</v>
       </c>
       <c r="F156" t="n">
-        <v>659</v>
+        <v>442</v>
       </c>
       <c r="G156" t="n">
-        <v>59969000</v>
+        <v>39912600</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5502,13 +5502,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>120100</v>
+        <v>279500</v>
       </c>
       <c r="F157" t="n">
-        <v>666</v>
+        <v>357</v>
       </c>
       <c r="G157" t="n">
-        <v>79986600</v>
+        <v>99781500</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5534,13 +5534,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2405</v>
+        <v>366000</v>
       </c>
       <c r="F158" t="n">
-        <v>415800</v>
+        <v>54</v>
       </c>
       <c r="G158" t="n">
-        <v>999999000</v>
+        <v>19764000</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5552,12 +5552,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5566,13 +5566,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>69000</v>
+        <v>91000</v>
       </c>
       <c r="F159" t="n">
-        <v>579</v>
+        <v>659</v>
       </c>
       <c r="G159" t="n">
-        <v>39951000</v>
+        <v>59969000</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5584,12 +5584,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>42300</v>
+        <v>120100</v>
       </c>
       <c r="F160" t="n">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="G160" t="n">
-        <v>29990700</v>
+        <v>79986600</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5616,29 +5616,125 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F161" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G161" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F162" t="n">
+        <v>579</v>
+      </c>
+      <c r="G162" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F163" t="n">
+        <v>709</v>
+      </c>
+      <c r="G163" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E161" t="n">
+      <c r="E164" t="n">
         <v>23350</v>
       </c>
-      <c r="F161" t="n">
+      <c r="F164" t="n">
         <v>856</v>
       </c>
-      <c r="G161" t="n">
+      <c r="G164" t="n">
         <v>19987600</v>
       </c>
-      <c r="H161" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,226 +473,228 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33300</v>
+        <v>24200</v>
       </c>
       <c r="F2" t="n">
-        <v>296.1438</v>
+        <v>422.9059</v>
       </c>
       <c r="G2" t="n">
-        <v>9861590.1</v>
+        <v>10234323</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9540</v>
+        <v>4005</v>
       </c>
       <c r="F3" t="n">
-        <v>1033.7097</v>
+        <v>5110.773</v>
       </c>
       <c r="G3" t="n">
-        <v>9861590.1</v>
+        <v>20468646</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58500</v>
+        <v>35050</v>
       </c>
       <c r="F4" t="n">
-        <v>168.5742</v>
+        <v>411.8056</v>
       </c>
       <c r="G4" t="n">
-        <v>9861590.1</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>14433786.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-17.14</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23850</v>
+        <v>39450</v>
       </c>
       <c r="F5" t="n">
-        <v>433.5542</v>
+        <v>470.9867</v>
       </c>
       <c r="G5" t="n">
-        <v>10340268.5</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>18580423.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-7.18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45450</v>
+        <v>33300</v>
       </c>
       <c r="F6" t="n">
-        <v>227.5087</v>
+        <v>296.1438</v>
       </c>
       <c r="G6" t="n">
-        <v>10340268.5</v>
+        <v>9861590.1</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15230</v>
+        <v>9540</v>
       </c>
       <c r="F7" t="n">
-        <v>1186.9772</v>
+        <v>1033.7097</v>
       </c>
       <c r="G7" t="n">
-        <v>18077663</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-5.87</v>
-      </c>
+        <v>9861590.1</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2655</v>
+        <v>58500</v>
       </c>
       <c r="F8" t="n">
-        <v>76798.0178</v>
+        <v>168.5742</v>
       </c>
       <c r="G8" t="n">
-        <v>203898737.2</v>
+        <v>9861590.1</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -704,24 +706,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30249.84</v>
+        <v>23850</v>
       </c>
       <c r="F9" t="n">
-        <v>341.8289</v>
+        <v>433.5542</v>
       </c>
       <c r="G9" t="n">
         <v>10340268.5</v>
@@ -736,12 +738,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,10 +752,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25550</v>
+        <v>45450</v>
       </c>
       <c r="F10" t="n">
-        <v>404.7072</v>
+        <v>227.5087</v>
       </c>
       <c r="G10" t="n">
         <v>10340268.5</v>
@@ -768,44 +770,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59900</v>
+        <v>15230</v>
       </c>
       <c r="F11" t="n">
-        <v>172.6255</v>
+        <v>1186.9772</v>
       </c>
       <c r="G11" t="n">
-        <v>10340268.5</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>18077663</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-5.87</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,111 +818,109 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>41050</v>
+        <v>2655</v>
       </c>
       <c r="F12" t="n">
-        <v>490.4266</v>
+        <v>76798.0178</v>
       </c>
       <c r="G12" t="n">
-        <v>20132010.4</v>
+        <v>203898737.2</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230000</v>
+        <v>30249.84</v>
       </c>
       <c r="F13" t="n">
-        <v>135.183</v>
+        <v>341.8289</v>
       </c>
       <c r="G13" t="n">
-        <v>31092084.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-16.92</v>
-      </c>
+        <v>10340268.5</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2595</v>
+        <v>25550</v>
       </c>
       <c r="F14" t="n">
-        <v>42895.584</v>
+        <v>404.7072</v>
       </c>
       <c r="G14" t="n">
-        <v>111314040.6</v>
+        <v>10340268.5</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>15870</v>
+        <v>59900</v>
       </c>
       <c r="F15" t="n">
-        <v>634.2788</v>
+        <v>172.6255</v>
       </c>
       <c r="G15" t="n">
-        <v>10066005.2</v>
+        <v>10340268.5</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -944,13 +946,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>29646.86</v>
+        <v>41050</v>
       </c>
       <c r="F16" t="n">
-        <v>339.5302</v>
+        <v>490.4266</v>
       </c>
       <c r="G16" t="n">
-        <v>10066005.2</v>
+        <v>20132010.4</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,29 +964,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9960</v>
+        <v>230000</v>
       </c>
       <c r="F17" t="n">
-        <v>1010.6431</v>
+        <v>135.183</v>
       </c>
       <c r="G17" t="n">
-        <v>10066005.2</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>31092084.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-16.92</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -994,27 +998,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59100</v>
+        <v>2595</v>
       </c>
       <c r="F18" t="n">
-        <v>681.2863</v>
+        <v>42895.584</v>
       </c>
       <c r="G18" t="n">
-        <v>40264020.8</v>
+        <v>111314040.6</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,24 +1030,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3385</v>
+        <v>15870</v>
       </c>
       <c r="F19" t="n">
-        <v>2973.7091</v>
+        <v>634.2788</v>
       </c>
       <c r="G19" t="n">
         <v>10066005.2</v>
@@ -1053,17 +1057,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,30 +1076,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26200</v>
+        <v>29646.86</v>
       </c>
       <c r="F20" t="n">
-        <v>382.0025</v>
+        <v>339.5302</v>
       </c>
       <c r="G20" t="n">
-        <v>10008466.3</v>
+        <v>10066005.2</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1104,30 +1108,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>94700</v>
+        <v>9960</v>
       </c>
       <c r="F21" t="n">
-        <v>105.686</v>
+        <v>1010.6431</v>
       </c>
       <c r="G21" t="n">
-        <v>10008466.3</v>
+        <v>10066005.2</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1136,62 +1140,62 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>42500</v>
+        <v>59100</v>
       </c>
       <c r="F22" t="n">
-        <v>470.9867</v>
+        <v>681.2863</v>
       </c>
       <c r="G22" t="n">
-        <v>20016932.7</v>
+        <v>40264020.8</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>26600</v>
+        <v>3385</v>
       </c>
       <c r="F23" t="n">
-        <v>361.0017</v>
+        <v>2973.7091</v>
       </c>
       <c r="G23" t="n">
-        <v>9602645.699999999</v>
+        <v>10066005.2</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1200,62 +1204,62 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10740</v>
+        <v>26200</v>
       </c>
       <c r="F24" t="n">
-        <v>894.1011</v>
+        <v>382.0025</v>
       </c>
       <c r="G24" t="n">
-        <v>9602645.699999999</v>
+        <v>10008466.3</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>16180</v>
+        <v>94700</v>
       </c>
       <c r="F25" t="n">
-        <v>1186.9772</v>
+        <v>105.686</v>
       </c>
       <c r="G25" t="n">
-        <v>19205291.4</v>
+        <v>10008466.3</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1264,13 +1268,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88400</v>
+        <v>42500</v>
       </c>
       <c r="F26" t="n">
-        <v>217.2544</v>
+        <v>470.9867</v>
       </c>
       <c r="G26" t="n">
-        <v>19205291.4</v>
+        <v>20016932.7</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1282,12 +1286,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1296,13 +1300,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>99100</v>
+        <v>26600</v>
       </c>
       <c r="F27" t="n">
-        <v>290.6956</v>
+        <v>361.0017</v>
       </c>
       <c r="G27" t="n">
-        <v>28807937.1</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1314,31 +1318,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>37350</v>
+        <v>10740</v>
       </c>
       <c r="F28" t="n">
-        <v>491.1229</v>
+        <v>894.1011</v>
       </c>
       <c r="G28" t="n">
-        <v>18343440.7</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-9.23</v>
-      </c>
+        <v>9602645.699999999</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1348,27 +1350,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2520</v>
+        <v>16180</v>
       </c>
       <c r="F29" t="n">
-        <v>33368.1327</v>
+        <v>1186.9772</v>
       </c>
       <c r="G29" t="n">
-        <v>84087694.5</v>
+        <v>19205291.4</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,31 +1382,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>16500</v>
+        <v>88400</v>
       </c>
       <c r="F30" t="n">
-        <v>856.421</v>
+        <v>217.2544</v>
       </c>
       <c r="G30" t="n">
-        <v>14130946.6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-22.8</v>
-      </c>
+        <v>19205291.4</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1414,24 +1414,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>27650</v>
+        <v>99100</v>
       </c>
       <c r="F31" t="n">
-        <v>1041.8784</v>
+        <v>290.6956</v>
       </c>
       <c r="G31" t="n">
         <v>28807937.1</v>
@@ -1446,140 +1446,144 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>9350</v>
+        <v>37350</v>
       </c>
       <c r="F32" t="n">
-        <v>1027.0209</v>
+        <v>491.1229</v>
       </c>
       <c r="G32" t="n">
-        <v>9602645.699999999</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>18343440.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-9.23</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>28650</v>
+        <v>2520</v>
       </c>
       <c r="F33" t="n">
-        <v>345.7839</v>
+        <v>33368.1327</v>
       </c>
       <c r="G33" t="n">
-        <v>9906708.4</v>
+        <v>84087694.5</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>11600</v>
+        <v>16500</v>
       </c>
       <c r="F34" t="n">
-        <v>854.0266</v>
+        <v>856.421</v>
       </c>
       <c r="G34" t="n">
-        <v>9906708.4</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>14130946.6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-22.8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>131000</v>
+        <v>27650</v>
       </c>
       <c r="F35" t="n">
-        <v>75.6237</v>
+        <v>1041.8784</v>
       </c>
       <c r="G35" t="n">
-        <v>9906708.4</v>
+        <v>28807937.1</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1588,13 +1592,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>33717.02</v>
+        <v>9350</v>
       </c>
       <c r="F36" t="n">
-        <v>293.8192</v>
+        <v>1027.0209</v>
       </c>
       <c r="G36" t="n">
-        <v>9906708.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1606,24 +1610,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4830</v>
+        <v>28650</v>
       </c>
       <c r="F37" t="n">
-        <v>2051.0783</v>
+        <v>345.7839</v>
       </c>
       <c r="G37" t="n">
         <v>9906708.4</v>
@@ -1638,78 +1642,76 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9430</v>
+        <v>11600</v>
       </c>
       <c r="F38" t="n">
-        <v>2101.1046</v>
+        <v>854.0266</v>
       </c>
       <c r="G38" t="n">
-        <v>19813416.7</v>
+        <v>9906708.4</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>79100</v>
+        <v>131000</v>
       </c>
       <c r="F39" t="n">
-        <v>205.0482</v>
+        <v>75.6237</v>
       </c>
       <c r="G39" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1718,64 +1720,62 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25250</v>
+        <v>33717.02</v>
       </c>
       <c r="F40" t="n">
-        <v>768.6917999999999</v>
+        <v>293.8192</v>
       </c>
       <c r="G40" t="n">
-        <v>19409469.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12510</v>
+        <v>4830</v>
       </c>
       <c r="F41" t="n">
-        <v>1443.4887</v>
+        <v>2051.0783</v>
       </c>
       <c r="G41" t="n">
-        <v>18058043.3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-11.28</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>126500</v>
+        <v>9430</v>
       </c>
       <c r="F42" t="n">
-        <v>383.5863</v>
+        <v>2101.1046</v>
       </c>
       <c r="G42" t="n">
-        <v>48523672.7</v>
+        <v>19813416.7</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1802,29 +1802,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2485</v>
+        <v>79100</v>
       </c>
       <c r="F43" t="n">
-        <v>42403.6617</v>
+        <v>205.0482</v>
       </c>
       <c r="G43" t="n">
-        <v>105373099.3</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>16219315.2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-15.22</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1834,27 +1836,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>45500</v>
+        <v>25250</v>
       </c>
       <c r="F44" t="n">
-        <v>213.2909</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>9704734.5</v>
+        <v>19409469.1</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1866,29 +1868,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17880</v>
+        <v>12510</v>
       </c>
       <c r="F45" t="n">
-        <v>1085.5408</v>
+        <v>1443.4887</v>
       </c>
       <c r="G45" t="n">
-        <v>19409469.1</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>18058043.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-11.28</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1898,31 +1902,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4460</v>
+        <v>126500</v>
       </c>
       <c r="F46" t="n">
-        <v>3137.3165</v>
+        <v>383.5863</v>
       </c>
       <c r="G46" t="n">
-        <v>13992431.8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-17.83</v>
-      </c>
+        <v>48523672.7</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1932,44 +1934,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3345</v>
+        <v>2485</v>
       </c>
       <c r="F47" t="n">
-        <v>11605.0637</v>
+        <v>42403.6617</v>
       </c>
       <c r="G47" t="n">
-        <v>38818938.1</v>
+        <v>105373099.3</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1978,130 +1980,128 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12120</v>
+        <v>45500</v>
       </c>
       <c r="F48" t="n">
-        <v>820.878</v>
+        <v>213.2909</v>
       </c>
       <c r="G48" t="n">
-        <v>9949041.199999999</v>
+        <v>9704734.5</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>248000</v>
+        <v>17880</v>
       </c>
       <c r="F49" t="n">
-        <v>81.12909999999999</v>
+        <v>1085.5408</v>
       </c>
       <c r="G49" t="n">
-        <v>20120019.7</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-19.98</v>
-      </c>
+        <v>19409469.1</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222500</v>
+        <v>4460</v>
       </c>
       <c r="F50" t="n">
-        <v>178.8592</v>
+        <v>3137.3165</v>
       </c>
       <c r="G50" t="n">
-        <v>39796164.7</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>13992431.8</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-17.83</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>54500</v>
+        <v>3345</v>
       </c>
       <c r="F51" t="n">
-        <v>504.0447</v>
+        <v>11605.0637</v>
       </c>
       <c r="G51" t="n">
-        <v>27470436.6</v>
-      </c>
-      <c r="H51" t="n">
-        <v>24.43</v>
-      </c>
+        <v>38818938.1</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2110,111 +2110,115 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>32350</v>
+        <v>12120</v>
       </c>
       <c r="F52" t="n">
-        <v>314.5779</v>
+        <v>820.878</v>
       </c>
       <c r="G52" t="n">
-        <v>10176595.1</v>
+        <v>9949041.199999999</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>13650</v>
+        <v>248000</v>
       </c>
       <c r="F53" t="n">
-        <v>745.5381</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>31950</v>
+        <v>222500</v>
       </c>
       <c r="F54" t="n">
-        <v>318.5163</v>
+        <v>178.8592</v>
       </c>
       <c r="G54" t="n">
-        <v>10176595.1</v>
+        <v>39796164.7</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>250500</v>
+        <v>54500</v>
       </c>
       <c r="F55" t="n">
-        <v>81.2503</v>
+        <v>504.0447</v>
       </c>
       <c r="G55" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H55" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2224,27 +2228,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>14100</v>
+        <v>32350</v>
       </c>
       <c r="F56" t="n">
-        <v>1443.4887</v>
+        <v>314.5779</v>
       </c>
       <c r="G56" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2256,31 +2260,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>31300</v>
+        <v>13650</v>
       </c>
       <c r="F57" t="n">
-        <v>1954.4702</v>
+        <v>745.5381</v>
       </c>
       <c r="G57" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H57" t="n">
-        <v>6.83</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2290,27 +2292,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2355</v>
+        <v>31950</v>
       </c>
       <c r="F58" t="n">
-        <v>65496.7248</v>
+        <v>318.5163</v>
       </c>
       <c r="G58" t="n">
-        <v>154244786.8</v>
+        <v>10176595.1</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2322,27 +2324,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>15810</v>
+        <v>250500</v>
       </c>
       <c r="F59" t="n">
-        <v>5149.4473</v>
+        <v>81.2503</v>
       </c>
       <c r="G59" t="n">
-        <v>81412761.09999999</v>
+        <v>20353190.3</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2354,27 +2356,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>28491.13</v>
+        <v>14100</v>
       </c>
       <c r="F60" t="n">
-        <v>357.1847</v>
+        <v>1443.4887</v>
       </c>
       <c r="G60" t="n">
-        <v>10176595.1</v>
+        <v>20353190.3</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2386,110 +2388,110 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4660</v>
+        <v>31300</v>
       </c>
       <c r="F61" t="n">
-        <v>4367.6374</v>
+        <v>1954.4702</v>
       </c>
       <c r="G61" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H61" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>44600</v>
+        <v>2355</v>
       </c>
       <c r="F62" t="n">
-        <v>1359.3974</v>
+        <v>65496.7248</v>
       </c>
       <c r="G62" t="n">
-        <v>60629123.5</v>
+        <v>154244786.8</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>20300</v>
+        <v>15810</v>
       </c>
       <c r="F63" t="n">
-        <v>1162.9429</v>
+        <v>5149.4473</v>
       </c>
       <c r="G63" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H63" t="n">
-        <v>7.9</v>
-      </c>
+        <v>81412761.09999999</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2498,49 +2500,47 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>13160</v>
+        <v>28491.13</v>
       </c>
       <c r="F64" t="n">
-        <v>767.846</v>
+        <v>357.1847</v>
       </c>
       <c r="G64" t="n">
-        <v>10104853.9</v>
+        <v>10176595.1</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>49050</v>
+        <v>4660</v>
       </c>
       <c r="F65" t="n">
-        <v>357.1039</v>
+        <v>4367.6374</v>
       </c>
       <c r="G65" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2550,31 +2550,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>37100</v>
+        <v>44600</v>
       </c>
       <c r="F66" t="n">
-        <v>604.321</v>
+        <v>1359.3974</v>
       </c>
       <c r="G66" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H66" t="n">
-        <v>15.04</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2584,29 +2582,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>123700</v>
+        <v>20300</v>
       </c>
       <c r="F67" t="n">
-        <v>490.1303</v>
+        <v>1162.9429</v>
       </c>
       <c r="G67" t="n">
-        <v>60629123.5</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>23607739.9</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2616,27 +2616,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>41150</v>
+        <v>13160</v>
       </c>
       <c r="F68" t="n">
-        <v>491.1229</v>
+        <v>767.846</v>
       </c>
       <c r="G68" t="n">
-        <v>20209707.8</v>
+        <v>10104853.9</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2648,29 +2648,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>31500</v>
+        <v>49050</v>
       </c>
       <c r="F69" t="n">
-        <v>320.789</v>
+        <v>357.1039</v>
       </c>
       <c r="G69" t="n">
-        <v>10104853.9</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2680,29 +2682,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228500</v>
+        <v>37100</v>
       </c>
       <c r="F70" t="n">
-        <v>88.4451</v>
+        <v>604.321</v>
       </c>
       <c r="G70" t="n">
-        <v>20209707.8</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2712,31 +2716,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>88500</v>
+        <v>123700</v>
       </c>
       <c r="F71" t="n">
-        <v>900.2261</v>
+        <v>490.1303</v>
       </c>
       <c r="G71" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2746,31 +2748,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>130100</v>
+        <v>41150</v>
       </c>
       <c r="F72" t="n">
-        <v>314.8563</v>
+        <v>491.1229</v>
       </c>
       <c r="G72" t="n">
-        <v>40962809.6</v>
-      </c>
-      <c r="H72" t="n">
-        <v>8.33</v>
-      </c>
+        <v>20209707.8</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2794,13 +2794,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2325</v>
+        <v>31500</v>
       </c>
       <c r="F73" t="n">
-        <v>21730.8686</v>
+        <v>320.789</v>
       </c>
       <c r="G73" t="n">
-        <v>50524269.6</v>
+        <v>10104853.9</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2812,27 +2812,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>32511.04</v>
+        <v>228500</v>
       </c>
       <c r="F74" t="n">
-        <v>932.439</v>
+        <v>88.4451</v>
       </c>
       <c r="G74" t="n">
-        <v>30314561.7</v>
+        <v>20209707.8</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2844,66 +2844,70 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4670</v>
+        <v>88500</v>
       </c>
       <c r="F75" t="n">
-        <v>6491.3408</v>
+        <v>900.2261</v>
       </c>
       <c r="G75" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2120</v>
+        <v>130100</v>
       </c>
       <c r="F76" t="n">
-        <v>63879.7502</v>
+        <v>314.8563</v>
       </c>
       <c r="G76" t="n">
-        <v>135425070.4</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H76" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2918,90 +2922,88 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2120</v>
+        <v>2325</v>
       </c>
       <c r="F77" t="n">
-        <v>3453.9051</v>
+        <v>21730.8686</v>
       </c>
       <c r="G77" t="n">
-        <v>7322278.8</v>
+        <v>50524269.6</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>22900</v>
+        <v>32511.04</v>
       </c>
       <c r="F78" t="n">
-        <v>1397.6406</v>
+        <v>932.439</v>
       </c>
       <c r="G78" t="n">
-        <v>32005969</v>
+        <v>30314561.7</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>73600</v>
+        <v>4670</v>
       </c>
       <c r="F79" t="n">
-        <v>299.9614</v>
+        <v>6491.3408</v>
       </c>
       <c r="G79" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H79" t="n">
-        <v>16.09</v>
-      </c>
+        <v>30314561.7</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3016,49 +3018,49 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2215</v>
+        <v>2120</v>
       </c>
       <c r="F80" t="n">
-        <v>28224.978</v>
+        <v>63879.7502</v>
       </c>
       <c r="G80" t="n">
-        <v>62518326.2</v>
+        <v>135425070.4</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>43800</v>
+        <v>2120</v>
       </c>
       <c r="F81" t="n">
-        <v>504.0447</v>
+        <v>3453.9051</v>
       </c>
       <c r="G81" t="n">
-        <v>22077158.2</v>
+        <v>7322278.8</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3070,27 +3072,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>23650</v>
+        <v>22900</v>
       </c>
       <c r="F82" t="n">
-        <v>451.106</v>
+        <v>1397.6406</v>
       </c>
       <c r="G82" t="n">
-        <v>10668656.3</v>
+        <v>32005969</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3102,206 +3104,208 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5730</v>
+        <v>73600</v>
       </c>
       <c r="F83" t="n">
-        <v>3723.7893</v>
+        <v>299.9614</v>
       </c>
       <c r="G83" t="n">
-        <v>21337312.7</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
+        <v>22077158.2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6080</v>
+        <v>2215</v>
       </c>
       <c r="F84" t="n">
-        <v>3255.5051</v>
+        <v>28224.978</v>
       </c>
       <c r="G84" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>62518326.2</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>95200</v>
+        <v>43800</v>
       </c>
       <c r="F85" t="n">
-        <v>221.6088</v>
+        <v>504.0447</v>
       </c>
       <c r="G85" t="n">
-        <v>21097154.4</v>
+        <v>22077158.2</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2205</v>
+        <v>23650</v>
       </c>
       <c r="F86" t="n">
-        <v>52623.2877</v>
+        <v>451.106</v>
       </c>
       <c r="G86" t="n">
-        <v>116034349.3</v>
+        <v>10668656.3</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>58700</v>
+        <v>5730</v>
       </c>
       <c r="F87" t="n">
-        <v>357.1039</v>
+        <v>3723.7893</v>
       </c>
       <c r="G87" t="n">
-        <v>20961998.6</v>
+        <v>21337312.7</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>13250</v>
+        <v>6080</v>
       </c>
       <c r="F88" t="n">
-        <v>791.0188000000001</v>
+        <v>3255.5051</v>
       </c>
       <c r="G88" t="n">
-        <v>10480999.3</v>
-      </c>
-      <c r="H88" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3310,49 +3314,47 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2360</v>
+        <v>95200</v>
       </c>
       <c r="F89" t="n">
-        <v>66616.5209</v>
+        <v>221.6088</v>
       </c>
       <c r="G89" t="n">
-        <v>157214989.3</v>
+        <v>21097154.4</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>38300</v>
+        <v>2205</v>
       </c>
       <c r="F90" t="n">
-        <v>500.7861</v>
+        <v>52623.2877</v>
       </c>
       <c r="G90" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>116034349.3</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3362,27 +3364,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>21150</v>
+        <v>58700</v>
       </c>
       <c r="F91" t="n">
-        <v>495.5555</v>
+        <v>357.1039</v>
       </c>
       <c r="G91" t="n">
-        <v>10480999.3</v>
+        <v>20961998.6</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3394,46 +3396,44 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>23650</v>
+        <v>13250</v>
       </c>
       <c r="F92" t="n">
-        <v>832.6201</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>19691465.3</v>
-      </c>
-      <c r="H92" t="n">
-        <v>1.28</v>
-      </c>
+        <v>10480999.3</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3442,111 +3442,115 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>12310</v>
+        <v>2360</v>
       </c>
       <c r="F93" t="n">
-        <v>2480.1654</v>
+        <v>66616.5209</v>
       </c>
       <c r="G93" t="n">
-        <v>30530836.4</v>
+        <v>157214989.3</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>40650</v>
+        <v>38300</v>
       </c>
       <c r="F94" t="n">
-        <v>751.0661</v>
+        <v>500.7861</v>
       </c>
       <c r="G94" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>19180107.1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-11.87</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>283500</v>
+        <v>21150</v>
       </c>
       <c r="F95" t="n">
-        <v>71.795</v>
+        <v>495.5555</v>
       </c>
       <c r="G95" t="n">
-        <v>20353890.9</v>
+        <v>10480999.3</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2390</v>
+        <v>23650</v>
       </c>
       <c r="F96" t="n">
-        <v>42581.3618</v>
+        <v>832.6201</v>
       </c>
       <c r="G96" t="n">
-        <v>101769454.6</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3556,44 +3560,44 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>20450</v>
+        <v>12310</v>
       </c>
       <c r="F97" t="n">
-        <v>995.3003</v>
+        <v>2480.1654</v>
       </c>
       <c r="G97" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3602,64 +3606,62 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>30200</v>
+        <v>40650</v>
       </c>
       <c r="F98" t="n">
-        <v>359.55</v>
+        <v>751.0661</v>
       </c>
       <c r="G98" t="n">
-        <v>10858410.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>208500</v>
+        <v>283500</v>
       </c>
       <c r="F99" t="n">
-        <v>338</v>
+        <v>71.795</v>
       </c>
       <c r="G99" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0.97</v>
-      </c>
+        <v>20353890.9</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3668,45 +3670,45 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>17720</v>
+        <v>2390</v>
       </c>
       <c r="F100" t="n">
-        <v>94.9217</v>
+        <v>42581.3618</v>
       </c>
       <c r="G100" t="n">
-        <v>1682012.5</v>
+        <v>101769454.6</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100500</v>
+        <v>20450</v>
       </c>
       <c r="F101" t="n">
-        <v>8.9518</v>
+        <v>995.3003</v>
       </c>
       <c r="G101" t="n">
-        <v>899652.6</v>
+        <v>20353890.9</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3718,27 +3720,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>11410</v>
+        <v>30200</v>
       </c>
       <c r="F102" t="n">
-        <v>6321.2722</v>
+        <v>359.55</v>
       </c>
       <c r="G102" t="n">
-        <v>72125715.8</v>
+        <v>10858410.6</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3750,29 +3752,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>12880</v>
+        <v>208500</v>
       </c>
       <c r="F103" t="n">
-        <v>713.2027</v>
+        <v>338</v>
       </c>
       <c r="G103" t="n">
-        <v>9186050.6</v>
-      </c>
-      <c r="H103" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3782,27 +3786,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>21200</v>
+        <v>17720</v>
       </c>
       <c r="F104" t="n">
-        <v>120.8659</v>
+        <v>94.9217</v>
       </c>
       <c r="G104" t="n">
-        <v>2562357.9</v>
+        <v>1682012.5</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3814,12 +3818,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3828,13 +3832,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>27700</v>
+        <v>100500</v>
       </c>
       <c r="F105" t="n">
-        <v>161.1835</v>
+        <v>8.9518</v>
       </c>
       <c r="G105" t="n">
-        <v>4464784.2</v>
+        <v>899652.6</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3846,27 +3850,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>21500</v>
+        <v>11410</v>
       </c>
       <c r="F106" t="n">
-        <v>129.2032</v>
+        <v>6321.2722</v>
       </c>
       <c r="G106" t="n">
-        <v>2777868.4</v>
+        <v>72125715.8</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3878,12 +3882,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3892,13 +3896,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>34100</v>
+        <v>12880</v>
       </c>
       <c r="F107" t="n">
-        <v>21.679</v>
+        <v>713.2027</v>
       </c>
       <c r="G107" t="n">
-        <v>739252.6</v>
+        <v>9186050.6</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3910,27 +3914,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>40850</v>
+        <v>21200</v>
       </c>
       <c r="F108" t="n">
-        <v>123.3915</v>
+        <v>120.8659</v>
       </c>
       <c r="G108" t="n">
-        <v>5040542.1</v>
+        <v>2562357.9</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3942,27 +3946,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>308000</v>
+        <v>27700</v>
       </c>
       <c r="F109" t="n">
-        <v>9.1744</v>
+        <v>161.1835</v>
       </c>
       <c r="G109" t="n">
-        <v>2825715.8</v>
+        <v>4464784.2</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3974,12 +3978,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3988,13 +3992,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6330</v>
+        <v>21500</v>
       </c>
       <c r="F110" t="n">
-        <v>50.5051</v>
+        <v>129.2032</v>
       </c>
       <c r="G110" t="n">
-        <v>319697.4</v>
+        <v>2777868.4</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -4006,12 +4010,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4020,13 +4024,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>31700</v>
+        <v>34100</v>
       </c>
       <c r="F111" t="n">
-        <v>158.7408</v>
+        <v>21.679</v>
       </c>
       <c r="G111" t="n">
-        <v>5032084.2</v>
+        <v>739252.6</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4038,27 +4042,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>68700</v>
+        <v>40850</v>
       </c>
       <c r="F112" t="n">
-        <v>16.0386</v>
+        <v>123.3915</v>
       </c>
       <c r="G112" t="n">
-        <v>1101852.6</v>
+        <v>5040542.1</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4070,12 +4074,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4084,13 +4088,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>256000</v>
+        <v>308000</v>
       </c>
       <c r="F113" t="n">
-        <v>45.4873</v>
+        <v>9.1744</v>
       </c>
       <c r="G113" t="n">
-        <v>11644736.8</v>
+        <v>2825715.8</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4102,12 +4106,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4116,13 +4120,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>91100</v>
+        <v>6330</v>
       </c>
       <c r="F114" t="n">
-        <v>19.6174</v>
+        <v>50.5051</v>
       </c>
       <c r="G114" t="n">
-        <v>1787142.1</v>
+        <v>319697.4</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4134,12 +4138,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4148,13 +4152,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>130900</v>
+        <v>31700</v>
       </c>
       <c r="F115" t="n">
-        <v>89.1437</v>
+        <v>158.7408</v>
       </c>
       <c r="G115" t="n">
-        <v>11668905.3</v>
+        <v>5032084.2</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4166,12 +4170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4180,13 +4184,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2400</v>
+        <v>68700</v>
       </c>
       <c r="F116" t="n">
-        <v>32820.1843</v>
+        <v>16.0386</v>
       </c>
       <c r="G116" t="n">
-        <v>78768442.40000001</v>
+        <v>1101852.6</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4198,12 +4202,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4212,13 +4216,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>41150</v>
+        <v>256000</v>
       </c>
       <c r="F117" t="n">
-        <v>38.7861</v>
+        <v>45.4873</v>
       </c>
       <c r="G117" t="n">
-        <v>1596047.4</v>
+        <v>11644736.8</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4230,27 +4234,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>49450</v>
+        <v>91100</v>
       </c>
       <c r="F118" t="n">
-        <v>83.90349999999999</v>
+        <v>19.6174</v>
       </c>
       <c r="G118" t="n">
-        <v>4149029</v>
+        <v>1787142.1</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4262,12 +4266,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4276,13 +4280,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>24750</v>
+        <v>130900</v>
       </c>
       <c r="F119" t="n">
-        <v>23.3799</v>
+        <v>89.1437</v>
       </c>
       <c r="G119" t="n">
-        <v>578652.6</v>
+        <v>11668905.3</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4294,12 +4298,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4308,194 +4312,192 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5450</v>
+        <v>2400</v>
       </c>
       <c r="F120" t="n">
-        <v>220.6267</v>
+        <v>32820.1843</v>
       </c>
       <c r="G120" t="n">
-        <v>1202415.4</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>327000</v>
+        <v>41150</v>
       </c>
       <c r="F121" t="n">
-        <v>54</v>
+        <v>38.7861</v>
       </c>
       <c r="G121" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>1596047.4</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5130</v>
+        <v>49450</v>
       </c>
       <c r="F122" t="n">
-        <v>4001.7913</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>20529189.5</v>
+        <v>4149029</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>27100</v>
+        <v>24750</v>
       </c>
       <c r="F123" t="n">
-        <v>376</v>
+        <v>23.3799</v>
       </c>
       <c r="G123" t="n">
-        <v>10189600</v>
+        <v>578652.6</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>67600</v>
+        <v>5450</v>
       </c>
       <c r="F124" t="n">
-        <v>998</v>
+        <v>220.6267</v>
       </c>
       <c r="G124" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H124" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>1202415.4</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>11900</v>
+        <v>327000</v>
       </c>
       <c r="F125" t="n">
-        <v>856</v>
+        <v>54</v>
       </c>
       <c r="G125" t="n">
-        <v>10186400</v>
-      </c>
-      <c r="H125" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4504,13 +4506,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>29300</v>
+        <v>5130</v>
       </c>
       <c r="F126" t="n">
-        <v>2434</v>
+        <v>4001.7913</v>
       </c>
       <c r="G126" t="n">
-        <v>71316200</v>
+        <v>20529189.5</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4522,27 +4524,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>119300</v>
+        <v>27100</v>
       </c>
       <c r="F127" t="n">
-        <v>171</v>
+        <v>376</v>
       </c>
       <c r="G127" t="n">
-        <v>20400300</v>
+        <v>10189600</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -4554,76 +4556,78 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2445</v>
+        <v>67600</v>
       </c>
       <c r="F128" t="n">
-        <v>82456</v>
+        <v>998</v>
       </c>
       <c r="G128" t="n">
-        <v>201604920</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>18910</v>
+        <v>11900</v>
       </c>
       <c r="F129" t="n">
-        <v>1068.0212</v>
+        <v>856</v>
       </c>
       <c r="G129" t="n">
-        <v>20196280</v>
+        <v>10186400</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4632,130 +4636,126 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>32250</v>
+        <v>29300</v>
       </c>
       <c r="F130" t="n">
-        <v>626</v>
+        <v>2434</v>
       </c>
       <c r="G130" t="n">
-        <v>20188500</v>
+        <v>71316200</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>82500</v>
+        <v>119300</v>
       </c>
       <c r="F131" t="n">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="G131" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>20400300</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>56800</v>
+        <v>2445</v>
       </c>
       <c r="F132" t="n">
-        <v>258</v>
+        <v>82456</v>
       </c>
       <c r="G132" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H132" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>201604920</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>83700</v>
+        <v>18910</v>
       </c>
       <c r="F133" t="n">
-        <v>120</v>
+        <v>1068.0212</v>
       </c>
       <c r="G133" t="n">
-        <v>10044000</v>
+        <v>20196280</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4764,177 +4764,179 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>43650</v>
+        <v>32250</v>
       </c>
       <c r="F134" t="n">
-        <v>462</v>
+        <v>626</v>
       </c>
       <c r="G134" t="n">
-        <v>20166300</v>
+        <v>20188500</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>59700</v>
+        <v>82500</v>
       </c>
       <c r="F135" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="G135" t="n">
-        <v>10089300</v>
-      </c>
-      <c r="H135" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>10930</v>
+        <v>56800</v>
       </c>
       <c r="F136" t="n">
-        <v>1833</v>
+        <v>258</v>
       </c>
       <c r="G136" t="n">
-        <v>20034690</v>
-      </c>
-      <c r="H136" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>19850</v>
+        <v>83700</v>
       </c>
       <c r="F137" t="n">
-        <v>505</v>
+        <v>120</v>
       </c>
       <c r="G137" t="n">
-        <v>10024250</v>
+        <v>10044000</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>26350</v>
+        <v>43650</v>
       </c>
       <c r="F138" t="n">
-        <v>380</v>
+        <v>462</v>
       </c>
       <c r="G138" t="n">
-        <v>10013000</v>
+        <v>20166300</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>23500</v>
+        <v>59700</v>
       </c>
       <c r="F139" t="n">
-        <v>833</v>
+        <v>169</v>
       </c>
       <c r="G139" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10089300</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4944,27 +4946,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>85200</v>
+        <v>10930</v>
       </c>
       <c r="F140" t="n">
-        <v>118</v>
+        <v>1833</v>
       </c>
       <c r="G140" t="n">
-        <v>10053600</v>
+        <v>20034690</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -4976,27 +4978,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>63400</v>
+        <v>19850</v>
       </c>
       <c r="F141" t="n">
-        <v>316</v>
+        <v>505</v>
       </c>
       <c r="G141" t="n">
-        <v>20034400</v>
+        <v>10024250</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -5008,27 +5010,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>110300</v>
+        <v>26350</v>
       </c>
       <c r="F142" t="n">
-        <v>91</v>
+        <v>380</v>
       </c>
       <c r="G142" t="n">
-        <v>10037300</v>
+        <v>10013000</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -5040,76 +5042,78 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>66100</v>
+        <v>23500</v>
       </c>
       <c r="F143" t="n">
-        <v>152</v>
+        <v>833</v>
       </c>
       <c r="G143" t="n">
-        <v>10047200</v>
-      </c>
-      <c r="H143" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>25800</v>
+        <v>85200</v>
       </c>
       <c r="F144" t="n">
-        <v>2713</v>
+        <v>118</v>
       </c>
       <c r="G144" t="n">
-        <v>69995400</v>
+        <v>10053600</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5118,77 +5122,77 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>206500</v>
+        <v>63400</v>
       </c>
       <c r="F145" t="n">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="G145" t="n">
-        <v>69797000</v>
+        <v>20034400</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>70100</v>
+        <v>110300</v>
       </c>
       <c r="F146" t="n">
-        <v>998</v>
+        <v>91</v>
       </c>
       <c r="G146" t="n">
-        <v>69959800</v>
+        <v>10037300</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>93300</v>
+        <v>66100</v>
       </c>
       <c r="F147" t="n">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="G147" t="n">
-        <v>19966200</v>
+        <v>10047200</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -5200,12 +5204,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5214,13 +5218,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>11300</v>
+        <v>25800</v>
       </c>
       <c r="F148" t="n">
-        <v>4424</v>
+        <v>2713</v>
       </c>
       <c r="G148" t="n">
-        <v>49991200</v>
+        <v>69995400</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -5232,12 +5236,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5246,13 +5250,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>19740</v>
+        <v>206500</v>
       </c>
       <c r="F149" t="n">
-        <v>2532</v>
+        <v>338</v>
       </c>
       <c r="G149" t="n">
-        <v>49981680</v>
+        <v>69797000</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5264,12 +5268,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5278,13 +5282,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>25150</v>
+        <v>70100</v>
       </c>
       <c r="F150" t="n">
-        <v>2385</v>
+        <v>998</v>
       </c>
       <c r="G150" t="n">
-        <v>59982750</v>
+        <v>69959800</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5296,12 +5300,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5310,13 +5314,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>22050</v>
+        <v>93300</v>
       </c>
       <c r="F151" t="n">
-        <v>2267</v>
+        <v>214</v>
       </c>
       <c r="G151" t="n">
-        <v>49987350</v>
+        <v>19966200</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5328,12 +5332,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5342,13 +5346,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>43150</v>
+        <v>11300</v>
       </c>
       <c r="F152" t="n">
-        <v>1390</v>
+        <v>4424</v>
       </c>
       <c r="G152" t="n">
-        <v>59978500</v>
+        <v>49991200</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5360,12 +5364,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5374,13 +5378,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>310000</v>
+        <v>19740</v>
       </c>
       <c r="F153" t="n">
-        <v>225</v>
+        <v>2532</v>
       </c>
       <c r="G153" t="n">
-        <v>69750000</v>
+        <v>49981680</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5392,12 +5396,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5406,13 +5410,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6240</v>
+        <v>25150</v>
       </c>
       <c r="F154" t="n">
-        <v>3205</v>
+        <v>2385</v>
       </c>
       <c r="G154" t="n">
-        <v>19999200</v>
+        <v>59982750</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5424,12 +5428,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5438,13 +5442,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>24000</v>
+        <v>22050</v>
       </c>
       <c r="F155" t="n">
-        <v>833</v>
+        <v>2267</v>
       </c>
       <c r="G155" t="n">
-        <v>19992000</v>
+        <v>49987350</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5456,12 +5460,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5470,13 +5474,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>90300</v>
+        <v>43150</v>
       </c>
       <c r="F156" t="n">
-        <v>442</v>
+        <v>1390</v>
       </c>
       <c r="G156" t="n">
-        <v>39912600</v>
+        <v>59978500</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5488,12 +5492,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5502,13 +5506,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>279500</v>
+        <v>310000</v>
       </c>
       <c r="F157" t="n">
-        <v>357</v>
+        <v>225</v>
       </c>
       <c r="G157" t="n">
-        <v>99781500</v>
+        <v>69750000</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5520,12 +5524,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5534,13 +5538,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>366000</v>
+        <v>6240</v>
       </c>
       <c r="F158" t="n">
-        <v>54</v>
+        <v>3205</v>
       </c>
       <c r="G158" t="n">
-        <v>19764000</v>
+        <v>19999200</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5552,12 +5556,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5566,13 +5570,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>91000</v>
+        <v>24000</v>
       </c>
       <c r="F159" t="n">
-        <v>659</v>
+        <v>833</v>
       </c>
       <c r="G159" t="n">
-        <v>59969000</v>
+        <v>19992000</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5584,12 +5588,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5598,13 +5602,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>120100</v>
+        <v>90300</v>
       </c>
       <c r="F160" t="n">
-        <v>666</v>
+        <v>442</v>
       </c>
       <c r="G160" t="n">
-        <v>79986600</v>
+        <v>39912600</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5616,12 +5620,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5630,13 +5634,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2405</v>
+        <v>279500</v>
       </c>
       <c r="F161" t="n">
-        <v>415800</v>
+        <v>357</v>
       </c>
       <c r="G161" t="n">
-        <v>999999000</v>
+        <v>99781500</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5648,12 +5652,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5662,13 +5666,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>69000</v>
+        <v>366000</v>
       </c>
       <c r="F162" t="n">
-        <v>579</v>
+        <v>54</v>
       </c>
       <c r="G162" t="n">
-        <v>39951000</v>
+        <v>19764000</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5680,12 +5684,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5694,13 +5698,13 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>42300</v>
+        <v>91000</v>
       </c>
       <c r="F163" t="n">
-        <v>709</v>
+        <v>659</v>
       </c>
       <c r="G163" t="n">
-        <v>29990700</v>
+        <v>59969000</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -5712,29 +5716,157 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>120100</v>
+      </c>
+      <c r="F164" t="n">
+        <v>666</v>
+      </c>
+      <c r="G164" t="n">
+        <v>79986600</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>KODEX 코스닥150선물인버스</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>251340</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F165" t="n">
+        <v>415800</v>
+      </c>
+      <c r="G165" t="n">
+        <v>999999000</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F166" t="n">
+        <v>579</v>
+      </c>
+      <c r="G166" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F167" t="n">
+        <v>709</v>
+      </c>
+      <c r="G167" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E164" t="n">
+      <c r="E168" t="n">
         <v>23350</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F168" t="n">
         <v>856</v>
       </c>
-      <c r="G164" t="n">
+      <c r="G168" t="n">
         <v>19987600</v>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,64 +473,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24200</v>
+        <v>2570</v>
       </c>
       <c r="F2" t="n">
-        <v>422.9059</v>
+        <v>45324.7565</v>
       </c>
       <c r="G2" t="n">
-        <v>10234323</v>
+        <v>116484624.2</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4005</v>
+        <v>25300</v>
       </c>
       <c r="F3" t="n">
-        <v>5110.773</v>
+        <v>812.8404</v>
       </c>
       <c r="G3" t="n">
-        <v>20468646</v>
+        <v>20564861.1</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,31 +542,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35050</v>
+        <v>24200</v>
       </c>
       <c r="F4" t="n">
-        <v>411.8056</v>
+        <v>422.9059</v>
       </c>
       <c r="G4" t="n">
-        <v>14433786.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-17.14</v>
-      </c>
+        <v>10234323</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,95 +574,97 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39450</v>
+        <v>4005</v>
       </c>
       <c r="F5" t="n">
-        <v>470.9867</v>
+        <v>5110.773</v>
       </c>
       <c r="G5" t="n">
-        <v>18580423.4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-7.18</v>
-      </c>
+        <v>20468646</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33300</v>
+        <v>35050</v>
       </c>
       <c r="F6" t="n">
-        <v>296.1438</v>
+        <v>411.8056</v>
       </c>
       <c r="G6" t="n">
-        <v>9861590.1</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>14433786.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-17.14</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9540</v>
+        <v>39450</v>
       </c>
       <c r="F7" t="n">
-        <v>1033.7097</v>
+        <v>470.9867</v>
       </c>
       <c r="G7" t="n">
-        <v>9861590.1</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>18580423.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-7.18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>58500</v>
+        <v>33300</v>
       </c>
       <c r="F8" t="n">
-        <v>168.5742</v>
+        <v>296.1438</v>
       </c>
       <c r="G8" t="n">
         <v>9861590.1</v>
@@ -701,64 +701,64 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23850</v>
+        <v>9540</v>
       </c>
       <c r="F9" t="n">
-        <v>433.5542</v>
+        <v>1033.7097</v>
       </c>
       <c r="G9" t="n">
-        <v>10340268.5</v>
+        <v>9861590.1</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>45450</v>
+        <v>58500</v>
       </c>
       <c r="F10" t="n">
-        <v>227.5087</v>
+        <v>168.5742</v>
       </c>
       <c r="G10" t="n">
-        <v>10340268.5</v>
+        <v>9861590.1</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,31 +770,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15230</v>
+        <v>23850</v>
       </c>
       <c r="F11" t="n">
-        <v>1186.9772</v>
+        <v>433.5542</v>
       </c>
       <c r="G11" t="n">
-        <v>18077663</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-5.87</v>
-      </c>
+        <v>10340268.5</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -804,12 +802,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -818,13 +816,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2655</v>
+        <v>45450</v>
       </c>
       <c r="F12" t="n">
-        <v>76798.0178</v>
+        <v>227.5087</v>
       </c>
       <c r="G12" t="n">
-        <v>203898737.2</v>
+        <v>10340268.5</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -836,29 +834,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30249.84</v>
+        <v>15230</v>
       </c>
       <c r="F13" t="n">
-        <v>341.8289</v>
+        <v>1186.9772</v>
       </c>
       <c r="G13" t="n">
-        <v>10340268.5</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>18077663</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-5.87</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25550</v>
+        <v>2655</v>
       </c>
       <c r="F14" t="n">
-        <v>404.7072</v>
+        <v>76798.0178</v>
       </c>
       <c r="G14" t="n">
-        <v>10340268.5</v>
+        <v>203898737.2</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>59900</v>
+        <v>30249.84</v>
       </c>
       <c r="F15" t="n">
-        <v>172.6255</v>
+        <v>341.8289</v>
       </c>
       <c r="G15" t="n">
         <v>10340268.5</v>
@@ -927,17 +927,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -946,49 +946,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>41050</v>
+        <v>25550</v>
       </c>
       <c r="F16" t="n">
-        <v>490.4266</v>
+        <v>404.7072</v>
       </c>
       <c r="G16" t="n">
-        <v>20132010.4</v>
+        <v>10340268.5</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230000</v>
+        <v>59900</v>
       </c>
       <c r="F17" t="n">
-        <v>135.183</v>
+        <v>172.6255</v>
       </c>
       <c r="G17" t="n">
-        <v>31092084.3</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-16.92</v>
-      </c>
+        <v>10340268.5</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -998,27 +996,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2595</v>
+        <v>41050</v>
       </c>
       <c r="F18" t="n">
-        <v>42895.584</v>
+        <v>490.4266</v>
       </c>
       <c r="G18" t="n">
-        <v>111314040.6</v>
+        <v>20132010.4</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1030,29 +1028,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15870</v>
+        <v>230000</v>
       </c>
       <c r="F19" t="n">
-        <v>634.2788</v>
+        <v>135.183</v>
       </c>
       <c r="G19" t="n">
-        <v>10066005.2</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>31092084.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-16.92</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1062,27 +1062,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>29646.86</v>
+        <v>2595</v>
       </c>
       <c r="F20" t="n">
-        <v>339.5302</v>
+        <v>42895.584</v>
       </c>
       <c r="G20" t="n">
-        <v>10066005.2</v>
+        <v>111314040.6</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1094,24 +1094,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9960</v>
+        <v>15870</v>
       </c>
       <c r="F21" t="n">
-        <v>1010.6431</v>
+        <v>634.2788</v>
       </c>
       <c r="G21" t="n">
         <v>10066005.2</v>
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>59100</v>
+        <v>29646.86</v>
       </c>
       <c r="F22" t="n">
-        <v>681.2863</v>
+        <v>339.5302</v>
       </c>
       <c r="G22" t="n">
-        <v>40264020.8</v>
+        <v>10066005.2</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3385</v>
+        <v>9960</v>
       </c>
       <c r="F23" t="n">
-        <v>2973.7091</v>
+        <v>1010.6431</v>
       </c>
       <c r="G23" t="n">
         <v>10066005.2</v>
@@ -1185,49 +1185,49 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>26200</v>
+        <v>59100</v>
       </c>
       <c r="F24" t="n">
-        <v>382.0025</v>
+        <v>681.2863</v>
       </c>
       <c r="G24" t="n">
-        <v>10008466.3</v>
+        <v>40264020.8</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>94700</v>
+        <v>3385</v>
       </c>
       <c r="F25" t="n">
-        <v>105.686</v>
+        <v>2973.7091</v>
       </c>
       <c r="G25" t="n">
-        <v>10008466.3</v>
+        <v>10066005.2</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1254,91 +1254,91 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>42500</v>
+        <v>26200</v>
       </c>
       <c r="F26" t="n">
-        <v>470.9867</v>
+        <v>382.0025</v>
       </c>
       <c r="G26" t="n">
-        <v>20016932.7</v>
+        <v>10008466.3</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>26600</v>
+        <v>94700</v>
       </c>
       <c r="F27" t="n">
-        <v>361.0017</v>
+        <v>105.686</v>
       </c>
       <c r="G27" t="n">
-        <v>9602645.699999999</v>
+        <v>10008466.3</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10740</v>
+        <v>42500</v>
       </c>
       <c r="F28" t="n">
-        <v>894.1011</v>
+        <v>470.9867</v>
       </c>
       <c r="G28" t="n">
-        <v>9602645.699999999</v>
+        <v>20016932.7</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1350,27 +1350,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>16180</v>
+        <v>26600</v>
       </c>
       <c r="F29" t="n">
-        <v>1186.9772</v>
+        <v>361.0017</v>
       </c>
       <c r="G29" t="n">
-        <v>19205291.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1382,27 +1382,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>88400</v>
+        <v>10740</v>
       </c>
       <c r="F30" t="n">
-        <v>217.2544</v>
+        <v>894.1011</v>
       </c>
       <c r="G30" t="n">
-        <v>19205291.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,27 +1414,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>99100</v>
+        <v>16180</v>
       </c>
       <c r="F31" t="n">
-        <v>290.6956</v>
+        <v>1186.9772</v>
       </c>
       <c r="G31" t="n">
-        <v>28807937.1</v>
+        <v>19205291.4</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,31 +1446,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37350</v>
+        <v>88400</v>
       </c>
       <c r="F32" t="n">
-        <v>491.1229</v>
+        <v>217.2544</v>
       </c>
       <c r="G32" t="n">
-        <v>18343440.7</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-9.23</v>
-      </c>
+        <v>19205291.4</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1480,27 +1478,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2520</v>
+        <v>99100</v>
       </c>
       <c r="F33" t="n">
-        <v>33368.1327</v>
+        <v>290.6956</v>
       </c>
       <c r="G33" t="n">
-        <v>84087694.5</v>
+        <v>28807937.1</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,12 +1510,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1526,16 +1524,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>16500</v>
+        <v>37350</v>
       </c>
       <c r="F34" t="n">
-        <v>856.421</v>
+        <v>491.1229</v>
       </c>
       <c r="G34" t="n">
-        <v>14130946.6</v>
+        <v>18343440.7</v>
       </c>
       <c r="H34" t="n">
-        <v>-22.8</v>
+        <v>-9.23</v>
       </c>
     </row>
     <row r="35">
@@ -1546,27 +1544,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>27650</v>
+        <v>2520</v>
       </c>
       <c r="F35" t="n">
-        <v>1041.8784</v>
+        <v>33368.1327</v>
       </c>
       <c r="G35" t="n">
-        <v>28807937.1</v>
+        <v>84087694.5</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1578,91 +1576,93 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9350</v>
+        <v>16500</v>
       </c>
       <c r="F36" t="n">
-        <v>1027.0209</v>
+        <v>856.421</v>
       </c>
       <c r="G36" t="n">
-        <v>9602645.699999999</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>14130946.6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-22.8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>28650</v>
+        <v>27650</v>
       </c>
       <c r="F37" t="n">
-        <v>345.7839</v>
+        <v>1041.8784</v>
       </c>
       <c r="G37" t="n">
-        <v>9906708.4</v>
+        <v>28807937.1</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11600</v>
+        <v>9350</v>
       </c>
       <c r="F38" t="n">
-        <v>854.0266</v>
+        <v>1027.0209</v>
       </c>
       <c r="G38" t="n">
-        <v>9906708.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1674,24 +1674,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>131000</v>
+        <v>28650</v>
       </c>
       <c r="F39" t="n">
-        <v>75.6237</v>
+        <v>345.7839</v>
       </c>
       <c r="G39" t="n">
         <v>9906708.4</v>
@@ -1706,24 +1706,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>33717.02</v>
+        <v>11600</v>
       </c>
       <c r="F40" t="n">
-        <v>293.8192</v>
+        <v>854.0266</v>
       </c>
       <c r="G40" t="n">
         <v>9906708.4</v>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4830</v>
+        <v>131000</v>
       </c>
       <c r="F41" t="n">
-        <v>2051.0783</v>
+        <v>75.6237</v>
       </c>
       <c r="G41" t="n">
         <v>9906708.4</v>
@@ -1770,93 +1770,91 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>9430</v>
+        <v>33717.02</v>
       </c>
       <c r="F42" t="n">
-        <v>2101.1046</v>
+        <v>293.8192</v>
       </c>
       <c r="G42" t="n">
-        <v>19813416.7</v>
+        <v>9906708.4</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>79100</v>
+        <v>4830</v>
       </c>
       <c r="F43" t="n">
-        <v>205.0482</v>
+        <v>2051.0783</v>
       </c>
       <c r="G43" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25250</v>
+        <v>9430</v>
       </c>
       <c r="F44" t="n">
-        <v>768.6917999999999</v>
+        <v>2101.1046</v>
       </c>
       <c r="G44" t="n">
-        <v>19409469.1</v>
+        <v>19813416.7</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1868,12 +1866,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1882,16 +1880,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12510</v>
+        <v>79100</v>
       </c>
       <c r="F45" t="n">
-        <v>1443.4887</v>
+        <v>205.0482</v>
       </c>
       <c r="G45" t="n">
-        <v>18058043.3</v>
+        <v>16219315.2</v>
       </c>
       <c r="H45" t="n">
-        <v>-11.28</v>
+        <v>-15.22</v>
       </c>
     </row>
     <row r="46">
@@ -1902,27 +1900,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>126500</v>
+        <v>25250</v>
       </c>
       <c r="F46" t="n">
-        <v>383.5863</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>48523672.7</v>
+        <v>19409469.1</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1934,29 +1932,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2485</v>
+        <v>12510</v>
       </c>
       <c r="F47" t="n">
-        <v>42403.6617</v>
+        <v>1443.4887</v>
       </c>
       <c r="G47" t="n">
-        <v>105373099.3</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>18058043.3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-11.28</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1966,27 +1966,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>45500</v>
+        <v>126500</v>
       </c>
       <c r="F48" t="n">
-        <v>213.2909</v>
+        <v>383.5863</v>
       </c>
       <c r="G48" t="n">
-        <v>9704734.5</v>
+        <v>48523672.7</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>17880</v>
+        <v>2485</v>
       </c>
       <c r="F49" t="n">
-        <v>1085.5408</v>
+        <v>42403.6617</v>
       </c>
       <c r="G49" t="n">
-        <v>19409469.1</v>
+        <v>105373099.3</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2030,31 +2030,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4460</v>
+        <v>45500</v>
       </c>
       <c r="F50" t="n">
-        <v>3137.3165</v>
+        <v>213.2909</v>
       </c>
       <c r="G50" t="n">
-        <v>13992431.8</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-17.83</v>
-      </c>
+        <v>9704734.5</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2064,95 +2062,95 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3345</v>
+        <v>17880</v>
       </c>
       <c r="F51" t="n">
-        <v>11605.0637</v>
+        <v>1085.5408</v>
       </c>
       <c r="G51" t="n">
-        <v>38818938.1</v>
+        <v>19409469.1</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>12120</v>
+        <v>4460</v>
       </c>
       <c r="F52" t="n">
-        <v>820.878</v>
+        <v>3137.3165</v>
       </c>
       <c r="G52" t="n">
-        <v>9949041.199999999</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>13992431.8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-17.83</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>248000</v>
+        <v>3345</v>
       </c>
       <c r="F53" t="n">
-        <v>81.12909999999999</v>
+        <v>11605.0637</v>
       </c>
       <c r="G53" t="n">
-        <v>20120019.7</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-19.98</v>
-      </c>
+        <v>38818938.1</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2162,12 +2160,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2176,13 +2174,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222500</v>
+        <v>12120</v>
       </c>
       <c r="F54" t="n">
-        <v>178.8592</v>
+        <v>820.878</v>
       </c>
       <c r="G54" t="n">
-        <v>39796164.7</v>
+        <v>9949041.199999999</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2194,12 +2192,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2208,32 +2206,32 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>54500</v>
+        <v>248000</v>
       </c>
       <c r="F55" t="n">
-        <v>504.0447</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>27470436.6</v>
+        <v>20120019.7</v>
       </c>
       <c r="H55" t="n">
-        <v>24.43</v>
+        <v>-19.98</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2242,47 +2240,49 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>32350</v>
+        <v>222500</v>
       </c>
       <c r="F56" t="n">
-        <v>314.5779</v>
+        <v>178.8592</v>
       </c>
       <c r="G56" t="n">
-        <v>10176595.1</v>
+        <v>39796164.7</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>13650</v>
+        <v>54500</v>
       </c>
       <c r="F57" t="n">
-        <v>745.5381</v>
+        <v>504.0447</v>
       </c>
       <c r="G57" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>31950</v>
+        <v>32350</v>
       </c>
       <c r="F58" t="n">
-        <v>318.5163</v>
+        <v>314.5779</v>
       </c>
       <c r="G58" t="n">
         <v>10176595.1</v>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>250500</v>
+        <v>13650</v>
       </c>
       <c r="F59" t="n">
-        <v>81.2503</v>
+        <v>745.5381</v>
       </c>
       <c r="G59" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2356,27 +2356,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>14100</v>
+        <v>31950</v>
       </c>
       <c r="F60" t="n">
-        <v>1443.4887</v>
+        <v>318.5163</v>
       </c>
       <c r="G60" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2388,31 +2388,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>31300</v>
+        <v>250500</v>
       </c>
       <c r="F61" t="n">
-        <v>1954.4702</v>
+        <v>81.2503</v>
       </c>
       <c r="G61" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H61" t="n">
-        <v>6.83</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2422,27 +2420,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2355</v>
+        <v>14100</v>
       </c>
       <c r="F62" t="n">
-        <v>65496.7248</v>
+        <v>1443.4887</v>
       </c>
       <c r="G62" t="n">
-        <v>154244786.8</v>
+        <v>20353190.3</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2454,29 +2452,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>15810</v>
+        <v>31300</v>
       </c>
       <c r="F63" t="n">
-        <v>5149.4473</v>
+        <v>1954.4702</v>
       </c>
       <c r="G63" t="n">
-        <v>81412761.09999999</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H63" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2486,27 +2486,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>28491.13</v>
+        <v>2355</v>
       </c>
       <c r="F64" t="n">
-        <v>357.1847</v>
+        <v>65496.7248</v>
       </c>
       <c r="G64" t="n">
-        <v>10176595.1</v>
+        <v>154244786.8</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2518,95 +2518,93 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4660</v>
+        <v>15810</v>
       </c>
       <c r="F65" t="n">
-        <v>4367.6374</v>
+        <v>5149.4473</v>
       </c>
       <c r="G65" t="n">
-        <v>20353190.3</v>
+        <v>81412761.09999999</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>44600</v>
+        <v>28491.13</v>
       </c>
       <c r="F66" t="n">
-        <v>1359.3974</v>
+        <v>357.1847</v>
       </c>
       <c r="G66" t="n">
-        <v>60629123.5</v>
+        <v>10176595.1</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>20300</v>
+        <v>4660</v>
       </c>
       <c r="F67" t="n">
-        <v>1162.9429</v>
+        <v>4367.6374</v>
       </c>
       <c r="G67" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H67" t="n">
-        <v>7.9</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2616,27 +2614,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>13160</v>
+        <v>44600</v>
       </c>
       <c r="F68" t="n">
-        <v>767.846</v>
+        <v>1359.3974</v>
       </c>
       <c r="G68" t="n">
-        <v>10104853.9</v>
+        <v>60629123.5</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2648,12 +2646,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2662,16 +2660,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>49050</v>
+        <v>20300</v>
       </c>
       <c r="F69" t="n">
-        <v>357.1039</v>
+        <v>1162.9429</v>
       </c>
       <c r="G69" t="n">
-        <v>17515946</v>
+        <v>23607739.9</v>
       </c>
       <c r="H69" t="n">
-        <v>-16.44</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="70">
@@ -2682,31 +2680,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>37100</v>
+        <v>13160</v>
       </c>
       <c r="F70" t="n">
-        <v>604.321</v>
+        <v>767.846</v>
       </c>
       <c r="G70" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H70" t="n">
-        <v>15.04</v>
-      </c>
+        <v>10104853.9</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2716,29 +2712,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>123700</v>
+        <v>49050</v>
       </c>
       <c r="F71" t="n">
-        <v>490.1303</v>
+        <v>357.1039</v>
       </c>
       <c r="G71" t="n">
-        <v>60629123.5</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>17515946</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2748,29 +2746,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>41150</v>
+        <v>37100</v>
       </c>
       <c r="F72" t="n">
-        <v>491.1229</v>
+        <v>604.321</v>
       </c>
       <c r="G72" t="n">
-        <v>20209707.8</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>22420310.5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>15.04</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2780,27 +2780,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>31500</v>
+        <v>123700</v>
       </c>
       <c r="F73" t="n">
-        <v>320.789</v>
+        <v>490.1303</v>
       </c>
       <c r="G73" t="n">
-        <v>10104853.9</v>
+        <v>60629123.5</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2812,24 +2812,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228500</v>
+        <v>41150</v>
       </c>
       <c r="F74" t="n">
-        <v>88.4451</v>
+        <v>491.1229</v>
       </c>
       <c r="G74" t="n">
         <v>20209707.8</v>
@@ -2844,31 +2844,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>88500</v>
+        <v>31500</v>
       </c>
       <c r="F75" t="n">
-        <v>900.2261</v>
+        <v>320.789</v>
       </c>
       <c r="G75" t="n">
-        <v>79670012.59999999</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-3.84</v>
-      </c>
+        <v>10104853.9</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2878,31 +2876,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>130100</v>
+        <v>228500</v>
       </c>
       <c r="F76" t="n">
-        <v>314.8563</v>
+        <v>88.4451</v>
       </c>
       <c r="G76" t="n">
-        <v>40962809.6</v>
-      </c>
-      <c r="H76" t="n">
-        <v>8.33</v>
-      </c>
+        <v>20209707.8</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2912,29 +2908,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2325</v>
+        <v>88500</v>
       </c>
       <c r="F77" t="n">
-        <v>21730.8686</v>
+        <v>900.2261</v>
       </c>
       <c r="G77" t="n">
-        <v>50524269.6</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
+        <v>79670012.59999999</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-3.84</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2944,29 +2942,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>32511.04</v>
+        <v>130100</v>
       </c>
       <c r="F78" t="n">
-        <v>932.439</v>
+        <v>314.8563</v>
       </c>
       <c r="G78" t="n">
-        <v>30314561.7</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>40962809.6</v>
+      </c>
+      <c r="H78" t="n">
+        <v>8.33</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2976,108 +2976,108 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4670</v>
+        <v>2325</v>
       </c>
       <c r="F79" t="n">
-        <v>6491.3408</v>
+        <v>21730.8686</v>
       </c>
       <c r="G79" t="n">
-        <v>30314561.7</v>
+        <v>50524269.6</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2120</v>
+        <v>32511.04</v>
       </c>
       <c r="F80" t="n">
-        <v>63879.7502</v>
+        <v>932.439</v>
       </c>
       <c r="G80" t="n">
-        <v>135425070.4</v>
+        <v>30314561.7</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2120</v>
+        <v>4670</v>
       </c>
       <c r="F81" t="n">
-        <v>3453.9051</v>
+        <v>6491.3408</v>
       </c>
       <c r="G81" t="n">
-        <v>7322278.8</v>
+        <v>30314561.7</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3086,49 +3086,47 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>22900</v>
+        <v>2120</v>
       </c>
       <c r="F82" t="n">
-        <v>1397.6406</v>
+        <v>63879.7502</v>
       </c>
       <c r="G82" t="n">
-        <v>32005969</v>
+        <v>135425070.4</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>73600</v>
+        <v>2120</v>
       </c>
       <c r="F83" t="n">
-        <v>299.9614</v>
+        <v>3453.9051</v>
       </c>
       <c r="G83" t="n">
-        <v>22077158.2</v>
-      </c>
-      <c r="H83" t="n">
-        <v>16.09</v>
-      </c>
+        <v>7322278.8</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3138,27 +3136,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2215</v>
+        <v>22900</v>
       </c>
       <c r="F84" t="n">
-        <v>28224.978</v>
+        <v>1397.6406</v>
       </c>
       <c r="G84" t="n">
-        <v>62518326.2</v>
+        <v>32005969</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3170,29 +3168,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>43800</v>
+        <v>73600</v>
       </c>
       <c r="F85" t="n">
-        <v>504.0447</v>
+        <v>299.9614</v>
       </c>
       <c r="G85" t="n">
         <v>22077158.2</v>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>16.09</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>23650</v>
+        <v>2215</v>
       </c>
       <c r="F86" t="n">
-        <v>451.106</v>
+        <v>28224.978</v>
       </c>
       <c r="G86" t="n">
-        <v>10668656.3</v>
+        <v>62518326.2</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3234,78 +3234,76 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5730</v>
+        <v>43800</v>
       </c>
       <c r="F87" t="n">
-        <v>3723.7893</v>
+        <v>504.0447</v>
       </c>
       <c r="G87" t="n">
-        <v>21337312.7</v>
+        <v>22077158.2</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6080</v>
+        <v>23650</v>
       </c>
       <c r="F88" t="n">
-        <v>3255.5051</v>
+        <v>451.106</v>
       </c>
       <c r="G88" t="n">
-        <v>19793471.1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-2.59</v>
-      </c>
+        <v>10668656.3</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3314,13 +3312,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>95200</v>
+        <v>5730</v>
       </c>
       <c r="F89" t="n">
-        <v>221.6088</v>
+        <v>3723.7893</v>
       </c>
       <c r="G89" t="n">
-        <v>21097154.4</v>
+        <v>21337312.7</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3332,91 +3330,93 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2205</v>
+        <v>6080</v>
       </c>
       <c r="F90" t="n">
-        <v>52623.2877</v>
+        <v>3255.5051</v>
       </c>
       <c r="G90" t="n">
-        <v>116034349.3</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
+        <v>19793471.1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-2.59</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>58700</v>
+        <v>95200</v>
       </c>
       <c r="F91" t="n">
-        <v>357.1039</v>
+        <v>221.6088</v>
       </c>
       <c r="G91" t="n">
-        <v>20961998.6</v>
+        <v>21097154.4</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>13250</v>
+        <v>2205</v>
       </c>
       <c r="F92" t="n">
-        <v>791.0188000000001</v>
+        <v>52623.2877</v>
       </c>
       <c r="G92" t="n">
-        <v>10480999.3</v>
+        <v>116034349.3</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3428,27 +3428,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2360</v>
+        <v>58700</v>
       </c>
       <c r="F93" t="n">
-        <v>66616.5209</v>
+        <v>357.1039</v>
       </c>
       <c r="G93" t="n">
-        <v>157214989.3</v>
+        <v>20961998.6</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3460,31 +3460,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>38300</v>
+        <v>13250</v>
       </c>
       <c r="F94" t="n">
-        <v>500.7861</v>
+        <v>791.0188000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>19180107.1</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-11.87</v>
-      </c>
+        <v>10480999.3</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3494,12 +3492,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3508,13 +3506,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>21150</v>
+        <v>2360</v>
       </c>
       <c r="F95" t="n">
-        <v>495.5555</v>
+        <v>66616.5209</v>
       </c>
       <c r="G95" t="n">
-        <v>10480999.3</v>
+        <v>157214989.3</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3526,12 +3524,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3540,32 +3538,32 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>23650</v>
+        <v>38300</v>
       </c>
       <c r="F96" t="n">
-        <v>832.6201</v>
+        <v>500.7861</v>
       </c>
       <c r="G96" t="n">
-        <v>19691465.3</v>
+        <v>19180107.1</v>
       </c>
       <c r="H96" t="n">
-        <v>1.28</v>
+        <v>-11.87</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3574,47 +3572,49 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>12310</v>
+        <v>21150</v>
       </c>
       <c r="F97" t="n">
-        <v>2480.1654</v>
+        <v>495.5555</v>
       </c>
       <c r="G97" t="n">
-        <v>30530836.4</v>
+        <v>10480999.3</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>40650</v>
+        <v>23650</v>
       </c>
       <c r="F98" t="n">
-        <v>751.0661</v>
+        <v>832.6201</v>
       </c>
       <c r="G98" t="n">
-        <v>30530836.4</v>
-      </c>
-      <c r="H98" t="inlineStr"/>
+        <v>19691465.3</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1.28</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3624,27 +3624,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>283500</v>
+        <v>12310</v>
       </c>
       <c r="F99" t="n">
-        <v>71.795</v>
+        <v>2480.1654</v>
       </c>
       <c r="G99" t="n">
-        <v>20353890.9</v>
+        <v>30530836.4</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3656,27 +3656,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2390</v>
+        <v>40650</v>
       </c>
       <c r="F100" t="n">
-        <v>42581.3618</v>
+        <v>751.0661</v>
       </c>
       <c r="G100" t="n">
-        <v>101769454.6</v>
+        <v>30530836.4</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3688,24 +3688,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>20450</v>
+        <v>283500</v>
       </c>
       <c r="F101" t="n">
-        <v>995.3003</v>
+        <v>71.795</v>
       </c>
       <c r="G101" t="n">
         <v>20353890.9</v>
@@ -3715,68 +3715,66 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>30200</v>
+        <v>2390</v>
       </c>
       <c r="F102" t="n">
-        <v>359.55</v>
+        <v>42581.3618</v>
       </c>
       <c r="G102" t="n">
-        <v>10858410.6</v>
+        <v>101769454.6</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>208500</v>
+        <v>20450</v>
       </c>
       <c r="F103" t="n">
-        <v>338</v>
+        <v>995.3003</v>
       </c>
       <c r="G103" t="n">
-        <v>70473000</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0.97</v>
-      </c>
+        <v>20353890.9</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3786,27 +3784,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>17720</v>
+        <v>30200</v>
       </c>
       <c r="F104" t="n">
-        <v>94.9217</v>
+        <v>359.55</v>
       </c>
       <c r="G104" t="n">
-        <v>1682012.5</v>
+        <v>10858410.6</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3818,29 +3816,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100500</v>
+        <v>208500</v>
       </c>
       <c r="F105" t="n">
-        <v>8.9518</v>
+        <v>338</v>
       </c>
       <c r="G105" t="n">
-        <v>899652.6</v>
-      </c>
-      <c r="H105" t="inlineStr"/>
+        <v>70473000</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3850,27 +3850,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>11410</v>
+        <v>17720</v>
       </c>
       <c r="F106" t="n">
-        <v>6321.2722</v>
+        <v>94.9217</v>
       </c>
       <c r="G106" t="n">
-        <v>72125715.8</v>
+        <v>1682012.5</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3896,13 +3896,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>12880</v>
+        <v>100500</v>
       </c>
       <c r="F107" t="n">
-        <v>713.2027</v>
+        <v>8.9518</v>
       </c>
       <c r="G107" t="n">
-        <v>9186050.6</v>
+        <v>899652.6</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3914,27 +3914,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>21200</v>
+        <v>11410</v>
       </c>
       <c r="F108" t="n">
-        <v>120.8659</v>
+        <v>6321.2722</v>
       </c>
       <c r="G108" t="n">
-        <v>2562357.9</v>
+        <v>72125715.8</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3946,12 +3946,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3960,13 +3960,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>27700</v>
+        <v>12880</v>
       </c>
       <c r="F109" t="n">
-        <v>161.1835</v>
+        <v>713.2027</v>
       </c>
       <c r="G109" t="n">
-        <v>4464784.2</v>
+        <v>9186050.6</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3978,27 +3978,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>21500</v>
+        <v>21200</v>
       </c>
       <c r="F110" t="n">
-        <v>129.2032</v>
+        <v>120.8659</v>
       </c>
       <c r="G110" t="n">
-        <v>2777868.4</v>
+        <v>2562357.9</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4024,13 +4024,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>34100</v>
+        <v>27700</v>
       </c>
       <c r="F111" t="n">
-        <v>21.679</v>
+        <v>161.1835</v>
       </c>
       <c r="G111" t="n">
-        <v>739252.6</v>
+        <v>4464784.2</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>40850</v>
+        <v>21500</v>
       </c>
       <c r="F112" t="n">
-        <v>123.3915</v>
+        <v>129.2032</v>
       </c>
       <c r="G112" t="n">
-        <v>5040542.1</v>
+        <v>2777868.4</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4074,27 +4074,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>308000</v>
+        <v>34100</v>
       </c>
       <c r="F113" t="n">
-        <v>9.1744</v>
+        <v>21.679</v>
       </c>
       <c r="G113" t="n">
-        <v>2825715.8</v>
+        <v>739252.6</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4120,13 +4120,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6330</v>
+        <v>40850</v>
       </c>
       <c r="F114" t="n">
-        <v>50.5051</v>
+        <v>123.3915</v>
       </c>
       <c r="G114" t="n">
-        <v>319697.4</v>
+        <v>5040542.1</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4138,27 +4138,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>31700</v>
+        <v>308000</v>
       </c>
       <c r="F115" t="n">
-        <v>158.7408</v>
+        <v>9.1744</v>
       </c>
       <c r="G115" t="n">
-        <v>5032084.2</v>
+        <v>2825715.8</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4170,27 +4170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>68700</v>
+        <v>6330</v>
       </c>
       <c r="F116" t="n">
-        <v>16.0386</v>
+        <v>50.5051</v>
       </c>
       <c r="G116" t="n">
-        <v>1101852.6</v>
+        <v>319697.4</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4202,27 +4202,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>256000</v>
+        <v>31700</v>
       </c>
       <c r="F117" t="n">
-        <v>45.4873</v>
+        <v>158.7408</v>
       </c>
       <c r="G117" t="n">
-        <v>11644736.8</v>
+        <v>5032084.2</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4234,27 +4234,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>91100</v>
+        <v>68700</v>
       </c>
       <c r="F118" t="n">
-        <v>19.6174</v>
+        <v>16.0386</v>
       </c>
       <c r="G118" t="n">
-        <v>1787142.1</v>
+        <v>1101852.6</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4266,27 +4266,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>130900</v>
+        <v>256000</v>
       </c>
       <c r="F119" t="n">
-        <v>89.1437</v>
+        <v>45.4873</v>
       </c>
       <c r="G119" t="n">
-        <v>11668905.3</v>
+        <v>11644736.8</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4298,27 +4298,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2400</v>
+        <v>91100</v>
       </c>
       <c r="F120" t="n">
-        <v>32820.1843</v>
+        <v>19.6174</v>
       </c>
       <c r="G120" t="n">
-        <v>78768442.40000001</v>
+        <v>1787142.1</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4330,27 +4330,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>41150</v>
+        <v>130900</v>
       </c>
       <c r="F121" t="n">
-        <v>38.7861</v>
+        <v>89.1437</v>
       </c>
       <c r="G121" t="n">
-        <v>1596047.4</v>
+        <v>11668905.3</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>49450</v>
+        <v>2400</v>
       </c>
       <c r="F122" t="n">
-        <v>83.90349999999999</v>
+        <v>32820.1843</v>
       </c>
       <c r="G122" t="n">
-        <v>4149029</v>
+        <v>78768442.40000001</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4394,27 +4394,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>범한퓨얼셀</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>382900</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>24750</v>
+        <v>41150</v>
       </c>
       <c r="F123" t="n">
-        <v>23.3799</v>
+        <v>38.7861</v>
       </c>
       <c r="G123" t="n">
-        <v>578652.6</v>
+        <v>1596047.4</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4440,54 +4440,52 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5450</v>
+        <v>49450</v>
       </c>
       <c r="F124" t="n">
-        <v>220.6267</v>
+        <v>83.90349999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>1202415.4</v>
+        <v>4149029</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>범한퓨얼셀</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>382900</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>327000</v>
+        <v>24750</v>
       </c>
       <c r="F125" t="n">
-        <v>54</v>
+        <v>23.3799</v>
       </c>
       <c r="G125" t="n">
-        <v>17658000</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-10.66</v>
-      </c>
+        <v>578652.6</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4502,85 +4500,85 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5130</v>
+        <v>5450</v>
       </c>
       <c r="F126" t="n">
-        <v>4001.7913</v>
+        <v>220.6267</v>
       </c>
       <c r="G126" t="n">
-        <v>20529189.5</v>
+        <v>1202415.4</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>27100</v>
+        <v>327000</v>
       </c>
       <c r="F127" t="n">
-        <v>376</v>
+        <v>54</v>
       </c>
       <c r="G127" t="n">
-        <v>10189600</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
+        <v>17658000</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-10.66</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>67600</v>
+        <v>5130</v>
       </c>
       <c r="F128" t="n">
-        <v>998</v>
+        <v>4001.7913</v>
       </c>
       <c r="G128" t="n">
-        <v>67464800</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-3.57</v>
-      </c>
+        <v>20529189.5</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4590,12 +4588,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4604,13 +4602,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>11900</v>
+        <v>27100</v>
       </c>
       <c r="F129" t="n">
-        <v>856</v>
+        <v>376</v>
       </c>
       <c r="G129" t="n">
-        <v>10186400</v>
+        <v>10189600</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4622,29 +4620,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>29300</v>
+        <v>67600</v>
       </c>
       <c r="F130" t="n">
-        <v>2434</v>
+        <v>998</v>
       </c>
       <c r="G130" t="n">
-        <v>71316200</v>
-      </c>
-      <c r="H130" t="inlineStr"/>
+        <v>67464800</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-3.57</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4654,27 +4654,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>119300</v>
+        <v>11900</v>
       </c>
       <c r="F131" t="n">
-        <v>171</v>
+        <v>856</v>
       </c>
       <c r="G131" t="n">
-        <v>20400300</v>
+        <v>10186400</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4686,91 +4686,91 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2445</v>
+        <v>29300</v>
       </c>
       <c r="F132" t="n">
-        <v>82456</v>
+        <v>2434</v>
       </c>
       <c r="G132" t="n">
-        <v>201604920</v>
+        <v>71316200</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>18910</v>
+        <v>119300</v>
       </c>
       <c r="F133" t="n">
-        <v>1068.0212</v>
+        <v>171</v>
       </c>
       <c r="G133" t="n">
-        <v>20196280</v>
+        <v>20400300</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>32250</v>
+        <v>2445</v>
       </c>
       <c r="F134" t="n">
-        <v>626</v>
+        <v>82456</v>
       </c>
       <c r="G134" t="n">
-        <v>20188500</v>
+        <v>201604920</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -4782,31 +4782,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>82500</v>
+        <v>18910</v>
       </c>
       <c r="F135" t="n">
-        <v>204</v>
+        <v>1068.0212</v>
       </c>
       <c r="G135" t="n">
-        <v>16830000</v>
-      </c>
-      <c r="H135" t="n">
-        <v>-8.640000000000001</v>
-      </c>
+        <v>20196280</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4816,36 +4814,34 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>56800</v>
+        <v>32250</v>
       </c>
       <c r="F136" t="n">
-        <v>258</v>
+        <v>626</v>
       </c>
       <c r="G136" t="n">
-        <v>14654400</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-17.68</v>
-      </c>
+        <v>20188500</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4860,51 +4856,55 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>83700</v>
+        <v>82500</v>
       </c>
       <c r="F137" t="n">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="G137" t="n">
-        <v>10044000</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
+        <v>16830000</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-8.640000000000001</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>43650</v>
+        <v>56800</v>
       </c>
       <c r="F138" t="n">
-        <v>462</v>
+        <v>258</v>
       </c>
       <c r="G138" t="n">
-        <v>20166300</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
+        <v>14654400</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-17.68</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4928,77 +4928,77 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>59700</v>
+        <v>83700</v>
       </c>
       <c r="F139" t="n">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="G139" t="n">
-        <v>10089300</v>
+        <v>10044000</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>10930</v>
+        <v>43650</v>
       </c>
       <c r="F140" t="n">
-        <v>1833</v>
+        <v>462</v>
       </c>
       <c r="G140" t="n">
-        <v>20034690</v>
+        <v>20166300</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>19850</v>
+        <v>59700</v>
       </c>
       <c r="F141" t="n">
-        <v>505</v>
+        <v>169</v>
       </c>
       <c r="G141" t="n">
-        <v>10024250</v>
+        <v>10089300</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -5010,12 +5010,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5024,13 +5024,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>26350</v>
+        <v>10930</v>
       </c>
       <c r="F142" t="n">
-        <v>380</v>
+        <v>1833</v>
       </c>
       <c r="G142" t="n">
-        <v>10013000</v>
+        <v>20034690</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -5042,31 +5042,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>23500</v>
+        <v>19850</v>
       </c>
       <c r="F143" t="n">
-        <v>833</v>
+        <v>505</v>
       </c>
       <c r="G143" t="n">
-        <v>19575500</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-2.08</v>
-      </c>
+        <v>10024250</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5076,27 +5074,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>85200</v>
+        <v>26350</v>
       </c>
       <c r="F144" t="n">
-        <v>118</v>
+        <v>380</v>
       </c>
       <c r="G144" t="n">
-        <v>10053600</v>
+        <v>10013000</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -5108,29 +5106,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>189300</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>63400</v>
+        <v>23500</v>
       </c>
       <c r="F145" t="n">
-        <v>316</v>
+        <v>833</v>
       </c>
       <c r="G145" t="n">
-        <v>20034400</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
+        <v>19575500</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-2.08</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5154,13 +5154,13 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>110300</v>
+        <v>85200</v>
       </c>
       <c r="F146" t="n">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="G146" t="n">
-        <v>10037300</v>
+        <v>10053600</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -5172,91 +5172,91 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>189300</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>66100</v>
+        <v>63400</v>
       </c>
       <c r="F147" t="n">
-        <v>152</v>
+        <v>316</v>
       </c>
       <c r="G147" t="n">
-        <v>10047200</v>
+        <v>20034400</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>25800</v>
+        <v>110300</v>
       </c>
       <c r="F148" t="n">
-        <v>2713</v>
+        <v>91</v>
       </c>
       <c r="G148" t="n">
-        <v>69995400</v>
+        <v>10037300</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>206500</v>
+        <v>66100</v>
       </c>
       <c r="F149" t="n">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="G149" t="n">
-        <v>69797000</v>
+        <v>10047200</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5282,13 +5282,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>70100</v>
+        <v>25800</v>
       </c>
       <c r="F150" t="n">
-        <v>998</v>
+        <v>2713</v>
       </c>
       <c r="G150" t="n">
-        <v>69959800</v>
+        <v>69995400</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5300,12 +5300,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5314,13 +5314,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>93300</v>
+        <v>206500</v>
       </c>
       <c r="F151" t="n">
-        <v>214</v>
+        <v>338</v>
       </c>
       <c r="G151" t="n">
-        <v>19966200</v>
+        <v>69797000</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5332,12 +5332,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5346,13 +5346,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>11300</v>
+        <v>70100</v>
       </c>
       <c r="F152" t="n">
-        <v>4424</v>
+        <v>998</v>
       </c>
       <c r="G152" t="n">
-        <v>49991200</v>
+        <v>69959800</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>19740</v>
+        <v>93300</v>
       </c>
       <c r="F153" t="n">
-        <v>2532</v>
+        <v>214</v>
       </c>
       <c r="G153" t="n">
-        <v>49981680</v>
+        <v>19966200</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5410,13 +5410,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>25150</v>
+        <v>11300</v>
       </c>
       <c r="F154" t="n">
-        <v>2385</v>
+        <v>4424</v>
       </c>
       <c r="G154" t="n">
-        <v>59982750</v>
+        <v>49991200</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>22050</v>
+        <v>19740</v>
       </c>
       <c r="F155" t="n">
-        <v>2267</v>
+        <v>2532</v>
       </c>
       <c r="G155" t="n">
-        <v>49987350</v>
+        <v>49981680</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5474,13 +5474,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>43150</v>
+        <v>25150</v>
       </c>
       <c r="F156" t="n">
-        <v>1390</v>
+        <v>2385</v>
       </c>
       <c r="G156" t="n">
-        <v>59978500</v>
+        <v>59982750</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5492,12 +5492,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>310000</v>
+        <v>22050</v>
       </c>
       <c r="F157" t="n">
-        <v>225</v>
+        <v>2267</v>
       </c>
       <c r="G157" t="n">
-        <v>69750000</v>
+        <v>49987350</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6240</v>
+        <v>43150</v>
       </c>
       <c r="F158" t="n">
-        <v>3205</v>
+        <v>1390</v>
       </c>
       <c r="G158" t="n">
-        <v>19999200</v>
+        <v>59978500</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5556,12 +5556,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>24000</v>
+        <v>310000</v>
       </c>
       <c r="F159" t="n">
-        <v>833</v>
+        <v>225</v>
       </c>
       <c r="G159" t="n">
-        <v>19992000</v>
+        <v>69750000</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5588,12 +5588,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>90300</v>
+        <v>6240</v>
       </c>
       <c r="F160" t="n">
-        <v>442</v>
+        <v>3205</v>
       </c>
       <c r="G160" t="n">
-        <v>39912600</v>
+        <v>19999200</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>138080</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>279500</v>
+        <v>24000</v>
       </c>
       <c r="F161" t="n">
-        <v>357</v>
+        <v>833</v>
       </c>
       <c r="G161" t="n">
-        <v>99781500</v>
+        <v>19992000</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5666,13 +5666,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>366000</v>
+        <v>90300</v>
       </c>
       <c r="F162" t="n">
-        <v>54</v>
+        <v>442</v>
       </c>
       <c r="G162" t="n">
-        <v>19764000</v>
+        <v>39912600</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>237690</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5698,13 +5698,13 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>91000</v>
+        <v>279500</v>
       </c>
       <c r="F163" t="n">
-        <v>659</v>
+        <v>357</v>
       </c>
       <c r="G163" t="n">
-        <v>59969000</v>
+        <v>99781500</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -5716,12 +5716,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>120100</v>
+        <v>366000</v>
       </c>
       <c r="F164" t="n">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="G164" t="n">
-        <v>79986600</v>
+        <v>19764000</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>237690</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5762,13 +5762,13 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2405</v>
+        <v>91000</v>
       </c>
       <c r="F165" t="n">
-        <v>415800</v>
+        <v>659</v>
       </c>
       <c r="G165" t="n">
-        <v>999999000</v>
+        <v>59969000</v>
       </c>
       <c r="H165" t="inlineStr"/>
     </row>
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5794,13 +5794,13 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>69000</v>
+        <v>120100</v>
       </c>
       <c r="F166" t="n">
-        <v>579</v>
+        <v>666</v>
       </c>
       <c r="G166" t="n">
-        <v>39951000</v>
+        <v>79986600</v>
       </c>
       <c r="H166" t="inlineStr"/>
     </row>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>42300</v>
+        <v>2405</v>
       </c>
       <c r="F167" t="n">
-        <v>709</v>
+        <v>415800</v>
       </c>
       <c r="G167" t="n">
-        <v>29990700</v>
+        <v>999999000</v>
       </c>
       <c r="H167" t="inlineStr"/>
     </row>
@@ -5844,29 +5844,93 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>298380</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F168" t="n">
+        <v>579</v>
+      </c>
+      <c r="G168" t="n">
+        <v>39951000</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>42300</v>
+      </c>
+      <c r="F169" t="n">
+        <v>709</v>
+      </c>
+      <c r="G169" t="n">
+        <v>29990700</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
           <t>범한퓨얼셀</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>382900</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E168" t="n">
+      <c r="E170" t="n">
         <v>23350</v>
       </c>
-      <c r="F168" t="n">
+      <c r="F170" t="n">
         <v>856</v>
       </c>
-      <c r="G168" t="n">
+      <c r="G170" t="n">
         <v>19987600</v>
       </c>
-      <c r="H168" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/kosdaq_long_short_index_history.xlsx
+++ b/docs/downloads/kosdaq_long_short_index_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,94 +492,94 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2570</v>
+        <v>26200</v>
       </c>
       <c r="F2" t="n">
-        <v>45324.7565</v>
+        <v>383.1082</v>
       </c>
       <c r="G2" t="n">
-        <v>116484624.2</v>
+        <v>10037434.6</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>도우인시스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>484120</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25300</v>
+        <v>47600</v>
       </c>
       <c r="F3" t="n">
-        <v>812.8404</v>
+        <v>210.8705</v>
       </c>
       <c r="G3" t="n">
-        <v>20564861.1</v>
+        <v>10037434.6</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>24200</v>
+        <v>2650</v>
       </c>
       <c r="F4" t="n">
-        <v>422.9059</v>
+        <v>62960.1497</v>
       </c>
       <c r="G4" t="n">
-        <v>10234323</v>
+        <v>166844396.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,307 +588,305 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4005</v>
+        <v>2790</v>
       </c>
       <c r="F5" t="n">
-        <v>5110.773</v>
+        <v>10792.9404</v>
       </c>
       <c r="G5" t="n">
-        <v>20468646</v>
+        <v>30112303.8</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>35050</v>
+        <v>2570</v>
       </c>
       <c r="F6" t="n">
-        <v>411.8056</v>
+        <v>45324.7565</v>
       </c>
       <c r="G6" t="n">
-        <v>14433786.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-17.14</v>
-      </c>
+        <v>116484624.2</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>도우인시스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>484120</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39450</v>
+        <v>25300</v>
       </c>
       <c r="F7" t="n">
-        <v>470.9867</v>
+        <v>812.8404</v>
       </c>
       <c r="G7" t="n">
-        <v>18580423.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-7.18</v>
-      </c>
+        <v>20564861.1</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>33300</v>
+        <v>24200</v>
       </c>
       <c r="F8" t="n">
-        <v>296.1438</v>
+        <v>422.9059</v>
       </c>
       <c r="G8" t="n">
-        <v>9861590.1</v>
+        <v>10234323</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9540</v>
+        <v>4005</v>
       </c>
       <c r="F9" t="n">
-        <v>1033.7097</v>
+        <v>5110.773</v>
       </c>
       <c r="G9" t="n">
-        <v>9861590.1</v>
+        <v>20468646</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>58500</v>
+        <v>35050</v>
       </c>
       <c r="F10" t="n">
-        <v>168.5742</v>
+        <v>411.8056</v>
       </c>
       <c r="G10" t="n">
-        <v>9861590.1</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>14433786.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-17.14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23850</v>
+        <v>39450</v>
       </c>
       <c r="F11" t="n">
-        <v>433.5542</v>
+        <v>470.9867</v>
       </c>
       <c r="G11" t="n">
-        <v>10340268.5</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>18580423.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-7.18</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45450</v>
+        <v>33300</v>
       </c>
       <c r="F12" t="n">
-        <v>227.5087</v>
+        <v>296.1438</v>
       </c>
       <c r="G12" t="n">
-        <v>10340268.5</v>
+        <v>9861590.1</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15230</v>
+        <v>9540</v>
       </c>
       <c r="F13" t="n">
-        <v>1186.9772</v>
+        <v>1033.7097</v>
       </c>
       <c r="G13" t="n">
-        <v>18077663</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-5.87</v>
-      </c>
+        <v>9861590.1</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2655</v>
+        <v>58500</v>
       </c>
       <c r="F14" t="n">
-        <v>76798.0178</v>
+        <v>168.5742</v>
       </c>
       <c r="G14" t="n">
-        <v>203898737.2</v>
+        <v>9861590.1</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -900,24 +898,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>30249.84</v>
+        <v>23850</v>
       </c>
       <c r="F15" t="n">
-        <v>341.8289</v>
+        <v>433.5542</v>
       </c>
       <c r="G15" t="n">
         <v>10340268.5</v>
@@ -932,12 +930,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -946,10 +944,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25550</v>
+        <v>45450</v>
       </c>
       <c r="F16" t="n">
-        <v>404.7072</v>
+        <v>227.5087</v>
       </c>
       <c r="G16" t="n">
         <v>10340268.5</v>
@@ -964,44 +962,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59900</v>
+        <v>15230</v>
       </c>
       <c r="F17" t="n">
-        <v>172.6255</v>
+        <v>1186.9772</v>
       </c>
       <c r="G17" t="n">
-        <v>10340268.5</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>18077663</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-5.87</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1010,111 +1010,109 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>41050</v>
+        <v>2655</v>
       </c>
       <c r="F18" t="n">
-        <v>490.4266</v>
+        <v>76798.0178</v>
       </c>
       <c r="G18" t="n">
-        <v>20132010.4</v>
+        <v>203898737.2</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230000</v>
+        <v>30249.84</v>
       </c>
       <c r="F19" t="n">
-        <v>135.183</v>
+        <v>341.8289</v>
       </c>
       <c r="G19" t="n">
-        <v>31092084.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-16.92</v>
-      </c>
+        <v>10340268.5</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2595</v>
+        <v>25550</v>
       </c>
       <c r="F20" t="n">
-        <v>42895.584</v>
+        <v>404.7072</v>
       </c>
       <c r="G20" t="n">
-        <v>111314040.6</v>
+        <v>10340268.5</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>15870</v>
+        <v>59900</v>
       </c>
       <c r="F21" t="n">
-        <v>634.2788</v>
+        <v>172.6255</v>
       </c>
       <c r="G21" t="n">
-        <v>10066005.2</v>
+        <v>10340268.5</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1126,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1140,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>29646.86</v>
+        <v>41050</v>
       </c>
       <c r="F22" t="n">
-        <v>339.5302</v>
+        <v>490.4266</v>
       </c>
       <c r="G22" t="n">
-        <v>10066005.2</v>
+        <v>20132010.4</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1158,29 +1156,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9960</v>
+        <v>230000</v>
       </c>
       <c r="F23" t="n">
-        <v>1010.6431</v>
+        <v>135.183</v>
       </c>
       <c r="G23" t="n">
-        <v>10066005.2</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>31092084.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-16.92</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1190,27 +1190,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>큐리옥스바이오시스템즈</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>445680</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>59100</v>
+        <v>2595</v>
       </c>
       <c r="F24" t="n">
-        <v>681.2863</v>
+        <v>42895.584</v>
       </c>
       <c r="G24" t="n">
-        <v>40264020.8</v>
+        <v>111314040.6</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1222,24 +1222,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3385</v>
+        <v>15870</v>
       </c>
       <c r="F25" t="n">
-        <v>2973.7091</v>
+        <v>634.2788</v>
       </c>
       <c r="G25" t="n">
         <v>10066005.2</v>
@@ -1249,17 +1249,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>091580</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1268,30 +1268,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>26200</v>
+        <v>29646.86</v>
       </c>
       <c r="F26" t="n">
-        <v>382.0025</v>
+        <v>339.5302</v>
       </c>
       <c r="G26" t="n">
-        <v>10008466.3</v>
+        <v>10066005.2</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1300,30 +1300,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>94700</v>
+        <v>9960</v>
       </c>
       <c r="F27" t="n">
-        <v>105.686</v>
+        <v>1010.6431</v>
       </c>
       <c r="G27" t="n">
-        <v>10008466.3</v>
+        <v>10066005.2</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>큐리옥스바이오시스템즈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>456160</t>
+          <t>445680</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1332,62 +1332,62 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>42500</v>
+        <v>59100</v>
       </c>
       <c r="F28" t="n">
-        <v>470.9867</v>
+        <v>681.2863</v>
       </c>
       <c r="G28" t="n">
-        <v>20016932.7</v>
+        <v>40264020.8</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>26600</v>
+        <v>3385</v>
       </c>
       <c r="F29" t="n">
-        <v>361.0017</v>
+        <v>2973.7091</v>
       </c>
       <c r="G29" t="n">
-        <v>9602645.699999999</v>
+        <v>10066005.2</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>상신이디피</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>091580</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1396,62 +1396,62 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10740</v>
+        <v>26200</v>
       </c>
       <c r="F30" t="n">
-        <v>894.1011</v>
+        <v>382.0025</v>
       </c>
       <c r="G30" t="n">
-        <v>9602645.699999999</v>
+        <v>10008466.3</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>인터로조</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>16180</v>
+        <v>94700</v>
       </c>
       <c r="F31" t="n">
-        <v>1186.9772</v>
+        <v>105.686</v>
       </c>
       <c r="G31" t="n">
-        <v>19205291.4</v>
+        <v>10008466.3</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>456160</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>88400</v>
+        <v>42500</v>
       </c>
       <c r="F32" t="n">
-        <v>217.2544</v>
+        <v>470.9867</v>
       </c>
       <c r="G32" t="n">
-        <v>19205291.4</v>
+        <v>20016932.7</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>99100</v>
+        <v>26600</v>
       </c>
       <c r="F33" t="n">
-        <v>290.6956</v>
+        <v>361.0017</v>
       </c>
       <c r="G33" t="n">
-        <v>28807937.1</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1510,31 +1510,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37350</v>
+        <v>10740</v>
       </c>
       <c r="F34" t="n">
-        <v>491.1229</v>
+        <v>894.1011</v>
       </c>
       <c r="G34" t="n">
-        <v>18343440.7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-9.23</v>
-      </c>
+        <v>9602645.699999999</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1544,27 +1542,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>인터로조</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2520</v>
+        <v>16180</v>
       </c>
       <c r="F35" t="n">
-        <v>33368.1327</v>
+        <v>1186.9772</v>
       </c>
       <c r="G35" t="n">
-        <v>84087694.5</v>
+        <v>19205291.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,31 +1574,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>16500</v>
+        <v>88400</v>
       </c>
       <c r="F36" t="n">
-        <v>856.421</v>
+        <v>217.2544</v>
       </c>
       <c r="G36" t="n">
-        <v>14130946.6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-22.8</v>
-      </c>
+        <v>19205291.4</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1610,24 +1606,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>신성에스티</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>416180</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>27650</v>
+        <v>99100</v>
       </c>
       <c r="F37" t="n">
-        <v>1041.8784</v>
+        <v>290.6956</v>
       </c>
       <c r="G37" t="n">
         <v>28807937.1</v>
@@ -1642,140 +1638,144 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9350</v>
+        <v>37350</v>
       </c>
       <c r="F38" t="n">
-        <v>1027.0209</v>
+        <v>491.1229</v>
       </c>
       <c r="G38" t="n">
-        <v>9602645.699999999</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>18343440.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-9.23</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>28650</v>
+        <v>2520</v>
       </c>
       <c r="F39" t="n">
-        <v>345.7839</v>
+        <v>33368.1327</v>
       </c>
       <c r="G39" t="n">
-        <v>9906708.4</v>
+        <v>84087694.5</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11600</v>
+        <v>16500</v>
       </c>
       <c r="F40" t="n">
-        <v>854.0266</v>
+        <v>856.421</v>
       </c>
       <c r="G40" t="n">
-        <v>9906708.4</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>14130946.6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-22.8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>신성에스티</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>416180</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>131000</v>
+        <v>27650</v>
       </c>
       <c r="F41" t="n">
-        <v>75.6237</v>
+        <v>1041.8784</v>
       </c>
       <c r="G41" t="n">
-        <v>9906708.4</v>
+        <v>28807937.1</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>33717.02</v>
+        <v>9350</v>
       </c>
       <c r="F42" t="n">
-        <v>293.8192</v>
+        <v>1027.0209</v>
       </c>
       <c r="G42" t="n">
-        <v>9906708.4</v>
+        <v>9602645.699999999</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1802,24 +1802,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>297090</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4830</v>
+        <v>28650</v>
       </c>
       <c r="F43" t="n">
-        <v>2051.0783</v>
+        <v>345.7839</v>
       </c>
       <c r="G43" t="n">
         <v>9906708.4</v>
@@ -1834,78 +1834,76 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>441270</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9430</v>
+        <v>11600</v>
       </c>
       <c r="F44" t="n">
-        <v>2101.1046</v>
+        <v>854.0266</v>
       </c>
       <c r="G44" t="n">
-        <v>19813416.7</v>
+        <v>9906708.4</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>79100</v>
+        <v>131000</v>
       </c>
       <c r="F45" t="n">
-        <v>205.0482</v>
+        <v>75.6237</v>
       </c>
       <c r="G45" t="n">
-        <v>16219315.2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-15.22</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1914,64 +1912,62 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>25250</v>
+        <v>33717.02</v>
       </c>
       <c r="F46" t="n">
-        <v>768.6917999999999</v>
+        <v>293.8192</v>
       </c>
       <c r="G46" t="n">
-        <v>19409469.1</v>
+        <v>9906708.4</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>12510</v>
+        <v>4830</v>
       </c>
       <c r="F47" t="n">
-        <v>1443.4887</v>
+        <v>2051.0783</v>
       </c>
       <c r="G47" t="n">
-        <v>18058043.3</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-11.28</v>
-      </c>
+        <v>9906708.4</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>441270</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1980,13 +1976,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>126500</v>
+        <v>9430</v>
       </c>
       <c r="F48" t="n">
-        <v>383.5863</v>
+        <v>2101.1046</v>
       </c>
       <c r="G48" t="n">
-        <v>48523672.7</v>
+        <v>19813416.7</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1998,29 +1994,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2485</v>
+        <v>79100</v>
       </c>
       <c r="F49" t="n">
-        <v>42403.6617</v>
+        <v>205.0482</v>
       </c>
       <c r="G49" t="n">
-        <v>105373099.3</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>16219315.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-15.22</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2030,27 +2028,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>45500</v>
+        <v>25250</v>
       </c>
       <c r="F50" t="n">
-        <v>213.2909</v>
+        <v>768.6917999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>9704734.5</v>
+        <v>19409469.1</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2062,29 +2060,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코스텍시스</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>355150</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>17880</v>
+        <v>12510</v>
       </c>
       <c r="F51" t="n">
-        <v>1085.5408</v>
+        <v>1443.4887</v>
       </c>
       <c r="G51" t="n">
-        <v>19409469.1</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>18058043.3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-11.28</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2094,31 +2094,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4460</v>
+        <v>126500</v>
       </c>
       <c r="F52" t="n">
-        <v>3137.3165</v>
+        <v>383.5863</v>
       </c>
       <c r="G52" t="n">
-        <v>13992431.8</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-17.83</v>
-      </c>
+        <v>48523672.7</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2128,44 +2126,44 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에스엠씨지</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>460870</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3345</v>
+        <v>2485</v>
       </c>
       <c r="F53" t="n">
-        <v>11605.0637</v>
+        <v>42403.6617</v>
       </c>
       <c r="G53" t="n">
-        <v>38818938.1</v>
+        <v>105373099.3</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2174,130 +2172,128 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>12120</v>
+        <v>45500</v>
       </c>
       <c r="F54" t="n">
-        <v>820.878</v>
+        <v>213.2909</v>
       </c>
       <c r="G54" t="n">
-        <v>9949041.199999999</v>
+        <v>9704734.5</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>코스텍시스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>355150</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>248000</v>
+        <v>17880</v>
       </c>
       <c r="F55" t="n">
-        <v>81.12909999999999</v>
+        <v>1085.5408</v>
       </c>
       <c r="G55" t="n">
-        <v>20120019.7</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-19.98</v>
-      </c>
+        <v>19409469.1</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222500</v>
+        <v>4460</v>
       </c>
       <c r="F56" t="n">
-        <v>178.8592</v>
+        <v>3137.3165</v>
       </c>
       <c r="G56" t="n">
-        <v>39796164.7</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>13992431.8</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-17.83</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>에스엠씨지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>354320</t>
+          <t>460870</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>54500</v>
+        <v>3345</v>
       </c>
       <c r="F57" t="n">
-        <v>504.0447</v>
+        <v>11605.0637</v>
       </c>
       <c r="G57" t="n">
-        <v>27470436.6</v>
-      </c>
-      <c r="H57" t="n">
-        <v>24.43</v>
-      </c>
+        <v>38818938.1</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2306,111 +2302,115 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>32350</v>
+        <v>12120</v>
       </c>
       <c r="F58" t="n">
-        <v>314.5779</v>
+        <v>820.878</v>
       </c>
       <c r="G58" t="n">
-        <v>10176595.1</v>
+        <v>9949041.199999999</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>유니테스트</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>086390</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>13650</v>
+        <v>248000</v>
       </c>
       <c r="F59" t="n">
-        <v>745.5381</v>
+        <v>81.12909999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>10176595.1</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>20120019.7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-19.98</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>31950</v>
+        <v>222500</v>
       </c>
       <c r="F60" t="n">
-        <v>318.5163</v>
+        <v>178.8592</v>
       </c>
       <c r="G60" t="n">
-        <v>10176595.1</v>
+        <v>39796164.7</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>250500</v>
+        <v>54500</v>
       </c>
       <c r="F61" t="n">
-        <v>81.2503</v>
+        <v>504.0447</v>
       </c>
       <c r="G61" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>27470436.6</v>
+      </c>
+      <c r="H61" t="n">
+        <v>24.43</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2420,27 +2420,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>에이엘티</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>14100</v>
+        <v>32350</v>
       </c>
       <c r="F62" t="n">
-        <v>1443.4887</v>
+        <v>314.5779</v>
       </c>
       <c r="G62" t="n">
-        <v>20353190.3</v>
+        <v>10176595.1</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2452,31 +2452,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>유니테스트</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>086390</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>31300</v>
+        <v>13650</v>
       </c>
       <c r="F63" t="n">
-        <v>1954.4702</v>
+        <v>745.5381</v>
       </c>
       <c r="G63" t="n">
-        <v>61174916</v>
-      </c>
-      <c r="H63" t="n">
-        <v>6.83</v>
-      </c>
+        <v>10176595.1</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2486,27 +2484,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KODEX 코스닥150선물인버스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>251340</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2355</v>
+        <v>31950</v>
       </c>
       <c r="F64" t="n">
-        <v>65496.7248</v>
+        <v>318.5163</v>
       </c>
       <c r="G64" t="n">
-        <v>154244786.8</v>
+        <v>10176595.1</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2518,27 +2516,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>15810</v>
+        <v>250500</v>
       </c>
       <c r="F65" t="n">
-        <v>5149.4473</v>
+        <v>81.2503</v>
       </c>
       <c r="G65" t="n">
-        <v>81412761.09999999</v>
+        <v>20353190.3</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2550,27 +2548,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>에이엘티</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>172670</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>28491.13</v>
+        <v>14100</v>
       </c>
       <c r="F66" t="n">
-        <v>357.1847</v>
+        <v>1443.4887</v>
       </c>
       <c r="G66" t="n">
-        <v>10176595.1</v>
+        <v>20353190.3</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2582,110 +2580,110 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>388790</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4660</v>
+        <v>31300</v>
       </c>
       <c r="F67" t="n">
-        <v>4367.6374</v>
+        <v>1954.4702</v>
       </c>
       <c r="G67" t="n">
-        <v>20353190.3</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>61174916</v>
+      </c>
+      <c r="H67" t="n">
+        <v>6.83</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>KODEX 코스닥150선물인버스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>251340</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>44600</v>
+        <v>2355</v>
       </c>
       <c r="F68" t="n">
-        <v>1359.3974</v>
+        <v>65496.7248</v>
       </c>
       <c r="G68" t="n">
-        <v>60629123.5</v>
+        <v>154244786.8</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한스바이오메드</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>042520</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>20300</v>
+        <v>15810</v>
       </c>
       <c r="F69" t="n">
-        <v>1162.9429</v>
+        <v>5149.4473</v>
       </c>
       <c r="G69" t="n">
-        <v>23607739.9</v>
-      </c>
-      <c r="H69" t="n">
-        <v>7.9</v>
-      </c>
+        <v>81412761.09999999</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2694,49 +2692,47 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>13160</v>
+        <v>28491.13</v>
       </c>
       <c r="F70" t="n">
-        <v>767.846</v>
+        <v>357.1847</v>
       </c>
       <c r="G70" t="n">
-        <v>10104853.9</v>
+        <v>10176595.1</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>388790</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>49050</v>
+        <v>4660</v>
       </c>
       <c r="F71" t="n">
-        <v>357.1039</v>
+        <v>4367.6374</v>
       </c>
       <c r="G71" t="n">
-        <v>17515946</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-16.44</v>
-      </c>
+        <v>20353190.3</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2746,31 +2742,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>028300</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>37100</v>
+        <v>44600</v>
       </c>
       <c r="F72" t="n">
-        <v>604.321</v>
+        <v>1359.3974</v>
       </c>
       <c r="G72" t="n">
-        <v>22420310.5</v>
-      </c>
-      <c r="H72" t="n">
-        <v>15.04</v>
-      </c>
+        <v>60629123.5</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2780,29 +2774,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>한스바이오메드</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>042520</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>123700</v>
+        <v>20300</v>
       </c>
       <c r="F73" t="n">
-        <v>490.1303</v>
+        <v>1162.9429</v>
       </c>
       <c r="G73" t="n">
-     